--- a/Excel/一方通行/艾拉.xlsx
+++ b/Excel/一方通行/艾拉.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1E263A9-5741-49A2-BD11-2F22FA7CAE23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8386D270-FCCA-4A99-8E27-208FFF09C55B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,6 +53,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>PC:</t>
@@ -61,6 +62,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -86,6 +88,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>PC:</t>
@@ -94,6 +97,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -101,13 +105,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="AZ1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
+    <comment ref="BB1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>PC:</t>
@@ -116,6 +121,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -126,13 +132,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="BP1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
+    <comment ref="BR1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:</t>
@@ -141,6 +148,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -148,13 +156,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="CR1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
+    <comment ref="CT1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:</t>
@@ -163,6 +172,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -188,6 +198,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:</t>
@@ -196,6 +207,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -211,6 +223,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:
@@ -220,6 +233,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -236,6 +250,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:</t>
@@ -244,6 +259,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -261,6 +277,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:</t>
@@ -269,6 +286,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -281,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="581">
   <si>
     <t>Id</t>
   </si>
@@ -2018,6 +2036,26 @@
   </si>
   <si>
     <t>减速,易伤,艾拉地雷标记</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>优先Buff</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义优先级</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>OrderBuff</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>OrderExpression</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
 </sst>
@@ -2037,6 +2075,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2044,18 +2083,21 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFFC000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2063,18 +2105,21 @@
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2087,6 +2132,7 @@
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2094,12 +2140,14 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2107,16 +2155,19 @@
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2196,7 +2247,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2262,6 +2313,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -6468,7 +6522,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:DQ783"/>
+  <dimension ref="A1:DS783"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.08203125" customWidth="1"/>
@@ -6508,49 +6562,49 @@
     <col min="38" max="39" width="8.33203125" customWidth="1"/>
     <col min="40" max="40" width="15" customWidth="1"/>
     <col min="41" max="41" width="13.25" customWidth="1"/>
-    <col min="42" max="43" width="11.83203125" customWidth="1"/>
-    <col min="44" max="44" width="18.4140625" customWidth="1"/>
-    <col min="45" max="45" width="12.25" customWidth="1"/>
-    <col min="46" max="46" width="11.9140625" customWidth="1"/>
-    <col min="47" max="47" width="19.58203125" customWidth="1"/>
-    <col min="48" max="48" width="12.6640625" customWidth="1"/>
-    <col min="50" max="50" width="7" customWidth="1"/>
-    <col min="51" max="51" width="11.75" customWidth="1"/>
-    <col min="52" max="52" width="19.75" customWidth="1"/>
-    <col min="53" max="53" width="5.08203125" customWidth="1"/>
-    <col min="54" max="54" width="8.5" customWidth="1"/>
-    <col min="55" max="55" width="13.5" customWidth="1"/>
-    <col min="56" max="56" width="14.6640625" customWidth="1"/>
-    <col min="57" max="57" width="10.1640625" customWidth="1"/>
-    <col min="58" max="58" width="8.25" customWidth="1"/>
-    <col min="59" max="65" width="8.33203125" customWidth="1"/>
-    <col min="66" max="68" width="11.25" customWidth="1"/>
-    <col min="69" max="69" width="6.58203125" customWidth="1"/>
-    <col min="70" max="71" width="8" customWidth="1"/>
-    <col min="72" max="72" width="7.33203125" style="7" customWidth="1"/>
-    <col min="73" max="74" width="8.5" style="7" customWidth="1"/>
-    <col min="75" max="76" width="7.83203125" style="7" customWidth="1"/>
-    <col min="77" max="77" width="22.1640625" style="7" customWidth="1"/>
-    <col min="78" max="78" width="13.5" customWidth="1"/>
-    <col min="79" max="79" width="21.1640625" customWidth="1"/>
-    <col min="80" max="80" width="15.75" customWidth="1"/>
-    <col min="81" max="81" width="15.58203125" customWidth="1"/>
-    <col min="82" max="82" width="12.83203125" customWidth="1"/>
-    <col min="83" max="83" width="16.1640625" customWidth="1"/>
-    <col min="85" max="85" width="16" customWidth="1"/>
-    <col min="86" max="87" width="12.83203125" customWidth="1"/>
-    <col min="88" max="88" width="23.58203125" customWidth="1"/>
-    <col min="89" max="89" width="12.83203125" customWidth="1"/>
-    <col min="90" max="90" width="17.08203125" customWidth="1"/>
-    <col min="97" max="97" width="14" customWidth="1"/>
-    <col min="98" max="98" width="8" customWidth="1"/>
-    <col min="100" max="100" width="11.08203125" customWidth="1"/>
-    <col min="101" max="101" width="13.75" customWidth="1"/>
-    <col min="108" max="108" width="15.5" customWidth="1"/>
-    <col min="112" max="112" width="9" hidden="1" customWidth="1"/>
+    <col min="42" max="45" width="11.83203125" customWidth="1"/>
+    <col min="46" max="46" width="18.4140625" customWidth="1"/>
+    <col min="47" max="47" width="12.25" customWidth="1"/>
+    <col min="48" max="48" width="11.9140625" customWidth="1"/>
+    <col min="49" max="49" width="19.58203125" customWidth="1"/>
+    <col min="50" max="50" width="12.6640625" customWidth="1"/>
+    <col min="52" max="52" width="7" customWidth="1"/>
+    <col min="53" max="53" width="11.75" customWidth="1"/>
+    <col min="54" max="54" width="19.75" customWidth="1"/>
+    <col min="55" max="55" width="5.08203125" customWidth="1"/>
+    <col min="56" max="56" width="8.5" customWidth="1"/>
+    <col min="57" max="57" width="13.5" customWidth="1"/>
+    <col min="58" max="58" width="14.6640625" customWidth="1"/>
+    <col min="59" max="59" width="10.1640625" customWidth="1"/>
+    <col min="60" max="60" width="8.25" customWidth="1"/>
+    <col min="61" max="67" width="8.33203125" customWidth="1"/>
+    <col min="68" max="70" width="11.25" customWidth="1"/>
+    <col min="71" max="71" width="6.58203125" customWidth="1"/>
+    <col min="72" max="73" width="8" customWidth="1"/>
+    <col min="74" max="74" width="7.33203125" style="7" customWidth="1"/>
+    <col min="75" max="76" width="8.5" style="7" customWidth="1"/>
+    <col min="77" max="78" width="7.83203125" style="7" customWidth="1"/>
+    <col min="79" max="79" width="22.1640625" style="7" customWidth="1"/>
+    <col min="80" max="80" width="13.5" customWidth="1"/>
+    <col min="81" max="81" width="21.1640625" customWidth="1"/>
+    <col min="82" max="82" width="15.75" customWidth="1"/>
+    <col min="83" max="83" width="15.58203125" customWidth="1"/>
+    <col min="84" max="84" width="12.83203125" customWidth="1"/>
+    <col min="85" max="85" width="16.1640625" customWidth="1"/>
+    <col min="87" max="87" width="16" customWidth="1"/>
+    <col min="88" max="89" width="12.83203125" customWidth="1"/>
+    <col min="90" max="90" width="23.58203125" customWidth="1"/>
+    <col min="91" max="91" width="12.83203125" customWidth="1"/>
+    <col min="92" max="92" width="17.08203125" customWidth="1"/>
+    <col min="99" max="99" width="14" customWidth="1"/>
+    <col min="100" max="100" width="8" customWidth="1"/>
+    <col min="102" max="102" width="11.08203125" customWidth="1"/>
+    <col min="103" max="103" width="13.75" customWidth="1"/>
+    <col min="110" max="110" width="15.5" customWidth="1"/>
+    <col min="114" max="114" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:113" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>160</v>
       </c>
@@ -6674,209 +6728,215 @@
       <c r="AQ1" t="s">
         <v>199</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AR1" s="23" t="s">
+        <v>576</v>
+      </c>
+      <c r="AS1" s="23" t="s">
+        <v>577</v>
+      </c>
+      <c r="AT1" t="s">
         <v>200</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AU1" t="s">
         <v>201</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AV1" t="s">
         <v>202</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AW1" t="s">
         <v>203</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AX1" t="s">
         <v>204</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AY1" t="s">
         <v>205</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AZ1" t="s">
         <v>206</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BA1" t="s">
         <v>207</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BB1" t="s">
         <v>208</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BC1" t="s">
         <v>209</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BD1" t="s">
         <v>210</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BE1" t="s">
         <v>211</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BF1" t="s">
         <v>212</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BG1" t="s">
         <v>213</v>
-      </c>
-      <c r="BF1" t="s">
-        <v>214</v>
       </c>
       <c r="BH1" t="s">
         <v>214</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
+        <v>214</v>
+      </c>
+      <c r="BK1" t="s">
         <v>215</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BL1" t="s">
         <v>216</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BM1" t="s">
         <v>217</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BN1" t="s">
         <v>218</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BO1" t="s">
         <v>219</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BP1" t="s">
         <v>220</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BQ1" t="s">
         <v>221</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BR1" t="s">
         <v>222</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BS1" t="s">
         <v>223</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BT1" t="s">
         <v>224</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BU1" t="s">
         <v>225</v>
       </c>
-      <c r="BT1" s="7" t="s">
+      <c r="BV1" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="BU1" s="7" t="s">
+      <c r="BW1" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="BV1" s="7" t="s">
+      <c r="BX1" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="BW1" s="7" t="s">
+      <c r="BY1" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="BX1" s="7" t="s">
+      <c r="BZ1" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="BY1" s="7" t="s">
+      <c r="CA1" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CB1" t="s">
         <v>232</v>
       </c>
-      <c r="CA1" s="7" t="s">
+      <c r="CC1" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CD1" t="s">
         <v>234</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="CE1" t="s">
         <v>235</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CF1" t="s">
         <v>236</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CG1" t="s">
         <v>237</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CH1" t="s">
         <v>238</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CI1" t="s">
         <v>239</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CJ1" t="s">
         <v>240</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CK1" t="s">
         <v>241</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="CL1" t="s">
         <v>242</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CM1" t="s">
         <v>243</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="CN1" t="s">
         <v>244</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CO1" t="s">
         <v>245</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CP1" t="s">
         <v>246</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CQ1" t="s">
         <v>247</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CR1" t="s">
         <v>224</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CS1" t="s">
         <v>248</v>
       </c>
-      <c r="CR1" t="s">
+      <c r="CT1" t="s">
         <v>249</v>
       </c>
-      <c r="CS1" t="s">
+      <c r="CU1" t="s">
         <v>250</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CV1" t="s">
         <v>251</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CW1" t="s">
         <v>252</v>
-      </c>
-      <c r="CV1" t="s">
-        <v>253</v>
-      </c>
-      <c r="CW1" t="s">
-        <v>254</v>
       </c>
       <c r="CX1" t="s">
         <v>253</v>
       </c>
       <c r="CY1" t="s">
+        <v>254</v>
+      </c>
+      <c r="CZ1" t="s">
+        <v>253</v>
+      </c>
+      <c r="DA1" t="s">
         <v>255</v>
       </c>
-      <c r="CZ1" t="s">
+      <c r="DB1" t="s">
         <v>256</v>
       </c>
-      <c r="DA1" t="s">
+      <c r="DC1" t="s">
         <v>257</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="DD1" t="s">
         <v>258</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="DE1" t="s">
         <v>259</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DF1" t="s">
         <v>260</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="DG1" t="s">
         <v>261</v>
       </c>
-      <c r="DF1" t="s">
+      <c r="DH1" t="s">
         <v>262</v>
       </c>
-      <c r="DG1" t="s">
+      <c r="DI1" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="2" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -7003,212 +7063,218 @@
       <c r="AQ2" t="s">
         <v>301</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AR2" s="23" t="s">
+        <v>578</v>
+      </c>
+      <c r="AS2" s="23" t="s">
+        <v>579</v>
+      </c>
+      <c r="AT2" t="s">
         <v>302</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AU2" t="s">
         <v>303</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AV2" t="s">
         <v>304</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AW2" t="s">
         <v>305</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AX2" t="s">
         <v>306</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AY2" t="s">
         <v>307</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AZ2" t="s">
         <v>308</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="BA2" t="s">
         <v>309</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BB2" t="s">
         <v>310</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BC2" t="s">
         <v>311</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BD2" t="s">
         <v>312</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BE2" t="s">
         <v>313</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BF2" t="s">
         <v>314</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BG2" t="s">
         <v>315</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BH2" t="s">
         <v>316</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BI2" t="s">
         <v>317</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BJ2" t="s">
         <v>318</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BK2" t="s">
         <v>319</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BL2" t="s">
         <v>320</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BM2" t="s">
         <v>321</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BN2" t="s">
         <v>322</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BO2" t="s">
         <v>79</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BP2" t="s">
         <v>323</v>
       </c>
-      <c r="BO2" t="s">
+      <c r="BQ2" t="s">
         <v>324</v>
       </c>
-      <c r="BP2" t="s">
+      <c r="BR2" t="s">
         <v>325</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BS2" t="s">
         <v>326</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BT2" t="s">
         <v>327</v>
       </c>
-      <c r="BS2" t="s">
+      <c r="BU2" t="s">
         <v>95</v>
       </c>
-      <c r="BT2" s="7" t="s">
+      <c r="BV2" s="7" t="s">
         <v>328</v>
       </c>
-      <c r="BU2" s="7" t="s">
+      <c r="BW2" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="BV2" s="7" t="s">
+      <c r="BX2" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="BW2" s="7" t="s">
+      <c r="BY2" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="BX2" s="7" t="s">
+      <c r="BZ2" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="BY2" s="7" t="s">
+      <c r="CA2" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="BZ2" t="s">
+      <c r="CB2" t="s">
         <v>334</v>
       </c>
-      <c r="CA2" t="s">
+      <c r="CC2" t="s">
         <v>335</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="CD2" t="s">
         <v>336</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="CE2" t="s">
         <v>337</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="CF2" t="s">
         <v>338</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="CG2" t="s">
         <v>339</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CH2" t="s">
         <v>340</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="CI2" t="s">
         <v>341</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="CJ2" t="s">
         <v>342</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="CK2" t="s">
         <v>343</v>
       </c>
-      <c r="CJ2" t="s">
+      <c r="CL2" t="s">
         <v>344</v>
       </c>
-      <c r="CK2" t="s">
+      <c r="CM2" t="s">
         <v>345</v>
       </c>
-      <c r="CL2" t="s">
+      <c r="CN2" t="s">
         <v>346</v>
       </c>
-      <c r="CM2" t="s">
+      <c r="CO2" t="s">
         <v>347</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="CP2" t="s">
         <v>348</v>
       </c>
-      <c r="CO2" t="s">
+      <c r="CQ2" t="s">
         <v>349</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="CR2" t="s">
         <v>350</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="CS2" t="s">
         <v>351</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="CT2" t="s">
         <v>352</v>
       </c>
-      <c r="CS2" t="s">
+      <c r="CU2" t="s">
         <v>353</v>
       </c>
-      <c r="CT2" t="s">
+      <c r="CV2" t="s">
         <v>354</v>
       </c>
-      <c r="CU2" t="s">
+      <c r="CW2" t="s">
         <v>355</v>
       </c>
-      <c r="CV2" t="s">
+      <c r="CX2" t="s">
         <v>356</v>
       </c>
-      <c r="CW2" t="s">
+      <c r="CY2" t="s">
         <v>357</v>
       </c>
-      <c r="CX2" t="s">
+      <c r="CZ2" t="s">
         <v>358</v>
       </c>
-      <c r="CY2" t="s">
+      <c r="DA2" t="s">
         <v>359</v>
       </c>
-      <c r="CZ2" t="s">
+      <c r="DB2" t="s">
         <v>360</v>
       </c>
-      <c r="DA2" t="s">
+      <c r="DC2" t="s">
         <v>361</v>
       </c>
-      <c r="DB2" t="s">
+      <c r="DD2" t="s">
         <v>362</v>
       </c>
-      <c r="DC2" t="s">
+      <c r="DE2" t="s">
         <v>363</v>
       </c>
-      <c r="DD2" t="s">
+      <c r="DF2" t="s">
         <v>364</v>
       </c>
-      <c r="DE2" t="s">
+      <c r="DG2" t="s">
         <v>365</v>
       </c>
-      <c r="DF2" t="s">
+      <c r="DH2" t="s">
         <v>366</v>
       </c>
-      <c r="DG2" t="s">
+      <c r="DI2" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="3" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -7335,182 +7401,182 @@
       <c r="AQ3" t="s">
         <v>2</v>
       </c>
-      <c r="AR3" t="s">
+      <c r="AR3" s="23" t="s">
+        <v>580</v>
+      </c>
+      <c r="AS3" s="23" t="s">
+        <v>580</v>
+      </c>
+      <c r="AT3" t="s">
         <v>374</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>117</v>
       </c>
       <c r="AU3" t="s">
         <v>116</v>
       </c>
       <c r="AV3" t="s">
-        <v>375</v>
+        <v>117</v>
       </c>
       <c r="AW3" t="s">
         <v>116</v>
       </c>
       <c r="AX3" t="s">
-        <v>117</v>
+        <v>375</v>
       </c>
       <c r="AY3" t="s">
         <v>116</v>
       </c>
       <c r="AZ3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="BA3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="BB3" t="s">
         <v>118</v>
       </c>
       <c r="BC3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BD3" t="s">
         <v>118</v>
       </c>
-      <c r="BD3" t="s">
+      <c r="BE3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BF3" t="s">
         <v>117</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>374</v>
       </c>
       <c r="BG3" t="s">
         <v>116</v>
       </c>
       <c r="BH3" t="s">
-        <v>117</v>
+        <v>374</v>
       </c>
       <c r="BI3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="BJ3" t="s">
         <v>117</v>
       </c>
       <c r="BK3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BM3" t="s">
         <v>118</v>
       </c>
-      <c r="BL3" t="s">
+      <c r="BN3" t="s">
         <v>118</v>
       </c>
-      <c r="BM3" t="s">
+      <c r="BO3" t="s">
         <v>119</v>
       </c>
-      <c r="BN3" t="s">
+      <c r="BP3" t="s">
         <v>119</v>
       </c>
-      <c r="BO3" t="s">
+      <c r="BQ3" t="s">
         <v>376</v>
       </c>
-      <c r="BP3" t="s">
+      <c r="BR3" t="s">
         <v>377</v>
       </c>
-      <c r="BQ3" t="s">
+      <c r="BS3" t="s">
         <v>117</v>
       </c>
-      <c r="BR3" t="s">
+      <c r="BT3" t="s">
         <v>117</v>
       </c>
-      <c r="BS3" t="s">
+      <c r="BU3" t="s">
         <v>116</v>
       </c>
-      <c r="BT3" s="7" t="s">
+      <c r="BV3" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="BU3" s="7" t="s">
+      <c r="BW3" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="BV3" s="7" t="s">
+      <c r="BX3" s="7" t="s">
         <v>118</v>
-      </c>
-      <c r="BW3" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="BX3" s="7" t="s">
-        <v>116</v>
       </c>
       <c r="BY3" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="BZ3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CA3" t="s">
-        <v>379</v>
+      <c r="BZ3" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="CA3" s="7" t="s">
+        <v>378</v>
       </c>
       <c r="CB3" t="s">
         <v>124</v>
       </c>
       <c r="CC3" t="s">
-        <v>124</v>
+        <v>379</v>
       </c>
       <c r="CD3" t="s">
         <v>124</v>
       </c>
       <c r="CE3" t="s">
+        <v>124</v>
+      </c>
+      <c r="CF3" t="s">
+        <v>124</v>
+      </c>
+      <c r="CG3" t="s">
         <v>380</v>
       </c>
-      <c r="CF3" t="s">
+      <c r="CH3" t="s">
         <v>381</v>
       </c>
-      <c r="CG3" t="s">
+      <c r="CI3" t="s">
         <v>2</v>
       </c>
-      <c r="CH3" t="s">
+      <c r="CJ3" t="s">
         <v>382</v>
       </c>
-      <c r="CI3" t="s">
+      <c r="CK3" t="s">
         <v>382</v>
       </c>
-      <c r="CJ3" t="s">
+      <c r="CL3" t="s">
         <v>125</v>
       </c>
-      <c r="CK3" t="s">
+      <c r="CM3" t="s">
         <v>120</v>
       </c>
-      <c r="CL3" t="s">
+      <c r="CN3" t="s">
         <v>120</v>
-      </c>
-      <c r="CM3" t="s">
-        <v>123</v>
-      </c>
-      <c r="CN3" t="s">
-        <v>123</v>
       </c>
       <c r="CO3" t="s">
         <v>123</v>
       </c>
       <c r="CP3" t="s">
-        <v>379</v>
+        <v>123</v>
       </c>
       <c r="CQ3" t="s">
         <v>123</v>
       </c>
       <c r="CR3" t="s">
+        <v>379</v>
+      </c>
+      <c r="CS3" t="s">
+        <v>123</v>
+      </c>
+      <c r="CT3" t="s">
         <v>116</v>
       </c>
-      <c r="CS3" t="s">
+      <c r="CU3" t="s">
         <v>125</v>
       </c>
-      <c r="CT3" t="s">
+      <c r="CV3" t="s">
         <v>383</v>
       </c>
-      <c r="CU3" t="s">
+      <c r="CW3" t="s">
         <v>384</v>
       </c>
-      <c r="CV3" t="s">
+      <c r="CX3" t="s">
         <v>384</v>
-      </c>
-      <c r="CW3" t="s">
-        <v>383</v>
-      </c>
-      <c r="CX3" t="s">
-        <v>383</v>
       </c>
       <c r="CY3" t="s">
         <v>383</v>
@@ -7522,10 +7588,10 @@
         <v>383</v>
       </c>
       <c r="DB3" t="s">
-        <v>116</v>
+        <v>383</v>
       </c>
       <c r="DC3" t="s">
-        <v>116</v>
+        <v>383</v>
       </c>
       <c r="DD3" t="s">
         <v>116</v>
@@ -7539,13 +7605,19 @@
       <c r="DG3" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="4" spans="1:111" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="DH3" t="s">
+        <v>116</v>
+      </c>
+      <c r="DI3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:113" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="5" spans="1:111" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:113" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
@@ -7560,14 +7632,16 @@
       <c r="V5" s="6"/>
       <c r="W5" s="6"/>
       <c r="X5" s="6"/>
-      <c r="BT5" s="7"/>
-      <c r="BU5" s="7"/>
+      <c r="AR5"/>
+      <c r="AS5"/>
       <c r="BV5" s="7"/>
       <c r="BW5" s="7"/>
       <c r="BX5" s="7"/>
       <c r="BY5" s="7"/>
-    </row>
-    <row r="6" spans="1:111" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="BZ5" s="7"/>
+      <c r="CA5" s="7"/>
+    </row>
+    <row r="6" spans="1:113" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>386</v>
       </c>
@@ -7585,14 +7659,16 @@
       <c r="V6" s="8"/>
       <c r="W6" s="8"/>
       <c r="X6" s="8"/>
-      <c r="BT6" s="10"/>
-      <c r="BU6" s="10"/>
+      <c r="AR6"/>
+      <c r="AS6"/>
       <c r="BV6" s="10"/>
       <c r="BW6" s="10"/>
       <c r="BX6" s="10"/>
       <c r="BY6" s="10"/>
-    </row>
-    <row r="7" spans="1:111" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="BZ6" s="10"/>
+      <c r="CA6" s="10"/>
+    </row>
+    <row r="7" spans="1:113" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
@@ -7607,14 +7683,16 @@
       <c r="V7" s="6"/>
       <c r="W7" s="6"/>
       <c r="X7" s="6"/>
-      <c r="BT7" s="7"/>
-      <c r="BU7" s="7"/>
+      <c r="AR7"/>
+      <c r="AS7"/>
       <c r="BV7" s="7"/>
       <c r="BW7" s="7"/>
       <c r="BX7" s="7"/>
       <c r="BY7" s="7"/>
-    </row>
-    <row r="8" spans="1:111" x14ac:dyDescent="0.25">
+      <c r="BZ7" s="7"/>
+      <c r="CA7" s="7"/>
+    </row>
+    <row r="8" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>130</v>
       </c>
@@ -7631,46 +7709,46 @@
       <c r="AO8" t="s">
         <v>388</v>
       </c>
-      <c r="AR8" t="s">
+      <c r="AT8" t="s">
         <v>389</v>
       </c>
-      <c r="AV8" t="s">
+      <c r="AX8" t="s">
         <v>390</v>
       </c>
-      <c r="AX8">
-        <v>1</v>
-      </c>
-      <c r="BB8">
-        <v>1</v>
-      </c>
-      <c r="BZ8" t="s">
+      <c r="AZ8">
+        <v>1</v>
+      </c>
+      <c r="BD8">
+        <v>1</v>
+      </c>
+      <c r="CB8" t="s">
         <v>391</v>
       </c>
-      <c r="CB8" t="s">
+      <c r="CD8" t="s">
         <v>392</v>
       </c>
-      <c r="CE8" t="s">
+      <c r="CG8" t="s">
         <v>393</v>
       </c>
-      <c r="CF8" t="s">
+      <c r="CH8" t="s">
         <v>394</v>
       </c>
-      <c r="CG8" t="s">
+      <c r="CI8" t="s">
         <v>395</v>
       </c>
-      <c r="CH8" t="s">
+      <c r="CJ8" t="s">
         <v>396</v>
       </c>
-      <c r="CL8" s="13"/>
-      <c r="CW8" t="s">
+      <c r="CN8" s="13"/>
+      <c r="CY8" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="9" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:113" x14ac:dyDescent="0.25">
       <c r="R9"/>
-      <c r="CL9" s="13"/>
-    </row>
-    <row r="10" spans="1:111" x14ac:dyDescent="0.25">
+      <c r="CN9" s="13"/>
+    </row>
+    <row r="10" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>398</v>
       </c>
@@ -7708,29 +7786,29 @@
       <c r="AG10" t="s">
         <v>405</v>
       </c>
-      <c r="BB10">
-        <v>1</v>
-      </c>
-      <c r="BM10" t="s">
+      <c r="BD10">
+        <v>1</v>
+      </c>
+      <c r="BO10" t="s">
         <v>406</v>
       </c>
-      <c r="BT10" s="7">
+      <c r="BV10" s="7">
         <v>0</v>
       </c>
-      <c r="BU10" s="7">
+      <c r="BW10" s="7">
         <v>18</v>
       </c>
-      <c r="BV10" s="7">
-        <v>1</v>
-      </c>
-      <c r="BW10" s="7" t="s">
+      <c r="BX10" s="7">
+        <v>1</v>
+      </c>
+      <c r="BY10" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="CS10" t="s">
+      <c r="CU10" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="11" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>408</v>
       </c>
@@ -7768,32 +7846,32 @@
       <c r="AG11" t="s">
         <v>405</v>
       </c>
-      <c r="BB11">
-        <v>1</v>
-      </c>
-      <c r="BT11" s="11"/>
-      <c r="BU11" s="11"/>
+      <c r="BD11">
+        <v>1</v>
+      </c>
       <c r="BV11" s="11"/>
       <c r="BW11" s="11"/>
       <c r="BX11" s="11"/>
       <c r="BY11" s="11"/>
-      <c r="CS11" t="s">
+      <c r="BZ11" s="11"/>
+      <c r="CA11" s="11"/>
+      <c r="CU11" t="s">
         <v>411</v>
       </c>
-      <c r="DB11">
-        <v>1</v>
-      </c>
       <c r="DD11">
         <v>1</v>
       </c>
-      <c r="DE11">
-        <v>1</v>
-      </c>
       <c r="DF11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:111" x14ac:dyDescent="0.25">
+      <c r="DG11">
+        <v>1</v>
+      </c>
+      <c r="DH11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>412</v>
       </c>
@@ -7824,38 +7902,38 @@
       <c r="AC12">
         <v>2</v>
       </c>
-      <c r="AT12">
+      <c r="AV12">
         <v>1.7</v>
       </c>
-      <c r="BB12">
+      <c r="BD12">
         <v>99</v>
       </c>
-      <c r="BT12"/>
-      <c r="BU12" s="11"/>
-      <c r="BV12" s="11"/>
+      <c r="BV12"/>
       <c r="BW12" s="11"/>
       <c r="BX12" s="11"/>
       <c r="BY12" s="11"/>
-      <c r="CE12" t="s">
+      <c r="BZ12" s="11"/>
+      <c r="CA12" s="11"/>
+      <c r="CG12" t="s">
         <v>393</v>
       </c>
-      <c r="CL12" t="s">
+      <c r="CN12" t="s">
         <v>414</v>
       </c>
-      <c r="CM12">
+      <c r="CO12">
         <v>-0.8</v>
       </c>
-      <c r="CP12">
+      <c r="CR12">
         <v>10</v>
       </c>
-      <c r="CV12" t="s">
+      <c r="CX12" t="s">
         <v>415</v>
       </c>
-      <c r="DF12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:111" x14ac:dyDescent="0.25">
+      <c r="DH12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>416</v>
       </c>
@@ -7886,42 +7964,42 @@
       <c r="AC13">
         <v>2</v>
       </c>
-      <c r="AT13">
+      <c r="AV13">
         <v>1.7</v>
       </c>
-      <c r="BB13">
+      <c r="BD13">
         <v>99</v>
       </c>
-      <c r="BT13"/>
-      <c r="BU13" s="11"/>
-      <c r="BV13" s="11"/>
+      <c r="BV13"/>
       <c r="BW13" s="11"/>
       <c r="BX13" s="11"/>
       <c r="BY13" s="11"/>
-      <c r="CE13" t="s">
+      <c r="BZ13" s="11"/>
+      <c r="CA13" s="11"/>
+      <c r="CG13" t="s">
         <v>393</v>
       </c>
-      <c r="CL13" t="s">
+      <c r="CN13" t="s">
         <v>414</v>
       </c>
-      <c r="CM13">
+      <c r="CO13">
         <v>-0.8</v>
       </c>
-      <c r="CP13">
+      <c r="CR13">
         <v>10</v>
       </c>
-      <c r="CV13" t="s">
+      <c r="CX13" t="s">
         <v>415</v>
       </c>
-      <c r="DF13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:111" x14ac:dyDescent="0.25">
+      <c r="DH13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:113" x14ac:dyDescent="0.25">
       <c r="R14"/>
-      <c r="CL14" s="13"/>
-    </row>
-    <row r="15" spans="1:111" x14ac:dyDescent="0.25">
+      <c r="CN14" s="13"/>
+    </row>
+    <row r="15" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>418</v>
       </c>
@@ -7959,43 +8037,43 @@
       <c r="AG15" t="s">
         <v>405</v>
       </c>
-      <c r="BB15">
-        <v>1</v>
-      </c>
-      <c r="BM15" t="s">
+      <c r="BD15">
+        <v>1</v>
+      </c>
+      <c r="BO15" t="s">
         <v>423</v>
       </c>
-      <c r="BN15" t="s">
+      <c r="BP15" t="s">
         <v>424</v>
       </c>
-      <c r="BR15">
+      <c r="BT15">
         <v>20</v>
       </c>
-      <c r="BT15" s="7">
+      <c r="BV15" s="7">
         <v>12</v>
       </c>
-      <c r="BU15" s="7">
+      <c r="BW15" s="7">
         <v>16</v>
       </c>
-      <c r="BV15" s="7">
-        <v>1</v>
-      </c>
-      <c r="BW15" s="7" t="s">
+      <c r="BX15" s="7">
+        <v>1</v>
+      </c>
+      <c r="BY15" s="7" t="s">
         <v>425</v>
       </c>
-      <c r="BX15"/>
-      <c r="BZ15" s="7"/>
-      <c r="CL15" t="s">
+      <c r="BZ15"/>
+      <c r="CB15" s="7"/>
+      <c r="CN15" t="s">
         <v>426</v>
       </c>
-      <c r="CM15">
+      <c r="CO15">
         <v>3</v>
       </c>
-      <c r="CP15">
+      <c r="CR15">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>427</v>
       </c>
@@ -8033,33 +8111,33 @@
       <c r="AG16" t="s">
         <v>405</v>
       </c>
-      <c r="BB16">
-        <v>1</v>
-      </c>
-      <c r="BT16" s="11"/>
-      <c r="BU16" s="11"/>
+      <c r="BD16">
+        <v>1</v>
+      </c>
       <c r="BV16" s="11"/>
       <c r="BW16" s="11"/>
-      <c r="BX16"/>
+      <c r="BX16" s="11"/>
       <c r="BY16" s="11"/>
-      <c r="BZ16" s="11"/>
-      <c r="CS16" t="s">
+      <c r="BZ16"/>
+      <c r="CA16" s="11"/>
+      <c r="CB16" s="11"/>
+      <c r="CU16" t="s">
         <v>428</v>
       </c>
-      <c r="DB16">
-        <v>1</v>
-      </c>
       <c r="DD16">
         <v>1</v>
       </c>
-      <c r="DE16">
-        <v>1</v>
-      </c>
       <c r="DF16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:121" x14ac:dyDescent="0.25">
+      <c r="DG16">
+        <v>1</v>
+      </c>
+      <c r="DH16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>429</v>
       </c>
@@ -8084,48 +8162,48 @@
       <c r="AO17" t="s">
         <v>388</v>
       </c>
-      <c r="AR17" t="s">
+      <c r="AT17" t="s">
         <v>431</v>
       </c>
-      <c r="AV17" t="s">
+      <c r="AX17" t="s">
         <v>390</v>
       </c>
-      <c r="AX17">
-        <v>1</v>
-      </c>
-      <c r="BB17">
-        <v>1</v>
-      </c>
-      <c r="BH17">
+      <c r="AZ17">
+        <v>1</v>
+      </c>
+      <c r="BD17">
+        <v>1</v>
+      </c>
+      <c r="BJ17">
         <v>1.1000000000000001</v>
       </c>
-      <c r="BI17">
-        <v>1</v>
-      </c>
-      <c r="BJ17">
-        <v>1</v>
-      </c>
-      <c r="BX17"/>
-      <c r="BZ17" t="s">
+      <c r="BK17">
+        <v>1</v>
+      </c>
+      <c r="BL17">
+        <v>1</v>
+      </c>
+      <c r="BZ17"/>
+      <c r="CB17" t="s">
         <v>432</v>
       </c>
-      <c r="CE17" t="s">
+      <c r="CG17" t="s">
         <v>393</v>
       </c>
-      <c r="CF17" t="s">
+      <c r="CH17" t="s">
         <v>394</v>
       </c>
-      <c r="CG17" t="s">
+      <c r="CI17" t="s">
         <v>395</v>
       </c>
-      <c r="CH17" t="s">
+      <c r="CJ17" t="s">
         <v>433</v>
       </c>
-      <c r="CW17" t="s">
+      <c r="CY17" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="18" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>424</v>
       </c>
@@ -8151,33 +8229,33 @@
       <c r="AG18" t="s">
         <v>405</v>
       </c>
-      <c r="BB18">
-        <v>1</v>
-      </c>
-      <c r="BQ18">
+      <c r="BD18">
+        <v>1</v>
+      </c>
+      <c r="BS18">
         <v>0.5</v>
       </c>
-      <c r="BX18"/>
-      <c r="BZ18" t="s">
+      <c r="BZ18"/>
+      <c r="CB18" t="s">
         <v>435</v>
       </c>
-      <c r="CE18" t="s">
+      <c r="CG18" t="s">
         <v>393</v>
       </c>
-      <c r="DB18">
-        <v>1</v>
-      </c>
       <c r="DD18">
         <v>1</v>
       </c>
-      <c r="DE18">
-        <v>1</v>
-      </c>
       <c r="DF18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:121" x14ac:dyDescent="0.25">
+      <c r="DG18">
+        <v>1</v>
+      </c>
+      <c r="DH18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>436</v>
       </c>
@@ -8206,33 +8284,33 @@
       <c r="AG19" t="s">
         <v>405</v>
       </c>
-      <c r="BB19">
-        <v>1</v>
-      </c>
-      <c r="BQ19">
+      <c r="BD19">
+        <v>1</v>
+      </c>
+      <c r="BS19">
         <v>0.5</v>
       </c>
-      <c r="BX19"/>
-      <c r="BZ19" t="s">
+      <c r="BZ19"/>
+      <c r="CB19" t="s">
         <v>438</v>
       </c>
-      <c r="CE19" t="s">
+      <c r="CG19" t="s">
         <v>393</v>
       </c>
-      <c r="DB19">
-        <v>1</v>
-      </c>
       <c r="DD19">
         <v>1</v>
       </c>
-      <c r="DE19">
-        <v>1</v>
-      </c>
       <c r="DF19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:121" x14ac:dyDescent="0.25">
+      <c r="DG19">
+        <v>1</v>
+      </c>
+      <c r="DH19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>439</v>
       </c>
@@ -8270,33 +8348,33 @@
       <c r="AG20" t="s">
         <v>405</v>
       </c>
-      <c r="BB20">
-        <v>1</v>
-      </c>
-      <c r="BT20"/>
-      <c r="BU20" s="11"/>
-      <c r="BV20" s="11"/>
+      <c r="BD20">
+        <v>1</v>
+      </c>
+      <c r="BV20"/>
       <c r="BW20" s="11"/>
       <c r="BX20" s="11"/>
       <c r="BY20" s="11"/>
       <c r="BZ20" s="11"/>
-      <c r="CS20" t="s">
+      <c r="CA20" s="11"/>
+      <c r="CB20" s="11"/>
+      <c r="CU20" t="s">
         <v>440</v>
       </c>
-      <c r="DB20">
-        <v>1</v>
-      </c>
       <c r="DD20">
         <v>1</v>
       </c>
-      <c r="DE20">
-        <v>1</v>
-      </c>
       <c r="DF20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:121" x14ac:dyDescent="0.25">
+      <c r="DG20">
+        <v>1</v>
+      </c>
+      <c r="DH20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>441</v>
       </c>
@@ -8327,35 +8405,35 @@
       <c r="AC21">
         <v>2</v>
       </c>
-      <c r="AT21">
+      <c r="AV21">
         <v>1.7</v>
       </c>
-      <c r="BB21">
+      <c r="BD21">
         <v>99</v>
       </c>
-      <c r="BT21"/>
-      <c r="BU21" s="11"/>
-      <c r="BV21" s="11"/>
+      <c r="BV21"/>
       <c r="BW21" s="11"/>
       <c r="BX21" s="11"/>
       <c r="BY21" s="11"/>
-      <c r="CE21" t="s">
+      <c r="BZ21" s="11"/>
+      <c r="CA21" s="11"/>
+      <c r="CG21" t="s">
         <v>393</v>
       </c>
-      <c r="CL21" t="s">
+      <c r="CN21" t="s">
         <v>442</v>
       </c>
-      <c r="CP21">
+      <c r="CR21">
         <v>5</v>
       </c>
-      <c r="CV21" t="s">
+      <c r="CX21" t="s">
         <v>415</v>
       </c>
-      <c r="DF21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:121" x14ac:dyDescent="0.25">
+      <c r="DH21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>443</v>
       </c>
@@ -8386,35 +8464,35 @@
       <c r="AC22">
         <v>2</v>
       </c>
-      <c r="AT22">
+      <c r="AV22">
         <v>1.7</v>
       </c>
-      <c r="BB22">
+      <c r="BD22">
         <v>99</v>
       </c>
-      <c r="BT22"/>
-      <c r="BU22" s="11"/>
-      <c r="BV22" s="11"/>
+      <c r="BV22"/>
       <c r="BW22" s="11"/>
       <c r="BX22" s="11"/>
       <c r="BY22" s="11"/>
-      <c r="CE22" t="s">
+      <c r="BZ22" s="11"/>
+      <c r="CA22" s="11"/>
+      <c r="CG22" t="s">
         <v>393</v>
       </c>
-      <c r="CL22" t="s">
+      <c r="CN22" t="s">
         <v>442</v>
       </c>
-      <c r="CP22">
+      <c r="CR22">
         <v>5</v>
       </c>
-      <c r="CV22" t="s">
+      <c r="CX22" t="s">
         <v>415</v>
       </c>
-      <c r="DF22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:121" x14ac:dyDescent="0.25">
+      <c r="DH22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
       <c r="J23" s="9"/>
       <c r="L23" s="9"/>
       <c r="M23"/>
@@ -8438,20 +8516,20 @@
       <c r="AE23" s="9"/>
       <c r="AF23" s="9"/>
       <c r="AJ23" s="9"/>
-      <c r="BT23"/>
-      <c r="BU23"/>
       <c r="BV23"/>
       <c r="BW23"/>
       <c r="BX23"/>
       <c r="BY23"/>
-      <c r="CX23" s="11"/>
-      <c r="CY23" s="11"/>
+      <c r="BZ23"/>
+      <c r="CA23"/>
       <c r="CZ23" s="11"/>
       <c r="DA23" s="11"/>
       <c r="DB23" s="11"/>
       <c r="DC23" s="11"/>
-    </row>
-    <row r="24" spans="1:121" x14ac:dyDescent="0.25">
+      <c r="DD23" s="11"/>
+      <c r="DE23" s="11"/>
+    </row>
+    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>444</v>
       </c>
@@ -8485,50 +8563,50 @@
       <c r="AG24" t="s">
         <v>405</v>
       </c>
-      <c r="BB24">
-        <v>1</v>
-      </c>
-      <c r="BM24" t="s">
+      <c r="BD24">
+        <v>1</v>
+      </c>
+      <c r="BO24" t="s">
         <v>448</v>
       </c>
-      <c r="BN24" t="s">
+      <c r="BP24" t="s">
         <v>449</v>
       </c>
-      <c r="BR24">
+      <c r="BT24">
         <v>40</v>
       </c>
-      <c r="BS24">
-        <v>1</v>
-      </c>
-      <c r="BT24" s="7">
+      <c r="BU24">
+        <v>1</v>
+      </c>
+      <c r="BV24" s="7">
         <v>24</v>
       </c>
-      <c r="BU24" s="7">
+      <c r="BW24" s="7">
         <v>34</v>
       </c>
-      <c r="BV24" s="7">
-        <v>1</v>
-      </c>
-      <c r="BW24" s="7" t="s">
+      <c r="BX24" s="7">
+        <v>1</v>
+      </c>
+      <c r="BY24" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="BY24" s="21" t="s">
+      <c r="CA24" s="21" t="s">
         <v>574</v>
       </c>
-      <c r="CL24" t="s">
+      <c r="CN24" t="s">
         <v>450</v>
       </c>
-      <c r="CM24" s="20" t="s">
+      <c r="CO24" s="20" t="s">
         <v>451</v>
       </c>
-      <c r="CP24">
+      <c r="CR24">
         <v>99999</v>
       </c>
-      <c r="CR24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:121" x14ac:dyDescent="0.25">
+      <c r="CT24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>452</v>
       </c>
@@ -8562,29 +8640,29 @@
       <c r="AG25" t="s">
         <v>405</v>
       </c>
-      <c r="BB25">
-        <v>1</v>
-      </c>
-      <c r="BT25" s="11"/>
-      <c r="BU25" s="11"/>
+      <c r="BD25">
+        <v>1</v>
+      </c>
       <c r="BV25" s="11"/>
       <c r="BW25" s="11"/>
       <c r="BX25" s="11"/>
       <c r="BY25" s="11"/>
-      <c r="CS25" t="s">
+      <c r="BZ25" s="11"/>
+      <c r="CA25" s="11"/>
+      <c r="CU25" t="s">
         <v>453</v>
       </c>
-      <c r="DB25">
-        <v>1</v>
-      </c>
-      <c r="DE25">
-        <v>1</v>
-      </c>
-      <c r="DF25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:121" x14ac:dyDescent="0.25">
+      <c r="DD25">
+        <v>1</v>
+      </c>
+      <c r="DG25">
+        <v>1</v>
+      </c>
+      <c r="DH25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>454</v>
       </c>
@@ -8608,44 +8686,44 @@
       <c r="AO26" t="s">
         <v>388</v>
       </c>
-      <c r="AR26" t="s">
+      <c r="AT26" t="s">
         <v>389</v>
       </c>
-      <c r="AV26" t="s">
+      <c r="AX26" t="s">
         <v>390</v>
       </c>
-      <c r="AX26">
-        <v>1</v>
-      </c>
-      <c r="BB26">
-        <v>1</v>
-      </c>
-      <c r="BY26" s="7" t="s">
+      <c r="AZ26">
+        <v>1</v>
+      </c>
+      <c r="BD26">
+        <v>1</v>
+      </c>
+      <c r="CA26" s="7" t="s">
         <v>425</v>
       </c>
-      <c r="BZ26" t="s">
+      <c r="CB26" t="s">
         <v>457</v>
       </c>
-      <c r="CB26" s="12" t="s">
+      <c r="CD26" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="CE26" t="s">
+      <c r="CG26" t="s">
         <v>393</v>
       </c>
-      <c r="CF26" t="s">
+      <c r="CH26" t="s">
         <v>394</v>
       </c>
-      <c r="CG26" t="s">
+      <c r="CI26" t="s">
         <v>395</v>
       </c>
-      <c r="CH26" t="s">
+      <c r="CJ26" t="s">
         <v>459</v>
       </c>
-      <c r="CW26" t="s">
+      <c r="CY26" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="27" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>460</v>
       </c>
@@ -8669,44 +8747,44 @@
       <c r="AO27" t="s">
         <v>388</v>
       </c>
-      <c r="AR27" t="s">
+      <c r="AT27" t="s">
         <v>389</v>
       </c>
-      <c r="AV27" t="s">
+      <c r="AX27" t="s">
         <v>390</v>
       </c>
-      <c r="AX27">
-        <v>1</v>
-      </c>
-      <c r="BB27">
-        <v>1</v>
-      </c>
-      <c r="BY27" s="7" t="s">
+      <c r="AZ27">
+        <v>1</v>
+      </c>
+      <c r="BD27">
+        <v>1</v>
+      </c>
+      <c r="CA27" s="7" t="s">
         <v>425</v>
       </c>
-      <c r="BZ27" t="s">
+      <c r="CB27" t="s">
         <v>457</v>
       </c>
-      <c r="CB27" s="12" t="s">
+      <c r="CD27" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="CE27" t="s">
+      <c r="CG27" t="s">
         <v>393</v>
       </c>
-      <c r="CF27" t="s">
+      <c r="CH27" t="s">
         <v>394</v>
       </c>
-      <c r="CG27" t="s">
+      <c r="CI27" t="s">
         <v>395</v>
       </c>
-      <c r="CH27" t="s">
+      <c r="CJ27" t="s">
         <v>461</v>
       </c>
-      <c r="CW27" t="s">
+      <c r="CY27" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="28" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>449</v>
       </c>
@@ -8728,29 +8806,29 @@
       <c r="AG28" t="s">
         <v>405</v>
       </c>
-      <c r="BB28">
-        <v>1</v>
-      </c>
-      <c r="BQ28">
+      <c r="BD28">
+        <v>1</v>
+      </c>
+      <c r="BS28">
         <v>0.5</v>
       </c>
-      <c r="BZ28" t="s">
+      <c r="CB28" t="s">
         <v>462</v>
       </c>
-      <c r="CE28" t="s">
+      <c r="CG28" t="s">
         <v>393</v>
       </c>
-      <c r="DB28">
-        <v>1</v>
-      </c>
-      <c r="DE28">
-        <v>1</v>
-      </c>
-      <c r="DF28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:121" x14ac:dyDescent="0.25">
+      <c r="DD28">
+        <v>1</v>
+      </c>
+      <c r="DG28">
+        <v>1</v>
+      </c>
+      <c r="DH28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>463</v>
       </c>
@@ -8775,29 +8853,29 @@
       <c r="AG29" t="s">
         <v>405</v>
       </c>
-      <c r="BB29">
-        <v>1</v>
-      </c>
-      <c r="BQ29">
+      <c r="BD29">
+        <v>1</v>
+      </c>
+      <c r="BS29">
         <v>0.5</v>
       </c>
-      <c r="BZ29" t="s">
+      <c r="CB29" t="s">
         <v>464</v>
       </c>
-      <c r="CE29" t="s">
+      <c r="CG29" t="s">
         <v>393</v>
       </c>
-      <c r="DB29">
-        <v>1</v>
-      </c>
-      <c r="DE29">
-        <v>1</v>
-      </c>
-      <c r="DF29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:121" x14ac:dyDescent="0.25">
+      <c r="DD29">
+        <v>1</v>
+      </c>
+      <c r="DG29">
+        <v>1</v>
+      </c>
+      <c r="DH29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>465</v>
       </c>
@@ -8831,29 +8909,29 @@
       <c r="AG30" t="s">
         <v>405</v>
       </c>
-      <c r="BB30">
-        <v>1</v>
-      </c>
-      <c r="BT30" s="11"/>
-      <c r="BU30" s="11"/>
+      <c r="BD30">
+        <v>1</v>
+      </c>
       <c r="BV30" s="11"/>
       <c r="BW30" s="11"/>
       <c r="BX30" s="11"/>
       <c r="BY30" s="11"/>
-      <c r="CS30" t="s">
+      <c r="BZ30" s="11"/>
+      <c r="CA30" s="11"/>
+      <c r="CU30" t="s">
         <v>466</v>
       </c>
-      <c r="DB30">
-        <v>1</v>
-      </c>
-      <c r="DE30">
-        <v>1</v>
-      </c>
-      <c r="DF30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:121" x14ac:dyDescent="0.25">
+      <c r="DD30">
+        <v>1</v>
+      </c>
+      <c r="DG30">
+        <v>1</v>
+      </c>
+      <c r="DH30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>467</v>
       </c>
@@ -8888,36 +8966,36 @@
       <c r="AG31" t="s">
         <v>405</v>
       </c>
-      <c r="BB31">
-        <v>1</v>
-      </c>
-      <c r="BM31" t="s">
+      <c r="BD31">
+        <v>1</v>
+      </c>
+      <c r="BO31" t="s">
         <v>468</v>
       </c>
-      <c r="BT31"/>
-      <c r="BU31" s="11"/>
-      <c r="BV31" s="11"/>
+      <c r="BV31"/>
       <c r="BW31" s="11"/>
       <c r="BX31" s="11"/>
       <c r="BY31" s="11"/>
       <c r="BZ31" s="11"/>
-      <c r="CL31" t="s">
+      <c r="CA31" s="11"/>
+      <c r="CB31" s="11"/>
+      <c r="CN31" t="s">
         <v>469</v>
       </c>
-      <c r="CP31">
+      <c r="CR31">
         <v>99999</v>
       </c>
-      <c r="DB31">
-        <v>1</v>
-      </c>
-      <c r="DE31">
-        <v>1</v>
-      </c>
-      <c r="DF31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:121" x14ac:dyDescent="0.25">
+      <c r="DD31">
+        <v>1</v>
+      </c>
+      <c r="DG31">
+        <v>1</v>
+      </c>
+      <c r="DH31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>468</v>
       </c>
@@ -8948,33 +9026,33 @@
       <c r="AG32" t="s">
         <v>405</v>
       </c>
-      <c r="AR32" t="s">
+      <c r="AT32" t="s">
         <v>470</v>
       </c>
-      <c r="BB32">
-        <v>1</v>
-      </c>
-      <c r="BT32"/>
-      <c r="BU32" s="11"/>
-      <c r="BV32" s="11"/>
+      <c r="BD32">
+        <v>1</v>
+      </c>
+      <c r="BV32"/>
       <c r="BW32" s="11"/>
       <c r="BX32" s="11"/>
       <c r="BY32" s="11"/>
       <c r="BZ32" s="11"/>
-      <c r="DB32">
-        <v>1</v>
-      </c>
-      <c r="DE32">
-        <v>1</v>
-      </c>
-      <c r="DF32">
-        <v>1</v>
-      </c>
-      <c r="DQ32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="CA32" s="11"/>
+      <c r="CB32" s="11"/>
+      <c r="DD32">
+        <v>1</v>
+      </c>
+      <c r="DG32">
+        <v>1</v>
+      </c>
+      <c r="DH32">
+        <v>1</v>
+      </c>
+      <c r="DS32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>471</v>
       </c>
@@ -9005,41 +9083,41 @@
       <c r="AC33">
         <v>2</v>
       </c>
-      <c r="AT33">
+      <c r="AV33">
         <v>1.7</v>
       </c>
-      <c r="BB33">
+      <c r="BD33">
         <v>99</v>
       </c>
-      <c r="BT33"/>
-      <c r="BU33" s="11"/>
-      <c r="BV33" s="11"/>
+      <c r="BV33"/>
       <c r="BW33" s="11"/>
       <c r="BX33" s="11"/>
       <c r="BY33" s="11"/>
-      <c r="CE33" t="s">
+      <c r="BZ33" s="11"/>
+      <c r="CA33" s="11"/>
+      <c r="CG33" t="s">
         <v>393</v>
       </c>
-      <c r="CL33" t="s">
+      <c r="CN33" t="s">
         <v>472</v>
       </c>
-      <c r="CM33">
+      <c r="CO33">
         <v>-0.8</v>
       </c>
-      <c r="CN33">
+      <c r="CP33">
         <v>0.35</v>
       </c>
-      <c r="CP33">
+      <c r="CR33">
         <v>7</v>
       </c>
-      <c r="CV33" t="s">
+      <c r="CX33" t="s">
         <v>415</v>
       </c>
-      <c r="DF33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="DH33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>473</v>
       </c>
@@ -9070,41 +9148,41 @@
       <c r="AC34">
         <v>2</v>
       </c>
-      <c r="AT34">
+      <c r="AV34">
         <v>1.7</v>
       </c>
-      <c r="BB34">
+      <c r="BD34">
         <v>99</v>
       </c>
-      <c r="BT34"/>
-      <c r="BU34" s="11"/>
-      <c r="BV34" s="11"/>
+      <c r="BV34"/>
       <c r="BW34" s="11"/>
       <c r="BX34" s="11"/>
       <c r="BY34" s="11"/>
-      <c r="CE34" t="s">
+      <c r="BZ34" s="11"/>
+      <c r="CA34" s="11"/>
+      <c r="CG34" t="s">
         <v>393</v>
       </c>
-      <c r="CL34" t="s">
+      <c r="CN34" t="s">
         <v>472</v>
       </c>
-      <c r="CM34">
+      <c r="CO34">
         <v>-0.8</v>
       </c>
-      <c r="CN34">
+      <c r="CP34">
         <v>0.35</v>
       </c>
-      <c r="CP34">
+      <c r="CR34">
         <v>7</v>
       </c>
-      <c r="CV34" t="s">
+      <c r="CX34" t="s">
         <v>415</v>
       </c>
-      <c r="DF34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="DH34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>150</v>
       </c>
@@ -9143,20 +9221,20 @@
       <c r="AC37">
         <v>2</v>
       </c>
-      <c r="AR37" t="s">
+      <c r="AT37" t="s">
         <v>470</v>
       </c>
-      <c r="BB37">
-        <v>1</v>
-      </c>
-      <c r="BT37"/>
-      <c r="BU37" s="11"/>
-      <c r="BV37" s="11"/>
+      <c r="BD37">
+        <v>1</v>
+      </c>
+      <c r="BV37"/>
       <c r="BW37" s="11"/>
       <c r="BX37" s="11"/>
       <c r="BY37" s="11"/>
-    </row>
-    <row r="38" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="BZ37" s="11"/>
+      <c r="CA37" s="11"/>
+    </row>
+    <row r="38" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>475</v>
       </c>
@@ -9187,26 +9265,26 @@
       <c r="AC38">
         <v>2</v>
       </c>
-      <c r="AT38">
+      <c r="AV38">
         <v>1.35</v>
       </c>
-      <c r="BB38">
-        <v>1</v>
-      </c>
-      <c r="BN38" t="s">
+      <c r="BD38">
+        <v>1</v>
+      </c>
+      <c r="BP38" t="s">
         <v>476</v>
       </c>
-      <c r="BT38"/>
-      <c r="BU38" s="11"/>
-      <c r="BV38" s="11"/>
+      <c r="BV38"/>
       <c r="BW38" s="11"/>
       <c r="BX38" s="11"/>
       <c r="BY38" s="11"/>
-      <c r="DF38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="BZ38" s="11"/>
+      <c r="CA38" s="11"/>
+      <c r="DH38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>476</v>
       </c>
@@ -9239,47 +9317,47 @@
       <c r="AC39">
         <v>2</v>
       </c>
-      <c r="AT39">
+      <c r="AV39">
         <v>1.7</v>
       </c>
-      <c r="BB39">
+      <c r="BD39">
         <v>99</v>
       </c>
-      <c r="BN39" t="s">
+      <c r="BP39" t="s">
         <v>477</v>
       </c>
-      <c r="BQ39">
+      <c r="BS39">
         <v>0.5</v>
       </c>
-      <c r="BT39"/>
-      <c r="BU39" s="11"/>
-      <c r="BV39" s="11"/>
+      <c r="BV39"/>
       <c r="BW39" s="11"/>
       <c r="BX39" s="11"/>
       <c r="BY39" s="11"/>
-      <c r="BZ39" t="s">
+      <c r="BZ39" s="11"/>
+      <c r="CA39" s="11"/>
+      <c r="CB39" t="s">
         <v>57</v>
       </c>
-      <c r="CE39" t="s">
+      <c r="CG39" t="s">
         <v>393</v>
       </c>
-      <c r="CL39" t="s">
+      <c r="CN39" t="s">
         <v>414</v>
       </c>
-      <c r="CM39">
+      <c r="CO39">
         <v>-0.8</v>
       </c>
-      <c r="CP39">
+      <c r="CR39">
         <v>10</v>
       </c>
-      <c r="CV39" t="s">
+      <c r="CX39" t="s">
         <v>415</v>
       </c>
-      <c r="DF39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="DH39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>156</v>
       </c>
@@ -9318,20 +9396,20 @@
       <c r="AC40">
         <v>2</v>
       </c>
-      <c r="AR40" t="s">
+      <c r="AT40" t="s">
         <v>470</v>
       </c>
-      <c r="BB40">
-        <v>1</v>
-      </c>
-      <c r="BT40"/>
-      <c r="BU40" s="11"/>
-      <c r="BV40" s="11"/>
+      <c r="BD40">
+        <v>1</v>
+      </c>
+      <c r="BV40"/>
       <c r="BW40" s="11"/>
       <c r="BX40" s="11"/>
       <c r="BY40" s="11"/>
-    </row>
-    <row r="41" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="BZ40" s="11"/>
+      <c r="CA40" s="11"/>
+    </row>
+    <row r="41" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>479</v>
       </c>
@@ -9362,26 +9440,26 @@
       <c r="AC41">
         <v>2</v>
       </c>
-      <c r="AT41">
+      <c r="AV41">
         <v>1.35</v>
       </c>
-      <c r="BB41">
-        <v>1</v>
-      </c>
-      <c r="BN41" t="s">
+      <c r="BD41">
+        <v>1</v>
+      </c>
+      <c r="BP41" t="s">
         <v>480</v>
       </c>
-      <c r="BT41"/>
-      <c r="BU41" s="11"/>
-      <c r="BV41" s="11"/>
+      <c r="BV41"/>
       <c r="BW41" s="11"/>
       <c r="BX41" s="11"/>
       <c r="BY41" s="11"/>
-      <c r="DF41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="BZ41" s="11"/>
+      <c r="CA41" s="11"/>
+      <c r="DH41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>480</v>
       </c>
@@ -9414,44 +9492,44 @@
       <c r="AC42">
         <v>2</v>
       </c>
-      <c r="AT42">
+      <c r="AV42">
         <v>1.7</v>
       </c>
-      <c r="BB42">
+      <c r="BD42">
         <v>99</v>
       </c>
-      <c r="BN42" t="s">
+      <c r="BP42" t="s">
         <v>477</v>
       </c>
-      <c r="BQ42">
+      <c r="BS42">
         <v>0.5</v>
       </c>
-      <c r="BT42"/>
-      <c r="BU42" s="11"/>
-      <c r="BV42" s="11"/>
+      <c r="BV42"/>
       <c r="BW42" s="11"/>
       <c r="BX42" s="11"/>
       <c r="BY42" s="11"/>
-      <c r="BZ42" t="s">
+      <c r="BZ42" s="11"/>
+      <c r="CA42" s="11"/>
+      <c r="CB42" t="s">
         <v>57</v>
       </c>
-      <c r="CE42" t="s">
+      <c r="CG42" t="s">
         <v>393</v>
       </c>
-      <c r="CL42" t="s">
+      <c r="CN42" t="s">
         <v>442</v>
       </c>
-      <c r="CP42">
+      <c r="CR42">
         <v>5</v>
       </c>
-      <c r="CV42" t="s">
+      <c r="CX42" t="s">
         <v>415</v>
       </c>
-      <c r="DF42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="DH42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>159</v>
       </c>
@@ -9486,20 +9564,20 @@
       <c r="AC43">
         <v>2</v>
       </c>
-      <c r="AR43" t="s">
+      <c r="AT43" t="s">
         <v>470</v>
       </c>
-      <c r="BB43">
-        <v>1</v>
-      </c>
-      <c r="BT43"/>
-      <c r="BU43" s="11"/>
-      <c r="BV43" s="11"/>
+      <c r="BD43">
+        <v>1</v>
+      </c>
+      <c r="BV43"/>
       <c r="BW43" s="11"/>
       <c r="BX43" s="11"/>
       <c r="BY43" s="11"/>
-    </row>
-    <row r="44" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="BZ43" s="11"/>
+      <c r="CA43" s="11"/>
+    </row>
+    <row r="44" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>482</v>
       </c>
@@ -9526,26 +9604,26 @@
       <c r="AC44">
         <v>2</v>
       </c>
-      <c r="AT44">
+      <c r="AV44">
         <v>1.35</v>
       </c>
-      <c r="BB44">
-        <v>1</v>
-      </c>
-      <c r="BN44" t="s">
+      <c r="BD44">
+        <v>1</v>
+      </c>
+      <c r="BP44" t="s">
         <v>483</v>
       </c>
-      <c r="BT44"/>
-      <c r="BU44" s="11"/>
-      <c r="BV44" s="11"/>
+      <c r="BV44"/>
       <c r="BW44" s="11"/>
       <c r="BX44" s="11"/>
       <c r="BY44" s="11"/>
-      <c r="DF44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="BZ44" s="11"/>
+      <c r="CA44" s="11"/>
+      <c r="DH44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>483</v>
       </c>
@@ -9574,50 +9652,50 @@
       <c r="AC45">
         <v>2</v>
       </c>
-      <c r="AT45">
+      <c r="AV45">
         <v>1.7</v>
       </c>
-      <c r="BB45">
+      <c r="BD45">
         <v>99</v>
       </c>
-      <c r="BN45" t="s">
+      <c r="BP45" t="s">
         <v>477</v>
       </c>
-      <c r="BQ45">
+      <c r="BS45">
         <v>0.5</v>
       </c>
-      <c r="BT45"/>
-      <c r="BU45" s="11"/>
-      <c r="BV45" s="11"/>
+      <c r="BV45"/>
       <c r="BW45" s="11"/>
       <c r="BX45" s="11"/>
       <c r="BY45" s="11"/>
-      <c r="BZ45" t="s">
+      <c r="BZ45" s="11"/>
+      <c r="CA45" s="11"/>
+      <c r="CB45" t="s">
         <v>57</v>
       </c>
-      <c r="CE45" t="s">
+      <c r="CG45" t="s">
         <v>393</v>
       </c>
-      <c r="CL45" s="22" t="s">
+      <c r="CN45" s="22" t="s">
         <v>575</v>
       </c>
-      <c r="CM45">
+      <c r="CO45">
         <v>-0.8</v>
       </c>
-      <c r="CN45">
+      <c r="CP45">
         <v>1.35</v>
       </c>
-      <c r="CP45">
+      <c r="CR45">
         <v>7</v>
       </c>
-      <c r="CV45" t="s">
+      <c r="CX45" t="s">
         <v>415</v>
       </c>
-      <c r="DF45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="DH45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>477</v>
       </c>
@@ -9652,1328 +9730,1328 @@
       <c r="AG46" t="s">
         <v>405</v>
       </c>
-      <c r="AV46" t="s">
+      <c r="AX46" t="s">
         <v>484</v>
       </c>
-      <c r="AX46">
-        <v>1</v>
-      </c>
       <c r="AZ46">
         <v>1</v>
       </c>
       <c r="BB46">
         <v>1</v>
       </c>
-      <c r="BT46"/>
-      <c r="BU46" s="11"/>
-      <c r="BV46" s="11"/>
+      <c r="BD46">
+        <v>1</v>
+      </c>
+      <c r="BV46"/>
       <c r="BW46" s="11"/>
       <c r="BX46" s="11"/>
       <c r="BY46" s="11"/>
-      <c r="DB46">
-        <v>1</v>
-      </c>
+      <c r="BZ46" s="11"/>
+      <c r="CA46" s="11"/>
       <c r="DD46">
         <v>1</v>
       </c>
-      <c r="DE46">
-        <v>1</v>
-      </c>
       <c r="DF46">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT50"/>
-    </row>
-    <row r="51" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT51"/>
-      <c r="CJ51" s="6"/>
-    </row>
-    <row r="52" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ52" s="6"/>
-    </row>
-    <row r="53" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ53" s="6"/>
-    </row>
-    <row r="54" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ54" s="6"/>
-    </row>
-    <row r="55" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ55" s="6"/>
-    </row>
-    <row r="56" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT56"/>
-    </row>
-    <row r="57" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ57" s="6"/>
-    </row>
-    <row r="58" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ58" s="6"/>
-    </row>
-    <row r="59" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ59" s="6"/>
-    </row>
-    <row r="60" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ60" s="6"/>
-    </row>
-    <row r="61" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT61"/>
-    </row>
-    <row r="62" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ62" s="6"/>
-    </row>
-    <row r="63" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ63" s="6"/>
-    </row>
-    <row r="64" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ64" s="6"/>
-    </row>
-    <row r="65" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ65" s="6"/>
-    </row>
-    <row r="68" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ68" s="6"/>
-    </row>
-    <row r="69" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ69" s="6"/>
-    </row>
-    <row r="70" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ70" s="6"/>
-    </row>
-    <row r="71" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ71" s="6"/>
-    </row>
-    <row r="72" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ72" s="6"/>
-    </row>
-    <row r="74" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT74"/>
-    </row>
-    <row r="75" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ75" s="6"/>
-    </row>
-    <row r="76" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ76" s="6"/>
-    </row>
-    <row r="77" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ77" s="6"/>
-    </row>
-    <row r="78" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ78" s="6"/>
-    </row>
-    <row r="82" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ82" s="6"/>
-    </row>
-    <row r="84" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT84"/>
-    </row>
-    <row r="85" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT85"/>
-      <c r="CJ85" s="6"/>
-    </row>
-    <row r="86" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ86" s="6"/>
-    </row>
-    <row r="87" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ87" s="6"/>
-    </row>
-    <row r="88" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ88" s="6"/>
-    </row>
-    <row r="89" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ89" s="6"/>
-    </row>
-    <row r="91" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT91"/>
-    </row>
-    <row r="92" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ92" s="6"/>
-    </row>
-    <row r="93" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ93" s="6"/>
-    </row>
-    <row r="95" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ95" s="6"/>
-    </row>
-    <row r="96" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ96" s="6"/>
-    </row>
-    <row r="98" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT98"/>
-    </row>
-    <row r="99" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ99" s="6"/>
-    </row>
-    <row r="102" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ102" s="6"/>
-    </row>
-    <row r="103" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ103" s="6"/>
-    </row>
-    <row r="106" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ106" s="6"/>
-    </row>
-    <row r="108" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ108" s="6"/>
-    </row>
-    <row r="110" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT110"/>
-    </row>
-    <row r="111" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ111" s="6"/>
-    </row>
-    <row r="112" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ112" s="6"/>
-    </row>
-    <row r="114" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ114" s="6"/>
-    </row>
-    <row r="115" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ115" s="6"/>
-    </row>
-    <row r="116" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ116" s="6"/>
-    </row>
-    <row r="121" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ121" s="6"/>
-    </row>
-    <row r="122" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ122" s="6"/>
-    </row>
-    <row r="125" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ125" s="6"/>
-    </row>
-    <row r="126" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ126" s="6"/>
-    </row>
-    <row r="130" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ130" s="6"/>
-    </row>
-    <row r="134" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ134" s="6"/>
-    </row>
-    <row r="136" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ136" s="6"/>
-    </row>
-    <row r="137" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ137" s="6"/>
-    </row>
-    <row r="139" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ139" s="6"/>
-    </row>
-    <row r="140" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ140" s="6"/>
-    </row>
-    <row r="142" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT142"/>
-    </row>
-    <row r="143" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT143"/>
-      <c r="CJ143" s="6"/>
-    </row>
-    <row r="144" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ144" s="6"/>
-    </row>
-    <row r="146" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ146" s="6"/>
-    </row>
-    <row r="155" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT155"/>
-    </row>
-    <row r="156" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT156"/>
-      <c r="CJ156" s="6"/>
-    </row>
-    <row r="157" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ157" s="6"/>
-    </row>
-    <row r="158" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ158" s="6"/>
-    </row>
-    <row r="159" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT159"/>
-    </row>
-    <row r="160" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT160"/>
-      <c r="CJ160" s="6"/>
-    </row>
-    <row r="161" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ161" s="6"/>
-    </row>
-    <row r="163" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT163"/>
-    </row>
-    <row r="164" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT164"/>
-      <c r="CJ164" s="6"/>
-    </row>
-    <row r="165" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ165" s="6"/>
-    </row>
-    <row r="167" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT167"/>
-    </row>
-    <row r="168" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ168" s="6"/>
-    </row>
-    <row r="171" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ171" s="6"/>
-    </row>
-    <row r="175" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ175" s="6"/>
-    </row>
-    <row r="177" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT177"/>
-    </row>
-    <row r="178" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ178" s="6"/>
-    </row>
-    <row r="185" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT185"/>
-    </row>
-    <row r="186" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ186" s="6"/>
-    </row>
-    <row r="187" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ187" s="6"/>
-    </row>
-    <row r="189" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT189"/>
-    </row>
-    <row r="190" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT190"/>
-      <c r="CJ190" s="6"/>
-    </row>
-    <row r="191" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ191" s="6"/>
-    </row>
-    <row r="197" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT197"/>
-    </row>
-    <row r="198" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT198"/>
-      <c r="CJ198" s="6"/>
-    </row>
-    <row r="199" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT199"/>
-      <c r="CJ199" s="6"/>
-    </row>
-    <row r="200" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ200" s="6"/>
-    </row>
-    <row r="205" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT205"/>
-    </row>
-    <row r="206" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT206"/>
-    </row>
-    <row r="210" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT210"/>
-    </row>
-    <row r="211" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ211" s="6"/>
-    </row>
-    <row r="212" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT212"/>
-    </row>
-    <row r="213" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ213" s="6"/>
-    </row>
-    <row r="223" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT223"/>
-    </row>
-    <row r="224" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ224" s="6"/>
-    </row>
-    <row r="226" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT226"/>
-    </row>
-    <row r="227" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ227" s="6"/>
-    </row>
-    <row r="235" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT235"/>
-    </row>
-    <row r="236" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ236" s="6"/>
-    </row>
-    <row r="240" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT240"/>
-    </row>
-    <row r="241" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ241" s="6"/>
-    </row>
-    <row r="243" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT243"/>
-    </row>
-    <row r="244" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ244" s="6"/>
-    </row>
-    <row r="260" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT260"/>
-    </row>
-    <row r="261" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT261"/>
-      <c r="CJ261" s="6"/>
-    </row>
-    <row r="262" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT262"/>
-      <c r="CJ262" s="6"/>
-    </row>
-    <row r="263" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT263"/>
-      <c r="CJ263" s="6"/>
-    </row>
-    <row r="264" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT264"/>
-    </row>
-    <row r="266" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT266"/>
-    </row>
-    <row r="267" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT267"/>
-      <c r="CJ267" s="6"/>
-    </row>
-    <row r="268" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT268"/>
-      <c r="CJ268" s="6"/>
-    </row>
-    <row r="269" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ269" s="6"/>
-    </row>
-    <row r="273" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT273"/>
-    </row>
-    <row r="274" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ274" s="6"/>
-    </row>
-    <row r="276" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT276"/>
-    </row>
-    <row r="277" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT277"/>
-      <c r="CJ277" s="6"/>
-    </row>
-    <row r="278" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT278"/>
-      <c r="CJ278" s="6"/>
-    </row>
-    <row r="279" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ279" s="6"/>
-    </row>
-    <row r="295" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT295"/>
-    </row>
-    <row r="296" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ296" s="6"/>
-    </row>
-    <row r="304" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ304" s="6"/>
-    </row>
-    <row r="305" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ305" s="6"/>
-    </row>
-    <row r="306" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ306" s="6"/>
-    </row>
-    <row r="307" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ307" s="6"/>
-    </row>
-    <row r="308" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ308" s="6"/>
-    </row>
-    <row r="310" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT310"/>
-    </row>
-    <row r="311" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ311" s="6"/>
-    </row>
-    <row r="312" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT312"/>
-    </row>
-    <row r="313" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT313"/>
-      <c r="CJ313" s="6"/>
-    </row>
-    <row r="314" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ314" s="6"/>
-    </row>
-    <row r="316" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT316"/>
-    </row>
-    <row r="317" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT317"/>
-      <c r="CJ317" s="6"/>
-    </row>
-    <row r="318" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT318"/>
-      <c r="CJ318" s="6"/>
-    </row>
-    <row r="319" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ319" s="6"/>
-    </row>
-    <row r="321" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ321" s="6"/>
-    </row>
-    <row r="323" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ323" s="6"/>
-    </row>
-    <row r="325" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ325" s="6"/>
-    </row>
-    <row r="328" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ328" s="6"/>
-    </row>
-    <row r="329" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ329" s="6"/>
-    </row>
-    <row r="330" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ330" s="6"/>
-    </row>
-    <row r="331" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ331" s="6"/>
-    </row>
-    <row r="332" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ332" s="6"/>
-    </row>
-    <row r="333" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ333" s="6"/>
-    </row>
-    <row r="334" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT334"/>
-    </row>
-    <row r="335" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT335"/>
-      <c r="CJ335" s="6"/>
-    </row>
-    <row r="336" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT336"/>
-      <c r="CJ336" s="6"/>
-    </row>
-    <row r="337" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ337" s="6"/>
-    </row>
-    <row r="338" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ338" s="6"/>
-    </row>
-    <row r="339" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ339" s="6"/>
-    </row>
-    <row r="340" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ340" s="6"/>
-    </row>
-    <row r="342" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ342" s="6"/>
-    </row>
-    <row r="343" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ343" s="6"/>
-    </row>
-    <row r="344" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT344"/>
-    </row>
-    <row r="345" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT345"/>
-      <c r="CJ345" s="6"/>
-    </row>
-    <row r="346" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT346"/>
-      <c r="CJ346" s="6"/>
-    </row>
-    <row r="347" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ347" s="6"/>
-    </row>
-    <row r="348" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ348" s="6"/>
-    </row>
-    <row r="350" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ350" s="6"/>
-    </row>
-    <row r="351" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ351" s="6"/>
-    </row>
-    <row r="352" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT352"/>
-      <c r="CJ352" s="6"/>
-    </row>
-    <row r="353" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT353"/>
-      <c r="CJ353" s="6"/>
-    </row>
-    <row r="354" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ354" s="6"/>
-    </row>
-    <row r="355" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ355" s="6"/>
-    </row>
-    <row r="356" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ356" s="6"/>
-    </row>
-    <row r="358" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT358"/>
-      <c r="CJ358" s="6"/>
-    </row>
-    <row r="359" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ359" s="6"/>
-    </row>
-    <row r="360" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ360" s="6"/>
-    </row>
-    <row r="362" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT362"/>
-      <c r="CJ362" s="6"/>
-    </row>
-    <row r="363" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT363"/>
-      <c r="CJ363" s="6"/>
-    </row>
-    <row r="364" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ364" s="6"/>
-    </row>
-    <row r="366" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ366" s="6"/>
-    </row>
-    <row r="368" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ368" s="6"/>
-    </row>
-    <row r="371" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ371" s="6"/>
-    </row>
-    <row r="372" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ372" s="6"/>
-    </row>
-    <row r="376" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT376"/>
-    </row>
-    <row r="377" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT377"/>
-      <c r="CJ377" s="6"/>
-    </row>
-    <row r="378" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT378"/>
-      <c r="CJ378" s="6"/>
-    </row>
-    <row r="379" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ379" s="6"/>
-    </row>
-    <row r="380" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ380" s="6"/>
-    </row>
-    <row r="381" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT381"/>
-    </row>
-    <row r="382" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ382" s="6"/>
-    </row>
-    <row r="384" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ384" s="6"/>
-    </row>
-    <row r="385" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ385" s="6"/>
-    </row>
-    <row r="387" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ387" s="6"/>
-    </row>
-    <row r="388" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ388" s="6"/>
-    </row>
-    <row r="389" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ389" s="6"/>
-    </row>
-    <row r="390" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ390" s="6"/>
-    </row>
-    <row r="391" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ391" s="6"/>
-    </row>
-    <row r="392" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ392" s="6"/>
-    </row>
-    <row r="393" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ393" s="6"/>
-    </row>
-    <row r="395" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT395"/>
-    </row>
-    <row r="396" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ396" s="6"/>
-    </row>
-    <row r="397" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ397" s="6"/>
-    </row>
-    <row r="430" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS430" s="14"/>
-      <c r="BT430" s="15"/>
-    </row>
-    <row r="431" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="DG46">
+        <v>1</v>
+      </c>
+      <c r="DH46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV50"/>
+    </row>
+    <row r="51" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV51"/>
+      <c r="CL51" s="6"/>
+    </row>
+    <row r="52" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL52" s="6"/>
+    </row>
+    <row r="53" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL53" s="6"/>
+    </row>
+    <row r="54" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL54" s="6"/>
+    </row>
+    <row r="55" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL55" s="6"/>
+    </row>
+    <row r="56" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV56"/>
+    </row>
+    <row r="57" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL57" s="6"/>
+    </row>
+    <row r="58" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL58" s="6"/>
+    </row>
+    <row r="59" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL59" s="6"/>
+    </row>
+    <row r="60" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL60" s="6"/>
+    </row>
+    <row r="61" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV61"/>
+    </row>
+    <row r="62" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL62" s="6"/>
+    </row>
+    <row r="63" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL63" s="6"/>
+    </row>
+    <row r="64" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL64" s="6"/>
+    </row>
+    <row r="65" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL65" s="6"/>
+    </row>
+    <row r="68" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL68" s="6"/>
+    </row>
+    <row r="69" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL69" s="6"/>
+    </row>
+    <row r="70" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL70" s="6"/>
+    </row>
+    <row r="71" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL71" s="6"/>
+    </row>
+    <row r="72" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL72" s="6"/>
+    </row>
+    <row r="74" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV74"/>
+    </row>
+    <row r="75" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL75" s="6"/>
+    </row>
+    <row r="76" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL76" s="6"/>
+    </row>
+    <row r="77" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL77" s="6"/>
+    </row>
+    <row r="78" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL78" s="6"/>
+    </row>
+    <row r="82" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL82" s="6"/>
+    </row>
+    <row r="84" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV84"/>
+    </row>
+    <row r="85" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV85"/>
+      <c r="CL85" s="6"/>
+    </row>
+    <row r="86" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL86" s="6"/>
+    </row>
+    <row r="87" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL87" s="6"/>
+    </row>
+    <row r="88" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL88" s="6"/>
+    </row>
+    <row r="89" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL89" s="6"/>
+    </row>
+    <row r="91" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV91"/>
+    </row>
+    <row r="92" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL92" s="6"/>
+    </row>
+    <row r="93" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL93" s="6"/>
+    </row>
+    <row r="95" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL95" s="6"/>
+    </row>
+    <row r="96" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL96" s="6"/>
+    </row>
+    <row r="98" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV98"/>
+    </row>
+    <row r="99" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL99" s="6"/>
+    </row>
+    <row r="102" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL102" s="6"/>
+    </row>
+    <row r="103" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL103" s="6"/>
+    </row>
+    <row r="106" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL106" s="6"/>
+    </row>
+    <row r="108" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL108" s="6"/>
+    </row>
+    <row r="110" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV110"/>
+    </row>
+    <row r="111" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL111" s="6"/>
+    </row>
+    <row r="112" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL112" s="6"/>
+    </row>
+    <row r="114" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL114" s="6"/>
+    </row>
+    <row r="115" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL115" s="6"/>
+    </row>
+    <row r="116" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL116" s="6"/>
+    </row>
+    <row r="121" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL121" s="6"/>
+    </row>
+    <row r="122" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL122" s="6"/>
+    </row>
+    <row r="125" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL125" s="6"/>
+    </row>
+    <row r="126" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL126" s="6"/>
+    </row>
+    <row r="130" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL130" s="6"/>
+    </row>
+    <row r="134" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL134" s="6"/>
+    </row>
+    <row r="136" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL136" s="6"/>
+    </row>
+    <row r="137" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL137" s="6"/>
+    </row>
+    <row r="139" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL139" s="6"/>
+    </row>
+    <row r="140" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL140" s="6"/>
+    </row>
+    <row r="142" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV142"/>
+    </row>
+    <row r="143" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV143"/>
+      <c r="CL143" s="6"/>
+    </row>
+    <row r="144" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL144" s="6"/>
+    </row>
+    <row r="146" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL146" s="6"/>
+    </row>
+    <row r="155" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV155"/>
+    </row>
+    <row r="156" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV156"/>
+      <c r="CL156" s="6"/>
+    </row>
+    <row r="157" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL157" s="6"/>
+    </row>
+    <row r="158" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL158" s="6"/>
+    </row>
+    <row r="159" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV159"/>
+    </row>
+    <row r="160" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV160"/>
+      <c r="CL160" s="6"/>
+    </row>
+    <row r="161" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL161" s="6"/>
+    </row>
+    <row r="163" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV163"/>
+    </row>
+    <row r="164" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV164"/>
+      <c r="CL164" s="6"/>
+    </row>
+    <row r="165" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL165" s="6"/>
+    </row>
+    <row r="167" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV167"/>
+    </row>
+    <row r="168" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL168" s="6"/>
+    </row>
+    <row r="171" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL171" s="6"/>
+    </row>
+    <row r="175" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL175" s="6"/>
+    </row>
+    <row r="177" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV177"/>
+    </row>
+    <row r="178" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL178" s="6"/>
+    </row>
+    <row r="185" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV185"/>
+    </row>
+    <row r="186" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL186" s="6"/>
+    </row>
+    <row r="187" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL187" s="6"/>
+    </row>
+    <row r="189" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV189"/>
+    </row>
+    <row r="190" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV190"/>
+      <c r="CL190" s="6"/>
+    </row>
+    <row r="191" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL191" s="6"/>
+    </row>
+    <row r="197" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV197"/>
+    </row>
+    <row r="198" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV198"/>
+      <c r="CL198" s="6"/>
+    </row>
+    <row r="199" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV199"/>
+      <c r="CL199" s="6"/>
+    </row>
+    <row r="200" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL200" s="6"/>
+    </row>
+    <row r="205" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV205"/>
+    </row>
+    <row r="206" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV206"/>
+    </row>
+    <row r="210" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV210"/>
+    </row>
+    <row r="211" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL211" s="6"/>
+    </row>
+    <row r="212" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV212"/>
+    </row>
+    <row r="213" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL213" s="6"/>
+    </row>
+    <row r="223" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV223"/>
+    </row>
+    <row r="224" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL224" s="6"/>
+    </row>
+    <row r="226" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV226"/>
+    </row>
+    <row r="227" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL227" s="6"/>
+    </row>
+    <row r="235" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV235"/>
+    </row>
+    <row r="236" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL236" s="6"/>
+    </row>
+    <row r="240" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV240"/>
+    </row>
+    <row r="241" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL241" s="6"/>
+    </row>
+    <row r="243" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV243"/>
+    </row>
+    <row r="244" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL244" s="6"/>
+    </row>
+    <row r="260" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV260"/>
+    </row>
+    <row r="261" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV261"/>
+      <c r="CL261" s="6"/>
+    </row>
+    <row r="262" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV262"/>
+      <c r="CL262" s="6"/>
+    </row>
+    <row r="263" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV263"/>
+      <c r="CL263" s="6"/>
+    </row>
+    <row r="264" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV264"/>
+    </row>
+    <row r="266" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV266"/>
+    </row>
+    <row r="267" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV267"/>
+      <c r="CL267" s="6"/>
+    </row>
+    <row r="268" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV268"/>
+      <c r="CL268" s="6"/>
+    </row>
+    <row r="269" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL269" s="6"/>
+    </row>
+    <row r="273" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV273"/>
+    </row>
+    <row r="274" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL274" s="6"/>
+    </row>
+    <row r="276" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV276"/>
+    </row>
+    <row r="277" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV277"/>
+      <c r="CL277" s="6"/>
+    </row>
+    <row r="278" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV278"/>
+      <c r="CL278" s="6"/>
+    </row>
+    <row r="279" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL279" s="6"/>
+    </row>
+    <row r="295" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV295"/>
+    </row>
+    <row r="296" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL296" s="6"/>
+    </row>
+    <row r="304" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL304" s="6"/>
+    </row>
+    <row r="305" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL305" s="6"/>
+    </row>
+    <row r="306" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL306" s="6"/>
+    </row>
+    <row r="307" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL307" s="6"/>
+    </row>
+    <row r="308" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL308" s="6"/>
+    </row>
+    <row r="310" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV310"/>
+    </row>
+    <row r="311" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL311" s="6"/>
+    </row>
+    <row r="312" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV312"/>
+    </row>
+    <row r="313" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV313"/>
+      <c r="CL313" s="6"/>
+    </row>
+    <row r="314" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL314" s="6"/>
+    </row>
+    <row r="316" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV316"/>
+    </row>
+    <row r="317" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV317"/>
+      <c r="CL317" s="6"/>
+    </row>
+    <row r="318" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV318"/>
+      <c r="CL318" s="6"/>
+    </row>
+    <row r="319" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL319" s="6"/>
+    </row>
+    <row r="321" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL321" s="6"/>
+    </row>
+    <row r="323" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL323" s="6"/>
+    </row>
+    <row r="325" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL325" s="6"/>
+    </row>
+    <row r="328" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL328" s="6"/>
+    </row>
+    <row r="329" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL329" s="6"/>
+    </row>
+    <row r="330" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL330" s="6"/>
+    </row>
+    <row r="331" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL331" s="6"/>
+    </row>
+    <row r="332" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL332" s="6"/>
+    </row>
+    <row r="333" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL333" s="6"/>
+    </row>
+    <row r="334" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV334"/>
+    </row>
+    <row r="335" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV335"/>
+      <c r="CL335" s="6"/>
+    </row>
+    <row r="336" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV336"/>
+      <c r="CL336" s="6"/>
+    </row>
+    <row r="337" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL337" s="6"/>
+    </row>
+    <row r="338" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL338" s="6"/>
+    </row>
+    <row r="339" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL339" s="6"/>
+    </row>
+    <row r="340" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL340" s="6"/>
+    </row>
+    <row r="342" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL342" s="6"/>
+    </row>
+    <row r="343" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL343" s="6"/>
+    </row>
+    <row r="344" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV344"/>
+    </row>
+    <row r="345" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV345"/>
+      <c r="CL345" s="6"/>
+    </row>
+    <row r="346" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV346"/>
+      <c r="CL346" s="6"/>
+    </row>
+    <row r="347" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL347" s="6"/>
+    </row>
+    <row r="348" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL348" s="6"/>
+    </row>
+    <row r="350" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL350" s="6"/>
+    </row>
+    <row r="351" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL351" s="6"/>
+    </row>
+    <row r="352" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV352"/>
+      <c r="CL352" s="6"/>
+    </row>
+    <row r="353" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV353"/>
+      <c r="CL353" s="6"/>
+    </row>
+    <row r="354" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL354" s="6"/>
+    </row>
+    <row r="355" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL355" s="6"/>
+    </row>
+    <row r="356" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL356" s="6"/>
+    </row>
+    <row r="358" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV358"/>
+      <c r="CL358" s="6"/>
+    </row>
+    <row r="359" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL359" s="6"/>
+    </row>
+    <row r="360" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL360" s="6"/>
+    </row>
+    <row r="362" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV362"/>
+      <c r="CL362" s="6"/>
+    </row>
+    <row r="363" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV363"/>
+      <c r="CL363" s="6"/>
+    </row>
+    <row r="364" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL364" s="6"/>
+    </row>
+    <row r="366" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL366" s="6"/>
+    </row>
+    <row r="368" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL368" s="6"/>
+    </row>
+    <row r="371" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL371" s="6"/>
+    </row>
+    <row r="372" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL372" s="6"/>
+    </row>
+    <row r="376" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV376"/>
+    </row>
+    <row r="377" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV377"/>
+      <c r="CL377" s="6"/>
+    </row>
+    <row r="378" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV378"/>
+      <c r="CL378" s="6"/>
+    </row>
+    <row r="379" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL379" s="6"/>
+    </row>
+    <row r="380" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL380" s="6"/>
+    </row>
+    <row r="381" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV381"/>
+    </row>
+    <row r="382" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL382" s="6"/>
+    </row>
+    <row r="384" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL384" s="6"/>
+    </row>
+    <row r="385" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL385" s="6"/>
+    </row>
+    <row r="387" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL387" s="6"/>
+    </row>
+    <row r="388" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL388" s="6"/>
+    </row>
+    <row r="389" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL389" s="6"/>
+    </row>
+    <row r="390" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL390" s="6"/>
+    </row>
+    <row r="391" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL391" s="6"/>
+    </row>
+    <row r="392" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL392" s="6"/>
+    </row>
+    <row r="393" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL393" s="6"/>
+    </row>
+    <row r="395" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV395"/>
+    </row>
+    <row r="396" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL396" s="6"/>
+    </row>
+    <row r="397" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL397" s="6"/>
+    </row>
+    <row r="430" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BU430" s="14"/>
+      <c r="BV430" s="15"/>
+    </row>
+    <row r="431" spans="8:90" x14ac:dyDescent="0.25">
       <c r="H431" s="14"/>
-      <c r="CJ431" s="14"/>
-    </row>
-    <row r="437" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT437"/>
-    </row>
-    <row r="438" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT438"/>
-      <c r="CJ438" s="6"/>
-    </row>
-    <row r="439" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT439"/>
-      <c r="CJ439" s="6"/>
-    </row>
-    <row r="440" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ440" s="6"/>
-    </row>
-    <row r="457" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT457"/>
-    </row>
-    <row r="458" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ458" s="6"/>
-    </row>
-    <row r="490" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT490"/>
-    </row>
-    <row r="491" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT491"/>
-      <c r="CJ491" s="6"/>
-    </row>
-    <row r="492" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ492" s="6"/>
-    </row>
-    <row r="508" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT508"/>
-    </row>
-    <row r="509" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ509" s="6"/>
-    </row>
-    <row r="515" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT515"/>
-    </row>
-    <row r="516" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT516"/>
-      <c r="CJ516" s="6"/>
-    </row>
-    <row r="517" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ517" s="6"/>
-    </row>
-    <row r="522" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT522"/>
-    </row>
-    <row r="523" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT523"/>
-      <c r="CJ523" s="6"/>
-    </row>
-    <row r="524" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT524"/>
-      <c r="CJ524" s="6"/>
-    </row>
-    <row r="525" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT525"/>
-      <c r="CJ525" s="6"/>
-    </row>
-    <row r="526" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT526"/>
-      <c r="CJ526" s="6"/>
-    </row>
-    <row r="527" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT527"/>
-      <c r="CJ527" s="6"/>
-    </row>
-    <row r="528" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT528"/>
-      <c r="CJ528" s="6"/>
-    </row>
-    <row r="529" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT529"/>
-      <c r="CJ529" s="6"/>
-    </row>
-    <row r="530" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT530"/>
-      <c r="CJ530" s="6"/>
-    </row>
-    <row r="531" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT531"/>
-      <c r="CJ531" s="6"/>
-    </row>
-    <row r="532" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT532"/>
-      <c r="CJ532" s="6"/>
-    </row>
-    <row r="533" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT533"/>
-      <c r="CJ533" s="6"/>
-    </row>
-    <row r="534" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT534"/>
-      <c r="CJ534" s="6"/>
-    </row>
-    <row r="535" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT535"/>
-      <c r="CJ535" s="6"/>
-    </row>
-    <row r="536" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT536"/>
-      <c r="CJ536" s="6"/>
-    </row>
-    <row r="537" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT537"/>
-      <c r="CJ537" s="6"/>
-    </row>
-    <row r="538" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ538" s="6"/>
-    </row>
-    <row r="542" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT542"/>
-    </row>
-    <row r="543" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT543"/>
-      <c r="CJ543" s="6"/>
-    </row>
-    <row r="544" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ544" s="6"/>
-    </row>
-    <row r="545" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT545"/>
-    </row>
-    <row r="546" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ546" s="6"/>
-    </row>
-    <row r="549" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT549"/>
-    </row>
-    <row r="550" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT550"/>
-      <c r="CJ550" s="6"/>
-    </row>
-    <row r="551" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ551" s="6"/>
-    </row>
-    <row r="582" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT582"/>
-    </row>
-    <row r="583" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT583"/>
-      <c r="CJ583" s="6"/>
-    </row>
-    <row r="584" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT584"/>
-      <c r="CJ584" s="6"/>
-    </row>
-    <row r="585" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT585"/>
-      <c r="CJ585" s="6"/>
-    </row>
-    <row r="586" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT586"/>
-      <c r="CJ586" s="6"/>
-    </row>
-    <row r="587" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT587"/>
-      <c r="CJ587" s="6"/>
-    </row>
-    <row r="588" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT588"/>
-      <c r="CJ588" s="6"/>
-    </row>
-    <row r="589" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT589"/>
-      <c r="CJ589" s="6"/>
-    </row>
-    <row r="590" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ590" s="6"/>
-    </row>
-    <row r="592" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT592"/>
-    </row>
-    <row r="593" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ593" s="6"/>
-    </row>
-    <row r="597" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT597"/>
-    </row>
-    <row r="598" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ598" s="6"/>
-    </row>
-    <row r="601" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT601"/>
-    </row>
-    <row r="602" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT602"/>
-      <c r="CJ602" s="6"/>
-    </row>
-    <row r="603" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT603"/>
-      <c r="CJ603" s="6"/>
-    </row>
-    <row r="604" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT604"/>
-      <c r="CJ604" s="6"/>
-    </row>
-    <row r="605" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ605" s="6"/>
-    </row>
-    <row r="612" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT612"/>
-    </row>
-    <row r="613" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ613" s="6"/>
-    </row>
-    <row r="616" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT616"/>
-    </row>
-    <row r="617" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT617"/>
-      <c r="CJ617" s="6"/>
-    </row>
-    <row r="618" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT618"/>
-      <c r="CJ618" s="6"/>
-    </row>
-    <row r="619" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT619"/>
-      <c r="CJ619" s="6"/>
-    </row>
-    <row r="620" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ620" s="6"/>
-    </row>
-    <row r="622" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT622"/>
-    </row>
-    <row r="623" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT623"/>
-      <c r="CJ623" s="6"/>
-    </row>
-    <row r="624" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ624" s="6"/>
-    </row>
-    <row r="625" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ625">
+      <c r="CL431" s="14"/>
+    </row>
+    <row r="437" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV437"/>
+    </row>
+    <row r="438" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV438"/>
+      <c r="CL438" s="6"/>
+    </row>
+    <row r="439" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV439"/>
+      <c r="CL439" s="6"/>
+    </row>
+    <row r="440" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL440" s="6"/>
+    </row>
+    <row r="457" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV457"/>
+    </row>
+    <row r="458" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL458" s="6"/>
+    </row>
+    <row r="490" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV490"/>
+    </row>
+    <row r="491" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV491"/>
+      <c r="CL491" s="6"/>
+    </row>
+    <row r="492" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL492" s="6"/>
+    </row>
+    <row r="508" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV508"/>
+    </row>
+    <row r="509" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL509" s="6"/>
+    </row>
+    <row r="515" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV515"/>
+    </row>
+    <row r="516" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV516"/>
+      <c r="CL516" s="6"/>
+    </row>
+    <row r="517" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL517" s="6"/>
+    </row>
+    <row r="522" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV522"/>
+    </row>
+    <row r="523" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV523"/>
+      <c r="CL523" s="6"/>
+    </row>
+    <row r="524" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV524"/>
+      <c r="CL524" s="6"/>
+    </row>
+    <row r="525" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV525"/>
+      <c r="CL525" s="6"/>
+    </row>
+    <row r="526" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV526"/>
+      <c r="CL526" s="6"/>
+    </row>
+    <row r="527" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV527"/>
+      <c r="CL527" s="6"/>
+    </row>
+    <row r="528" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV528"/>
+      <c r="CL528" s="6"/>
+    </row>
+    <row r="529" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV529"/>
+      <c r="CL529" s="6"/>
+    </row>
+    <row r="530" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV530"/>
+      <c r="CL530" s="6"/>
+    </row>
+    <row r="531" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV531"/>
+      <c r="CL531" s="6"/>
+    </row>
+    <row r="532" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV532"/>
+      <c r="CL532" s="6"/>
+    </row>
+    <row r="533" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV533"/>
+      <c r="CL533" s="6"/>
+    </row>
+    <row r="534" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV534"/>
+      <c r="CL534" s="6"/>
+    </row>
+    <row r="535" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV535"/>
+      <c r="CL535" s="6"/>
+    </row>
+    <row r="536" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV536"/>
+      <c r="CL536" s="6"/>
+    </row>
+    <row r="537" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV537"/>
+      <c r="CL537" s="6"/>
+    </row>
+    <row r="538" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL538" s="6"/>
+    </row>
+    <row r="542" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV542"/>
+    </row>
+    <row r="543" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV543"/>
+      <c r="CL543" s="6"/>
+    </row>
+    <row r="544" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL544" s="6"/>
+    </row>
+    <row r="545" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV545"/>
+    </row>
+    <row r="546" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL546" s="6"/>
+    </row>
+    <row r="549" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV549"/>
+    </row>
+    <row r="550" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV550"/>
+      <c r="CL550" s="6"/>
+    </row>
+    <row r="551" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL551" s="6"/>
+    </row>
+    <row r="582" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV582"/>
+    </row>
+    <row r="583" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV583"/>
+      <c r="CL583" s="6"/>
+    </row>
+    <row r="584" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV584"/>
+      <c r="CL584" s="6"/>
+    </row>
+    <row r="585" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV585"/>
+      <c r="CL585" s="6"/>
+    </row>
+    <row r="586" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV586"/>
+      <c r="CL586" s="6"/>
+    </row>
+    <row r="587" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV587"/>
+      <c r="CL587" s="6"/>
+    </row>
+    <row r="588" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV588"/>
+      <c r="CL588" s="6"/>
+    </row>
+    <row r="589" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV589"/>
+      <c r="CL589" s="6"/>
+    </row>
+    <row r="590" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL590" s="6"/>
+    </row>
+    <row r="592" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV592"/>
+    </row>
+    <row r="593" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL593" s="6"/>
+    </row>
+    <row r="597" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV597"/>
+    </row>
+    <row r="598" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL598" s="6"/>
+    </row>
+    <row r="601" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV601"/>
+    </row>
+    <row r="602" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV602"/>
+      <c r="CL602" s="6"/>
+    </row>
+    <row r="603" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV603"/>
+      <c r="CL603" s="6"/>
+    </row>
+    <row r="604" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV604"/>
+      <c r="CL604" s="6"/>
+    </row>
+    <row r="605" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL605" s="6"/>
+    </row>
+    <row r="612" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV612"/>
+    </row>
+    <row r="613" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL613" s="6"/>
+    </row>
+    <row r="616" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV616"/>
+    </row>
+    <row r="617" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV617"/>
+      <c r="CL617" s="6"/>
+    </row>
+    <row r="618" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV618"/>
+      <c r="CL618" s="6"/>
+    </row>
+    <row r="619" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV619"/>
+      <c r="CL619" s="6"/>
+    </row>
+    <row r="620" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL620" s="6"/>
+    </row>
+    <row r="622" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV622"/>
+    </row>
+    <row r="623" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV623"/>
+      <c r="CL623" s="6"/>
+    </row>
+    <row r="624" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL624" s="6"/>
+    </row>
+    <row r="625" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL625">
         <v>0.15</v>
       </c>
     </row>
-    <row r="627" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ627">
+    <row r="627" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL627">
         <v>0.2</v>
       </c>
     </row>
-    <row r="628" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ628">
+    <row r="628" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL628">
         <v>0.1</v>
       </c>
     </row>
-    <row r="630" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ630">
+    <row r="630" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL630">
         <v>0.2</v>
       </c>
     </row>
-    <row r="637" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ637">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="639" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ639">
+    <row r="637" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL637">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="639" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL639">
         <v>0.4</v>
       </c>
     </row>
-    <row r="640" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ640">
+    <row r="640" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL640">
         <v>0.6</v>
       </c>
     </row>
-    <row r="643" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ643">
+    <row r="643" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL643">
         <v>0.5</v>
       </c>
     </row>
-    <row r="644" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ644">
+    <row r="644" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL644">
         <v>0.66700000000000004</v>
       </c>
     </row>
-    <row r="645" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ645">
+    <row r="645" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL645">
         <v>0.2</v>
       </c>
     </row>
-    <row r="648" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT648"/>
-    </row>
-    <row r="649" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT649"/>
-      <c r="CJ649" s="6"/>
-    </row>
-    <row r="650" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT650"/>
-      <c r="CJ650" s="6"/>
-    </row>
-    <row r="651" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT651"/>
-      <c r="CJ651" s="6"/>
-    </row>
-    <row r="652" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT652"/>
-      <c r="CJ652" s="6"/>
-    </row>
-    <row r="653" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT653"/>
-      <c r="CJ653" s="6"/>
-    </row>
-    <row r="654" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT654"/>
-      <c r="CJ654" s="6"/>
-    </row>
-    <row r="655" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT655"/>
-      <c r="CJ655" s="6"/>
-    </row>
-    <row r="656" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT656"/>
-      <c r="CJ656" s="6"/>
-    </row>
-    <row r="657" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ657" s="6"/>
-    </row>
-    <row r="658" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT658"/>
-    </row>
-    <row r="659" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ659" s="6"/>
-    </row>
-    <row r="668" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT668"/>
-    </row>
-    <row r="669" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT669"/>
-      <c r="CJ669" s="6"/>
-    </row>
-    <row r="670" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT670"/>
-      <c r="CJ670" s="6"/>
-    </row>
-    <row r="671" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT671"/>
-      <c r="CJ671" s="6"/>
-    </row>
-    <row r="672" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT672"/>
-      <c r="CJ672" s="6"/>
-    </row>
-    <row r="673" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT673"/>
-      <c r="CJ673" s="6"/>
-    </row>
-    <row r="674" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT674"/>
-      <c r="CJ674" s="6"/>
-    </row>
-    <row r="675" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT675"/>
-      <c r="CJ675" s="6"/>
-    </row>
-    <row r="676" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ676" s="6"/>
-    </row>
-    <row r="677" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT677"/>
-    </row>
-    <row r="678" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ678" s="6"/>
-    </row>
-    <row r="683" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT683"/>
-    </row>
-    <row r="684" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT684"/>
-      <c r="CJ684" s="6"/>
-    </row>
-    <row r="685" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ685" s="6"/>
-    </row>
-    <row r="686" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT686"/>
-    </row>
-    <row r="687" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT687"/>
-      <c r="CJ687" s="6"/>
-    </row>
-    <row r="688" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ688" s="6"/>
-    </row>
-    <row r="689" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT689"/>
-    </row>
-    <row r="690" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT690"/>
-      <c r="CJ690" s="6"/>
-    </row>
-    <row r="691" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT691"/>
-      <c r="CJ691" s="6"/>
-    </row>
-    <row r="692" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT692"/>
-      <c r="CJ692" s="6"/>
-    </row>
-    <row r="693" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ693" s="6"/>
-    </row>
-    <row r="697" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT697"/>
-    </row>
-    <row r="698" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT698"/>
-      <c r="CJ698" s="6"/>
-    </row>
-    <row r="699" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT699"/>
-      <c r="CJ699" s="6"/>
-    </row>
-    <row r="700" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ700" s="6"/>
-    </row>
-    <row r="701" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT701"/>
-    </row>
-    <row r="702" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ702" s="6"/>
-    </row>
-    <row r="703" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS703" s="14"/>
-      <c r="BT703" s="15"/>
-    </row>
-    <row r="704" spans="8:88" x14ac:dyDescent="0.25">
+    <row r="648" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV648"/>
+    </row>
+    <row r="649" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV649"/>
+      <c r="CL649" s="6"/>
+    </row>
+    <row r="650" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV650"/>
+      <c r="CL650" s="6"/>
+    </row>
+    <row r="651" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV651"/>
+      <c r="CL651" s="6"/>
+    </row>
+    <row r="652" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV652"/>
+      <c r="CL652" s="6"/>
+    </row>
+    <row r="653" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV653"/>
+      <c r="CL653" s="6"/>
+    </row>
+    <row r="654" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV654"/>
+      <c r="CL654" s="6"/>
+    </row>
+    <row r="655" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV655"/>
+      <c r="CL655" s="6"/>
+    </row>
+    <row r="656" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV656"/>
+      <c r="CL656" s="6"/>
+    </row>
+    <row r="657" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL657" s="6"/>
+    </row>
+    <row r="658" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV658"/>
+    </row>
+    <row r="659" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL659" s="6"/>
+    </row>
+    <row r="668" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV668"/>
+    </row>
+    <row r="669" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV669"/>
+      <c r="CL669" s="6"/>
+    </row>
+    <row r="670" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV670"/>
+      <c r="CL670" s="6"/>
+    </row>
+    <row r="671" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV671"/>
+      <c r="CL671" s="6"/>
+    </row>
+    <row r="672" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV672"/>
+      <c r="CL672" s="6"/>
+    </row>
+    <row r="673" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV673"/>
+      <c r="CL673" s="6"/>
+    </row>
+    <row r="674" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV674"/>
+      <c r="CL674" s="6"/>
+    </row>
+    <row r="675" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV675"/>
+      <c r="CL675" s="6"/>
+    </row>
+    <row r="676" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL676" s="6"/>
+    </row>
+    <row r="677" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV677"/>
+    </row>
+    <row r="678" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL678" s="6"/>
+    </row>
+    <row r="683" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV683"/>
+    </row>
+    <row r="684" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV684"/>
+      <c r="CL684" s="6"/>
+    </row>
+    <row r="685" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL685" s="6"/>
+    </row>
+    <row r="686" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV686"/>
+    </row>
+    <row r="687" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV687"/>
+      <c r="CL687" s="6"/>
+    </row>
+    <row r="688" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL688" s="6"/>
+    </row>
+    <row r="689" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV689"/>
+    </row>
+    <row r="690" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV690"/>
+      <c r="CL690" s="6"/>
+    </row>
+    <row r="691" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV691"/>
+      <c r="CL691" s="6"/>
+    </row>
+    <row r="692" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV692"/>
+      <c r="CL692" s="6"/>
+    </row>
+    <row r="693" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="CL693" s="6"/>
+    </row>
+    <row r="697" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV697"/>
+    </row>
+    <row r="698" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV698"/>
+      <c r="CL698" s="6"/>
+    </row>
+    <row r="699" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV699"/>
+      <c r="CL699" s="6"/>
+    </row>
+    <row r="700" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="CL700" s="6"/>
+    </row>
+    <row r="701" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV701"/>
+    </row>
+    <row r="702" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="CL702" s="6"/>
+    </row>
+    <row r="703" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BU703" s="14"/>
+      <c r="BV703" s="15"/>
+    </row>
+    <row r="704" spans="8:90" x14ac:dyDescent="0.25">
       <c r="H704" s="14"/>
-      <c r="CJ704" s="14"/>
-    </row>
-    <row r="721" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT721"/>
-    </row>
-    <row r="722" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT722"/>
-      <c r="CJ722" s="6"/>
-    </row>
-    <row r="723" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT723"/>
-      <c r="CJ723" s="6"/>
-    </row>
-    <row r="724" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT724"/>
-      <c r="CJ724" s="6"/>
-    </row>
-    <row r="725" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ725" s="6"/>
-    </row>
-    <row r="726" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT726"/>
-    </row>
-    <row r="727" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT727"/>
-      <c r="CJ727" s="6"/>
-    </row>
-    <row r="728" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS728" s="14"/>
-      <c r="BT728" s="15"/>
-      <c r="CJ728" s="6"/>
-    </row>
-    <row r="729" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="CL704" s="14"/>
+    </row>
+    <row r="721" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV721"/>
+    </row>
+    <row r="722" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV722"/>
+      <c r="CL722" s="6"/>
+    </row>
+    <row r="723" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV723"/>
+      <c r="CL723" s="6"/>
+    </row>
+    <row r="724" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV724"/>
+      <c r="CL724" s="6"/>
+    </row>
+    <row r="725" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="CL725" s="6"/>
+    </row>
+    <row r="726" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV726"/>
+    </row>
+    <row r="727" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV727"/>
+      <c r="CL727" s="6"/>
+    </row>
+    <row r="728" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BU728" s="14"/>
+      <c r="BV728" s="15"/>
+      <c r="CL728" s="6"/>
+    </row>
+    <row r="729" spans="8:90" x14ac:dyDescent="0.25">
       <c r="H729" s="14"/>
-      <c r="CJ729" s="14"/>
-    </row>
-    <row r="732" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT732"/>
-    </row>
-    <row r="733" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT733"/>
-      <c r="CJ733" s="6"/>
-    </row>
-    <row r="734" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT734"/>
-      <c r="CJ734" s="6"/>
-    </row>
-    <row r="735" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT735"/>
-      <c r="CJ735" s="6"/>
-    </row>
-    <row r="736" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT736"/>
-      <c r="CJ736" s="6"/>
-    </row>
-    <row r="737" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT737"/>
-      <c r="CJ737" s="6"/>
-    </row>
-    <row r="738" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT738"/>
-      <c r="CJ738" s="6"/>
-    </row>
-    <row r="739" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT739"/>
-      <c r="CJ739" s="6"/>
-    </row>
-    <row r="740" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ740" s="6"/>
-    </row>
-    <row r="742" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT742"/>
-    </row>
-    <row r="743" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT743"/>
-      <c r="CJ743" s="6"/>
-    </row>
-    <row r="744" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT744"/>
-      <c r="CJ744" s="6"/>
-    </row>
-    <row r="745" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT745"/>
-      <c r="CJ745" s="6"/>
-    </row>
-    <row r="746" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT746"/>
-      <c r="CJ746" s="6"/>
-    </row>
-    <row r="747" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT747"/>
-      <c r="CJ747" s="6"/>
-    </row>
-    <row r="748" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ748" s="6"/>
-    </row>
-    <row r="749" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT749"/>
-    </row>
-    <row r="750" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT750"/>
-      <c r="CJ750" s="6"/>
-    </row>
-    <row r="751" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT751"/>
-      <c r="CJ751" s="6"/>
-    </row>
-    <row r="752" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT752"/>
-      <c r="CJ752" s="6"/>
-    </row>
-    <row r="753" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT753"/>
-      <c r="CJ753" s="6"/>
-    </row>
-    <row r="754" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT754"/>
-      <c r="CJ754" s="6"/>
-    </row>
-    <row r="755" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT755"/>
-      <c r="CJ755" s="6"/>
-    </row>
-    <row r="756" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT756"/>
-      <c r="CJ756" s="6"/>
-    </row>
-    <row r="757" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT757"/>
-      <c r="CJ757" s="6"/>
-    </row>
-    <row r="758" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT758"/>
-      <c r="CJ758" s="6"/>
-    </row>
-    <row r="759" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT759"/>
-      <c r="CJ759" s="6"/>
-    </row>
-    <row r="760" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT760"/>
-      <c r="CJ760" s="6"/>
-    </row>
-    <row r="761" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT761"/>
-      <c r="CJ761" s="6"/>
-    </row>
-    <row r="762" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT762"/>
-      <c r="CJ762" s="6"/>
-    </row>
-    <row r="763" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT763"/>
-      <c r="CJ763" s="6"/>
-    </row>
-    <row r="764" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT764"/>
-      <c r="CJ764" s="6"/>
-    </row>
-    <row r="765" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT765"/>
-      <c r="CJ765" s="6"/>
-    </row>
-    <row r="766" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT766"/>
-      <c r="CJ766" s="6"/>
-    </row>
-    <row r="767" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT767"/>
-      <c r="CJ767" s="6"/>
-    </row>
-    <row r="768" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT768"/>
-      <c r="CJ768" s="6"/>
-    </row>
-    <row r="769" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT769"/>
-      <c r="CJ769" s="6"/>
-    </row>
-    <row r="770" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT770"/>
-      <c r="CJ770" s="6"/>
-    </row>
-    <row r="771" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT771"/>
-      <c r="CJ771" s="6"/>
-    </row>
-    <row r="772" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT772"/>
-      <c r="CJ772" s="6"/>
-    </row>
-    <row r="773" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT773"/>
-      <c r="CJ773" s="6"/>
-    </row>
-    <row r="774" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT774"/>
-      <c r="CJ774" s="6"/>
-    </row>
-    <row r="775" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT775"/>
-      <c r="CJ775" s="6"/>
-    </row>
-    <row r="776" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT776"/>
-      <c r="CJ776" s="6"/>
-    </row>
-    <row r="777" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT777"/>
-      <c r="CJ777" s="6"/>
-    </row>
-    <row r="778" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT778"/>
-      <c r="CJ778" s="6"/>
-    </row>
-    <row r="779" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ779" s="6"/>
-    </row>
-    <row r="780" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT780"/>
-    </row>
-    <row r="781" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT781"/>
-      <c r="CJ781" s="6"/>
-    </row>
-    <row r="782" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT782"/>
-      <c r="CJ782" s="6"/>
-    </row>
-    <row r="783" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ783" s="6"/>
+      <c r="CL729" s="14"/>
+    </row>
+    <row r="732" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV732"/>
+    </row>
+    <row r="733" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV733"/>
+      <c r="CL733" s="6"/>
+    </row>
+    <row r="734" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV734"/>
+      <c r="CL734" s="6"/>
+    </row>
+    <row r="735" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV735"/>
+      <c r="CL735" s="6"/>
+    </row>
+    <row r="736" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV736"/>
+      <c r="CL736" s="6"/>
+    </row>
+    <row r="737" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV737"/>
+      <c r="CL737" s="6"/>
+    </row>
+    <row r="738" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV738"/>
+      <c r="CL738" s="6"/>
+    </row>
+    <row r="739" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV739"/>
+      <c r="CL739" s="6"/>
+    </row>
+    <row r="740" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL740" s="6"/>
+    </row>
+    <row r="742" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV742"/>
+    </row>
+    <row r="743" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV743"/>
+      <c r="CL743" s="6"/>
+    </row>
+    <row r="744" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV744"/>
+      <c r="CL744" s="6"/>
+    </row>
+    <row r="745" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV745"/>
+      <c r="CL745" s="6"/>
+    </row>
+    <row r="746" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV746"/>
+      <c r="CL746" s="6"/>
+    </row>
+    <row r="747" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV747"/>
+      <c r="CL747" s="6"/>
+    </row>
+    <row r="748" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL748" s="6"/>
+    </row>
+    <row r="749" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV749"/>
+    </row>
+    <row r="750" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV750"/>
+      <c r="CL750" s="6"/>
+    </row>
+    <row r="751" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV751"/>
+      <c r="CL751" s="6"/>
+    </row>
+    <row r="752" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV752"/>
+      <c r="CL752" s="6"/>
+    </row>
+    <row r="753" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV753"/>
+      <c r="CL753" s="6"/>
+    </row>
+    <row r="754" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV754"/>
+      <c r="CL754" s="6"/>
+    </row>
+    <row r="755" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV755"/>
+      <c r="CL755" s="6"/>
+    </row>
+    <row r="756" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV756"/>
+      <c r="CL756" s="6"/>
+    </row>
+    <row r="757" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV757"/>
+      <c r="CL757" s="6"/>
+    </row>
+    <row r="758" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV758"/>
+      <c r="CL758" s="6"/>
+    </row>
+    <row r="759" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV759"/>
+      <c r="CL759" s="6"/>
+    </row>
+    <row r="760" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV760"/>
+      <c r="CL760" s="6"/>
+    </row>
+    <row r="761" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV761"/>
+      <c r="CL761" s="6"/>
+    </row>
+    <row r="762" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV762"/>
+      <c r="CL762" s="6"/>
+    </row>
+    <row r="763" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV763"/>
+      <c r="CL763" s="6"/>
+    </row>
+    <row r="764" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV764"/>
+      <c r="CL764" s="6"/>
+    </row>
+    <row r="765" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV765"/>
+      <c r="CL765" s="6"/>
+    </row>
+    <row r="766" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV766"/>
+      <c r="CL766" s="6"/>
+    </row>
+    <row r="767" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV767"/>
+      <c r="CL767" s="6"/>
+    </row>
+    <row r="768" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV768"/>
+      <c r="CL768" s="6"/>
+    </row>
+    <row r="769" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV769"/>
+      <c r="CL769" s="6"/>
+    </row>
+    <row r="770" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV770"/>
+      <c r="CL770" s="6"/>
+    </row>
+    <row r="771" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV771"/>
+      <c r="CL771" s="6"/>
+    </row>
+    <row r="772" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV772"/>
+      <c r="CL772" s="6"/>
+    </row>
+    <row r="773" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV773"/>
+      <c r="CL773" s="6"/>
+    </row>
+    <row r="774" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV774"/>
+      <c r="CL774" s="6"/>
+    </row>
+    <row r="775" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV775"/>
+      <c r="CL775" s="6"/>
+    </row>
+    <row r="776" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV776"/>
+      <c r="CL776" s="6"/>
+    </row>
+    <row r="777" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV777"/>
+      <c r="CL777" s="6"/>
+    </row>
+    <row r="778" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV778"/>
+      <c r="CL778" s="6"/>
+    </row>
+    <row r="779" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL779" s="6"/>
+    </row>
+    <row r="780" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV780"/>
+    </row>
+    <row r="781" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV781"/>
+      <c r="CL781" s="6"/>
+    </row>
+    <row r="782" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV782"/>
+      <c r="CL782" s="6"/>
+    </row>
+    <row r="783" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL783" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="14" type="noConversion"/>

--- a/Excel/一方通行/艾拉.xlsx
+++ b/Excel/一方通行/艾拉.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8386D270-FCCA-4A99-8E27-208FFF09C55B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B475ADF-E6B5-44BA-84B0-D36366CA0179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1043" uniqueCount="581">
   <si>
     <t>Id</t>
   </si>
@@ -11411,16 +11411,21 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A2:I4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
     <col min="3" max="3" width="27.25" customWidth="1"/>
     <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="9" max="9" width="9" customWidth="1"/>
+    <col min="10" max="10" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -11446,10 +11451,13 @@
         <v>530</v>
       </c>
       <c r="I2" t="s">
+        <v>342</v>
+      </c>
+      <c r="J2" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -11475,10 +11483,13 @@
         <v>118</v>
       </c>
       <c r="I3" t="s">
+        <v>382</v>
+      </c>
+      <c r="J3" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>394</v>
       </c>

--- a/Excel/一方通行/艾拉.xlsx
+++ b/Excel/一方通行/艾拉.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B475ADF-E6B5-44BA-84B0-D36366CA0179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B94FE389-D1A7-427E-BAB6-2B9B8F017E2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1043" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="581">
   <si>
     <t>Id</t>
   </si>
@@ -388,12 +388,6 @@
     <t>高度</t>
   </si>
   <si>
-    <t>高台单位？</t>
-  </si>
-  <si>
-    <t>地面</t>
-  </si>
-  <si>
     <t>阻挡个数</t>
   </si>
   <si>
@@ -548,12 +542,6 @@
   </si>
   <si>
     <t>Height</t>
-  </si>
-  <si>
-    <t>CanSetHigh</t>
-  </si>
-  <si>
-    <t>CanSetGround</t>
   </si>
   <si>
     <t>StopCount</t>
@@ -2057,6 +2045,22 @@
   <si>
     <t>string</t>
     <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>可部署位</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>CanSetPos</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>string[]</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>全地形</t>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2662,7 +2666,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BS587"/>
+  <dimension ref="A1:BR587"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1"/>
@@ -2692,22 +2696,22 @@
     <col min="34" max="34" width="13.83203125" customWidth="1"/>
     <col min="35" max="35" width="34.5" customWidth="1"/>
     <col min="36" max="37" width="9.83203125" customWidth="1"/>
-    <col min="43" max="43" width="12.5" customWidth="1"/>
-    <col min="50" max="50" width="24.33203125" customWidth="1"/>
-    <col min="52" max="52" width="17.75" customWidth="1"/>
-    <col min="53" max="53" width="7.83203125" customWidth="1"/>
-    <col min="56" max="56" width="24.25" customWidth="1"/>
-    <col min="57" max="57" width="13.25" customWidth="1"/>
-    <col min="58" max="58" width="16.08203125" customWidth="1"/>
-    <col min="59" max="59" width="8" customWidth="1"/>
-    <col min="64" max="64" width="39.58203125" customWidth="1"/>
-    <col min="65" max="65" width="14" customWidth="1"/>
-    <col min="66" max="66" width="14.83203125" customWidth="1"/>
-    <col min="67" max="70" width="14" customWidth="1"/>
-    <col min="71" max="71" width="19.1640625" customWidth="1"/>
+    <col min="42" max="42" width="12.5" customWidth="1"/>
+    <col min="49" max="49" width="24.33203125" customWidth="1"/>
+    <col min="51" max="51" width="17.75" customWidth="1"/>
+    <col min="52" max="52" width="7.83203125" customWidth="1"/>
+    <col min="55" max="55" width="24.25" customWidth="1"/>
+    <col min="56" max="56" width="13.25" customWidth="1"/>
+    <col min="57" max="57" width="16.08203125" customWidth="1"/>
+    <col min="58" max="58" width="8" customWidth="1"/>
+    <col min="63" max="63" width="39.58203125" customWidth="1"/>
+    <col min="64" max="64" width="14" customWidth="1"/>
+    <col min="65" max="65" width="14.83203125" customWidth="1"/>
+    <col min="66" max="69" width="14" customWidth="1"/>
+    <col min="70" max="70" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="D1" t="s">
         <v>5</v>
       </c>
@@ -2783,274 +2787,268 @@
       <c r="AL1" t="s">
         <v>28</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AM1" s="23" t="s">
+        <v>577</v>
+      </c>
+      <c r="AN1" t="s">
         <v>29</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>30</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>31</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>32</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" t="s">
         <v>33</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>34</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>35</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>36</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>37</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>38</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>39</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>40</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BC1" t="s">
         <v>41</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BD1" t="s">
         <v>42</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>43</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>44</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>45</v>
       </c>
-      <c r="BG1" t="s">
-        <v>46</v>
-      </c>
-      <c r="BH1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:71" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" t="s">
         <v>48</v>
       </c>
-      <c r="C2" t="s">
+      <c r="G2" t="s">
         <v>49</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>50</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>51</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>52</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>53</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>54</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>55</v>
       </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
         <v>56</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>57</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>58</v>
       </c>
-      <c r="O2" t="s">
+      <c r="Q2" t="s">
         <v>59</v>
       </c>
-      <c r="P2" t="s">
+      <c r="R2" t="s">
         <v>60</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="S2" t="s">
         <v>61</v>
       </c>
-      <c r="R2" t="s">
+      <c r="T2" t="s">
         <v>62</v>
       </c>
-      <c r="S2" t="s">
+      <c r="U2" t="s">
         <v>63</v>
       </c>
-      <c r="T2" t="s">
+      <c r="V2" t="s">
         <v>64</v>
       </c>
-      <c r="U2" t="s">
+      <c r="W2" t="s">
         <v>65</v>
       </c>
-      <c r="V2" t="s">
+      <c r="X2" t="s">
         <v>66</v>
       </c>
-      <c r="W2" t="s">
+      <c r="Y2" t="s">
         <v>67</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Z2" t="s">
         <v>68</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AA2" t="s">
         <v>69</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AB2" t="s">
         <v>70</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AC2" t="s">
         <v>71</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AD2" t="s">
         <v>72</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AE2" t="s">
         <v>73</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AF2" t="s">
         <v>74</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AG2" t="s">
         <v>75</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AH2" t="s">
         <v>76</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AI2" t="s">
         <v>77</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AJ2" t="s">
         <v>78</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AK2" t="s">
         <v>79</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AL2" t="s">
         <v>80</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AM2" s="23" t="s">
+        <v>578</v>
+      </c>
+      <c r="AN2" t="s">
         <v>81</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AO2" t="s">
         <v>82</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AP2" t="s">
         <v>83</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AQ2" t="s">
         <v>84</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AR2" t="s">
         <v>85</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AS2" t="s">
         <v>86</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AT2" t="s">
         <v>87</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AU2" t="s">
         <v>88</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AV2" t="s">
         <v>89</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AW2" t="s">
         <v>90</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AX2" t="s">
         <v>91</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AY2" t="s">
         <v>92</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AZ2" t="s">
         <v>93</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="BA2" t="s">
         <v>94</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="BB2" t="s">
         <v>95</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BC2" t="s">
         <v>96</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BD2" t="s">
         <v>97</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BE2" t="s">
         <v>98</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BF2" t="s">
         <v>99</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BG2" t="s">
         <v>100</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BH2" t="s">
         <v>101</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BI2" t="s">
         <v>102</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BJ2" t="s">
         <v>103</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BK2" t="s">
         <v>104</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BL2" t="s">
         <v>105</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BM2" t="s">
         <v>106</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BN2" t="s">
         <v>107</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BO2" t="s">
         <v>108</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BP2" t="s">
         <v>109</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BQ2" t="s">
         <v>110</v>
       </c>
-      <c r="BO2" t="s">
+      <c r="BR2" t="s">
         <v>111</v>
       </c>
-      <c r="BP2" t="s">
-        <v>112</v>
-      </c>
-      <c r="BQ2" t="s">
-        <v>113</v>
-      </c>
-      <c r="BR2" t="s">
-        <v>114</v>
-      </c>
-      <c r="BS2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="3" spans="1:71" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -3058,88 +3056,88 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F3" t="s">
         <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H3" t="s">
         <v>2</v>
       </c>
       <c r="I3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="J3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="K3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="L3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="M3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="N3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="O3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="P3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="Q3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="R3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="S3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="T3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="U3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="V3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="W3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="X3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Y3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Z3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="AA3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AB3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="AC3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AD3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="AE3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AF3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AG3" t="s">
         <v>2</v>
@@ -3148,61 +3146,61 @@
         <v>2</v>
       </c>
       <c r="AI3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AJ3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AK3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AL3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AM3" s="23" t="s">
+        <v>579</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AU3" t="s">
         <v>116</v>
       </c>
-      <c r="AN3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>118</v>
-      </c>
       <c r="AV3" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="AW3" t="s">
         <v>117</v>
       </c>
       <c r="AX3" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="AY3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="AZ3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="BA3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BB3" t="s">
-        <v>122</v>
+        <v>2</v>
       </c>
       <c r="BC3" t="s">
         <v>2</v>
@@ -3214,60 +3212,57 @@
         <v>2</v>
       </c>
       <c r="BF3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BH3" t="s">
         <v>2</v>
       </c>
-      <c r="BG3" t="s">
-        <v>123</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>118</v>
-      </c>
       <c r="BI3" t="s">
+        <v>120</v>
+      </c>
+      <c r="BJ3" t="s">
         <v>2</v>
       </c>
-      <c r="BJ3" t="s">
-        <v>124</v>
-      </c>
       <c r="BK3" t="s">
-        <v>2</v>
+        <v>121</v>
       </c>
       <c r="BL3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="BM3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BN3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BO3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BP3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BQ3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="BR3" t="s">
-        <v>124</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="4" spans="1:71" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F4" t="str">
         <f>"char_"&amp;E4&amp;"_"&amp;D4</f>
@@ -3319,90 +3314,87 @@
         <v>4</v>
       </c>
       <c r="AH4" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>126</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>127</v>
+      </c>
+      <c r="AM4" s="23" t="s">
+        <v>580</v>
+      </c>
+      <c r="AN4">
+        <v>1</v>
+      </c>
+      <c r="AO4">
+        <v>0.5</v>
+      </c>
+      <c r="AV4">
+        <v>0.25</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>128</v>
+      </c>
+      <c r="BB4" t="s">
         <v>129</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="BC4" t="s">
         <v>130</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="BD4" t="s">
         <v>131</v>
       </c>
-      <c r="AM4">
-        <v>1</v>
-      </c>
-      <c r="AN4">
-        <v>1</v>
-      </c>
-      <c r="AO4">
-        <v>1</v>
-      </c>
-      <c r="AP4">
-        <v>0.5</v>
-      </c>
-      <c r="AW4">
-        <v>0.25</v>
-      </c>
-      <c r="BB4" t="s">
+      <c r="BE4" t="s">
         <v>132</v>
       </c>
-      <c r="BC4" t="s">
+      <c r="BF4" t="s">
         <v>133</v>
       </c>
-      <c r="BD4" t="s">
+      <c r="BG4">
+        <v>6</v>
+      </c>
+      <c r="BH4" t="s">
         <v>134</v>
       </c>
-      <c r="BE4" t="s">
+      <c r="BI4" t="s">
         <v>135</v>
       </c>
-      <c r="BF4" t="s">
+      <c r="BJ4" t="s">
         <v>136</v>
       </c>
-      <c r="BG4" t="s">
+      <c r="BL4" t="s">
         <v>137</v>
       </c>
-      <c r="BH4">
-        <v>6</v>
-      </c>
-      <c r="BI4" t="s">
+      <c r="BM4" t="s">
         <v>138</v>
       </c>
-      <c r="BJ4" t="s">
+      <c r="BO4" t="s">
         <v>139</v>
       </c>
-      <c r="BK4" t="s">
+      <c r="BP4" t="s">
+        <v>139</v>
+      </c>
+      <c r="BR4">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:70" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>140</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="B5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D5" t="s">
         <v>141</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="E5" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="BP4" t="s">
+      <c r="F5" t="s">
         <v>143</v>
-      </c>
-      <c r="BQ4" t="s">
-        <v>143</v>
-      </c>
-      <c r="BS4">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>144</v>
-      </c>
-      <c r="B5" t="s">
-        <v>126</v>
-      </c>
-      <c r="D5" t="s">
-        <v>145</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="F5" t="s">
-        <v>147</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -3447,86 +3439,83 @@
         <v>1</v>
       </c>
       <c r="AG5" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="AH5" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="AI5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="AJ5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="AK5">
         <v>1</v>
       </c>
-      <c r="AM5">
-        <v>1</v>
+      <c r="AM5" s="23" t="s">
+        <v>580</v>
       </c>
       <c r="AN5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO5">
         <v>0</v>
       </c>
-      <c r="AP5">
-        <v>0</v>
-      </c>
-      <c r="AW5">
+      <c r="AV5">
         <v>0.25</v>
       </c>
-      <c r="BB5" t="s">
-        <v>132</v>
-      </c>
-      <c r="BD5" t="s">
-        <v>151</v>
+      <c r="BA5" t="s">
+        <v>128</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>147</v>
+      </c>
+      <c r="BD5" t="str">
+        <f t="shared" ref="BD5:BD7" si="0">"half_"&amp;D5</f>
+        <v>half_deepcl</v>
       </c>
       <c r="BE5" t="str">
-        <f t="shared" ref="BE5:BE7" si="0">"half_"&amp;D5</f>
-        <v>half_deepcl</v>
-      </c>
-      <c r="BF5" t="str">
-        <f t="shared" ref="BF5:BF7" si="1">D5</f>
+        <f t="shared" ref="BE5:BE7" si="1">D5</f>
         <v>deepcl</v>
       </c>
-      <c r="BG5" t="s">
+      <c r="BF5" t="s">
+        <v>133</v>
+      </c>
+      <c r="BG5">
+        <v>6</v>
+      </c>
+      <c r="BH5" t="s">
+        <v>148</v>
+      </c>
+      <c r="BI5" t="s">
+        <v>149</v>
+      </c>
+      <c r="BL5" t="s">
         <v>137</v>
       </c>
-      <c r="BH5">
-        <v>6</v>
-      </c>
-      <c r="BI5" t="s">
-        <v>152</v>
-      </c>
-      <c r="BJ5" t="s">
-        <v>153</v>
-      </c>
       <c r="BM5" t="s">
+        <v>138</v>
+      </c>
+      <c r="BR5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:70" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6" t="s">
         <v>141</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="E6" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="BS5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>154</v>
-      </c>
-      <c r="B6" t="s">
-        <v>126</v>
-      </c>
-      <c r="D6" t="s">
-        <v>145</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>146</v>
-      </c>
       <c r="F6" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -3571,86 +3560,83 @@
         <v>1</v>
       </c>
       <c r="AG6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="AH6" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="AI6" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="AJ6" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="AK6">
         <v>1</v>
       </c>
-      <c r="AM6">
-        <v>1</v>
+      <c r="AM6" s="23" t="s">
+        <v>580</v>
       </c>
       <c r="AN6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO6">
         <v>0</v>
       </c>
-      <c r="AP6">
-        <v>0</v>
-      </c>
-      <c r="AW6">
+      <c r="AV6">
         <v>0.25</v>
       </c>
-      <c r="BB6" t="s">
-        <v>132</v>
-      </c>
-      <c r="BD6" t="s">
-        <v>151</v>
-      </c>
-      <c r="BE6" t="str">
+      <c r="BA6" t="s">
+        <v>128</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>147</v>
+      </c>
+      <c r="BD6" t="str">
         <f t="shared" si="0"/>
         <v>half_deepcl</v>
       </c>
-      <c r="BF6" t="str">
+      <c r="BE6" t="str">
         <f t="shared" si="1"/>
         <v>deepcl</v>
       </c>
-      <c r="BG6" t="s">
+      <c r="BF6" t="s">
+        <v>133</v>
+      </c>
+      <c r="BG6">
+        <v>6</v>
+      </c>
+      <c r="BH6" t="s">
+        <v>148</v>
+      </c>
+      <c r="BI6" t="s">
+        <v>149</v>
+      </c>
+      <c r="BL6" t="s">
         <v>137</v>
       </c>
-      <c r="BH6">
-        <v>6</v>
-      </c>
-      <c r="BI6" t="s">
-        <v>152</v>
-      </c>
-      <c r="BJ6" t="s">
+      <c r="BM6" t="s">
+        <v>138</v>
+      </c>
+      <c r="BR6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:70" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>153</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="B7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D7" t="s">
         <v>141</v>
       </c>
-      <c r="BN6" t="s">
+      <c r="E7" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="BS6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>157</v>
-      </c>
-      <c r="B7" t="s">
-        <v>126</v>
-      </c>
-      <c r="D7" t="s">
-        <v>145</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>146</v>
-      </c>
       <c r="F7" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -3695,2404 +3681,2401 @@
         <v>1</v>
       </c>
       <c r="AG7" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="AH7" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="AI7" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AJ7" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="AK7">
         <v>1</v>
       </c>
-      <c r="AM7">
-        <v>1</v>
+      <c r="AM7" s="23" t="s">
+        <v>580</v>
       </c>
       <c r="AN7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO7">
         <v>0</v>
       </c>
-      <c r="AP7">
-        <v>0</v>
-      </c>
-      <c r="AW7">
+      <c r="AV7">
         <v>0.25</v>
       </c>
-      <c r="BB7" t="s">
-        <v>132</v>
-      </c>
-      <c r="BD7" t="s">
-        <v>151</v>
-      </c>
-      <c r="BE7" t="str">
+      <c r="BA7" t="s">
+        <v>128</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>147</v>
+      </c>
+      <c r="BD7" t="str">
         <f t="shared" si="0"/>
         <v>half_deepcl</v>
       </c>
-      <c r="BF7" t="str">
+      <c r="BE7" t="str">
         <f t="shared" si="1"/>
         <v>deepcl</v>
       </c>
-      <c r="BG7" t="s">
+      <c r="BF7" t="s">
+        <v>133</v>
+      </c>
+      <c r="BG7">
+        <v>6</v>
+      </c>
+      <c r="BH7" t="s">
+        <v>148</v>
+      </c>
+      <c r="BI7" t="s">
+        <v>149</v>
+      </c>
+      <c r="BL7" t="s">
         <v>137</v>
       </c>
-      <c r="BH7">
-        <v>6</v>
-      </c>
-      <c r="BI7" t="s">
-        <v>152</v>
-      </c>
-      <c r="BJ7" t="s">
-        <v>153</v>
-      </c>
       <c r="BM7" t="s">
-        <v>141</v>
-      </c>
-      <c r="BN7" t="s">
-        <v>142</v>
-      </c>
-      <c r="BS7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+      <c r="BR7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D25" s="18"/>
       <c r="E25" s="17"/>
-      <c r="BO25" s="19"/>
-      <c r="BR25" s="19"/>
-    </row>
-    <row r="26" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN25" s="19"/>
+      <c r="BQ25" s="19"/>
+    </row>
+    <row r="26" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D26" s="18"/>
       <c r="E26" s="17"/>
-      <c r="BO26" s="19"/>
-      <c r="BR26" s="19"/>
-    </row>
-    <row r="27" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN26" s="19"/>
+      <c r="BQ26" s="19"/>
+    </row>
+    <row r="27" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D27" s="18"/>
       <c r="E27" s="17"/>
-      <c r="BO27" s="19"/>
-      <c r="BR27" s="19"/>
-    </row>
-    <row r="28" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN27" s="19"/>
+      <c r="BQ27" s="19"/>
+    </row>
+    <row r="28" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D28" s="18"/>
       <c r="E28" s="17"/>
-      <c r="BO28" s="19"/>
-      <c r="BR28" s="19"/>
-    </row>
-    <row r="29" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN28" s="19"/>
+      <c r="BQ28" s="19"/>
+    </row>
+    <row r="29" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D29" s="18"/>
       <c r="E29" s="17"/>
-      <c r="BO29" s="19"/>
-      <c r="BR29" s="19"/>
-    </row>
-    <row r="30" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN29" s="19"/>
+      <c r="BQ29" s="19"/>
+    </row>
+    <row r="30" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D30" s="18"/>
       <c r="E30" s="17"/>
-      <c r="BO30" s="19"/>
-      <c r="BR30" s="19"/>
-    </row>
-    <row r="31" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN30" s="19"/>
+      <c r="BQ30" s="19"/>
+    </row>
+    <row r="31" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D31" s="18"/>
       <c r="E31" s="17"/>
-      <c r="BO31" s="19"/>
-      <c r="BR31" s="19"/>
-    </row>
-    <row r="32" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN31" s="19"/>
+      <c r="BQ31" s="19"/>
+    </row>
+    <row r="32" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D32" s="18"/>
       <c r="E32" s="17"/>
-      <c r="BR32" s="19"/>
-    </row>
-    <row r="33" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ32" s="19"/>
+    </row>
+    <row r="33" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D33" s="18"/>
       <c r="E33" s="17"/>
-      <c r="BR33" s="19"/>
-    </row>
-    <row r="34" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ33" s="19"/>
+    </row>
+    <row r="34" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D34" s="18"/>
       <c r="E34" s="17"/>
-      <c r="BR34" s="19"/>
-    </row>
-    <row r="35" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ34" s="19"/>
+    </row>
+    <row r="35" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D35" s="18"/>
       <c r="E35" s="17"/>
-      <c r="BO35" s="19"/>
-      <c r="BR35" s="19"/>
-    </row>
-    <row r="36" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN35" s="19"/>
+      <c r="BQ35" s="19"/>
+    </row>
+    <row r="36" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D36" s="18"/>
       <c r="E36" s="17"/>
-      <c r="BO36" s="19"/>
-      <c r="BR36" s="19"/>
-    </row>
-    <row r="37" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN36" s="19"/>
+      <c r="BQ36" s="19"/>
+    </row>
+    <row r="37" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D37" s="18"/>
       <c r="E37" s="17"/>
-      <c r="BO37" s="19"/>
-      <c r="BR37" s="19"/>
-    </row>
-    <row r="38" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN37" s="19"/>
+      <c r="BQ37" s="19"/>
+    </row>
+    <row r="38" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D38" s="18"/>
       <c r="E38" s="17"/>
-      <c r="BO38" s="19"/>
-      <c r="BR38" s="19"/>
-    </row>
-    <row r="39" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN38" s="19"/>
+      <c r="BQ38" s="19"/>
+    </row>
+    <row r="39" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D39" s="18"/>
       <c r="E39" s="17"/>
-      <c r="BO39" s="19"/>
-      <c r="BR39" s="19"/>
-    </row>
-    <row r="40" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN39" s="19"/>
+      <c r="BQ39" s="19"/>
+    </row>
+    <row r="40" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D40" s="18"/>
       <c r="E40" s="17"/>
-      <c r="BO40" s="19"/>
-      <c r="BR40" s="19"/>
-    </row>
-    <row r="41" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN40" s="19"/>
+      <c r="BQ40" s="19"/>
+    </row>
+    <row r="41" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D41" s="18"/>
       <c r="E41" s="17"/>
-      <c r="BO41" s="19"/>
-      <c r="BR41" s="19"/>
-    </row>
-    <row r="42" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN41" s="19"/>
+      <c r="BQ41" s="19"/>
+    </row>
+    <row r="42" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D42" s="18"/>
       <c r="E42" s="17"/>
-      <c r="BO42" s="19"/>
-      <c r="BR42" s="19"/>
-    </row>
-    <row r="43" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN42" s="19"/>
+      <c r="BQ42" s="19"/>
+    </row>
+    <row r="43" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D43" s="18"/>
       <c r="E43" s="17"/>
-      <c r="BO43" s="19"/>
-      <c r="BR43" s="19"/>
-    </row>
-    <row r="44" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN43" s="19"/>
+      <c r="BQ43" s="19"/>
+    </row>
+    <row r="44" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D44" s="18"/>
       <c r="E44" s="17"/>
-      <c r="BO44" s="19"/>
-      <c r="BR44" s="19"/>
-    </row>
-    <row r="45" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN44" s="19"/>
+      <c r="BQ44" s="19"/>
+    </row>
+    <row r="45" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D45" s="18"/>
       <c r="E45" s="17"/>
-      <c r="BO45" s="19"/>
-      <c r="BR45" s="19"/>
-    </row>
-    <row r="46" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN45" s="19"/>
+      <c r="BQ45" s="19"/>
+    </row>
+    <row r="46" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D46" s="18"/>
       <c r="E46" s="17"/>
-      <c r="BO46" s="19"/>
-      <c r="BR46" s="19"/>
-    </row>
-    <row r="47" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN46" s="19"/>
+      <c r="BQ46" s="19"/>
+    </row>
+    <row r="47" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D47" s="18"/>
       <c r="E47" s="17"/>
-      <c r="BO47" s="19"/>
-      <c r="BR47" s="19"/>
-    </row>
-    <row r="48" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN47" s="19"/>
+      <c r="BQ47" s="19"/>
+    </row>
+    <row r="48" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D48" s="18"/>
       <c r="E48" s="17"/>
-      <c r="BO48" s="19"/>
-      <c r="BR48" s="19"/>
-    </row>
-    <row r="49" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN48" s="19"/>
+      <c r="BQ48" s="19"/>
+    </row>
+    <row r="49" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D49" s="18"/>
       <c r="E49" s="17"/>
-      <c r="BO49" s="19"/>
-      <c r="BR49" s="19"/>
-    </row>
-    <row r="50" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN49" s="19"/>
+      <c r="BQ49" s="19"/>
+    </row>
+    <row r="50" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D50" s="18"/>
       <c r="E50" s="17"/>
-      <c r="BO50" s="19"/>
-      <c r="BR50" s="19"/>
-    </row>
-    <row r="51" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN50" s="19"/>
+      <c r="BQ50" s="19"/>
+    </row>
+    <row r="51" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D51" s="18"/>
       <c r="E51" s="17"/>
-      <c r="BO51" s="19"/>
-      <c r="BR51" s="19"/>
-    </row>
-    <row r="52" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN51" s="19"/>
+      <c r="BQ51" s="19"/>
+    </row>
+    <row r="52" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D52" s="18"/>
       <c r="E52" s="17"/>
-      <c r="BO52" s="19"/>
-      <c r="BR52" s="19"/>
-    </row>
-    <row r="53" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN52" s="19"/>
+      <c r="BQ52" s="19"/>
+    </row>
+    <row r="53" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D53" s="18"/>
       <c r="E53" s="17"/>
-      <c r="BO53" s="19"/>
-      <c r="BR53" s="19"/>
-    </row>
-    <row r="54" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN53" s="19"/>
+      <c r="BQ53" s="19"/>
+    </row>
+    <row r="54" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D54" s="18"/>
       <c r="E54" s="17"/>
-      <c r="BO54" s="19"/>
-      <c r="BR54" s="19"/>
-    </row>
-    <row r="55" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN54" s="19"/>
+      <c r="BQ54" s="19"/>
+    </row>
+    <row r="55" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D55" s="18"/>
       <c r="E55" s="17"/>
-      <c r="BO55" s="19"/>
-      <c r="BR55" s="19"/>
-    </row>
-    <row r="56" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN55" s="19"/>
+      <c r="BQ55" s="19"/>
+    </row>
+    <row r="56" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D56" s="18"/>
       <c r="E56" s="17"/>
-      <c r="BO56" s="19"/>
-      <c r="BR56" s="19"/>
-    </row>
-    <row r="57" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN56" s="19"/>
+      <c r="BQ56" s="19"/>
+    </row>
+    <row r="57" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D57" s="18"/>
       <c r="E57" s="17"/>
-      <c r="BO57" s="19"/>
-      <c r="BR57" s="19"/>
-    </row>
-    <row r="58" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN57" s="19"/>
+      <c r="BQ57" s="19"/>
+    </row>
+    <row r="58" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D58" s="18"/>
       <c r="E58" s="17"/>
-      <c r="BO58" s="19"/>
-      <c r="BR58" s="19"/>
-    </row>
-    <row r="59" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN58" s="19"/>
+      <c r="BQ58" s="19"/>
+    </row>
+    <row r="59" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D59" s="18"/>
       <c r="E59" s="17"/>
-      <c r="BO59" s="19"/>
-      <c r="BR59" s="19"/>
-    </row>
-    <row r="60" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN59" s="19"/>
+      <c r="BQ59" s="19"/>
+    </row>
+    <row r="60" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D60" s="18"/>
       <c r="E60" s="17"/>
-      <c r="BO60" s="19"/>
-      <c r="BR60" s="19"/>
-    </row>
-    <row r="61" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN60" s="19"/>
+      <c r="BQ60" s="19"/>
+    </row>
+    <row r="61" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D61" s="18"/>
       <c r="E61" s="17"/>
-      <c r="BO61" s="19"/>
-      <c r="BR61" s="19"/>
-    </row>
-    <row r="62" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN61" s="19"/>
+      <c r="BQ61" s="19"/>
+    </row>
+    <row r="62" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D62" s="18"/>
       <c r="E62" s="17"/>
-      <c r="BO62" s="19"/>
-      <c r="BR62" s="19"/>
-    </row>
-    <row r="63" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN62" s="19"/>
+      <c r="BQ62" s="19"/>
+    </row>
+    <row r="63" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D63" s="18"/>
       <c r="E63" s="17"/>
-      <c r="BO63" s="19"/>
-      <c r="BR63" s="19"/>
-    </row>
-    <row r="64" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN63" s="19"/>
+      <c r="BQ63" s="19"/>
+    </row>
+    <row r="64" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D64" s="18"/>
       <c r="E64" s="17"/>
-      <c r="BO64" s="19"/>
-      <c r="BR64" s="19"/>
-    </row>
-    <row r="65" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN64" s="19"/>
+      <c r="BQ64" s="19"/>
+    </row>
+    <row r="65" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D65" s="18"/>
       <c r="E65" s="17"/>
-      <c r="BO65" s="19"/>
-      <c r="BR65" s="19"/>
-    </row>
-    <row r="66" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN65" s="19"/>
+      <c r="BQ65" s="19"/>
+    </row>
+    <row r="66" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D66" s="18"/>
       <c r="E66" s="17"/>
-      <c r="BO66" s="19"/>
-      <c r="BR66" s="19"/>
-    </row>
-    <row r="67" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN66" s="19"/>
+      <c r="BQ66" s="19"/>
+    </row>
+    <row r="67" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D67" s="18"/>
       <c r="E67" s="17"/>
-      <c r="BO67" s="19"/>
-      <c r="BR67" s="19"/>
-    </row>
-    <row r="68" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN67" s="19"/>
+      <c r="BQ67" s="19"/>
+    </row>
+    <row r="68" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D68" s="18"/>
       <c r="E68" s="17"/>
-      <c r="BO68" s="19"/>
-      <c r="BR68" s="19"/>
-    </row>
-    <row r="69" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN68" s="19"/>
+      <c r="BQ68" s="19"/>
+    </row>
+    <row r="69" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D69" s="18"/>
       <c r="E69" s="17"/>
-      <c r="BO69" s="19"/>
-      <c r="BR69" s="19"/>
-    </row>
-    <row r="70" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN69" s="19"/>
+      <c r="BQ69" s="19"/>
+    </row>
+    <row r="70" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D70" s="18"/>
       <c r="E70" s="17"/>
-      <c r="BO70" s="19"/>
-      <c r="BR70" s="19"/>
-    </row>
-    <row r="71" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN70" s="19"/>
+      <c r="BQ70" s="19"/>
+    </row>
+    <row r="71" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D71" s="18"/>
       <c r="E71" s="17"/>
-      <c r="BO71" s="19"/>
-      <c r="BR71" s="19"/>
-    </row>
-    <row r="72" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN71" s="19"/>
+      <c r="BQ71" s="19"/>
+    </row>
+    <row r="72" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D72" s="18"/>
       <c r="E72" s="17"/>
-      <c r="BO72" s="19"/>
-      <c r="BR72" s="19"/>
-    </row>
-    <row r="73" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN72" s="19"/>
+      <c r="BQ72" s="19"/>
+    </row>
+    <row r="73" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D73" s="18"/>
       <c r="E73" s="17"/>
-      <c r="BO73" s="19"/>
-      <c r="BR73" s="19"/>
-    </row>
-    <row r="74" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN73" s="19"/>
+      <c r="BQ73" s="19"/>
+    </row>
+    <row r="74" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D74" s="18"/>
       <c r="E74" s="17"/>
-      <c r="BO74" s="19"/>
-      <c r="BR74" s="19"/>
-    </row>
-    <row r="75" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN74" s="19"/>
+      <c r="BQ74" s="19"/>
+    </row>
+    <row r="75" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D75" s="18"/>
       <c r="E75" s="17"/>
-      <c r="BO75" s="19"/>
-      <c r="BR75" s="19"/>
-    </row>
-    <row r="76" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN75" s="19"/>
+      <c r="BQ75" s="19"/>
+    </row>
+    <row r="76" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D76" s="18"/>
       <c r="E76" s="17"/>
-      <c r="BO76" s="19"/>
-      <c r="BR76" s="19"/>
-    </row>
-    <row r="77" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN76" s="19"/>
+      <c r="BQ76" s="19"/>
+    </row>
+    <row r="77" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D77" s="18"/>
       <c r="E77" s="17"/>
-      <c r="BO77" s="19"/>
-      <c r="BR77" s="19"/>
-    </row>
-    <row r="78" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN77" s="19"/>
+      <c r="BQ77" s="19"/>
+    </row>
+    <row r="78" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D78" s="18"/>
       <c r="E78" s="17"/>
-      <c r="BO78" s="19"/>
-      <c r="BR78" s="19"/>
-    </row>
-    <row r="79" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN78" s="19"/>
+      <c r="BQ78" s="19"/>
+    </row>
+    <row r="79" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D79" s="18"/>
       <c r="E79" s="17"/>
-      <c r="BO79" s="19"/>
-      <c r="BR79" s="19"/>
-    </row>
-    <row r="80" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN79" s="19"/>
+      <c r="BQ79" s="19"/>
+    </row>
+    <row r="80" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D80" s="18"/>
       <c r="E80" s="17"/>
-      <c r="BO80" s="19"/>
-      <c r="BR80" s="19"/>
-    </row>
-    <row r="81" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN80" s="19"/>
+      <c r="BQ80" s="19"/>
+    </row>
+    <row r="81" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D81" s="18"/>
       <c r="E81" s="17"/>
-      <c r="BO81" s="19"/>
-      <c r="BR81" s="19"/>
-    </row>
-    <row r="82" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN81" s="19"/>
+      <c r="BQ81" s="19"/>
+    </row>
+    <row r="82" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D82" s="18"/>
       <c r="E82" s="17"/>
-      <c r="BO82" s="19"/>
-      <c r="BR82" s="19"/>
-    </row>
-    <row r="83" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN82" s="19"/>
+      <c r="BQ82" s="19"/>
+    </row>
+    <row r="83" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D83" s="18"/>
       <c r="E83" s="17"/>
-      <c r="BO83" s="19"/>
-      <c r="BR83" s="19"/>
-    </row>
-    <row r="84" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN83" s="19"/>
+      <c r="BQ83" s="19"/>
+    </row>
+    <row r="84" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D84" s="18"/>
       <c r="E84" s="17"/>
-      <c r="BO84" s="19"/>
-      <c r="BR84" s="19"/>
-    </row>
-    <row r="85" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN84" s="19"/>
+      <c r="BQ84" s="19"/>
+    </row>
+    <row r="85" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D85" s="18"/>
       <c r="E85" s="17"/>
-      <c r="BO85" s="19"/>
-      <c r="BR85" s="19"/>
-    </row>
-    <row r="86" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN85" s="19"/>
+      <c r="BQ85" s="19"/>
+    </row>
+    <row r="86" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D86" s="18"/>
       <c r="E86" s="17"/>
-      <c r="BO86" s="19"/>
-      <c r="BR86" s="19"/>
-    </row>
-    <row r="87" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN86" s="19"/>
+      <c r="BQ86" s="19"/>
+    </row>
+    <row r="87" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D87" s="18"/>
       <c r="E87" s="17"/>
-      <c r="BO87" s="19"/>
-      <c r="BR87" s="19"/>
-    </row>
-    <row r="88" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN87" s="19"/>
+      <c r="BQ87" s="19"/>
+    </row>
+    <row r="88" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D88" s="18"/>
       <c r="E88" s="17"/>
-      <c r="BO88" s="19"/>
-      <c r="BR88" s="19"/>
-    </row>
-    <row r="89" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN88" s="19"/>
+      <c r="BQ88" s="19"/>
+    </row>
+    <row r="89" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D89" s="18"/>
       <c r="E89" s="17"/>
-      <c r="BO89" s="19"/>
-      <c r="BR89" s="19"/>
-    </row>
-    <row r="90" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN89" s="19"/>
+      <c r="BQ89" s="19"/>
+    </row>
+    <row r="90" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D90" s="18"/>
       <c r="E90" s="17"/>
-      <c r="BO90" s="19"/>
-      <c r="BR90" s="19"/>
-    </row>
-    <row r="91" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN90" s="19"/>
+      <c r="BQ90" s="19"/>
+    </row>
+    <row r="91" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D91" s="18"/>
       <c r="E91" s="17"/>
-      <c r="BO91" s="19"/>
-      <c r="BR91" s="19"/>
-    </row>
-    <row r="92" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN91" s="19"/>
+      <c r="BQ91" s="19"/>
+    </row>
+    <row r="92" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D92" s="18"/>
       <c r="E92" s="17"/>
-      <c r="BO92" s="19"/>
-      <c r="BR92" s="19"/>
-    </row>
-    <row r="93" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN92" s="19"/>
+      <c r="BQ92" s="19"/>
+    </row>
+    <row r="93" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D93" s="18"/>
       <c r="E93" s="17"/>
-      <c r="BO93" s="19"/>
-      <c r="BR93" s="19"/>
-    </row>
-    <row r="94" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN93" s="19"/>
+      <c r="BQ93" s="19"/>
+    </row>
+    <row r="94" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D94" s="18"/>
       <c r="E94" s="17"/>
-      <c r="BO94" s="19"/>
-      <c r="BR94" s="19"/>
-    </row>
-    <row r="95" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN94" s="19"/>
+      <c r="BQ94" s="19"/>
+    </row>
+    <row r="95" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D95" s="18"/>
       <c r="E95" s="17"/>
-      <c r="BO95" s="19"/>
-      <c r="BR95" s="19"/>
-    </row>
-    <row r="96" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN95" s="19"/>
+      <c r="BQ95" s="19"/>
+    </row>
+    <row r="96" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D96" s="18"/>
       <c r="E96" s="17"/>
-      <c r="BO96" s="19"/>
-      <c r="BR96" s="19"/>
-    </row>
-    <row r="97" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN96" s="19"/>
+      <c r="BQ96" s="19"/>
+    </row>
+    <row r="97" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D97" s="18"/>
       <c r="E97" s="17"/>
-      <c r="BO97" s="19"/>
-      <c r="BR97" s="19"/>
-    </row>
-    <row r="98" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN97" s="19"/>
+      <c r="BQ97" s="19"/>
+    </row>
+    <row r="98" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D98" s="18"/>
       <c r="E98" s="17"/>
-      <c r="BO98" s="19"/>
-      <c r="BR98" s="19"/>
-    </row>
-    <row r="99" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN98" s="19"/>
+      <c r="BQ98" s="19"/>
+    </row>
+    <row r="99" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D99" s="18"/>
       <c r="E99" s="17"/>
-      <c r="BO99" s="19"/>
-      <c r="BR99" s="19"/>
-    </row>
-    <row r="100" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN99" s="19"/>
+      <c r="BQ99" s="19"/>
+    </row>
+    <row r="100" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D100" s="18"/>
       <c r="E100" s="17"/>
-      <c r="BO100" s="19"/>
-      <c r="BR100" s="19"/>
-    </row>
-    <row r="101" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN100" s="19"/>
+      <c r="BQ100" s="19"/>
+    </row>
+    <row r="101" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D101" s="18"/>
       <c r="E101" s="17"/>
-      <c r="BO101" s="19"/>
-      <c r="BR101" s="19"/>
-    </row>
-    <row r="102" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN101" s="19"/>
+      <c r="BQ101" s="19"/>
+    </row>
+    <row r="102" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D102" s="18"/>
       <c r="E102" s="17"/>
-      <c r="BO102" s="19"/>
-      <c r="BR102" s="19"/>
-    </row>
-    <row r="103" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN102" s="19"/>
+      <c r="BQ102" s="19"/>
+    </row>
+    <row r="103" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D103" s="18"/>
       <c r="E103" s="17"/>
-      <c r="BO103" s="19"/>
-      <c r="BR103" s="19"/>
-    </row>
-    <row r="104" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN103" s="19"/>
+      <c r="BQ103" s="19"/>
+    </row>
+    <row r="104" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D104" s="18"/>
       <c r="E104" s="17"/>
-      <c r="BO104" s="19"/>
-      <c r="BR104" s="19"/>
-    </row>
-    <row r="105" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN104" s="19"/>
+      <c r="BQ104" s="19"/>
+    </row>
+    <row r="105" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D105" s="18"/>
       <c r="E105" s="17"/>
-      <c r="BO105" s="19"/>
-      <c r="BR105" s="19"/>
-    </row>
-    <row r="106" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN105" s="19"/>
+      <c r="BQ105" s="19"/>
+    </row>
+    <row r="106" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D106" s="18"/>
       <c r="E106" s="17"/>
-      <c r="BO106" s="19"/>
-      <c r="BR106" s="19"/>
-    </row>
-    <row r="107" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN106" s="19"/>
+      <c r="BQ106" s="19"/>
+    </row>
+    <row r="107" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D107" s="18"/>
       <c r="E107" s="17"/>
-      <c r="BO107" s="19"/>
-      <c r="BR107" s="19"/>
-    </row>
-    <row r="108" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN107" s="19"/>
+      <c r="BQ107" s="19"/>
+    </row>
+    <row r="108" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D108" s="18"/>
       <c r="E108" s="17"/>
-      <c r="BO108" s="19"/>
-      <c r="BR108" s="19"/>
-    </row>
-    <row r="109" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN108" s="19"/>
+      <c r="BQ108" s="19"/>
+    </row>
+    <row r="109" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D109" s="18"/>
       <c r="E109" s="17"/>
-      <c r="BO109" s="19"/>
-      <c r="BR109" s="19"/>
-    </row>
-    <row r="110" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN109" s="19"/>
+      <c r="BQ109" s="19"/>
+    </row>
+    <row r="110" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D110" s="18"/>
       <c r="E110" s="17"/>
-      <c r="BO110" s="19"/>
-      <c r="BR110" s="19"/>
-    </row>
-    <row r="111" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN110" s="19"/>
+      <c r="BQ110" s="19"/>
+    </row>
+    <row r="111" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D111" s="18"/>
       <c r="E111" s="17"/>
-      <c r="BO111" s="19"/>
-      <c r="BR111" s="19"/>
-    </row>
-    <row r="112" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN111" s="19"/>
+      <c r="BQ111" s="19"/>
+    </row>
+    <row r="112" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D112" s="18"/>
       <c r="E112" s="17"/>
-      <c r="BO112" s="19"/>
-      <c r="BR112" s="19"/>
-    </row>
-    <row r="113" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN112" s="19"/>
+      <c r="BQ112" s="19"/>
+    </row>
+    <row r="113" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D113" s="18"/>
       <c r="E113" s="17"/>
-      <c r="BO113" s="19"/>
-      <c r="BR113" s="19"/>
-    </row>
-    <row r="114" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN113" s="19"/>
+      <c r="BQ113" s="19"/>
+    </row>
+    <row r="114" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D114" s="18"/>
       <c r="E114" s="17"/>
-      <c r="BO114" s="19"/>
-      <c r="BR114" s="19"/>
-    </row>
-    <row r="115" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN114" s="19"/>
+      <c r="BQ114" s="19"/>
+    </row>
+    <row r="115" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D115" s="18"/>
       <c r="E115" s="17"/>
-      <c r="BO115" s="19"/>
-      <c r="BR115" s="19"/>
-    </row>
-    <row r="116" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN115" s="19"/>
+      <c r="BQ115" s="19"/>
+    </row>
+    <row r="116" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D116" s="18"/>
       <c r="E116" s="17"/>
-      <c r="BO116" s="19"/>
-      <c r="BR116" s="19"/>
-    </row>
-    <row r="117" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN116" s="19"/>
+      <c r="BQ116" s="19"/>
+    </row>
+    <row r="117" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D117" s="18"/>
       <c r="E117" s="17"/>
-      <c r="BO117" s="19"/>
-      <c r="BR117" s="19"/>
-    </row>
-    <row r="118" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN117" s="19"/>
+      <c r="BQ117" s="19"/>
+    </row>
+    <row r="118" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D118" s="18"/>
       <c r="E118" s="17"/>
-      <c r="BO118" s="19"/>
-      <c r="BR118" s="19"/>
-    </row>
-    <row r="119" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN118" s="19"/>
+      <c r="BQ118" s="19"/>
+    </row>
+    <row r="119" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D119" s="18"/>
       <c r="E119" s="17"/>
-      <c r="BO119" s="19"/>
-      <c r="BR119" s="19"/>
-    </row>
-    <row r="120" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN119" s="19"/>
+      <c r="BQ119" s="19"/>
+    </row>
+    <row r="120" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D120" s="18"/>
       <c r="E120" s="17"/>
-      <c r="BO120" s="19"/>
-      <c r="BR120" s="19"/>
-    </row>
-    <row r="121" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN120" s="19"/>
+      <c r="BQ120" s="19"/>
+    </row>
+    <row r="121" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D121" s="18"/>
       <c r="E121" s="17"/>
-      <c r="BO121" s="19"/>
-      <c r="BR121" s="19"/>
-    </row>
-    <row r="122" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN121" s="19"/>
+      <c r="BQ121" s="19"/>
+    </row>
+    <row r="122" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D122" s="18"/>
       <c r="E122" s="17"/>
-      <c r="BO122" s="19"/>
-      <c r="BR122" s="19"/>
-    </row>
-    <row r="123" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN122" s="19"/>
+      <c r="BQ122" s="19"/>
+    </row>
+    <row r="123" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D123" s="18"/>
       <c r="E123" s="17"/>
-      <c r="BO123" s="19"/>
-      <c r="BR123" s="19"/>
-    </row>
-    <row r="124" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN123" s="19"/>
+      <c r="BQ123" s="19"/>
+    </row>
+    <row r="124" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D124" s="18"/>
       <c r="E124" s="17"/>
-      <c r="BO124" s="19"/>
-      <c r="BR124" s="19"/>
-    </row>
-    <row r="125" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN124" s="19"/>
+      <c r="BQ124" s="19"/>
+    </row>
+    <row r="125" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D125" s="18"/>
       <c r="E125" s="17"/>
-      <c r="BO125" s="19"/>
-      <c r="BR125" s="19"/>
-    </row>
-    <row r="126" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN125" s="19"/>
+      <c r="BQ125" s="19"/>
+    </row>
+    <row r="126" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D126" s="18"/>
       <c r="E126" s="17"/>
-      <c r="BO126" s="19"/>
-      <c r="BR126" s="19"/>
-    </row>
-    <row r="127" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN126" s="19"/>
+      <c r="BQ126" s="19"/>
+    </row>
+    <row r="127" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D127" s="18"/>
       <c r="E127" s="17"/>
-      <c r="BO127" s="19"/>
-      <c r="BR127" s="19"/>
-    </row>
-    <row r="128" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN127" s="19"/>
+      <c r="BQ127" s="19"/>
+    </row>
+    <row r="128" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D128" s="18"/>
       <c r="E128" s="17"/>
-      <c r="BO128" s="19"/>
-      <c r="BR128" s="19"/>
-    </row>
-    <row r="129" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN128" s="19"/>
+      <c r="BQ128" s="19"/>
+    </row>
+    <row r="129" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D129" s="18"/>
       <c r="E129" s="17"/>
-      <c r="BO129" s="19"/>
-      <c r="BR129" s="19"/>
-    </row>
-    <row r="130" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN129" s="19"/>
+      <c r="BQ129" s="19"/>
+    </row>
+    <row r="130" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D130" s="18"/>
       <c r="E130" s="17"/>
-      <c r="BO130" s="19"/>
-      <c r="BR130" s="19"/>
-    </row>
-    <row r="131" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN130" s="19"/>
+      <c r="BQ130" s="19"/>
+    </row>
+    <row r="131" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D131" s="18"/>
       <c r="E131" s="17"/>
-      <c r="BO131" s="19"/>
-      <c r="BR131" s="19"/>
-    </row>
-    <row r="132" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN131" s="19"/>
+      <c r="BQ131" s="19"/>
+    </row>
+    <row r="132" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D132" s="18"/>
       <c r="E132" s="17"/>
-      <c r="BO132" s="19"/>
-      <c r="BR132" s="19"/>
-    </row>
-    <row r="133" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN132" s="19"/>
+      <c r="BQ132" s="19"/>
+    </row>
+    <row r="133" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D133" s="18"/>
       <c r="E133" s="17"/>
-      <c r="BO133" s="19"/>
-      <c r="BR133" s="19"/>
-    </row>
-    <row r="134" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN133" s="19"/>
+      <c r="BQ133" s="19"/>
+    </row>
+    <row r="134" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D134" s="18"/>
       <c r="E134" s="17"/>
-      <c r="BO134" s="19"/>
-      <c r="BR134" s="19"/>
-    </row>
-    <row r="135" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN134" s="19"/>
+      <c r="BQ134" s="19"/>
+    </row>
+    <row r="135" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D135" s="18"/>
       <c r="E135" s="17"/>
-      <c r="BO135" s="19"/>
-      <c r="BR135" s="19"/>
-    </row>
-    <row r="136" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN135" s="19"/>
+      <c r="BQ135" s="19"/>
+    </row>
+    <row r="136" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D136" s="18"/>
       <c r="E136" s="17"/>
-      <c r="BO136" s="19"/>
-      <c r="BR136" s="19"/>
-    </row>
-    <row r="137" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN136" s="19"/>
+      <c r="BQ136" s="19"/>
+    </row>
+    <row r="137" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D137" s="18"/>
       <c r="E137" s="17"/>
-      <c r="BO137" s="19"/>
-      <c r="BR137" s="19"/>
-    </row>
-    <row r="138" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN137" s="19"/>
+      <c r="BQ137" s="19"/>
+    </row>
+    <row r="138" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D138" s="18"/>
       <c r="E138" s="17"/>
-      <c r="BO138" s="19"/>
-      <c r="BR138" s="19"/>
-    </row>
-    <row r="139" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN138" s="19"/>
+      <c r="BQ138" s="19"/>
+    </row>
+    <row r="139" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D139" s="18"/>
       <c r="E139" s="17"/>
-      <c r="BO139" s="19"/>
-      <c r="BR139" s="19"/>
-    </row>
-    <row r="140" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN139" s="19"/>
+      <c r="BQ139" s="19"/>
+    </row>
+    <row r="140" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D140" s="18"/>
       <c r="E140" s="17"/>
-      <c r="BO140" s="19"/>
-      <c r="BR140" s="19"/>
-    </row>
-    <row r="141" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN140" s="19"/>
+      <c r="BQ140" s="19"/>
+    </row>
+    <row r="141" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D141" s="18"/>
       <c r="E141" s="17"/>
-      <c r="BO141" s="19"/>
-      <c r="BR141" s="19"/>
-    </row>
-    <row r="142" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN141" s="19"/>
+      <c r="BQ141" s="19"/>
+    </row>
+    <row r="142" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D142" s="18"/>
       <c r="E142" s="17"/>
-      <c r="BO142" s="19"/>
-      <c r="BR142" s="19"/>
-    </row>
-    <row r="143" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN142" s="19"/>
+      <c r="BQ142" s="19"/>
+    </row>
+    <row r="143" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D143" s="18"/>
       <c r="E143" s="17"/>
-      <c r="BO143" s="19"/>
-      <c r="BR143" s="19"/>
-    </row>
-    <row r="144" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN143" s="19"/>
+      <c r="BQ143" s="19"/>
+    </row>
+    <row r="144" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D144" s="18"/>
       <c r="E144" s="17"/>
-      <c r="BO144" s="19"/>
-      <c r="BR144" s="19"/>
-    </row>
-    <row r="145" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN144" s="19"/>
+      <c r="BQ144" s="19"/>
+    </row>
+    <row r="145" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D145" s="18"/>
       <c r="E145" s="17"/>
-      <c r="BO145" s="19"/>
-      <c r="BR145" s="19"/>
-    </row>
-    <row r="146" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN145" s="19"/>
+      <c r="BQ145" s="19"/>
+    </row>
+    <row r="146" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D146" s="18"/>
       <c r="E146" s="17"/>
-      <c r="BO146" s="19"/>
-      <c r="BR146" s="19"/>
-    </row>
-    <row r="147" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN146" s="19"/>
+      <c r="BQ146" s="19"/>
+    </row>
+    <row r="147" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D147" s="18"/>
       <c r="E147" s="17"/>
-      <c r="BO147" s="19"/>
-      <c r="BR147" s="19"/>
-    </row>
-    <row r="148" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN147" s="19"/>
+      <c r="BQ147" s="19"/>
+    </row>
+    <row r="148" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D148" s="18"/>
       <c r="E148" s="17"/>
-      <c r="BO148" s="19"/>
-      <c r="BR148" s="19"/>
-    </row>
-    <row r="149" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN148" s="19"/>
+      <c r="BQ148" s="19"/>
+    </row>
+    <row r="149" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D149" s="18"/>
       <c r="E149" s="17"/>
-      <c r="BO149" s="19"/>
-      <c r="BR149" s="19"/>
-    </row>
-    <row r="150" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN149" s="19"/>
+      <c r="BQ149" s="19"/>
+    </row>
+    <row r="150" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D150" s="18"/>
       <c r="E150" s="17"/>
-      <c r="BO150" s="19"/>
-      <c r="BR150" s="19"/>
-    </row>
-    <row r="151" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN150" s="19"/>
+      <c r="BQ150" s="19"/>
+    </row>
+    <row r="151" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D151" s="18"/>
       <c r="E151" s="17"/>
-      <c r="BO151" s="19"/>
-      <c r="BR151" s="19"/>
-    </row>
-    <row r="152" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN151" s="19"/>
+      <c r="BQ151" s="19"/>
+    </row>
+    <row r="152" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D152" s="18"/>
       <c r="E152" s="17"/>
-      <c r="BO152" s="19"/>
-      <c r="BR152" s="19"/>
-    </row>
-    <row r="153" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN152" s="19"/>
+      <c r="BQ152" s="19"/>
+    </row>
+    <row r="153" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D153" s="18"/>
       <c r="E153" s="17"/>
-      <c r="BO153" s="19"/>
-      <c r="BR153" s="19"/>
-    </row>
-    <row r="154" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN153" s="19"/>
+      <c r="BQ153" s="19"/>
+    </row>
+    <row r="154" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D154" s="18"/>
       <c r="E154" s="17"/>
-      <c r="BO154" s="19"/>
-      <c r="BR154" s="19"/>
-    </row>
-    <row r="155" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN154" s="19"/>
+      <c r="BQ154" s="19"/>
+    </row>
+    <row r="155" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D155" s="18"/>
       <c r="E155" s="17"/>
-      <c r="BO155" s="19"/>
-      <c r="BR155" s="19"/>
-    </row>
-    <row r="156" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN155" s="19"/>
+      <c r="BQ155" s="19"/>
+    </row>
+    <row r="156" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D156" s="18"/>
       <c r="E156" s="17"/>
-      <c r="BO156" s="19"/>
-      <c r="BR156" s="19"/>
-    </row>
-    <row r="157" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN156" s="19"/>
+      <c r="BQ156" s="19"/>
+    </row>
+    <row r="157" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D157" s="18"/>
       <c r="E157" s="17"/>
-      <c r="BO157" s="19"/>
-      <c r="BR157" s="19"/>
-    </row>
-    <row r="158" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN157" s="19"/>
+      <c r="BQ157" s="19"/>
+    </row>
+    <row r="158" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D158" s="18"/>
       <c r="E158" s="17"/>
-      <c r="BO158" s="19"/>
-      <c r="BR158" s="19"/>
-    </row>
-    <row r="159" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN158" s="19"/>
+      <c r="BQ158" s="19"/>
+    </row>
+    <row r="159" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D159" s="18"/>
       <c r="E159" s="17"/>
-      <c r="BO159" s="19"/>
-      <c r="BR159" s="19"/>
-    </row>
-    <row r="160" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN159" s="19"/>
+      <c r="BQ159" s="19"/>
+    </row>
+    <row r="160" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D160" s="18"/>
       <c r="E160" s="17"/>
-      <c r="BO160" s="19"/>
-      <c r="BR160" s="19"/>
-    </row>
-    <row r="161" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN160" s="19"/>
+      <c r="BQ160" s="19"/>
+    </row>
+    <row r="161" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D161" s="18"/>
       <c r="E161" s="17"/>
-      <c r="BO161" s="19"/>
-      <c r="BR161" s="19"/>
-    </row>
-    <row r="162" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN161" s="19"/>
+      <c r="BQ161" s="19"/>
+    </row>
+    <row r="162" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D162" s="18"/>
       <c r="E162" s="17"/>
-      <c r="BO162" s="19"/>
-      <c r="BR162" s="19"/>
-    </row>
-    <row r="163" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN162" s="19"/>
+      <c r="BQ162" s="19"/>
+    </row>
+    <row r="163" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D163" s="18"/>
       <c r="E163" s="17"/>
-      <c r="BO163" s="19"/>
-      <c r="BR163" s="19"/>
-    </row>
-    <row r="164" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN163" s="19"/>
+      <c r="BQ163" s="19"/>
+    </row>
+    <row r="164" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D164" s="18"/>
       <c r="E164" s="17"/>
-      <c r="BO164" s="19"/>
-      <c r="BR164" s="19"/>
-    </row>
-    <row r="165" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN164" s="19"/>
+      <c r="BQ164" s="19"/>
+    </row>
+    <row r="165" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D165" s="18"/>
       <c r="E165" s="17"/>
-      <c r="BO165" s="19"/>
-      <c r="BR165" s="19"/>
-    </row>
-    <row r="166" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN165" s="19"/>
+      <c r="BQ165" s="19"/>
+    </row>
+    <row r="166" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D166" s="18"/>
       <c r="E166" s="17"/>
-      <c r="BO166" s="19"/>
-      <c r="BR166" s="19"/>
-    </row>
-    <row r="167" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN166" s="19"/>
+      <c r="BQ166" s="19"/>
+    </row>
+    <row r="167" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D167" s="18"/>
       <c r="E167" s="17"/>
-      <c r="BO167" s="19"/>
-      <c r="BR167" s="19"/>
-    </row>
-    <row r="168" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN167" s="19"/>
+      <c r="BQ167" s="19"/>
+    </row>
+    <row r="168" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D168" s="18"/>
       <c r="E168" s="17"/>
-      <c r="BO168" s="19"/>
-      <c r="BR168" s="19"/>
-    </row>
-    <row r="169" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN168" s="19"/>
+      <c r="BQ168" s="19"/>
+    </row>
+    <row r="169" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D169" s="18"/>
       <c r="E169" s="17"/>
-      <c r="BO169" s="19"/>
-      <c r="BR169" s="19"/>
-    </row>
-    <row r="170" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN169" s="19"/>
+      <c r="BQ169" s="19"/>
+    </row>
+    <row r="170" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D170" s="18"/>
       <c r="E170" s="17"/>
-      <c r="BO170" s="19"/>
-      <c r="BR170" s="19"/>
-    </row>
-    <row r="171" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN170" s="19"/>
+      <c r="BQ170" s="19"/>
+    </row>
+    <row r="171" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D171" s="18"/>
       <c r="E171" s="17"/>
-      <c r="BO171" s="19"/>
-      <c r="BR171" s="19"/>
-    </row>
-    <row r="172" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN171" s="19"/>
+      <c r="BQ171" s="19"/>
+    </row>
+    <row r="172" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D172" s="18"/>
       <c r="E172" s="17"/>
-      <c r="BO172" s="19"/>
-      <c r="BR172" s="19"/>
-    </row>
-    <row r="173" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN172" s="19"/>
+      <c r="BQ172" s="19"/>
+    </row>
+    <row r="173" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D173" s="18"/>
       <c r="E173" s="17"/>
-      <c r="BO173" s="19"/>
-      <c r="BR173" s="19"/>
-    </row>
-    <row r="174" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN173" s="19"/>
+      <c r="BQ173" s="19"/>
+    </row>
+    <row r="174" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D174" s="18"/>
       <c r="E174" s="17"/>
-      <c r="BO174" s="19"/>
-      <c r="BR174" s="19"/>
-    </row>
-    <row r="175" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN174" s="19"/>
+      <c r="BQ174" s="19"/>
+    </row>
+    <row r="175" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D175" s="18"/>
       <c r="E175" s="17"/>
-      <c r="BO175" s="19"/>
-      <c r="BR175" s="19"/>
-    </row>
-    <row r="176" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN175" s="19"/>
+      <c r="BQ175" s="19"/>
+    </row>
+    <row r="176" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D176" s="18"/>
       <c r="E176" s="17"/>
-      <c r="BO176" s="19"/>
-      <c r="BR176" s="19"/>
-    </row>
-    <row r="177" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN176" s="19"/>
+      <c r="BQ176" s="19"/>
+    </row>
+    <row r="177" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D177" s="18"/>
       <c r="E177" s="17"/>
-      <c r="BO177" s="19"/>
-      <c r="BR177" s="19"/>
-    </row>
-    <row r="178" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN177" s="19"/>
+      <c r="BQ177" s="19"/>
+    </row>
+    <row r="178" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D178" s="18"/>
       <c r="E178" s="17"/>
-      <c r="BO178" s="19"/>
-      <c r="BR178" s="19"/>
-    </row>
-    <row r="179" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN178" s="19"/>
+      <c r="BQ178" s="19"/>
+    </row>
+    <row r="179" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D179" s="18"/>
       <c r="E179" s="17"/>
-      <c r="BO179" s="19"/>
-      <c r="BR179" s="19"/>
-    </row>
-    <row r="180" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN179" s="19"/>
+      <c r="BQ179" s="19"/>
+    </row>
+    <row r="180" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D180" s="18"/>
       <c r="E180" s="17"/>
-      <c r="BO180" s="19"/>
-      <c r="BR180" s="19"/>
-    </row>
-    <row r="181" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN180" s="19"/>
+      <c r="BQ180" s="19"/>
+    </row>
+    <row r="181" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D181" s="18"/>
       <c r="E181" s="17"/>
-      <c r="BO181" s="19"/>
-      <c r="BR181" s="19"/>
-    </row>
-    <row r="182" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN181" s="19"/>
+      <c r="BQ181" s="19"/>
+    </row>
+    <row r="182" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D182" s="18"/>
       <c r="E182" s="17"/>
-      <c r="BO182" s="19"/>
-      <c r="BR182" s="19"/>
-    </row>
-    <row r="183" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN182" s="19"/>
+      <c r="BQ182" s="19"/>
+    </row>
+    <row r="183" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D183" s="18"/>
       <c r="E183" s="17"/>
-      <c r="BO183" s="19"/>
-      <c r="BR183" s="19"/>
-    </row>
-    <row r="184" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN183" s="19"/>
+      <c r="BQ183" s="19"/>
+    </row>
+    <row r="184" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D184" s="18"/>
       <c r="E184" s="17"/>
-      <c r="BO184" s="19"/>
-      <c r="BR184" s="19"/>
-    </row>
-    <row r="185" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN184" s="19"/>
+      <c r="BQ184" s="19"/>
+    </row>
+    <row r="185" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D185" s="18"/>
       <c r="E185" s="17"/>
-      <c r="BO185" s="19"/>
-      <c r="BR185" s="19"/>
-    </row>
-    <row r="186" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN185" s="19"/>
+      <c r="BQ185" s="19"/>
+    </row>
+    <row r="186" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D186" s="18"/>
       <c r="E186" s="17"/>
-      <c r="BO186" s="19"/>
-      <c r="BR186" s="19"/>
-    </row>
-    <row r="187" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN186" s="19"/>
+      <c r="BQ186" s="19"/>
+    </row>
+    <row r="187" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D187" s="18"/>
       <c r="E187" s="17"/>
-      <c r="BO187" s="19"/>
-      <c r="BR187" s="19"/>
-    </row>
-    <row r="188" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN187" s="19"/>
+      <c r="BQ187" s="19"/>
+    </row>
+    <row r="188" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D188" s="18"/>
       <c r="E188" s="17"/>
-      <c r="BO188" s="19"/>
-      <c r="BR188" s="19"/>
-    </row>
-    <row r="189" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN188" s="19"/>
+      <c r="BQ188" s="19"/>
+    </row>
+    <row r="189" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D189" s="18"/>
       <c r="E189" s="17"/>
-      <c r="BO189" s="19"/>
-      <c r="BR189" s="19"/>
-    </row>
-    <row r="190" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN189" s="19"/>
+      <c r="BQ189" s="19"/>
+    </row>
+    <row r="190" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D190" s="18"/>
       <c r="E190" s="17"/>
-      <c r="BO190" s="19"/>
-      <c r="BR190" s="19"/>
-    </row>
-    <row r="191" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN190" s="19"/>
+      <c r="BQ190" s="19"/>
+    </row>
+    <row r="191" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D191" s="18"/>
       <c r="E191" s="17"/>
-      <c r="BO191" s="19"/>
-      <c r="BR191" s="19"/>
-    </row>
-    <row r="192" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN191" s="19"/>
+      <c r="BQ191" s="19"/>
+    </row>
+    <row r="192" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D192" s="18"/>
       <c r="E192" s="17"/>
-      <c r="BO192" s="19"/>
-      <c r="BR192" s="19"/>
-    </row>
-    <row r="193" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN192" s="19"/>
+      <c r="BQ192" s="19"/>
+    </row>
+    <row r="193" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D193" s="18"/>
       <c r="E193" s="17"/>
-      <c r="BO193" s="19"/>
-      <c r="BR193" s="19"/>
-    </row>
-    <row r="194" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN193" s="19"/>
+      <c r="BQ193" s="19"/>
+    </row>
+    <row r="194" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D194" s="18"/>
       <c r="E194" s="17"/>
-      <c r="BO194" s="19"/>
-      <c r="BR194" s="19"/>
-    </row>
-    <row r="195" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN194" s="19"/>
+      <c r="BQ194" s="19"/>
+    </row>
+    <row r="195" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D195" s="18"/>
       <c r="E195" s="17"/>
-      <c r="BO195" s="19"/>
-      <c r="BR195" s="19"/>
-    </row>
-    <row r="196" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN195" s="19"/>
+      <c r="BQ195" s="19"/>
+    </row>
+    <row r="196" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D196" s="18"/>
       <c r="E196" s="17"/>
-      <c r="BO196" s="19"/>
-      <c r="BR196" s="19"/>
-    </row>
-    <row r="197" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN196" s="19"/>
+      <c r="BQ196" s="19"/>
+    </row>
+    <row r="197" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D197" s="18"/>
       <c r="E197" s="17"/>
-      <c r="BO197" s="19"/>
-      <c r="BR197" s="19"/>
-    </row>
-    <row r="198" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN197" s="19"/>
+      <c r="BQ197" s="19"/>
+    </row>
+    <row r="198" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D198" s="18"/>
       <c r="E198" s="17"/>
-      <c r="BO198" s="19"/>
-      <c r="BR198" s="19"/>
-    </row>
-    <row r="199" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN198" s="19"/>
+      <c r="BQ198" s="19"/>
+    </row>
+    <row r="199" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D199" s="18"/>
       <c r="E199" s="17"/>
-      <c r="BO199" s="19"/>
-      <c r="BR199" s="19"/>
-    </row>
-    <row r="200" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN199" s="19"/>
+      <c r="BQ199" s="19"/>
+    </row>
+    <row r="200" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D200" s="18"/>
       <c r="E200" s="17"/>
-      <c r="BO200" s="19"/>
-      <c r="BR200" s="19"/>
-    </row>
-    <row r="201" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN200" s="19"/>
+      <c r="BQ200" s="19"/>
+    </row>
+    <row r="201" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D201" s="18"/>
       <c r="E201" s="17"/>
-      <c r="BO201" s="19"/>
-      <c r="BR201" s="19"/>
-    </row>
-    <row r="202" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN201" s="19"/>
+      <c r="BQ201" s="19"/>
+    </row>
+    <row r="202" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D202" s="18"/>
       <c r="E202" s="17"/>
-      <c r="BO202" s="19"/>
-      <c r="BR202" s="19"/>
-    </row>
-    <row r="203" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN202" s="19"/>
+      <c r="BQ202" s="19"/>
+    </row>
+    <row r="203" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D203" s="18"/>
       <c r="E203" s="17"/>
-      <c r="BO203" s="19"/>
-      <c r="BR203" s="19"/>
-    </row>
-    <row r="204" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN203" s="19"/>
+      <c r="BQ203" s="19"/>
+    </row>
+    <row r="204" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D204" s="18"/>
       <c r="E204" s="17"/>
-      <c r="BO204" s="19"/>
-      <c r="BR204" s="19"/>
-    </row>
-    <row r="205" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN204" s="19"/>
+      <c r="BQ204" s="19"/>
+    </row>
+    <row r="205" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D205" s="18"/>
       <c r="E205" s="17"/>
-      <c r="BO205" s="19"/>
-      <c r="BR205" s="19"/>
-    </row>
-    <row r="206" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN205" s="19"/>
+      <c r="BQ205" s="19"/>
+    </row>
+    <row r="206" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D206" s="18"/>
       <c r="E206" s="17"/>
-      <c r="BO206" s="19"/>
-      <c r="BR206" s="19"/>
-    </row>
-    <row r="207" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN206" s="19"/>
+      <c r="BQ206" s="19"/>
+    </row>
+    <row r="207" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D207" s="18"/>
       <c r="E207" s="17"/>
-      <c r="BO207" s="19"/>
-      <c r="BR207" s="19"/>
-    </row>
-    <row r="208" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN207" s="19"/>
+      <c r="BQ207" s="19"/>
+    </row>
+    <row r="208" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D208" s="18"/>
       <c r="E208" s="17"/>
-      <c r="BO208" s="19"/>
-      <c r="BR208" s="19"/>
-    </row>
-    <row r="209" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN208" s="19"/>
+      <c r="BQ208" s="19"/>
+    </row>
+    <row r="209" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D209" s="18"/>
       <c r="E209" s="17"/>
-      <c r="BO209" s="19"/>
-      <c r="BR209" s="19"/>
-    </row>
-    <row r="210" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN209" s="19"/>
+      <c r="BQ209" s="19"/>
+    </row>
+    <row r="210" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D210" s="18"/>
       <c r="E210" s="17"/>
-      <c r="BO210" s="19"/>
-      <c r="BR210" s="19"/>
-    </row>
-    <row r="211" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN210" s="19"/>
+      <c r="BQ210" s="19"/>
+    </row>
+    <row r="211" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D211" s="18"/>
       <c r="E211" s="17"/>
-      <c r="BO211" s="19"/>
-      <c r="BR211" s="19"/>
-    </row>
-    <row r="212" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN211" s="19"/>
+      <c r="BQ211" s="19"/>
+    </row>
+    <row r="212" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D212" s="18"/>
       <c r="E212" s="17"/>
-      <c r="BO212" s="19"/>
-      <c r="BR212" s="19"/>
-    </row>
-    <row r="213" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN212" s="19"/>
+      <c r="BQ212" s="19"/>
+    </row>
+    <row r="213" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D213" s="18"/>
       <c r="E213" s="17"/>
-      <c r="BO213" s="19"/>
-      <c r="BR213" s="19"/>
-    </row>
-    <row r="214" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN213" s="19"/>
+      <c r="BQ213" s="19"/>
+    </row>
+    <row r="214" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D214" s="18"/>
       <c r="E214" s="17"/>
-      <c r="BO214" s="19"/>
-      <c r="BR214" s="19"/>
-    </row>
-    <row r="215" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN214" s="19"/>
+      <c r="BQ214" s="19"/>
+    </row>
+    <row r="215" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D215" s="18"/>
       <c r="E215" s="17"/>
-      <c r="BO215" s="19"/>
-      <c r="BR215" s="19"/>
-    </row>
-    <row r="216" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN215" s="19"/>
+      <c r="BQ215" s="19"/>
+    </row>
+    <row r="216" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D216" s="18"/>
       <c r="E216" s="17"/>
-      <c r="BO216" s="19"/>
-      <c r="BR216" s="19"/>
-    </row>
-    <row r="217" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN216" s="19"/>
+      <c r="BQ216" s="19"/>
+    </row>
+    <row r="217" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D217" s="18"/>
       <c r="E217" s="17"/>
-      <c r="BO217" s="19"/>
-      <c r="BR217" s="19"/>
-    </row>
-    <row r="218" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN217" s="19"/>
+      <c r="BQ217" s="19"/>
+    </row>
+    <row r="218" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D218" s="18"/>
       <c r="E218" s="17"/>
-      <c r="BO218" s="19"/>
-      <c r="BR218" s="19"/>
-    </row>
-    <row r="219" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN218" s="19"/>
+      <c r="BQ218" s="19"/>
+    </row>
+    <row r="219" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D219" s="18"/>
       <c r="E219" s="17"/>
-      <c r="BO219" s="19"/>
-      <c r="BR219" s="19"/>
-    </row>
-    <row r="220" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN219" s="19"/>
+      <c r="BQ219" s="19"/>
+    </row>
+    <row r="220" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D220" s="18"/>
       <c r="E220" s="17"/>
-      <c r="BO220" s="19"/>
-      <c r="BR220" s="19"/>
-    </row>
-    <row r="221" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN220" s="19"/>
+      <c r="BQ220" s="19"/>
+    </row>
+    <row r="221" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D221" s="18"/>
       <c r="E221" s="17"/>
-      <c r="BO221" s="19"/>
-      <c r="BR221" s="19"/>
-    </row>
-    <row r="222" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN221" s="19"/>
+      <c r="BQ221" s="19"/>
+    </row>
+    <row r="222" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D222" s="18"/>
       <c r="E222" s="17"/>
-      <c r="BO222" s="19"/>
-      <c r="BR222" s="19"/>
-    </row>
-    <row r="223" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN222" s="19"/>
+      <c r="BQ222" s="19"/>
+    </row>
+    <row r="223" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D223" s="18"/>
       <c r="E223" s="17"/>
-      <c r="BO223" s="19"/>
-      <c r="BR223" s="19"/>
-    </row>
-    <row r="224" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN223" s="19"/>
+      <c r="BQ223" s="19"/>
+    </row>
+    <row r="224" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D224" s="18"/>
       <c r="E224" s="17"/>
-      <c r="BO224" s="19"/>
-      <c r="BR224" s="19"/>
-    </row>
-    <row r="225" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN224" s="19"/>
+      <c r="BQ224" s="19"/>
+    </row>
+    <row r="225" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D225" s="18"/>
       <c r="E225" s="17"/>
-      <c r="BO225" s="19"/>
-      <c r="BR225" s="19"/>
-    </row>
-    <row r="226" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN225" s="19"/>
+      <c r="BQ225" s="19"/>
+    </row>
+    <row r="226" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D226" s="18"/>
       <c r="E226" s="17"/>
-      <c r="BO226" s="19"/>
-      <c r="BR226" s="19"/>
-    </row>
-    <row r="227" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN226" s="19"/>
+      <c r="BQ226" s="19"/>
+    </row>
+    <row r="227" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D227" s="18"/>
       <c r="E227" s="17"/>
-      <c r="BO227" s="19"/>
-      <c r="BR227" s="19"/>
-    </row>
-    <row r="228" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN227" s="19"/>
+      <c r="BQ227" s="19"/>
+    </row>
+    <row r="228" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D228" s="18"/>
       <c r="E228" s="17"/>
-      <c r="BO228" s="19"/>
-      <c r="BR228" s="19"/>
-    </row>
-    <row r="229" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN228" s="19"/>
+      <c r="BQ228" s="19"/>
+    </row>
+    <row r="229" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D229" s="18"/>
       <c r="E229" s="17"/>
-      <c r="BO229" s="19"/>
-      <c r="BR229" s="19"/>
-    </row>
-    <row r="230" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN229" s="19"/>
+      <c r="BQ229" s="19"/>
+    </row>
+    <row r="230" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D230" s="18"/>
       <c r="E230" s="17"/>
-      <c r="BO230" s="19"/>
-      <c r="BR230" s="19"/>
-    </row>
-    <row r="231" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN230" s="19"/>
+      <c r="BQ230" s="19"/>
+    </row>
+    <row r="231" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D231" s="18"/>
       <c r="E231" s="17"/>
-      <c r="BO231" s="19"/>
-      <c r="BR231" s="19"/>
-    </row>
-    <row r="232" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN231" s="19"/>
+      <c r="BQ231" s="19"/>
+    </row>
+    <row r="232" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D232" s="18"/>
       <c r="E232" s="17"/>
-      <c r="BR232" s="19"/>
-    </row>
-    <row r="233" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ232" s="19"/>
+    </row>
+    <row r="233" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D233" s="18"/>
       <c r="E233" s="17"/>
-      <c r="BO233" s="19"/>
-      <c r="BR233" s="19"/>
-    </row>
-    <row r="234" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN233" s="19"/>
+      <c r="BQ233" s="19"/>
+    </row>
+    <row r="234" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D234" s="18"/>
       <c r="E234" s="17"/>
-      <c r="BO234" s="19"/>
-      <c r="BR234" s="19"/>
-    </row>
-    <row r="235" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN234" s="19"/>
+      <c r="BQ234" s="19"/>
+    </row>
+    <row r="235" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D235" s="18"/>
       <c r="E235" s="17"/>
-      <c r="BO235" s="19"/>
-      <c r="BR235" s="19"/>
-    </row>
-    <row r="236" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN235" s="19"/>
+      <c r="BQ235" s="19"/>
+    </row>
+    <row r="236" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D236" s="18"/>
       <c r="E236" s="17"/>
-      <c r="BO236" s="19"/>
-      <c r="BR236" s="19"/>
-    </row>
-    <row r="237" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN236" s="19"/>
+      <c r="BQ236" s="19"/>
+    </row>
+    <row r="237" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D237" s="18"/>
       <c r="E237" s="17"/>
-      <c r="BO237" s="19"/>
-      <c r="BR237" s="19"/>
-    </row>
-    <row r="238" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN237" s="19"/>
+      <c r="BQ237" s="19"/>
+    </row>
+    <row r="238" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D238" s="18"/>
       <c r="E238" s="17"/>
-      <c r="BO238" s="19"/>
-      <c r="BR238" s="19"/>
-    </row>
-    <row r="239" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN238" s="19"/>
+      <c r="BQ238" s="19"/>
+    </row>
+    <row r="239" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D239" s="18"/>
       <c r="E239" s="17"/>
-      <c r="BO239" s="19"/>
-      <c r="BR239" s="19"/>
-    </row>
-    <row r="240" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN239" s="19"/>
+      <c r="BQ239" s="19"/>
+    </row>
+    <row r="240" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D240" s="18"/>
       <c r="E240" s="17"/>
-      <c r="BO240" s="19"/>
-      <c r="BR240" s="19"/>
-    </row>
-    <row r="241" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN240" s="19"/>
+      <c r="BQ240" s="19"/>
+    </row>
+    <row r="241" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D241" s="18"/>
       <c r="E241" s="17"/>
-      <c r="BO241" s="19"/>
-      <c r="BR241" s="19"/>
-    </row>
-    <row r="242" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN241" s="19"/>
+      <c r="BQ241" s="19"/>
+    </row>
+    <row r="242" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D242" s="18"/>
       <c r="E242" s="17"/>
-      <c r="BO242" s="19"/>
-      <c r="BR242" s="19"/>
-    </row>
-    <row r="243" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN242" s="19"/>
+      <c r="BQ242" s="19"/>
+    </row>
+    <row r="243" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D243" s="18"/>
       <c r="E243" s="17"/>
-      <c r="BO243" s="19"/>
-      <c r="BR243" s="19"/>
-    </row>
-    <row r="244" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN243" s="19"/>
+      <c r="BQ243" s="19"/>
+    </row>
+    <row r="244" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D244" s="18"/>
       <c r="E244" s="17"/>
-      <c r="BO244" s="19"/>
-      <c r="BR244" s="19"/>
-    </row>
-    <row r="245" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN244" s="19"/>
+      <c r="BQ244" s="19"/>
+    </row>
+    <row r="245" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D245" s="18"/>
       <c r="E245" s="17"/>
-      <c r="BO245" s="19"/>
-      <c r="BR245" s="19"/>
-    </row>
-    <row r="246" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN245" s="19"/>
+      <c r="BQ245" s="19"/>
+    </row>
+    <row r="246" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D246" s="18"/>
       <c r="E246" s="17"/>
-      <c r="BO246" s="19"/>
-      <c r="BR246" s="19"/>
-    </row>
-    <row r="247" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN246" s="19"/>
+      <c r="BQ246" s="19"/>
+    </row>
+    <row r="247" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D247" s="18"/>
       <c r="E247" s="17"/>
-      <c r="BO247" s="19"/>
-      <c r="BR247" s="19"/>
-    </row>
-    <row r="248" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN247" s="19"/>
+      <c r="BQ247" s="19"/>
+    </row>
+    <row r="248" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D248" s="18"/>
       <c r="E248" s="17"/>
-      <c r="BO248" s="19"/>
-      <c r="BR248" s="19"/>
-    </row>
-    <row r="249" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN248" s="19"/>
+      <c r="BQ248" s="19"/>
+    </row>
+    <row r="249" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D249" s="18"/>
       <c r="E249" s="17"/>
-      <c r="BO249" s="19"/>
-      <c r="BR249" s="19"/>
-    </row>
-    <row r="250" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN249" s="19"/>
+      <c r="BQ249" s="19"/>
+    </row>
+    <row r="250" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D250" s="18"/>
       <c r="E250" s="17"/>
-      <c r="BO250" s="19"/>
-      <c r="BR250" s="19"/>
-    </row>
-    <row r="251" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN250" s="19"/>
+      <c r="BQ250" s="19"/>
+    </row>
+    <row r="251" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D251" s="18"/>
       <c r="E251" s="17"/>
-      <c r="BO251" s="19"/>
-      <c r="BR251" s="19"/>
-    </row>
-    <row r="252" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN251" s="19"/>
+      <c r="BQ251" s="19"/>
+    </row>
+    <row r="252" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D252" s="18"/>
       <c r="E252" s="17"/>
-      <c r="BO252" s="19"/>
-      <c r="BR252" s="19"/>
-    </row>
-    <row r="253" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN252" s="19"/>
+      <c r="BQ252" s="19"/>
+    </row>
+    <row r="253" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D253" s="18"/>
       <c r="E253" s="17"/>
-      <c r="BO253" s="19"/>
-      <c r="BR253" s="19"/>
-    </row>
-    <row r="254" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN253" s="19"/>
+      <c r="BQ253" s="19"/>
+    </row>
+    <row r="254" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D254" s="18"/>
       <c r="E254" s="17"/>
-      <c r="BO254" s="19"/>
-      <c r="BR254" s="19"/>
-    </row>
-    <row r="255" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN254" s="19"/>
+      <c r="BQ254" s="19"/>
+    </row>
+    <row r="255" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D255" s="18"/>
       <c r="E255" s="17"/>
-      <c r="BO255" s="19"/>
-      <c r="BR255" s="19"/>
-    </row>
-    <row r="256" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN255" s="19"/>
+      <c r="BQ255" s="19"/>
+    </row>
+    <row r="256" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D256" s="18"/>
       <c r="E256" s="17"/>
-      <c r="BO256" s="19"/>
-      <c r="BR256" s="19"/>
-    </row>
-    <row r="257" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN256" s="19"/>
+      <c r="BQ256" s="19"/>
+    </row>
+    <row r="257" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D257" s="18"/>
       <c r="E257" s="17"/>
-      <c r="BO257" s="19"/>
-      <c r="BR257" s="19"/>
-    </row>
-    <row r="258" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN257" s="19"/>
+      <c r="BQ257" s="19"/>
+    </row>
+    <row r="258" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D258" s="18"/>
       <c r="E258" s="17"/>
-      <c r="BO258" s="19"/>
-      <c r="BR258" s="19"/>
-    </row>
-    <row r="259" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN258" s="19"/>
+      <c r="BQ258" s="19"/>
+    </row>
+    <row r="259" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D259" s="18"/>
       <c r="E259" s="17"/>
-      <c r="BO259" s="19"/>
-      <c r="BR259" s="19"/>
-    </row>
-    <row r="260" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN259" s="19"/>
+      <c r="BQ259" s="19"/>
+    </row>
+    <row r="260" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D260" s="18"/>
       <c r="E260" s="17"/>
-      <c r="BO260" s="19"/>
-      <c r="BR260" s="19"/>
-    </row>
-    <row r="261" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN260" s="19"/>
+      <c r="BQ260" s="19"/>
+    </row>
+    <row r="261" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D261" s="18"/>
       <c r="E261" s="17"/>
-      <c r="BO261" s="19"/>
-      <c r="BR261" s="19"/>
-    </row>
-    <row r="262" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN261" s="19"/>
+      <c r="BQ261" s="19"/>
+    </row>
+    <row r="262" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D262" s="18"/>
       <c r="E262" s="17"/>
-      <c r="BO262" s="19"/>
-      <c r="BR262" s="19"/>
-    </row>
-    <row r="263" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN262" s="19"/>
+      <c r="BQ262" s="19"/>
+    </row>
+    <row r="263" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D263" s="18"/>
       <c r="E263" s="17"/>
-      <c r="BO263" s="19"/>
-      <c r="BR263" s="19"/>
-    </row>
-    <row r="264" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN263" s="19"/>
+      <c r="BQ263" s="19"/>
+    </row>
+    <row r="264" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D264" s="18"/>
       <c r="E264" s="17"/>
-      <c r="BO264" s="19"/>
-      <c r="BR264" s="19"/>
-    </row>
-    <row r="265" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN264" s="19"/>
+      <c r="BQ264" s="19"/>
+    </row>
+    <row r="265" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D265" s="18"/>
       <c r="E265" s="17"/>
-      <c r="BO265" s="19"/>
-      <c r="BR265" s="19"/>
-    </row>
-    <row r="266" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN265" s="19"/>
+      <c r="BQ265" s="19"/>
+    </row>
+    <row r="266" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D266" s="18"/>
       <c r="E266" s="17"/>
-      <c r="BO266" s="19"/>
-      <c r="BR266" s="19"/>
-    </row>
-    <row r="267" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN266" s="19"/>
+      <c r="BQ266" s="19"/>
+    </row>
+    <row r="267" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D267" s="18"/>
       <c r="E267" s="17"/>
-      <c r="BO267" s="19"/>
-      <c r="BR267" s="19"/>
-    </row>
-    <row r="268" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN267" s="19"/>
+      <c r="BQ267" s="19"/>
+    </row>
+    <row r="268" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D268" s="18"/>
       <c r="E268" s="17"/>
-      <c r="BO268" s="19"/>
-      <c r="BR268" s="19"/>
-    </row>
-    <row r="269" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN268" s="19"/>
+      <c r="BQ268" s="19"/>
+    </row>
+    <row r="269" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D269" s="18"/>
       <c r="E269" s="17"/>
-      <c r="BO269" s="19"/>
-      <c r="BR269" s="19"/>
-    </row>
-    <row r="270" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN269" s="19"/>
+      <c r="BQ269" s="19"/>
+    </row>
+    <row r="270" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D270" s="18"/>
       <c r="E270" s="17"/>
-      <c r="BO270" s="19"/>
-      <c r="BR270" s="19"/>
-    </row>
-    <row r="271" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN270" s="19"/>
+      <c r="BQ270" s="19"/>
+    </row>
+    <row r="271" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D271" s="18"/>
       <c r="E271" s="17"/>
-      <c r="BO271" s="19"/>
-      <c r="BR271" s="19"/>
-    </row>
-    <row r="272" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN271" s="19"/>
+      <c r="BQ271" s="19"/>
+    </row>
+    <row r="272" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D272" s="18"/>
       <c r="E272" s="17"/>
-      <c r="BO272" s="19"/>
-      <c r="BR272" s="19"/>
-    </row>
-    <row r="273" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN272" s="19"/>
+      <c r="BQ272" s="19"/>
+    </row>
+    <row r="273" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D273" s="18"/>
       <c r="E273" s="17"/>
-      <c r="BO273" s="19"/>
-      <c r="BR273" s="19"/>
-    </row>
-    <row r="274" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN273" s="19"/>
+      <c r="BQ273" s="19"/>
+    </row>
+    <row r="274" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D274" s="18"/>
       <c r="E274" s="17"/>
-      <c r="BO274" s="19"/>
-      <c r="BR274" s="19"/>
-    </row>
-    <row r="275" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN274" s="19"/>
+      <c r="BQ274" s="19"/>
+    </row>
+    <row r="275" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D275" s="18"/>
       <c r="E275" s="17"/>
-      <c r="BR275" s="19"/>
-    </row>
-    <row r="276" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ275" s="19"/>
+    </row>
+    <row r="276" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D276" s="18"/>
       <c r="E276" s="17"/>
-      <c r="BO276" s="19"/>
-      <c r="BR276" s="19"/>
-    </row>
-    <row r="277" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN276" s="19"/>
+      <c r="BQ276" s="19"/>
+    </row>
+    <row r="277" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D277" s="18"/>
       <c r="E277" s="17"/>
-      <c r="BO277" s="19"/>
-      <c r="BR277" s="19"/>
-    </row>
-    <row r="278" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN277" s="19"/>
+      <c r="BQ277" s="19"/>
+    </row>
+    <row r="278" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D278" s="18"/>
       <c r="E278" s="17"/>
-      <c r="BO278" s="19"/>
-      <c r="BR278" s="19"/>
-    </row>
-    <row r="279" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN278" s="19"/>
+      <c r="BQ278" s="19"/>
+    </row>
+    <row r="279" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D279" s="18"/>
       <c r="E279" s="17"/>
-      <c r="BO279" s="19"/>
-      <c r="BR279" s="19"/>
-    </row>
-    <row r="280" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN279" s="19"/>
+      <c r="BQ279" s="19"/>
+    </row>
+    <row r="280" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D280" s="18"/>
       <c r="E280" s="17"/>
-      <c r="BO280" s="19"/>
-      <c r="BR280" s="19"/>
-    </row>
-    <row r="281" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN280" s="19"/>
+      <c r="BQ280" s="19"/>
+    </row>
+    <row r="281" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D281" s="18"/>
       <c r="E281" s="17"/>
-      <c r="BO281" s="19"/>
-      <c r="BR281" s="19"/>
-    </row>
-    <row r="282" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN281" s="19"/>
+      <c r="BQ281" s="19"/>
+    </row>
+    <row r="282" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D282" s="18"/>
       <c r="E282" s="17"/>
-      <c r="BO282" s="19"/>
-      <c r="BR282" s="19"/>
-    </row>
-    <row r="283" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN282" s="19"/>
+      <c r="BQ282" s="19"/>
+    </row>
+    <row r="283" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D283" s="18"/>
       <c r="E283" s="17"/>
-      <c r="BO283" s="19"/>
-      <c r="BR283" s="19"/>
-    </row>
-    <row r="284" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN283" s="19"/>
+      <c r="BQ283" s="19"/>
+    </row>
+    <row r="284" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D284" s="18"/>
       <c r="E284" s="17"/>
-      <c r="BO284" s="19"/>
-      <c r="BR284" s="19"/>
-    </row>
-    <row r="285" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN284" s="19"/>
+      <c r="BQ284" s="19"/>
+    </row>
+    <row r="285" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D285" s="18"/>
       <c r="E285" s="17"/>
-      <c r="BO285" s="19"/>
-      <c r="BR285" s="19"/>
-    </row>
-    <row r="286" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN285" s="19"/>
+      <c r="BQ285" s="19"/>
+    </row>
+    <row r="286" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D286" s="18"/>
       <c r="E286" s="17"/>
-      <c r="BO286" s="19"/>
-      <c r="BR286" s="19"/>
-    </row>
-    <row r="287" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN286" s="19"/>
+      <c r="BQ286" s="19"/>
+    </row>
+    <row r="287" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D287" s="18"/>
       <c r="E287" s="17"/>
-      <c r="BO287" s="19"/>
-      <c r="BR287" s="19"/>
-    </row>
-    <row r="288" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN287" s="19"/>
+      <c r="BQ287" s="19"/>
+    </row>
+    <row r="288" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D288" s="18"/>
       <c r="E288" s="17"/>
-      <c r="BO288" s="19"/>
-      <c r="BR288" s="19"/>
-    </row>
-    <row r="289" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN288" s="19"/>
+      <c r="BQ288" s="19"/>
+    </row>
+    <row r="289" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D289" s="18"/>
       <c r="E289" s="17"/>
-      <c r="BO289" s="19"/>
-      <c r="BR289" s="19"/>
-    </row>
-    <row r="290" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN289" s="19"/>
+      <c r="BQ289" s="19"/>
+    </row>
+    <row r="290" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D290" s="18"/>
       <c r="E290" s="17"/>
-      <c r="BO290" s="19"/>
-      <c r="BR290" s="19"/>
-    </row>
-    <row r="291" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN290" s="19"/>
+      <c r="BQ290" s="19"/>
+    </row>
+    <row r="291" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D291" s="18"/>
       <c r="E291" s="17"/>
-      <c r="BO291" s="19"/>
-      <c r="BR291" s="19"/>
-    </row>
-    <row r="292" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN291" s="19"/>
+      <c r="BQ291" s="19"/>
+    </row>
+    <row r="292" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D292" s="18"/>
       <c r="E292" s="17"/>
-      <c r="BO292" s="19"/>
-      <c r="BR292" s="19"/>
-    </row>
-    <row r="293" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN292" s="19"/>
+      <c r="BQ292" s="19"/>
+    </row>
+    <row r="293" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D293" s="18"/>
       <c r="E293" s="17"/>
-      <c r="BO293" s="19"/>
-      <c r="BR293" s="19"/>
-    </row>
-    <row r="294" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN293" s="19"/>
+      <c r="BQ293" s="19"/>
+    </row>
+    <row r="294" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D294" s="18"/>
       <c r="E294" s="17"/>
-      <c r="BO294" s="19"/>
-      <c r="BR294" s="19"/>
-    </row>
-    <row r="295" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN294" s="19"/>
+      <c r="BQ294" s="19"/>
+    </row>
+    <row r="295" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D295" s="18"/>
       <c r="E295" s="17"/>
-      <c r="BO295" s="19"/>
-      <c r="BR295" s="19"/>
-    </row>
-    <row r="296" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN295" s="19"/>
+      <c r="BQ295" s="19"/>
+    </row>
+    <row r="296" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D296" s="18"/>
       <c r="E296" s="17"/>
-      <c r="BO296" s="19"/>
-      <c r="BR296" s="19"/>
-    </row>
-    <row r="297" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN296" s="19"/>
+      <c r="BQ296" s="19"/>
+    </row>
+    <row r="297" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D297" s="18"/>
       <c r="E297" s="17"/>
-      <c r="BO297" s="19"/>
-      <c r="BR297" s="19"/>
-    </row>
-    <row r="298" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN297" s="19"/>
+      <c r="BQ297" s="19"/>
+    </row>
+    <row r="298" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D298" s="18"/>
       <c r="E298" s="17"/>
-      <c r="BO298" s="19"/>
-      <c r="BR298" s="19"/>
-    </row>
-    <row r="299" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN298" s="19"/>
+      <c r="BQ298" s="19"/>
+    </row>
+    <row r="299" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D299" s="18"/>
       <c r="E299" s="17"/>
-      <c r="BO299" s="19"/>
-      <c r="BR299" s="19"/>
-    </row>
-    <row r="300" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN299" s="19"/>
+      <c r="BQ299" s="19"/>
+    </row>
+    <row r="300" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D300" s="18"/>
       <c r="E300" s="17"/>
-      <c r="BO300" s="19"/>
-      <c r="BR300" s="19"/>
-    </row>
-    <row r="301" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN300" s="19"/>
+      <c r="BQ300" s="19"/>
+    </row>
+    <row r="301" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D301" s="18"/>
       <c r="E301" s="17"/>
-      <c r="BO301" s="19"/>
-      <c r="BR301" s="19"/>
-    </row>
-    <row r="302" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN301" s="19"/>
+      <c r="BQ301" s="19"/>
+    </row>
+    <row r="302" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D302" s="18"/>
       <c r="E302" s="17"/>
-      <c r="BO302" s="19"/>
-      <c r="BR302" s="19"/>
-    </row>
-    <row r="303" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN302" s="19"/>
+      <c r="BQ302" s="19"/>
+    </row>
+    <row r="303" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D303" s="18"/>
       <c r="E303" s="17"/>
-      <c r="BO303" s="19"/>
-      <c r="BR303" s="19"/>
-    </row>
-    <row r="304" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN303" s="19"/>
+      <c r="BQ303" s="19"/>
+    </row>
+    <row r="304" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D304" s="18"/>
       <c r="E304" s="17"/>
-      <c r="BO304" s="19"/>
-      <c r="BR304" s="19"/>
-    </row>
-    <row r="305" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN304" s="19"/>
+      <c r="BQ304" s="19"/>
+    </row>
+    <row r="305" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D305" s="18"/>
       <c r="E305" s="17"/>
-      <c r="BO305" s="19"/>
-      <c r="BR305" s="19"/>
-    </row>
-    <row r="306" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN305" s="19"/>
+      <c r="BQ305" s="19"/>
+    </row>
+    <row r="306" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D306" s="18"/>
       <c r="E306" s="17"/>
-      <c r="BO306" s="19"/>
-      <c r="BR306" s="19"/>
-    </row>
-    <row r="307" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN306" s="19"/>
+      <c r="BQ306" s="19"/>
+    </row>
+    <row r="307" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D307" s="18"/>
       <c r="E307" s="17"/>
-      <c r="BO307" s="19"/>
-      <c r="BR307" s="19"/>
-    </row>
-    <row r="308" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN307" s="19"/>
+      <c r="BQ307" s="19"/>
+    </row>
+    <row r="308" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D308" s="18"/>
       <c r="E308" s="17"/>
-      <c r="BO308" s="19"/>
-      <c r="BR308" s="19"/>
-    </row>
-    <row r="309" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN308" s="19"/>
+      <c r="BQ308" s="19"/>
+    </row>
+    <row r="309" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D309" s="18"/>
       <c r="E309" s="17"/>
-      <c r="BO309" s="19"/>
-      <c r="BR309" s="19"/>
-    </row>
-    <row r="310" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN309" s="19"/>
+      <c r="BQ309" s="19"/>
+    </row>
+    <row r="310" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D310" s="18"/>
       <c r="E310" s="17"/>
-      <c r="BO310" s="19"/>
-      <c r="BR310" s="19"/>
-    </row>
-    <row r="311" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN310" s="19"/>
+      <c r="BQ310" s="19"/>
+    </row>
+    <row r="311" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D311" s="18"/>
       <c r="E311" s="17"/>
-      <c r="BO311" s="19"/>
-      <c r="BR311" s="19"/>
-    </row>
-    <row r="312" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN311" s="19"/>
+      <c r="BQ311" s="19"/>
+    </row>
+    <row r="312" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D312" s="18"/>
       <c r="E312" s="17"/>
-      <c r="BO312" s="19"/>
-      <c r="BR312" s="19"/>
-    </row>
-    <row r="313" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN312" s="19"/>
+      <c r="BQ312" s="19"/>
+    </row>
+    <row r="313" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D313" s="18"/>
       <c r="E313" s="17"/>
-      <c r="BO313" s="19"/>
-      <c r="BR313" s="19"/>
-    </row>
-    <row r="314" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN313" s="19"/>
+      <c r="BQ313" s="19"/>
+    </row>
+    <row r="314" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D314" s="18"/>
       <c r="E314" s="17"/>
-      <c r="BO314" s="19"/>
-      <c r="BR314" s="19"/>
-    </row>
-    <row r="315" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN314" s="19"/>
+      <c r="BQ314" s="19"/>
+    </row>
+    <row r="315" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D315" s="18"/>
       <c r="E315" s="17"/>
-      <c r="BO315" s="19"/>
-      <c r="BR315" s="19"/>
-    </row>
-    <row r="316" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN315" s="19"/>
+      <c r="BQ315" s="19"/>
+    </row>
+    <row r="316" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D316" s="18"/>
       <c r="E316" s="17"/>
-      <c r="BO316" s="19"/>
-      <c r="BR316" s="19"/>
-    </row>
-    <row r="317" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN316" s="19"/>
+      <c r="BQ316" s="19"/>
+    </row>
+    <row r="317" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D317" s="18"/>
       <c r="E317" s="17"/>
-      <c r="BO317" s="19"/>
-      <c r="BR317" s="19"/>
-    </row>
-    <row r="318" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN317" s="19"/>
+      <c r="BQ317" s="19"/>
+    </row>
+    <row r="318" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D318" s="18"/>
       <c r="E318" s="17"/>
-      <c r="BO318" s="19"/>
-      <c r="BR318" s="19"/>
-    </row>
-    <row r="319" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN318" s="19"/>
+      <c r="BQ318" s="19"/>
+    </row>
+    <row r="319" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D319" s="18"/>
       <c r="E319" s="17"/>
-      <c r="BO319" s="19"/>
-      <c r="BR319" s="19"/>
-    </row>
-    <row r="320" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN319" s="19"/>
+      <c r="BQ319" s="19"/>
+    </row>
+    <row r="320" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D320" s="18"/>
       <c r="E320" s="17"/>
-      <c r="BO320" s="19"/>
-      <c r="BR320" s="19"/>
-    </row>
-    <row r="321" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN320" s="19"/>
+      <c r="BQ320" s="19"/>
+    </row>
+    <row r="321" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D321" s="18"/>
       <c r="E321" s="17"/>
-      <c r="BO321" s="19"/>
-      <c r="BR321" s="19"/>
-    </row>
-    <row r="322" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN321" s="19"/>
+      <c r="BQ321" s="19"/>
+    </row>
+    <row r="322" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D322" s="18"/>
       <c r="E322" s="17"/>
-      <c r="BO322" s="19"/>
-      <c r="BR322" s="19"/>
-    </row>
-    <row r="323" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN322" s="19"/>
+      <c r="BQ322" s="19"/>
+    </row>
+    <row r="323" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D323" s="18"/>
       <c r="E323" s="17"/>
-      <c r="BO323" s="19"/>
-      <c r="BR323" s="19"/>
-    </row>
-    <row r="324" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN323" s="19"/>
+      <c r="BQ323" s="19"/>
+    </row>
+    <row r="324" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D324" s="18"/>
       <c r="E324" s="17"/>
-      <c r="BO324" s="19"/>
-      <c r="BR324" s="19"/>
-    </row>
-    <row r="325" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN324" s="19"/>
+      <c r="BQ324" s="19"/>
+    </row>
+    <row r="325" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D325" s="18"/>
       <c r="E325" s="17"/>
-      <c r="BO325" s="19"/>
-      <c r="BR325" s="19"/>
-    </row>
-    <row r="326" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN325" s="19"/>
+      <c r="BQ325" s="19"/>
+    </row>
+    <row r="326" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D326" s="18"/>
       <c r="E326" s="17"/>
-      <c r="BO326" s="19"/>
-      <c r="BR326" s="19"/>
-    </row>
-    <row r="327" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN326" s="19"/>
+      <c r="BQ326" s="19"/>
+    </row>
+    <row r="327" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D327" s="18"/>
       <c r="E327" s="17"/>
-      <c r="BO327" s="19"/>
-      <c r="BR327" s="19"/>
-    </row>
-    <row r="328" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN327" s="19"/>
+      <c r="BQ327" s="19"/>
+    </row>
+    <row r="328" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D328" s="18"/>
       <c r="E328" s="17"/>
-      <c r="BO328" s="19"/>
-      <c r="BR328" s="19"/>
-    </row>
-    <row r="329" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN328" s="19"/>
+      <c r="BQ328" s="19"/>
+    </row>
+    <row r="329" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D329" s="18"/>
       <c r="E329" s="17"/>
-      <c r="BO329" s="19"/>
-      <c r="BR329" s="19"/>
-    </row>
-    <row r="330" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN329" s="19"/>
+      <c r="BQ329" s="19"/>
+    </row>
+    <row r="330" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D330" s="18"/>
       <c r="E330" s="17"/>
-      <c r="BO330" s="19"/>
-      <c r="BR330" s="19"/>
-    </row>
-    <row r="331" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN330" s="19"/>
+      <c r="BQ330" s="19"/>
+    </row>
+    <row r="331" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D331" s="18"/>
       <c r="E331" s="17"/>
-      <c r="BR331" s="19"/>
-    </row>
-    <row r="332" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ331" s="19"/>
+    </row>
+    <row r="332" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D332" s="18"/>
       <c r="E332" s="17"/>
-      <c r="BR332" s="19"/>
-    </row>
-    <row r="333" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ332" s="19"/>
+    </row>
+    <row r="333" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D333" s="18"/>
       <c r="E333" s="17"/>
-      <c r="BR333" s="19"/>
-    </row>
-    <row r="334" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ333" s="19"/>
+    </row>
+    <row r="334" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D334" s="18"/>
       <c r="E334" s="17"/>
-      <c r="BO334" s="19"/>
-      <c r="BR334" s="19"/>
-    </row>
-    <row r="335" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN334" s="19"/>
+      <c r="BQ334" s="19"/>
+    </row>
+    <row r="335" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D335" s="18"/>
       <c r="E335" s="17"/>
-      <c r="BO335" s="19"/>
-      <c r="BR335" s="19"/>
-    </row>
-    <row r="336" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN335" s="19"/>
+      <c r="BQ335" s="19"/>
+    </row>
+    <row r="336" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D336" s="18"/>
       <c r="E336" s="17"/>
-      <c r="BO336" s="19"/>
-      <c r="BR336" s="19"/>
-    </row>
-    <row r="337" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN336" s="19"/>
+      <c r="BQ336" s="19"/>
+    </row>
+    <row r="337" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D337" s="18"/>
       <c r="E337" s="17"/>
-      <c r="BO337" s="19"/>
-      <c r="BR337" s="19"/>
-    </row>
-    <row r="338" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN337" s="19"/>
+      <c r="BQ337" s="19"/>
+    </row>
+    <row r="338" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D338" s="18"/>
       <c r="E338" s="17"/>
-      <c r="BO338" s="19"/>
-      <c r="BR338" s="19"/>
-    </row>
-    <row r="339" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN338" s="19"/>
+      <c r="BQ338" s="19"/>
+    </row>
+    <row r="339" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D339" s="18"/>
       <c r="E339" s="17"/>
-      <c r="BO339" s="19"/>
-      <c r="BR339" s="19"/>
-    </row>
-    <row r="340" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN339" s="19"/>
+      <c r="BQ339" s="19"/>
+    </row>
+    <row r="340" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D340" s="18"/>
       <c r="E340" s="17"/>
-      <c r="BO340" s="19"/>
-      <c r="BR340" s="19"/>
-    </row>
-    <row r="341" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN340" s="19"/>
+      <c r="BQ340" s="19"/>
+    </row>
+    <row r="341" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D341" s="18"/>
       <c r="E341" s="17"/>
-      <c r="BO341" s="19"/>
-      <c r="BR341" s="19"/>
-    </row>
-    <row r="342" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN341" s="19"/>
+      <c r="BQ341" s="19"/>
+    </row>
+    <row r="342" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D342" s="18"/>
       <c r="E342" s="17"/>
-      <c r="BO342" s="19"/>
-      <c r="BR342" s="19"/>
-    </row>
-    <row r="343" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN342" s="19"/>
+      <c r="BQ342" s="19"/>
+    </row>
+    <row r="343" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D343" s="18"/>
       <c r="E343" s="17"/>
-      <c r="BO343" s="19"/>
-      <c r="BR343" s="19"/>
-    </row>
-    <row r="344" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN343" s="19"/>
+      <c r="BQ343" s="19"/>
+    </row>
+    <row r="344" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D344" s="18"/>
       <c r="E344" s="17"/>
-      <c r="BO344" s="19"/>
-      <c r="BR344" s="19"/>
-    </row>
-    <row r="345" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN344" s="19"/>
+      <c r="BQ344" s="19"/>
+    </row>
+    <row r="345" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D345" s="18"/>
       <c r="E345" s="17"/>
-      <c r="BO345" s="19"/>
-      <c r="BR345" s="19"/>
-    </row>
-    <row r="346" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN345" s="19"/>
+      <c r="BQ345" s="19"/>
+    </row>
+    <row r="346" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D346" s="18"/>
       <c r="E346" s="17"/>
-      <c r="BO346" s="19"/>
-      <c r="BR346" s="19"/>
-    </row>
-    <row r="347" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN346" s="19"/>
+      <c r="BQ346" s="19"/>
+    </row>
+    <row r="347" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D347" s="18"/>
       <c r="E347" s="17"/>
-      <c r="BO347" s="19"/>
-      <c r="BR347" s="19"/>
-    </row>
-    <row r="348" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN347" s="19"/>
+      <c r="BQ347" s="19"/>
+    </row>
+    <row r="348" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D348" s="18"/>
       <c r="E348" s="17"/>
-      <c r="BO348" s="19"/>
-      <c r="BR348" s="19"/>
-    </row>
-    <row r="349" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN348" s="19"/>
+      <c r="BQ348" s="19"/>
+    </row>
+    <row r="349" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D349" s="18"/>
       <c r="E349" s="17"/>
-      <c r="BO349" s="19"/>
-      <c r="BR349" s="19"/>
-    </row>
-    <row r="350" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN349" s="19"/>
+      <c r="BQ349" s="19"/>
+    </row>
+    <row r="350" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D350" s="18"/>
       <c r="E350" s="17"/>
-      <c r="BO350" s="19"/>
-      <c r="BR350" s="19"/>
-    </row>
-    <row r="351" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN350" s="19"/>
+      <c r="BQ350" s="19"/>
+    </row>
+    <row r="351" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D351" s="18"/>
       <c r="E351" s="17"/>
-      <c r="BO351" s="19"/>
-      <c r="BR351" s="19"/>
-    </row>
-    <row r="352" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN351" s="19"/>
+      <c r="BQ351" s="19"/>
+    </row>
+    <row r="352" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D352" s="18"/>
       <c r="E352" s="17"/>
-      <c r="BO352" s="19"/>
-      <c r="BR352" s="19"/>
-    </row>
-    <row r="353" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN352" s="19"/>
+      <c r="BQ352" s="19"/>
+    </row>
+    <row r="353" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D353" s="18"/>
       <c r="E353" s="17"/>
-      <c r="BO353" s="19"/>
-      <c r="BR353" s="19"/>
-    </row>
-    <row r="354" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN353" s="19"/>
+      <c r="BQ353" s="19"/>
+    </row>
+    <row r="354" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D354" s="18"/>
       <c r="E354" s="17"/>
-      <c r="BO354" s="19"/>
-      <c r="BR354" s="19"/>
-    </row>
-    <row r="355" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN354" s="19"/>
+      <c r="BQ354" s="19"/>
+    </row>
+    <row r="355" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D355" s="18"/>
       <c r="E355" s="17"/>
-      <c r="BO355" s="19"/>
-      <c r="BR355" s="19"/>
-    </row>
-    <row r="356" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN355" s="19"/>
+      <c r="BQ355" s="19"/>
+    </row>
+    <row r="356" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D356" s="18"/>
       <c r="E356" s="17"/>
-      <c r="BO356" s="19"/>
-      <c r="BR356" s="19"/>
-    </row>
-    <row r="357" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN356" s="19"/>
+      <c r="BQ356" s="19"/>
+    </row>
+    <row r="357" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D357" s="18"/>
       <c r="E357" s="17"/>
-      <c r="BO357" s="19"/>
-      <c r="BR357" s="19"/>
-    </row>
-    <row r="358" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN357" s="19"/>
+      <c r="BQ357" s="19"/>
+    </row>
+    <row r="358" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D358" s="18"/>
       <c r="E358" s="17"/>
-      <c r="BO358" s="19"/>
-      <c r="BR358" s="19"/>
-    </row>
-    <row r="359" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN358" s="19"/>
+      <c r="BQ358" s="19"/>
+    </row>
+    <row r="359" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D359" s="18"/>
       <c r="E359" s="17"/>
-      <c r="BO359" s="19"/>
-      <c r="BR359" s="19"/>
-    </row>
-    <row r="360" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN359" s="19"/>
+      <c r="BQ359" s="19"/>
+    </row>
+    <row r="360" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D360" s="18"/>
       <c r="E360" s="17"/>
-      <c r="BO360" s="19"/>
-      <c r="BR360" s="19"/>
-    </row>
-    <row r="361" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN360" s="19"/>
+      <c r="BQ360" s="19"/>
+    </row>
+    <row r="361" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D361" s="18"/>
       <c r="E361" s="17"/>
-      <c r="BO361" s="19"/>
-      <c r="BR361" s="19"/>
-    </row>
-    <row r="362" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN361" s="19"/>
+      <c r="BQ361" s="19"/>
+    </row>
+    <row r="362" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D362" s="18"/>
       <c r="E362" s="17"/>
-      <c r="BO362" s="19"/>
-      <c r="BR362" s="19"/>
-    </row>
-    <row r="363" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN362" s="19"/>
+      <c r="BQ362" s="19"/>
+    </row>
+    <row r="363" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D363" s="18"/>
       <c r="E363" s="17"/>
-      <c r="BO363" s="19"/>
-      <c r="BR363" s="19"/>
-    </row>
-    <row r="364" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN363" s="19"/>
+      <c r="BQ363" s="19"/>
+    </row>
+    <row r="364" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D364" s="18"/>
       <c r="E364" s="17"/>
-      <c r="BO364" s="19"/>
-      <c r="BR364" s="19"/>
-    </row>
-    <row r="365" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN364" s="19"/>
+      <c r="BQ364" s="19"/>
+    </row>
+    <row r="365" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D365" s="18"/>
       <c r="E365" s="17"/>
-      <c r="BO365" s="19"/>
-      <c r="BR365" s="19"/>
-    </row>
-    <row r="366" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN365" s="19"/>
+      <c r="BQ365" s="19"/>
+    </row>
+    <row r="366" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D366" s="18"/>
       <c r="E366" s="17"/>
-      <c r="BO366" s="19"/>
-      <c r="BR366" s="19"/>
-    </row>
-    <row r="367" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN366" s="19"/>
+      <c r="BQ366" s="19"/>
+    </row>
+    <row r="367" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D367" s="18"/>
       <c r="E367" s="17"/>
-      <c r="BO367" s="19"/>
-      <c r="BR367" s="19"/>
-    </row>
-    <row r="368" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN367" s="19"/>
+      <c r="BQ367" s="19"/>
+    </row>
+    <row r="368" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D368" s="18"/>
       <c r="E368" s="17"/>
-      <c r="BR368" s="19"/>
-    </row>
-    <row r="369" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ368" s="19"/>
+    </row>
+    <row r="369" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D369" s="18"/>
       <c r="E369" s="17"/>
-      <c r="BR369" s="19"/>
-    </row>
-    <row r="370" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ369" s="19"/>
+    </row>
+    <row r="370" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D370" s="18"/>
       <c r="E370" s="17"/>
-      <c r="BO370" s="19"/>
-      <c r="BR370" s="19"/>
-    </row>
-    <row r="371" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN370" s="19"/>
+      <c r="BQ370" s="19"/>
+    </row>
+    <row r="371" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D371" s="18"/>
       <c r="E371" s="17"/>
-      <c r="BO371" s="19"/>
-      <c r="BR371" s="19"/>
-    </row>
-    <row r="372" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN371" s="19"/>
+      <c r="BQ371" s="19"/>
+    </row>
+    <row r="372" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D372" s="18"/>
       <c r="E372" s="17"/>
-      <c r="BO372" s="19"/>
-      <c r="BR372" s="19"/>
-    </row>
-    <row r="373" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN372" s="19"/>
+      <c r="BQ372" s="19"/>
+    </row>
+    <row r="373" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D373" s="18"/>
       <c r="E373" s="17"/>
-      <c r="BO373" s="19"/>
-      <c r="BR373" s="19"/>
-    </row>
-    <row r="374" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN373" s="19"/>
+      <c r="BQ373" s="19"/>
+    </row>
+    <row r="374" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D374" s="18"/>
       <c r="E374" s="17"/>
-      <c r="BO374" s="19"/>
-      <c r="BR374" s="19"/>
-    </row>
-    <row r="375" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN374" s="19"/>
+      <c r="BQ374" s="19"/>
+    </row>
+    <row r="375" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D375" s="18"/>
       <c r="E375" s="17"/>
-      <c r="BO375" s="19"/>
-      <c r="BR375" s="19"/>
-    </row>
-    <row r="376" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN375" s="19"/>
+      <c r="BQ375" s="19"/>
+    </row>
+    <row r="376" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D376" s="18"/>
       <c r="E376" s="17"/>
-      <c r="BO376" s="19"/>
-      <c r="BR376" s="19"/>
-    </row>
-    <row r="377" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN376" s="19"/>
+      <c r="BQ376" s="19"/>
+    </row>
+    <row r="377" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D377" s="18"/>
       <c r="E377" s="17"/>
-      <c r="BO377" s="19"/>
-      <c r="BR377" s="19"/>
-    </row>
-    <row r="378" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN377" s="19"/>
+      <c r="BQ377" s="19"/>
+    </row>
+    <row r="378" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D378" s="18"/>
       <c r="E378" s="17"/>
-      <c r="BO378" s="19"/>
-      <c r="BR378" s="19"/>
-    </row>
-    <row r="379" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN378" s="19"/>
+      <c r="BQ378" s="19"/>
+    </row>
+    <row r="379" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D379" s="18"/>
       <c r="E379" s="17"/>
-      <c r="BO379" s="19"/>
-      <c r="BR379" s="19"/>
-    </row>
-    <row r="380" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN379" s="19"/>
+      <c r="BQ379" s="19"/>
+    </row>
+    <row r="380" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D380" s="18"/>
       <c r="E380" s="17"/>
-      <c r="BO380" s="19"/>
-      <c r="BR380" s="19"/>
-    </row>
-    <row r="381" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN380" s="19"/>
+      <c r="BQ380" s="19"/>
+    </row>
+    <row r="381" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D381" s="18"/>
       <c r="E381" s="17"/>
-      <c r="BO381" s="19"/>
-      <c r="BR381" s="19"/>
-    </row>
-    <row r="382" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN381" s="19"/>
+      <c r="BQ381" s="19"/>
+    </row>
+    <row r="382" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D382" s="18"/>
       <c r="E382" s="17"/>
-      <c r="BO382" s="19"/>
-      <c r="BR382" s="19"/>
-    </row>
-    <row r="383" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN382" s="19"/>
+      <c r="BQ382" s="19"/>
+    </row>
+    <row r="383" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D383" s="18"/>
       <c r="E383" s="17"/>
-      <c r="BO383" s="19"/>
-      <c r="BR383" s="19"/>
-    </row>
-    <row r="384" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN383" s="19"/>
+      <c r="BQ383" s="19"/>
+    </row>
+    <row r="384" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D384" s="18"/>
       <c r="E384" s="17"/>
-      <c r="BO384" s="19"/>
-      <c r="BR384" s="19"/>
-    </row>
-    <row r="385" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN384" s="19"/>
+      <c r="BQ384" s="19"/>
+    </row>
+    <row r="385" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D385" s="18"/>
       <c r="E385" s="17"/>
-      <c r="BO385" s="19"/>
-      <c r="BR385" s="19"/>
-    </row>
-    <row r="386" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN385" s="19"/>
+      <c r="BQ385" s="19"/>
+    </row>
+    <row r="386" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D386" s="18"/>
       <c r="E386" s="17"/>
-      <c r="BO386" s="19"/>
-      <c r="BR386" s="19"/>
-    </row>
-    <row r="387" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN386" s="19"/>
+      <c r="BQ386" s="19"/>
+    </row>
+    <row r="387" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D387" s="18"/>
       <c r="E387" s="17"/>
-      <c r="BO387" s="19"/>
-      <c r="BR387" s="19"/>
-    </row>
-    <row r="388" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN387" s="19"/>
+      <c r="BQ387" s="19"/>
+    </row>
+    <row r="388" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D388" s="18"/>
       <c r="E388" s="17"/>
-      <c r="BO388" s="19"/>
-      <c r="BR388" s="19"/>
-    </row>
-    <row r="389" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN388" s="19"/>
+      <c r="BQ388" s="19"/>
+    </row>
+    <row r="389" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D389" s="18"/>
       <c r="E389" s="17"/>
-      <c r="BO389" s="19"/>
-      <c r="BR389" s="19"/>
-    </row>
-    <row r="390" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN389" s="19"/>
+      <c r="BQ389" s="19"/>
+    </row>
+    <row r="390" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D390" s="18"/>
       <c r="E390" s="17"/>
-      <c r="BO390" s="19"/>
-      <c r="BR390" s="19"/>
-    </row>
-    <row r="391" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN390" s="19"/>
+      <c r="BQ390" s="19"/>
+    </row>
+    <row r="391" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D391" s="18"/>
       <c r="E391" s="17"/>
-      <c r="BO391" s="19"/>
-      <c r="BR391" s="19"/>
-    </row>
-    <row r="392" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN391" s="19"/>
+      <c r="BQ391" s="19"/>
+    </row>
+    <row r="392" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D392" s="18"/>
       <c r="E392" s="17"/>
-      <c r="BO392" s="19"/>
-      <c r="BR392" s="19"/>
-    </row>
-    <row r="393" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN392" s="19"/>
+      <c r="BQ392" s="19"/>
+    </row>
+    <row r="393" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D393" s="18"/>
       <c r="E393" s="17"/>
-      <c r="BR393" s="19"/>
-    </row>
-    <row r="394" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ393" s="19"/>
+    </row>
+    <row r="394" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D394" s="18"/>
       <c r="E394" s="17"/>
-      <c r="BR394" s="19"/>
-    </row>
-    <row r="395" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ394" s="19"/>
+    </row>
+    <row r="395" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D395" s="18"/>
       <c r="E395" s="17"/>
-      <c r="BO395" s="19"/>
-      <c r="BR395" s="19"/>
-    </row>
-    <row r="396" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN395" s="19"/>
+      <c r="BQ395" s="19"/>
+    </row>
+    <row r="396" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D396" s="18"/>
       <c r="E396" s="17"/>
-      <c r="BO396" s="19"/>
-      <c r="BR396" s="19"/>
-    </row>
-    <row r="397" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN396" s="19"/>
+      <c r="BQ396" s="19"/>
+    </row>
+    <row r="397" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D397" s="18"/>
       <c r="E397" s="17"/>
-      <c r="BR397" s="19"/>
-    </row>
-    <row r="398" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ397" s="19"/>
+    </row>
+    <row r="398" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D398" s="18"/>
       <c r="E398" s="17"/>
-      <c r="BR398" s="19"/>
-    </row>
-    <row r="399" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BQ398" s="19"/>
+    </row>
+    <row r="399" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D399" s="18"/>
       <c r="E399" s="17"/>
-      <c r="BO399" s="19"/>
-      <c r="BR399" s="19"/>
-    </row>
-    <row r="400" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN399" s="19"/>
+      <c r="BQ399" s="19"/>
+    </row>
+    <row r="400" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D400" s="18"/>
       <c r="E400" s="17"/>
-      <c r="BO400" s="19"/>
-      <c r="BR400" s="19"/>
-    </row>
-    <row r="401" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN400" s="19"/>
+      <c r="BQ400" s="19"/>
+    </row>
+    <row r="401" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D401" s="18"/>
       <c r="E401" s="17"/>
-      <c r="BO401" s="19"/>
-      <c r="BR401" s="19"/>
-    </row>
-    <row r="402" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN401" s="19"/>
+      <c r="BQ401" s="19"/>
+    </row>
+    <row r="402" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D402" s="18"/>
       <c r="E402" s="17"/>
-      <c r="BO402" s="19"/>
-      <c r="BR402" s="19"/>
-    </row>
-    <row r="403" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN402" s="19"/>
+      <c r="BQ402" s="19"/>
+    </row>
+    <row r="403" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D403" s="18"/>
       <c r="E403" s="17"/>
-      <c r="BO403" s="19"/>
-      <c r="BR403" s="19"/>
-    </row>
-    <row r="404" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN403" s="19"/>
+      <c r="BQ403" s="19"/>
+    </row>
+    <row r="404" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D404" s="18"/>
       <c r="E404" s="17"/>
-      <c r="BO404" s="19"/>
-      <c r="BR404" s="19"/>
-    </row>
-    <row r="405" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN404" s="19"/>
+      <c r="BQ404" s="19"/>
+    </row>
+    <row r="405" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D405" s="18"/>
       <c r="E405" s="17"/>
-      <c r="BO405" s="19"/>
-      <c r="BR405" s="19"/>
-    </row>
-    <row r="406" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN405" s="19"/>
+      <c r="BQ405" s="19"/>
+    </row>
+    <row r="406" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D406" s="18"/>
       <c r="E406" s="17"/>
-      <c r="BO406" s="19"/>
-      <c r="BR406" s="19"/>
-    </row>
-    <row r="407" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN406" s="19"/>
+      <c r="BQ406" s="19"/>
+    </row>
+    <row r="407" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D407" s="18"/>
       <c r="E407" s="17"/>
-      <c r="BO407" s="19"/>
-      <c r="BR407" s="19"/>
-    </row>
-    <row r="408" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN407" s="19"/>
+      <c r="BQ407" s="19"/>
+    </row>
+    <row r="408" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D408" s="18"/>
       <c r="E408" s="17"/>
-      <c r="BO408" s="19"/>
-      <c r="BR408" s="19"/>
-    </row>
-    <row r="409" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN408" s="19"/>
+      <c r="BQ408" s="19"/>
+    </row>
+    <row r="409" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D409" s="18"/>
       <c r="E409" s="17"/>
-      <c r="BO409" s="19"/>
-      <c r="BR409" s="19"/>
-    </row>
-    <row r="410" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN409" s="19"/>
+      <c r="BQ409" s="19"/>
+    </row>
+    <row r="410" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D410" s="18"/>
       <c r="E410" s="17"/>
-      <c r="BO410" s="19"/>
-      <c r="BR410" s="19"/>
-    </row>
-    <row r="411" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN410" s="19"/>
+      <c r="BQ410" s="19"/>
+    </row>
+    <row r="411" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D411" s="18"/>
       <c r="E411" s="17"/>
-      <c r="BO411" s="19"/>
-      <c r="BR411" s="19"/>
-    </row>
-    <row r="412" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN411" s="19"/>
+      <c r="BQ411" s="19"/>
+    </row>
+    <row r="412" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D412" s="18"/>
       <c r="E412" s="17"/>
-      <c r="BO412" s="19"/>
-      <c r="BR412" s="19"/>
-    </row>
-    <row r="413" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN412" s="19"/>
+      <c r="BQ412" s="19"/>
+    </row>
+    <row r="413" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D413" s="18"/>
       <c r="E413" s="17"/>
-      <c r="BO413" s="19"/>
-      <c r="BR413" s="19"/>
-    </row>
-    <row r="414" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN413" s="19"/>
+      <c r="BQ413" s="19"/>
+    </row>
+    <row r="414" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D414" s="18"/>
       <c r="E414" s="17"/>
-      <c r="BO414" s="19"/>
-      <c r="BR414" s="19"/>
-    </row>
-    <row r="415" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN414" s="19"/>
+      <c r="BQ414" s="19"/>
+    </row>
+    <row r="415" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D415" s="18"/>
       <c r="E415" s="17"/>
-      <c r="BO415" s="19"/>
-      <c r="BR415" s="19"/>
-    </row>
-    <row r="416" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="BN415" s="19"/>
+      <c r="BQ415" s="19"/>
+    </row>
+    <row r="416" spans="4:69" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D416" s="18"/>
       <c r="E416" s="17"/>
     </row>
@@ -6606,334 +6589,334 @@
   <sheetData>
     <row r="1" spans="1:113" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G1" t="s">
         <v>160</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>161</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>162</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>163</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M1" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="J1" t="s">
+      <c r="N1" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="U1" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="V1" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="W1" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="X1" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="Y1" t="s">
         <v>177</v>
       </c>
-      <c r="U1" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="V1" s="6" t="s">
+      <c r="Z1" t="s">
         <v>178</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="AA1" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="AB1" t="s">
         <v>180</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AC1" t="s">
         <v>181</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AD1" t="s">
         <v>182</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AE1" t="s">
         <v>183</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AF1" t="s">
         <v>184</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AG1" t="s">
         <v>185</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AH1" t="s">
         <v>186</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AI1" t="s">
         <v>187</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AJ1" t="s">
         <v>188</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AK1" t="s">
         <v>189</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AL1" t="s">
         <v>190</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AM1" t="s">
         <v>191</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AN1" t="s">
         <v>192</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AO1" t="s">
         <v>193</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AP1" t="s">
         <v>194</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AQ1" t="s">
         <v>195</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AR1" s="23" t="s">
+        <v>572</v>
+      </c>
+      <c r="AS1" s="23" t="s">
+        <v>573</v>
+      </c>
+      <c r="AT1" t="s">
         <v>196</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AU1" t="s">
         <v>197</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AV1" t="s">
         <v>198</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AW1" t="s">
         <v>199</v>
       </c>
-      <c r="AR1" s="23" t="s">
-        <v>576</v>
-      </c>
-      <c r="AS1" s="23" t="s">
-        <v>577</v>
-      </c>
-      <c r="AT1" t="s">
+      <c r="AX1" t="s">
         <v>200</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AY1" t="s">
         <v>201</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AZ1" t="s">
         <v>202</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="BA1" t="s">
         <v>203</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="BB1" t="s">
         <v>204</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BC1" t="s">
         <v>205</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BD1" t="s">
         <v>206</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BE1" t="s">
         <v>207</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BF1" t="s">
         <v>208</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BG1" t="s">
         <v>209</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BH1" t="s">
         <v>210</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BJ1" t="s">
+        <v>210</v>
+      </c>
+      <c r="BK1" t="s">
         <v>211</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BL1" t="s">
         <v>212</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BM1" t="s">
         <v>213</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BN1" t="s">
         <v>214</v>
       </c>
-      <c r="BJ1" t="s">
-        <v>214</v>
-      </c>
-      <c r="BK1" t="s">
+      <c r="BO1" t="s">
         <v>215</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BP1" t="s">
         <v>216</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BQ1" t="s">
         <v>217</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BR1" t="s">
         <v>218</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BS1" t="s">
         <v>219</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BT1" t="s">
         <v>220</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BU1" t="s">
         <v>221</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BV1" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BW1" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BX1" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BY1" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="BV1" s="7" t="s">
+      <c r="BZ1" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="BW1" s="7" t="s">
+      <c r="CA1" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="BX1" s="7" t="s">
+      <c r="CB1" t="s">
         <v>228</v>
       </c>
-      <c r="BY1" s="7" t="s">
+      <c r="CC1" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="BZ1" s="7" t="s">
+      <c r="CD1" t="s">
         <v>230</v>
       </c>
-      <c r="CA1" s="7" t="s">
+      <c r="CE1" t="s">
         <v>231</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CF1" t="s">
         <v>232</v>
       </c>
-      <c r="CC1" s="7" t="s">
+      <c r="CG1" t="s">
         <v>233</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CH1" t="s">
         <v>234</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CI1" t="s">
         <v>235</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CJ1" t="s">
         <v>236</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CK1" t="s">
         <v>237</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CL1" t="s">
         <v>238</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CM1" t="s">
         <v>239</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="CN1" t="s">
         <v>240</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CO1" t="s">
         <v>241</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="CP1" t="s">
         <v>242</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CQ1" t="s">
         <v>243</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CR1" t="s">
+        <v>220</v>
+      </c>
+      <c r="CS1" t="s">
         <v>244</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CT1" t="s">
         <v>245</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CU1" t="s">
         <v>246</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CV1" t="s">
         <v>247</v>
       </c>
-      <c r="CR1" t="s">
-        <v>224</v>
-      </c>
-      <c r="CS1" t="s">
+      <c r="CW1" t="s">
         <v>248</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CX1" t="s">
         <v>249</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CY1" t="s">
         <v>250</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CZ1" t="s">
+        <v>249</v>
+      </c>
+      <c r="DA1" t="s">
         <v>251</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="DB1" t="s">
         <v>252</v>
       </c>
-      <c r="CX1" t="s">
+      <c r="DC1" t="s">
         <v>253</v>
       </c>
-      <c r="CY1" t="s">
+      <c r="DD1" t="s">
         <v>254</v>
       </c>
-      <c r="CZ1" t="s">
-        <v>253</v>
-      </c>
-      <c r="DA1" t="s">
+      <c r="DE1" t="s">
         <v>255</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="DF1" t="s">
         <v>256</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="DG1" t="s">
         <v>257</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DH1" t="s">
         <v>258</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="DI1" t="s">
         <v>259</v>
-      </c>
-      <c r="DF1" t="s">
-        <v>260</v>
-      </c>
-      <c r="DG1" t="s">
-        <v>261</v>
-      </c>
-      <c r="DH1" t="s">
-        <v>262</v>
-      </c>
-      <c r="DI1" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="2" spans="1:113" x14ac:dyDescent="0.25">
@@ -6941,337 +6924,337 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" t="s">
+        <v>260</v>
+      </c>
+      <c r="F2" t="s">
+        <v>261</v>
+      </c>
+      <c r="G2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" t="s">
+        <v>262</v>
+      </c>
+      <c r="I2" t="s">
+        <v>263</v>
+      </c>
+      <c r="J2" t="s">
+        <v>264</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="U2" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="V2" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="W2" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="X2" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>279</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>280</v>
+      </c>
+      <c r="AA2" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>282</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>283</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>284</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>285</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>286</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>287</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>288</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>289</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>290</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>291</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>292</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>293</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>294</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>295</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>296</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>297</v>
+      </c>
+      <c r="AR2" s="23" t="s">
+        <v>574</v>
+      </c>
+      <c r="AS2" s="23" t="s">
+        <v>575</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>298</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>299</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>300</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>301</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>302</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>303</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>304</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>305</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>306</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>307</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>308</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>309</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>310</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>311</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>312</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>313</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>314</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>315</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>316</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>317</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>318</v>
+      </c>
+      <c r="BO2" t="s">
         <v>77</v>
       </c>
-      <c r="E2" t="s">
-        <v>264</v>
-      </c>
-      <c r="F2" t="s">
-        <v>265</v>
-      </c>
-      <c r="G2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H2" t="s">
-        <v>266</v>
-      </c>
-      <c r="I2" t="s">
-        <v>267</v>
-      </c>
-      <c r="J2" t="s">
-        <v>268</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="O2" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="P2" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="Q2" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="R2" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="S2" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="T2" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="U2" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="V2" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="W2" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="X2" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>283</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>284</v>
-      </c>
-      <c r="AA2" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>286</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>287</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>288</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>289</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>290</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>291</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>292</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>293</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>294</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>295</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>296</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>297</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>298</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>299</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>300</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>301</v>
-      </c>
-      <c r="AR2" s="23" t="s">
-        <v>578</v>
-      </c>
-      <c r="AS2" s="23" t="s">
-        <v>579</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>302</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>303</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>304</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>305</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>306</v>
-      </c>
-      <c r="AY2" t="s">
-        <v>307</v>
-      </c>
-      <c r="AZ2" t="s">
-        <v>308</v>
-      </c>
-      <c r="BA2" t="s">
-        <v>309</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>310</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>311</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>312</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>313</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>314</v>
-      </c>
-      <c r="BG2" t="s">
-        <v>315</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>316</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>317</v>
-      </c>
-      <c r="BJ2" t="s">
-        <v>318</v>
-      </c>
-      <c r="BK2" t="s">
+      <c r="BP2" t="s">
         <v>319</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BQ2" t="s">
         <v>320</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BR2" t="s">
         <v>321</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BS2" t="s">
         <v>322</v>
       </c>
-      <c r="BO2" t="s">
-        <v>79</v>
-      </c>
-      <c r="BP2" t="s">
+      <c r="BT2" t="s">
         <v>323</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BU2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV2" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BW2" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="BS2" t="s">
+      <c r="BX2" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="BT2" t="s">
+      <c r="BY2" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="BU2" t="s">
-        <v>95</v>
-      </c>
-      <c r="BV2" s="7" t="s">
+      <c r="BZ2" s="7" t="s">
         <v>328</v>
       </c>
-      <c r="BW2" s="7" t="s">
+      <c r="CA2" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="BX2" s="7" t="s">
+      <c r="CB2" t="s">
         <v>330</v>
       </c>
-      <c r="BY2" s="7" t="s">
+      <c r="CC2" t="s">
         <v>331</v>
       </c>
-      <c r="BZ2" s="7" t="s">
+      <c r="CD2" t="s">
         <v>332</v>
       </c>
-      <c r="CA2" s="7" t="s">
+      <c r="CE2" t="s">
         <v>333</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="CF2" t="s">
         <v>334</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="CG2" t="s">
         <v>335</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="CH2" t="s">
         <v>336</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="CI2" t="s">
         <v>337</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CJ2" t="s">
         <v>338</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="CK2" t="s">
         <v>339</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="CL2" t="s">
         <v>340</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="CM2" t="s">
         <v>341</v>
       </c>
-      <c r="CJ2" t="s">
+      <c r="CN2" t="s">
         <v>342</v>
       </c>
-      <c r="CK2" t="s">
+      <c r="CO2" t="s">
         <v>343</v>
       </c>
-      <c r="CL2" t="s">
+      <c r="CP2" t="s">
         <v>344</v>
       </c>
-      <c r="CM2" t="s">
+      <c r="CQ2" t="s">
         <v>345</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="CR2" t="s">
         <v>346</v>
       </c>
-      <c r="CO2" t="s">
+      <c r="CS2" t="s">
         <v>347</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="CT2" t="s">
         <v>348</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="CU2" t="s">
         <v>349</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="CV2" t="s">
         <v>350</v>
       </c>
-      <c r="CS2" t="s">
+      <c r="CW2" t="s">
         <v>351</v>
       </c>
-      <c r="CT2" t="s">
+      <c r="CX2" t="s">
         <v>352</v>
       </c>
-      <c r="CU2" t="s">
+      <c r="CY2" t="s">
         <v>353</v>
       </c>
-      <c r="CV2" t="s">
+      <c r="CZ2" t="s">
         <v>354</v>
       </c>
-      <c r="CW2" t="s">
+      <c r="DA2" t="s">
         <v>355</v>
       </c>
-      <c r="CX2" t="s">
+      <c r="DB2" t="s">
         <v>356</v>
       </c>
-      <c r="CY2" t="s">
+      <c r="DC2" t="s">
         <v>357</v>
       </c>
-      <c r="CZ2" t="s">
+      <c r="DD2" t="s">
         <v>358</v>
       </c>
-      <c r="DA2" t="s">
+      <c r="DE2" t="s">
         <v>359</v>
       </c>
-      <c r="DB2" t="s">
+      <c r="DF2" t="s">
         <v>360</v>
       </c>
-      <c r="DC2" t="s">
+      <c r="DG2" t="s">
         <v>361</v>
       </c>
-      <c r="DD2" t="s">
+      <c r="DH2" t="s">
         <v>362</v>
       </c>
-      <c r="DE2" t="s">
+      <c r="DI2" t="s">
         <v>363</v>
-      </c>
-      <c r="DF2" t="s">
-        <v>364</v>
-      </c>
-      <c r="DG2" t="s">
-        <v>365</v>
-      </c>
-      <c r="DH2" t="s">
-        <v>366</v>
-      </c>
-      <c r="DI2" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="3" spans="1:113" x14ac:dyDescent="0.25">
@@ -7291,330 +7274,330 @@
         <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H3" t="s">
         <v>2</v>
       </c>
       <c r="I3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J3" t="s">
+        <v>364</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O3" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="J3" t="s">
-        <v>368</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="M3" s="6" t="s">
+      <c r="P3" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="T3" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="U3" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="V3" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="W3" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="X3" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA3" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>367</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AI3" t="s">
         <v>118</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="P3" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q3" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="S3" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="T3" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="U3" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="V3" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="W3" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="X3" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>116</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AA3" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>371</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>122</v>
       </c>
       <c r="AJ3" t="s">
         <v>3</v>
       </c>
       <c r="AK3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AL3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AM3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AN3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="AO3" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="AP3" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="AQ3" t="s">
         <v>2</v>
       </c>
       <c r="AR3" s="23" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="AS3" s="23" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="AT3" t="s">
+        <v>370</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>371</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>370</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BN3" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO3" t="s">
+        <v>115</v>
+      </c>
+      <c r="BP3" t="s">
+        <v>115</v>
+      </c>
+      <c r="BQ3" t="s">
+        <v>372</v>
+      </c>
+      <c r="BR3" t="s">
+        <v>373</v>
+      </c>
+      <c r="BS3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>112</v>
+      </c>
+      <c r="BV3" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="BW3" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="BX3" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="BY3" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="AU3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>117</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX3" t="s">
+      <c r="BZ3" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="CA3" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>120</v>
+      </c>
+      <c r="CC3" t="s">
         <v>375</v>
       </c>
-      <c r="AY3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>374</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BO3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BQ3" t="s">
+      <c r="CD3" t="s">
+        <v>120</v>
+      </c>
+      <c r="CE3" t="s">
+        <v>120</v>
+      </c>
+      <c r="CF3" t="s">
+        <v>120</v>
+      </c>
+      <c r="CG3" t="s">
         <v>376</v>
       </c>
-      <c r="BR3" t="s">
+      <c r="CH3" t="s">
         <v>377</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BT3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BU3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BV3" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="BW3" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="BX3" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="BY3" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="BZ3" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="CA3" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="CB3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CC3" t="s">
-        <v>379</v>
-      </c>
-      <c r="CD3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CE3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CF3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CG3" t="s">
-        <v>380</v>
-      </c>
-      <c r="CH3" t="s">
-        <v>381</v>
       </c>
       <c r="CI3" t="s">
         <v>2</v>
       </c>
       <c r="CJ3" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="CK3" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="CL3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="CM3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="CN3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="CO3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="CP3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="CQ3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="CR3" t="s">
+        <v>375</v>
+      </c>
+      <c r="CS3" t="s">
+        <v>119</v>
+      </c>
+      <c r="CT3" t="s">
+        <v>112</v>
+      </c>
+      <c r="CU3" t="s">
+        <v>121</v>
+      </c>
+      <c r="CV3" t="s">
         <v>379</v>
       </c>
-      <c r="CS3" t="s">
-        <v>123</v>
-      </c>
-      <c r="CT3" t="s">
-        <v>116</v>
-      </c>
-      <c r="CU3" t="s">
-        <v>125</v>
-      </c>
-      <c r="CV3" t="s">
-        <v>383</v>
-      </c>
       <c r="CW3" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="CX3" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="CY3" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="CZ3" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="DA3" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="DB3" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="DC3" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="DD3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="DE3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="DF3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="DG3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="DH3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="DI3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:113" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
     </row>
     <row r="5" spans="1:113" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -7643,7 +7626,7 @@
     </row>
     <row r="6" spans="1:113" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="K6" s="8"/>
       <c r="L6" s="8"/>
@@ -7694,10 +7677,10 @@
     </row>
     <row r="8" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C8" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="R8"/>
       <c r="AC8">
@@ -7707,41 +7690,41 @@
         <v>1</v>
       </c>
       <c r="AO8" t="s">
+        <v>384</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>385</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>386</v>
+      </c>
+      <c r="AZ8">
+        <v>1</v>
+      </c>
+      <c r="BD8">
+        <v>1</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>387</v>
+      </c>
+      <c r="CD8" t="s">
         <v>388</v>
       </c>
-      <c r="AT8" t="s">
+      <c r="CG8" t="s">
         <v>389</v>
       </c>
-      <c r="AX8" t="s">
+      <c r="CH8" t="s">
         <v>390</v>
       </c>
-      <c r="AZ8">
-        <v>1</v>
-      </c>
-      <c r="BD8">
-        <v>1</v>
-      </c>
-      <c r="CB8" t="s">
+      <c r="CI8" t="s">
         <v>391</v>
       </c>
-      <c r="CD8" t="s">
+      <c r="CJ8" t="s">
         <v>392</v>
-      </c>
-      <c r="CG8" t="s">
-        <v>393</v>
-      </c>
-      <c r="CH8" t="s">
-        <v>394</v>
-      </c>
-      <c r="CI8" t="s">
-        <v>395</v>
-      </c>
-      <c r="CJ8" t="s">
-        <v>396</v>
       </c>
       <c r="CN8" s="13"/>
       <c r="CY8" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9" spans="1:113" x14ac:dyDescent="0.25">
@@ -7750,28 +7733,28 @@
     </row>
     <row r="10" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>394</v>
+      </c>
+      <c r="C10" t="s">
+        <v>395</v>
+      </c>
+      <c r="D10" t="s">
+        <v>396</v>
+      </c>
+      <c r="E10" t="s">
+        <v>397</v>
+      </c>
+      <c r="F10" t="s">
         <v>398</v>
-      </c>
-      <c r="C10" t="s">
-        <v>399</v>
-      </c>
-      <c r="D10" t="s">
-        <v>400</v>
-      </c>
-      <c r="E10" t="s">
-        <v>401</v>
-      </c>
-      <c r="F10" t="s">
-        <v>402</v>
       </c>
       <c r="G10">
         <v>3</v>
       </c>
       <c r="J10" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="M10"/>
       <c r="N10"/>
@@ -7784,13 +7767,13 @@
         <v>1</v>
       </c>
       <c r="AG10" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BD10">
         <v>1</v>
       </c>
       <c r="BO10" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="BV10" s="7">
         <v>0</v>
@@ -7802,27 +7785,27 @@
         <v>1</v>
       </c>
       <c r="BY10" s="7" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="CU10" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
     </row>
     <row r="11" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="C11" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="I11">
         <v>1</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="M11"/>
       <c r="N11"/>
@@ -7844,7 +7827,7 @@
         <v>1</v>
       </c>
       <c r="AG11" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BD11">
         <v>1</v>
@@ -7856,7 +7839,7 @@
       <c r="BZ11" s="11"/>
       <c r="CA11" s="11"/>
       <c r="CU11" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="DD11">
         <v>1</v>
@@ -7873,19 +7856,19 @@
     </row>
     <row r="12" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C12" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="I12">
         <v>1</v>
       </c>
       <c r="K12" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="L12" s="9" t="s">
         <v>409</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>413</v>
       </c>
       <c r="M12"/>
       <c r="N12"/>
@@ -7915,10 +7898,10 @@
       <c r="BZ12" s="11"/>
       <c r="CA12" s="11"/>
       <c r="CG12" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="CN12" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="CO12">
         <v>-0.8</v>
@@ -7927,7 +7910,7 @@
         <v>10</v>
       </c>
       <c r="CX12" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="DH12">
         <v>1</v>
@@ -7935,19 +7918,19 @@
     </row>
     <row r="13" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="C13" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="I13">
         <v>1</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="M13"/>
       <c r="N13"/>
@@ -7977,10 +7960,10 @@
       <c r="BZ13" s="11"/>
       <c r="CA13" s="11"/>
       <c r="CG13" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="CN13" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="CO13">
         <v>-0.8</v>
@@ -7989,7 +7972,7 @@
         <v>10</v>
       </c>
       <c r="CX13" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="DH13">
         <v>1</v>
@@ -8001,28 +7984,28 @@
     </row>
     <row r="15" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="C15" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="D15" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="E15" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="F15" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="G15">
         <v>3</v>
       </c>
       <c r="J15" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="M15"/>
       <c r="N15"/>
@@ -8035,16 +8018,16 @@
         <v>1</v>
       </c>
       <c r="AG15" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BD15">
         <v>1</v>
       </c>
       <c r="BO15" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="BP15" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="BT15">
         <v>20</v>
@@ -8059,12 +8042,12 @@
         <v>1</v>
       </c>
       <c r="BY15" s="7" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="BZ15"/>
       <c r="CB15" s="7"/>
       <c r="CN15" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="CO15">
         <v>3</v>
@@ -8075,19 +8058,19 @@
     </row>
     <row r="16" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C16" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="I16">
         <v>1</v>
       </c>
       <c r="K16" s="9" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="M16"/>
       <c r="N16"/>
@@ -8109,7 +8092,7 @@
         <v>1</v>
       </c>
       <c r="AG16" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BD16">
         <v>1</v>
@@ -8122,7 +8105,7 @@
       <c r="CA16" s="11"/>
       <c r="CB16" s="11"/>
       <c r="CU16" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="DD16">
         <v>1</v>
@@ -8139,15 +8122,15 @@
     </row>
     <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="C17" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="M17"/>
       <c r="N17"/>
       <c r="O17" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="Y17" s="6"/>
       <c r="Z17" s="6"/>
@@ -8160,13 +8143,13 @@
         <v>1</v>
       </c>
       <c r="AO17" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="AT17" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="AX17" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="AZ17">
         <v>1</v>
@@ -8185,36 +8168,36 @@
       </c>
       <c r="BZ17"/>
       <c r="CB17" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="CG17" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="CH17" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="CI17" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="CJ17" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="CY17" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="C18" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="I18">
         <v>1</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="M18"/>
       <c r="N18"/>
@@ -8227,7 +8210,7 @@
         <v>1</v>
       </c>
       <c r="AG18" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BD18">
         <v>1</v>
@@ -8237,10 +8220,10 @@
       </c>
       <c r="BZ18"/>
       <c r="CB18" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="CG18" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="DD18">
         <v>1</v>
@@ -8257,19 +8240,19 @@
     </row>
     <row r="19" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="C19" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="I19">
         <v>1</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="M19"/>
       <c r="N19"/>
@@ -8282,7 +8265,7 @@
         <v>1</v>
       </c>
       <c r="AG19" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BD19">
         <v>1</v>
@@ -8292,10 +8275,10 @@
       </c>
       <c r="BZ19"/>
       <c r="CB19" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="CG19" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="DD19">
         <v>1</v>
@@ -8312,19 +8295,19 @@
     </row>
     <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C20" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="I20">
         <v>1</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="M20"/>
       <c r="N20"/>
@@ -8346,7 +8329,7 @@
         <v>1</v>
       </c>
       <c r="AG20" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BD20">
         <v>1</v>
@@ -8359,7 +8342,7 @@
       <c r="CA20" s="11"/>
       <c r="CB20" s="11"/>
       <c r="CU20" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="DD20">
         <v>1</v>
@@ -8376,19 +8359,19 @@
     </row>
     <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="C21" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="I21">
         <v>1</v>
       </c>
       <c r="K21" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="L21" s="9" t="s">
         <v>409</v>
-      </c>
-      <c r="L21" s="9" t="s">
-        <v>413</v>
       </c>
       <c r="M21"/>
       <c r="N21"/>
@@ -8418,16 +8401,16 @@
       <c r="BZ21" s="11"/>
       <c r="CA21" s="11"/>
       <c r="CG21" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="CN21" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="CR21">
         <v>5</v>
       </c>
       <c r="CX21" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="DH21">
         <v>1</v>
@@ -8435,19 +8418,19 @@
     </row>
     <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="C22" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="I22">
         <v>1</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="M22"/>
       <c r="N22"/>
@@ -8477,16 +8460,16 @@
       <c r="BZ22" s="11"/>
       <c r="CA22" s="11"/>
       <c r="CG22" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="CN22" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="CR22">
         <v>5</v>
       </c>
       <c r="CX22" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="DH22">
         <v>1</v>
@@ -8531,28 +8514,28 @@
     </row>
     <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="C24" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="D24" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="E24" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="F24" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="G24">
         <v>3</v>
       </c>
       <c r="J24" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="M24"/>
       <c r="N24"/>
@@ -8561,16 +8544,16 @@
         <v>1</v>
       </c>
       <c r="AG24" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BD24">
         <v>1</v>
       </c>
       <c r="BO24" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="BP24" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="BT24">
         <v>40</v>
@@ -8588,16 +8571,16 @@
         <v>1</v>
       </c>
       <c r="BY24" s="7" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="CA24" s="21" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="CN24" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="CO24" s="20" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="CR24">
         <v>99999</v>
@@ -8608,19 +8591,19 @@
     </row>
     <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="C25" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="I25">
         <v>1</v>
       </c>
       <c r="K25" s="9" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="L25" s="9" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="M25"/>
       <c r="N25"/>
@@ -8638,7 +8621,7 @@
         <v>1</v>
       </c>
       <c r="AG25" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BD25">
         <v>1</v>
@@ -8650,7 +8633,7 @@
       <c r="BZ25" s="11"/>
       <c r="CA25" s="11"/>
       <c r="CU25" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="DD25">
         <v>1</v>
@@ -8664,18 +8647,18 @@
     </row>
     <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="C26" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="M26"/>
       <c r="N26"/>
       <c r="O26" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="R26" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="AC26">
         <v>2</v>
@@ -8684,59 +8667,59 @@
         <v>1</v>
       </c>
       <c r="AO26" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="AT26" t="s">
+        <v>385</v>
+      </c>
+      <c r="AX26" t="s">
+        <v>386</v>
+      </c>
+      <c r="AZ26">
+        <v>1</v>
+      </c>
+      <c r="BD26">
+        <v>1</v>
+      </c>
+      <c r="CA26" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="CB26" t="s">
+        <v>453</v>
+      </c>
+      <c r="CD26" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="CG26" t="s">
         <v>389</v>
       </c>
-      <c r="AX26" t="s">
+      <c r="CH26" t="s">
         <v>390</v>
       </c>
-      <c r="AZ26">
-        <v>1</v>
-      </c>
-      <c r="BD26">
-        <v>1</v>
-      </c>
-      <c r="CA26" s="7" t="s">
-        <v>425</v>
-      </c>
-      <c r="CB26" t="s">
-        <v>457</v>
-      </c>
-      <c r="CD26" s="12" t="s">
-        <v>458</v>
-      </c>
-      <c r="CG26" t="s">
+      <c r="CI26" t="s">
+        <v>391</v>
+      </c>
+      <c r="CJ26" t="s">
+        <v>455</v>
+      </c>
+      <c r="CY26" t="s">
         <v>393</v>
-      </c>
-      <c r="CH26" t="s">
-        <v>394</v>
-      </c>
-      <c r="CI26" t="s">
-        <v>395</v>
-      </c>
-      <c r="CJ26" t="s">
-        <v>459</v>
-      </c>
-      <c r="CY26" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="C27" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="M27"/>
       <c r="N27"/>
       <c r="O27" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="Q27" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="AC27">
         <v>2</v>
@@ -8745,57 +8728,57 @@
         <v>1</v>
       </c>
       <c r="AO27" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="AT27" t="s">
+        <v>385</v>
+      </c>
+      <c r="AX27" t="s">
+        <v>386</v>
+      </c>
+      <c r="AZ27">
+        <v>1</v>
+      </c>
+      <c r="BD27">
+        <v>1</v>
+      </c>
+      <c r="CA27" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="CB27" t="s">
+        <v>453</v>
+      </c>
+      <c r="CD27" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="CG27" t="s">
         <v>389</v>
       </c>
-      <c r="AX27" t="s">
+      <c r="CH27" t="s">
         <v>390</v>
       </c>
-      <c r="AZ27">
-        <v>1</v>
-      </c>
-      <c r="BD27">
-        <v>1</v>
-      </c>
-      <c r="CA27" s="7" t="s">
-        <v>425</v>
-      </c>
-      <c r="CB27" t="s">
+      <c r="CI27" t="s">
+        <v>391</v>
+      </c>
+      <c r="CJ27" t="s">
         <v>457</v>
       </c>
-      <c r="CD27" s="12" t="s">
-        <v>458</v>
-      </c>
-      <c r="CG27" t="s">
+      <c r="CY27" t="s">
         <v>393</v>
-      </c>
-      <c r="CH27" t="s">
-        <v>394</v>
-      </c>
-      <c r="CI27" t="s">
-        <v>395</v>
-      </c>
-      <c r="CJ27" t="s">
-        <v>461</v>
-      </c>
-      <c r="CY27" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="C28" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="I28">
         <v>1</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="M28"/>
       <c r="N28"/>
@@ -8804,7 +8787,7 @@
         <v>1</v>
       </c>
       <c r="AG28" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BD28">
         <v>1</v>
@@ -8813,10 +8796,10 @@
         <v>0.5</v>
       </c>
       <c r="CB28" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="CG28" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="DD28">
         <v>1</v>
@@ -8830,19 +8813,19 @@
     </row>
     <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="C29" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="I29">
         <v>1</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="M29"/>
       <c r="N29"/>
@@ -8851,7 +8834,7 @@
         <v>1</v>
       </c>
       <c r="AG29" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BD29">
         <v>1</v>
@@ -8860,10 +8843,10 @@
         <v>0.5</v>
       </c>
       <c r="CB29" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="CG29" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="DD29">
         <v>1</v>
@@ -8877,19 +8860,19 @@
     </row>
     <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="C30" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="I30">
         <v>1</v>
       </c>
       <c r="K30" s="9" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="M30"/>
       <c r="N30"/>
@@ -8907,7 +8890,7 @@
         <v>1</v>
       </c>
       <c r="AG30" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BD30">
         <v>1</v>
@@ -8919,7 +8902,7 @@
       <c r="BZ30" s="11"/>
       <c r="CA30" s="11"/>
       <c r="CU30" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="DD30">
         <v>1</v>
@@ -8933,19 +8916,19 @@
     </row>
     <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="C31" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="I31">
         <v>1</v>
       </c>
       <c r="K31" s="9" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="L31" s="9" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="M31"/>
       <c r="N31" s="9">
@@ -8964,13 +8947,13 @@
         <v>1</v>
       </c>
       <c r="AG31" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BD31">
         <v>1</v>
       </c>
       <c r="BO31" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="BV31"/>
       <c r="BW31" s="11"/>
@@ -8980,7 +8963,7 @@
       <c r="CA31" s="11"/>
       <c r="CB31" s="11"/>
       <c r="CN31" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="CR31">
         <v>99999</v>
@@ -8997,10 +8980,10 @@
     </row>
     <row r="32" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="C32" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="I32">
         <v>1</v>
@@ -9024,10 +9007,10 @@
         <v>1</v>
       </c>
       <c r="AG32" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="AT32" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="BD32">
         <v>1</v>
@@ -9054,19 +9037,19 @@
     </row>
     <row r="33" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="C33" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="I33">
         <v>1</v>
       </c>
       <c r="K33" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="L33" s="9" t="s">
         <v>409</v>
-      </c>
-      <c r="L33" s="9" t="s">
-        <v>413</v>
       </c>
       <c r="M33"/>
       <c r="N33"/>
@@ -9096,10 +9079,10 @@
       <c r="BZ33" s="11"/>
       <c r="CA33" s="11"/>
       <c r="CG33" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="CN33" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="CO33">
         <v>-0.8</v>
@@ -9111,7 +9094,7 @@
         <v>7</v>
       </c>
       <c r="CX33" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="DH33">
         <v>1</v>
@@ -9119,19 +9102,19 @@
     </row>
     <row r="34" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="C34" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="I34">
         <v>1</v>
       </c>
       <c r="K34" s="9" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="L34" s="9" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="M34"/>
       <c r="N34"/>
@@ -9161,10 +9144,10 @@
       <c r="BZ34" s="11"/>
       <c r="CA34" s="11"/>
       <c r="CG34" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="CN34" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="CO34">
         <v>-0.8</v>
@@ -9176,7 +9159,7 @@
         <v>7</v>
       </c>
       <c r="CX34" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="DH34">
         <v>1</v>
@@ -9184,22 +9167,22 @@
     </row>
     <row r="37" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C37" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="D37" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="E37" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="F37" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="K37" s="9" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="L37" s="9"/>
       <c r="M37"/>
@@ -9222,7 +9205,7 @@
         <v>2</v>
       </c>
       <c r="AT37" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="BD37">
         <v>1</v>
@@ -9236,10 +9219,10 @@
     </row>
     <row r="38" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="C38" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="I38">
         <v>1</v>
@@ -9272,7 +9255,7 @@
         <v>1</v>
       </c>
       <c r="BP38" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="BV38"/>
       <c r="BW38" s="11"/>
@@ -9286,16 +9269,16 @@
     </row>
     <row r="39" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="C39" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="I39">
         <v>1</v>
       </c>
       <c r="K39" s="9" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="L39" s="9"/>
       <c r="M39"/>
@@ -9324,7 +9307,7 @@
         <v>99</v>
       </c>
       <c r="BP39" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="BS39">
         <v>0.5</v>
@@ -9336,13 +9319,13 @@
       <c r="BZ39" s="11"/>
       <c r="CA39" s="11"/>
       <c r="CB39" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="CG39" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="CN39" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="CO39">
         <v>-0.8</v>
@@ -9351,7 +9334,7 @@
         <v>10</v>
       </c>
       <c r="CX39" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="DH39">
         <v>1</v>
@@ -9359,22 +9342,22 @@
     </row>
     <row r="40" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C40" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="D40" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="E40" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="F40" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="K40" s="9" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="L40" s="9"/>
       <c r="M40"/>
@@ -9397,7 +9380,7 @@
         <v>2</v>
       </c>
       <c r="AT40" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="BD40">
         <v>1</v>
@@ -9411,10 +9394,10 @@
     </row>
     <row r="41" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="C41" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="I41">
         <v>1</v>
@@ -9447,7 +9430,7 @@
         <v>1</v>
       </c>
       <c r="BP41" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="BV41"/>
       <c r="BW41" s="11"/>
@@ -9461,16 +9444,16 @@
     </row>
     <row r="42" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="C42" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="I42">
         <v>1</v>
       </c>
       <c r="K42" s="9" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="L42" s="9"/>
       <c r="M42"/>
@@ -9499,7 +9482,7 @@
         <v>99</v>
       </c>
       <c r="BP42" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="BS42">
         <v>0.5</v>
@@ -9511,19 +9494,19 @@
       <c r="BZ42" s="11"/>
       <c r="CA42" s="11"/>
       <c r="CB42" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="CG42" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="CN42" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="CR42">
         <v>5</v>
       </c>
       <c r="CX42" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="DH42">
         <v>1</v>
@@ -9531,22 +9514,22 @@
     </row>
     <row r="43" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C43" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="D43" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="E43" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="F43" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="K43" s="9" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="L43" s="9"/>
       <c r="M43"/>
@@ -9565,7 +9548,7 @@
         <v>2</v>
       </c>
       <c r="AT43" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="BD43">
         <v>1</v>
@@ -9579,10 +9562,10 @@
     </row>
     <row r="44" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="C44" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="I44">
         <v>1</v>
@@ -9611,7 +9594,7 @@
         <v>1</v>
       </c>
       <c r="BP44" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="BV44"/>
       <c r="BW44" s="11"/>
@@ -9625,16 +9608,16 @@
     </row>
     <row r="45" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="C45" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="I45">
         <v>1</v>
       </c>
       <c r="K45" s="9" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="L45" s="9"/>
       <c r="M45"/>
@@ -9659,7 +9642,7 @@
         <v>99</v>
       </c>
       <c r="BP45" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="BS45">
         <v>0.5</v>
@@ -9671,13 +9654,13 @@
       <c r="BZ45" s="11"/>
       <c r="CA45" s="11"/>
       <c r="CB45" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="CG45" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="CN45" s="22" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="CO45">
         <v>-0.8</v>
@@ -9689,7 +9672,7 @@
         <v>7</v>
       </c>
       <c r="CX45" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="DH45">
         <v>1</v>
@@ -9697,16 +9680,16 @@
     </row>
     <row r="46" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="C46" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="I46">
         <v>1</v>
       </c>
       <c r="K46" s="9" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="L46" s="9"/>
       <c r="M46"/>
@@ -9728,10 +9711,10 @@
         <v>1</v>
       </c>
       <c r="AG46" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="AX46" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="AZ46">
         <v>1</v>
@@ -11084,34 +11067,34 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
+        <v>481</v>
+      </c>
+      <c r="F1" t="s">
+        <v>482</v>
+      </c>
+      <c r="G1" t="s">
+        <v>483</v>
+      </c>
+      <c r="H1" t="s">
+        <v>484</v>
+      </c>
+      <c r="I1" t="s">
         <v>485</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>486</v>
       </c>
-      <c r="G1" t="s">
+      <c r="L1" t="s">
         <v>487</v>
       </c>
-      <c r="H1" t="s">
+      <c r="M1" t="s">
         <v>488</v>
       </c>
-      <c r="I1" t="s">
+      <c r="N1" t="s">
         <v>489</v>
       </c>
-      <c r="J1" t="s">
+      <c r="O1" t="s">
         <v>490</v>
-      </c>
-      <c r="L1" t="s">
-        <v>491</v>
-      </c>
-      <c r="M1" t="s">
-        <v>492</v>
-      </c>
-      <c r="N1" t="s">
-        <v>493</v>
-      </c>
-      <c r="O1" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -11119,46 +11102,46 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
+        <v>491</v>
+      </c>
+      <c r="F2" t="s">
+        <v>492</v>
+      </c>
+      <c r="G2" t="s">
+        <v>493</v>
+      </c>
+      <c r="H2" t="s">
+        <v>494</v>
+      </c>
+      <c r="I2" t="s">
         <v>495</v>
       </c>
-      <c r="F2" t="s">
+      <c r="J2" t="s">
         <v>496</v>
       </c>
-      <c r="G2" t="s">
+      <c r="K2" t="s">
         <v>497</v>
       </c>
-      <c r="H2" t="s">
+      <c r="L2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M2" t="s">
         <v>498</v>
       </c>
-      <c r="I2" t="s">
+      <c r="N2" t="s">
         <v>499</v>
       </c>
-      <c r="J2" t="s">
+      <c r="O2" t="s">
         <v>500</v>
       </c>
-      <c r="K2" t="s">
-        <v>501</v>
-      </c>
-      <c r="L2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M2" t="s">
-        <v>502</v>
-      </c>
-      <c r="N2" t="s">
-        <v>503</v>
-      </c>
-      <c r="O2" t="s">
-        <v>504</v>
-      </c>
       <c r="P2" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -11172,78 +11155,78 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="J3" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="K3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="L3" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="M3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="N3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="O3" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="P3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C4" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="AA4" s="2"/>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="C5" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="H5">
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="AA5" s="2"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="C6" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -11252,64 +11235,64 @@
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C7" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="H7">
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="C8" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H8">
         <v>1</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="C9" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="H9">
         <v>1</v>
       </c>
       <c r="J9" t="s">
+        <v>507</v>
+      </c>
+      <c r="P9" s="2" t="s">
         <v>511</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="C10" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H10">
         <v>1</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
     </row>
   </sheetData>
@@ -11335,7 +11318,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -11343,13 +11326,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D2" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -11360,46 +11343,46 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="D3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B4" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D4" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="B5" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="C5" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="D5" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="B6" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="D6" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
@@ -11422,7 +11405,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -11430,31 +11413,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" t="s">
         <v>48</v>
       </c>
-      <c r="C2" t="s">
-        <v>50</v>
-      </c>
       <c r="D2" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="E2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F2" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="G2" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="H2" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="I2" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="J2" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -11471,33 +11454,33 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I3" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B4" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C4" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="E4">
         <v>200</v>
@@ -11530,34 +11513,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C1" t="s">
+        <v>529</v>
+      </c>
+      <c r="D1" t="s">
+        <v>530</v>
+      </c>
+      <c r="E1" t="s">
+        <v>531</v>
+      </c>
+      <c r="F1" t="s">
         <v>532</v>
       </c>
-      <c r="C1" t="s">
+      <c r="H1" t="s">
         <v>533</v>
       </c>
-      <c r="D1" t="s">
+      <c r="I1" t="s">
         <v>534</v>
       </c>
-      <c r="E1" t="s">
+      <c r="J1" t="s">
         <v>535</v>
       </c>
-      <c r="F1" t="s">
+      <c r="K1" t="s">
         <v>536</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
         <v>537</v>
-      </c>
-      <c r="I1" t="s">
-        <v>538</v>
-      </c>
-      <c r="J1" t="s">
-        <v>539</v>
-      </c>
-      <c r="K1" t="s">
-        <v>540</v>
-      </c>
-      <c r="L1" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -11565,37 +11548,37 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>538</v>
+      </c>
+      <c r="C2" t="s">
+        <v>539</v>
+      </c>
+      <c r="D2" t="s">
+        <v>540</v>
+      </c>
+      <c r="E2" t="s">
+        <v>541</v>
+      </c>
+      <c r="F2" t="s">
         <v>542</v>
       </c>
-      <c r="C2" t="s">
+      <c r="G2" t="s">
         <v>543</v>
       </c>
-      <c r="D2" t="s">
+      <c r="H2" t="s">
         <v>544</v>
       </c>
-      <c r="E2" t="s">
+      <c r="I2" t="s">
         <v>545</v>
       </c>
-      <c r="F2" t="s">
+      <c r="J2" t="s">
         <v>546</v>
       </c>
-      <c r="G2" t="s">
-        <v>547</v>
-      </c>
-      <c r="H2" t="s">
-        <v>548</v>
-      </c>
-      <c r="I2" t="s">
-        <v>549</v>
-      </c>
-      <c r="J2" t="s">
-        <v>550</v>
-      </c>
       <c r="K2" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="L2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -11606,42 +11589,42 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D3" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="E3" t="s">
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="J3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="K3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="L3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="B4" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -11680,31 +11663,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" t="s">
+        <v>549</v>
+      </c>
+      <c r="E2" t="s">
+        <v>550</v>
+      </c>
+      <c r="F2" t="s">
         <v>77</v>
       </c>
-      <c r="D2" t="s">
-        <v>553</v>
-      </c>
-      <c r="E2" t="s">
-        <v>554</v>
-      </c>
-      <c r="F2" t="s">
-        <v>79</v>
-      </c>
       <c r="G2" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="H2" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="I2" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="J2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -11721,22 +11704,22 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H3" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="I3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="J3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -11765,28 +11748,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>561</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -11794,28 +11777,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>569</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -11823,10 +11806,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>2</v>

--- a/Excel/一方通行/艾拉.xlsx
+++ b/Excel/一方通行/艾拉.xlsx
@@ -23,7 +23,7 @@
     <sheet name="ContractData" sheetId="11" r:id="rId8"/>
     <sheet name="SpineData" sheetId="12" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="584">
   <si>
     <t>Id</t>
   </si>
@@ -313,6 +313,9 @@
     <t>UnitData[]</t>
   </si>
   <si>
+    <t>艾拉</t>
+  </si>
+  <si>
     <t>#</t>
   </si>
   <si>
@@ -370,6 +373,9 @@
     <t>部署策略</t>
   </si>
   <si>
+    <t>可部署上限</t>
+  </si>
+  <si>
     <t>仇恨等级</t>
   </si>
   <si>
@@ -526,6 +532,9 @@
     <t>RedeployPolicy</t>
   </si>
   <si>
+    <t>BuildCountLimit</t>
+  </si>
+  <si>
     <t>Hatred</t>
   </si>
   <si>
@@ -676,9 +685,6 @@
     <t>System.Collections.Generic.Dictionary&lt;string,object&gt;</t>
   </si>
   <si>
-    <t>艾拉</t>
-  </si>
-  <si>
     <t>干员</t>
   </si>
   <si>
@@ -1996,6 +2002,9 @@
     <t>MapHp</t>
   </si>
   <si>
+    <t>UnitTypeEnum[]</t>
+  </si>
+  <si>
     <t>仅单面</t>
   </si>
   <si>
@@ -2042,20 +2051,14 @@
   </si>
   <si>
     <t>BackSkelPath</t>
-  </si>
-  <si>
-    <t>UnitTypeEnum[]</t>
-  </si>
-  <si>
-    <t>艾拉</t>
-    <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2068,19 +2071,6 @@
       <name val="宋体"/>
       <family val="3"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -2114,17 +2104,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1">
+  <cellXfs count="3">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2429,11 +2422,11 @@
   <dimension ref="A2:B4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="9" style="1"/>
+    <col min="1" max="2" width="9" customWidth="1" style="1"/>
+    <col min="3" max="16384" width="9" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2441,7 +2434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -2449,1107 +2442,1301 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" s="1" t="s">
-        <v>125</v>
+        <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>125</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BS7"/>
+  <dimension ref="A1:BT7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.58203125" style="1" customWidth="1"/>
-    <col min="2" max="3" width="9" style="1" customWidth="1"/>
-    <col min="4" max="5" width="8.58203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.58203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.25" style="1" customWidth="1"/>
-    <col min="8" max="10" width="9" style="1" customWidth="1"/>
-    <col min="11" max="11" width="6" style="1" customWidth="1"/>
-    <col min="12" max="12" width="4.08203125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="5.58203125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="4" style="1" customWidth="1"/>
-    <col min="15" max="15" width="7.75" style="1" customWidth="1"/>
-    <col min="16" max="16" width="10.83203125" style="1" customWidth="1"/>
-    <col min="17" max="18" width="3.83203125" style="1" customWidth="1"/>
-    <col min="19" max="20" width="3.58203125" style="1" customWidth="1"/>
-    <col min="21" max="21" width="10.25" style="1" customWidth="1"/>
-    <col min="22" max="22" width="9.58203125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="10.75" style="1" customWidth="1"/>
-    <col min="24" max="24" width="12.83203125" style="1" customWidth="1"/>
-    <col min="25" max="25" width="13.08203125" style="1" customWidth="1"/>
-    <col min="26" max="26" width="10.75" style="1" customWidth="1"/>
-    <col min="27" max="28" width="9" style="1" customWidth="1"/>
-    <col min="29" max="29" width="8" style="1" customWidth="1"/>
-    <col min="30" max="30" width="17.08203125" style="1" customWidth="1"/>
-    <col min="31" max="31" width="9" style="1" customWidth="1"/>
-    <col min="32" max="32" width="9.75" style="1" customWidth="1"/>
-    <col min="33" max="33" width="7.83203125" style="1" customWidth="1"/>
-    <col min="34" max="34" width="15.83203125" style="1" customWidth="1"/>
-    <col min="35" max="35" width="13.83203125" style="1" customWidth="1"/>
-    <col min="36" max="36" width="34.5" style="1" customWidth="1"/>
-    <col min="37" max="38" width="9.83203125" style="1" customWidth="1"/>
-    <col min="39" max="42" width="9" style="1" customWidth="1"/>
-    <col min="43" max="43" width="12.5" style="1" customWidth="1"/>
-    <col min="44" max="49" width="9" style="1" customWidth="1"/>
-    <col min="50" max="50" width="24.33203125" style="1" customWidth="1"/>
-    <col min="51" max="51" width="9" style="1" customWidth="1"/>
-    <col min="52" max="52" width="17.75" style="1" customWidth="1"/>
-    <col min="53" max="53" width="7.83203125" style="1" customWidth="1"/>
-    <col min="54" max="55" width="9" style="1" customWidth="1"/>
-    <col min="56" max="56" width="24.25" style="1" customWidth="1"/>
-    <col min="57" max="57" width="13.25" style="1" customWidth="1"/>
-    <col min="58" max="58" width="16.08203125" style="1" customWidth="1"/>
-    <col min="59" max="59" width="8" style="1" customWidth="1"/>
-    <col min="60" max="63" width="9" style="1" customWidth="1"/>
-    <col min="64" max="64" width="39.58203125" style="1" customWidth="1"/>
-    <col min="65" max="65" width="14" style="1" customWidth="1"/>
-    <col min="66" max="66" width="14.83203125" style="1" customWidth="1"/>
-    <col min="67" max="70" width="14" style="1" customWidth="1"/>
-    <col min="71" max="71" width="19.1640625" style="1" customWidth="1"/>
-    <col min="72" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="22.58203125" customWidth="1" style="2"/>
+    <col min="2" max="2" width="9" customWidth="1" style="2"/>
+    <col min="3" max="3" width="9" customWidth="1" style="2"/>
+    <col min="4" max="4" width="8.58203125" customWidth="1" style="2"/>
+    <col min="5" max="5" width="8.58203125" customWidth="1" style="2"/>
+    <col min="6" max="6" width="19.58203125" customWidth="1" style="2"/>
+    <col min="7" max="7" width="8.25" customWidth="1" style="2"/>
+    <col min="8" max="8" width="9" customWidth="1" style="2"/>
+    <col min="9" max="9" width="9" customWidth="1" style="2"/>
+    <col min="10" max="10" width="9" customWidth="1" style="2"/>
+    <col min="11" max="11" width="6" customWidth="1" style="2"/>
+    <col min="12" max="12" width="4.08203125" customWidth="1" style="2"/>
+    <col min="13" max="13" width="5.58203125" customWidth="1" style="2"/>
+    <col min="14" max="14" width="4" customWidth="1" style="2"/>
+    <col min="15" max="15" width="7.75" customWidth="1" style="2"/>
+    <col min="16" max="16" width="10.83203125" customWidth="1" style="2"/>
+    <col min="17" max="17" width="3.83203125" customWidth="1" style="2"/>
+    <col min="18" max="18" width="3.83203125" customWidth="1" style="2"/>
+    <col min="19" max="19" width="3.58203125" customWidth="1" style="2"/>
+    <col min="20" max="20" width="3.58203125" customWidth="1" style="2"/>
+    <col min="21" max="21" width="10.25" customWidth="1" style="2"/>
+    <col min="22" max="22" width="9.58203125" customWidth="1" style="2"/>
+    <col min="23" max="23" width="10.75" customWidth="1" style="2"/>
+    <col min="24" max="24" width="12.83203125" customWidth="1" style="2"/>
+    <col min="25" max="25" width="13.08203125" customWidth="1" style="2"/>
+    <col min="26" max="26" width="10.75" customWidth="1" style="2"/>
+    <col min="27" max="27" width="9" customWidth="1" style="2"/>
+    <col min="28" max="28" width="9" customWidth="1" style="2"/>
+    <col min="29" max="29" width="8" customWidth="1" style="2"/>
+    <col min="30" max="30" width="17.08203125" customWidth="1" style="2"/>
+    <col min="31" max="31" width="9" customWidth="1" style="2"/>
+    <col min="32" max="32" width="9" customWidth="1" style="2"/>
+    <col min="33" max="33" width="9.75" customWidth="1" style="2"/>
+    <col min="34" max="34" width="7.83203125" customWidth="1" style="2"/>
+    <col min="35" max="35" width="15.83203125" customWidth="1" style="2"/>
+    <col min="36" max="36" width="13.83203125" customWidth="1" style="2"/>
+    <col min="37" max="37" width="34.5" customWidth="1" style="2"/>
+    <col min="38" max="38" width="9.83203125" customWidth="1" style="2"/>
+    <col min="39" max="39" width="9.83203125" customWidth="1" style="2"/>
+    <col min="40" max="40" width="9" customWidth="1" style="2"/>
+    <col min="41" max="41" width="9" customWidth="1" style="2"/>
+    <col min="42" max="42" width="9" customWidth="1" style="2"/>
+    <col min="43" max="43" width="9" customWidth="1" style="2"/>
+    <col min="44" max="44" width="12.5" customWidth="1" style="2"/>
+    <col min="45" max="45" width="9" customWidth="1" style="2"/>
+    <col min="46" max="46" width="9" customWidth="1" style="2"/>
+    <col min="47" max="47" width="9" customWidth="1" style="2"/>
+    <col min="48" max="48" width="9" customWidth="1" style="2"/>
+    <col min="49" max="49" width="9" customWidth="1" style="2"/>
+    <col min="50" max="50" width="9" customWidth="1" style="2"/>
+    <col min="51" max="51" width="24.33203125" customWidth="1" style="2"/>
+    <col min="52" max="52" width="9" customWidth="1" style="2"/>
+    <col min="53" max="53" width="17.75" customWidth="1" style="2"/>
+    <col min="54" max="54" width="7.83203125" customWidth="1" style="2"/>
+    <col min="55" max="55" width="9" customWidth="1" style="2"/>
+    <col min="56" max="56" width="9" customWidth="1" style="2"/>
+    <col min="57" max="57" width="24.25" customWidth="1" style="2"/>
+    <col min="58" max="58" width="13.25" customWidth="1" style="2"/>
+    <col min="59" max="59" width="16.08203125" customWidth="1" style="2"/>
+    <col min="60" max="60" width="8" customWidth="1" style="2"/>
+    <col min="61" max="61" width="9" customWidth="1" style="2"/>
+    <col min="62" max="62" width="9" customWidth="1" style="2"/>
+    <col min="63" max="63" width="9" customWidth="1" style="2"/>
+    <col min="64" max="64" width="9" customWidth="1" style="2"/>
+    <col min="65" max="65" width="39.58203125" customWidth="1" style="2"/>
+    <col min="66" max="66" width="14" customWidth="1" style="2"/>
+    <col min="67" max="67" width="14.83203125" customWidth="1" style="2"/>
+    <col min="68" max="68" width="14" customWidth="1" style="2"/>
+    <col min="69" max="69" width="14" customWidth="1" style="2"/>
+    <col min="70" max="70" width="14" customWidth="1" style="2"/>
+    <col min="71" max="71" width="14" customWidth="1" style="2"/>
+    <col min="72" max="72" width="19.1640625" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="D1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AG1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH1" s="2"/>
+      <c r="AI1" s="2"/>
+      <c r="AJ1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AK1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AM1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AN1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AO1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AP1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AQ1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AS1" s="2"/>
+      <c r="AT1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AU1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AW1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AX1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AY1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AZ1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="BA1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="BB1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="BC1" s="2"/>
+      <c r="BD1" s="2"/>
+      <c r="BE1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="BF1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="BG1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="BH1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="BI1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="BJ1" s="2"/>
+      <c r="BK1" s="2"/>
+      <c r="BL1" s="2"/>
+      <c r="BM1" s="2"/>
+      <c r="BN1" s="2"/>
+      <c r="BO1" s="2"/>
+      <c r="BP1" s="2"/>
+      <c r="BQ1" s="2"/>
+      <c r="BR1" s="2"/>
+      <c r="BS1" s="2"/>
+      <c r="BT1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AF2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AH2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AI2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AK2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AM2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AN2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AP2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AQ2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AR2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AS2" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AT2" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AU2" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AV2" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AW2" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AX2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AY2" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AZ2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="BA2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="BB2" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="BC2" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="BD2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BE2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BF2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BG2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BH2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="BI2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="BJ2" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="BK2" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BL2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="BM2" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="BN2" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="BO2" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="BP2" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="BQ2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="BR2" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="BS2" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="BT2" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AE3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AF3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AH3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AK3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="AL3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AO3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AP3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AQ3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AR3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AS3" s="2"/>
+      <c r="AT3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AU3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AV3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AW3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AX3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AY3" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BA3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BB3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BC3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BD3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BE3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BF3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BG3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BH3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="BI3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BJ3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BK3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BL3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BM3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BN3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BO3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BP3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BQ3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BR3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BS3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BT3" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B4" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G4" s="2">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2">
+        <v>2</v>
+      </c>
+      <c r="J4" s="2">
+        <v>90</v>
+      </c>
+      <c r="K4" s="2">
+        <v>1468</v>
+      </c>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2">
+        <v>755</v>
+      </c>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2">
+        <v>203</v>
+      </c>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2">
+        <v>0</v>
+      </c>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2">
+        <v>12</v>
+      </c>
+      <c r="T4" s="2">
+        <v>-2</v>
+      </c>
+      <c r="U4" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="V4" s="2">
+        <v>70</v>
+      </c>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="Z4" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="AA4" s="2"/>
+      <c r="AB4" s="2"/>
+      <c r="AC4" s="2">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="2"/>
+      <c r="AE4" s="2"/>
+      <c r="AF4" s="2"/>
+      <c r="AG4" s="2"/>
+      <c r="AH4" s="2"/>
+      <c r="AI4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="AJ4" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="AK4" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="AL4" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AM4" s="2"/>
+      <c r="AN4" s="2"/>
+      <c r="AO4" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AP4" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ4" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="AR4" s="2"/>
+      <c r="AS4" s="2"/>
+      <c r="AT4" s="2"/>
+      <c r="AU4" s="2"/>
+      <c r="AV4" s="2"/>
+      <c r="AW4" s="2"/>
+      <c r="AX4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="AY4" s="2"/>
+      <c r="AZ4" s="2"/>
+      <c r="BA4" s="2"/>
+      <c r="BB4" s="2"/>
+      <c r="BC4" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="BD4" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="BE4" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="BF4" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="BG4" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="BH4" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="BI4" s="2">
+        <v>6</v>
+      </c>
+      <c r="BJ4" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="BK4" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="BL4" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="BM4" s="2"/>
+      <c r="BN4" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="BO4" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="BP4" s="2"/>
+      <c r="BQ4" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="BR4" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="BS4" s="2"/>
+      <c r="BT4" s="2">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2">
+        <v>2</v>
+      </c>
+      <c r="J5" s="2">
+        <v>90</v>
+      </c>
+      <c r="K5" s="2">
+        <v>1000</v>
+      </c>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2">
+        <v>100</v>
+      </c>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2">
+        <v>0</v>
+      </c>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2">
+        <v>0</v>
+      </c>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="T5" s="2"/>
+      <c r="U5" s="2">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2">
+        <v>5</v>
+      </c>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="Z5" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="2"/>
+      <c r="AB5" s="2"/>
+      <c r="AC5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="2"/>
+      <c r="AF5" s="2"/>
+      <c r="AG5" s="2"/>
+      <c r="AH5" s="2"/>
+      <c r="AI5" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="AJ5" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="AK5" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AL5" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="AM5" s="2">
+        <v>1</v>
+      </c>
+      <c r="AN5" s="2"/>
+      <c r="AO5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AP5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR5" s="2"/>
+      <c r="AS5" s="2"/>
+      <c r="AT5" s="2"/>
+      <c r="AU5" s="2"/>
+      <c r="AV5" s="2"/>
+      <c r="AW5" s="2"/>
+      <c r="AX5" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="AY5" s="2"/>
+      <c r="AZ5" s="2"/>
+      <c r="BA5" s="2"/>
+      <c r="BB5" s="2"/>
+      <c r="BC5" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="BD5" s="2"/>
+      <c r="BE5" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="BF5" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="BG5" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="BH5" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="BI5" s="2">
         <v>6</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="BE1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="BF1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="BG1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="BH1" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="BJ5" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="BK5" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="BL5" s="2"/>
+      <c r="BM5" s="2"/>
+      <c r="BN5" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="BO5" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="BP5" s="2"/>
+      <c r="BQ5" s="2"/>
+      <c r="BR5" s="2"/>
+      <c r="BS5" s="2"/>
+      <c r="BT5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2">
+        <v>2</v>
+      </c>
+      <c r="J6" s="2">
+        <v>90</v>
+      </c>
+      <c r="K6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2">
+        <v>100</v>
+      </c>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AE2" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AF2" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="AG2" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH2" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="AI2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ2" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK2" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="AL2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="AM2" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AN2" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="AO2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AP2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AQ2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="AR2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="AS2" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="AT2" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AU2" s="1" t="s">
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2">
+        <v>5</v>
+      </c>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2">
+        <v>5</v>
+      </c>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
+      <c r="Y6" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="Z6" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="2"/>
+      <c r="AB6" s="2"/>
+      <c r="AC6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="2"/>
+      <c r="AF6" s="2"/>
+      <c r="AG6" s="2"/>
+      <c r="AH6" s="2"/>
+      <c r="AI6" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="AJ6" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="AK6" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="AL6" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="AM6" s="2">
+        <v>1</v>
+      </c>
+      <c r="AN6" s="2"/>
+      <c r="AO6" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AP6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="2"/>
+      <c r="AS6" s="2"/>
+      <c r="AT6" s="2"/>
+      <c r="AU6" s="2"/>
+      <c r="AV6" s="2"/>
+      <c r="AW6" s="2"/>
+      <c r="AX6" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="AY6" s="2"/>
+      <c r="AZ6" s="2"/>
+      <c r="BA6" s="2"/>
+      <c r="BB6" s="2"/>
+      <c r="BC6" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="BD6" s="2"/>
+      <c r="BE6" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="BF6" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="BG6" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="BH6" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="BI6" s="2">
+        <v>6</v>
+      </c>
+      <c r="BJ6" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="BK6" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="BL6" s="2"/>
+      <c r="BM6" s="2"/>
+      <c r="BN6" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="BO6" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="BP6" s="2"/>
+      <c r="BQ6" s="2"/>
+      <c r="BR6" s="2"/>
+      <c r="BS6" s="2"/>
+      <c r="BT6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1</v>
+      </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2">
+        <v>2</v>
+      </c>
+      <c r="J7" s="2">
         <v>90</v>
       </c>
-      <c r="AV2" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AW2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="AX2" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AY2" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="AZ2" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="BA2" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="BB2" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="BC2" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="BD2" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="BE2" s="1" t="s">
+      <c r="K7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2">
         <v>100</v>
       </c>
-      <c r="BF2" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="BG2" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="BH2" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="BI2" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="BJ2" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="BK2" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="BL2" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="BM2" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="BN2" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="BO2" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="BP2" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="BQ2" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="BR2" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="BS2" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="3" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="Z3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="AA3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AB3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="AC3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AD3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AE3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AF3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AG3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AH3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AI3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AJ3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="AK3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="AL3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="AN3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="AO3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AP3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="AQ3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AS3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="AT3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AU3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AV3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AW3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="AY3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AZ3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="BA3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="BB3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="BC3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="BD3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="BE3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="BF3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="BG3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="BH3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="BI3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="BJ3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="BK3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="BL3" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="BM3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="BN3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="BO3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="BP3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="BQ3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="BR3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="BS3" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="4" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1</v>
-      </c>
-      <c r="I4" s="1">
-        <v>2</v>
-      </c>
-      <c r="J4" s="1">
-        <v>90</v>
-      </c>
-      <c r="K4" s="1">
-        <v>1468</v>
-      </c>
-      <c r="M4" s="1">
-        <v>755</v>
-      </c>
-      <c r="O4" s="1">
-        <v>203</v>
-      </c>
-      <c r="Q4" s="1">
+      <c r="N7" s="2"/>
+      <c r="O7" s="2">
         <v>0</v>
       </c>
-      <c r="S4" s="1">
-        <v>12</v>
-      </c>
-      <c r="T4" s="1">
-        <v>-2</v>
-      </c>
-      <c r="U4" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="V4" s="1">
-        <v>70</v>
-      </c>
-      <c r="Y4" s="1">
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2">
+        <v>0</v>
+      </c>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2">
+        <v>5</v>
+      </c>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2">
+        <v>5</v>
+      </c>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
+      <c r="Y7" s="2">
         <v>0.05</v>
       </c>
-      <c r="Z4" s="1">
-        <v>0.85</v>
-      </c>
-      <c r="AC4" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH4" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="AI4" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="AJ4" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="AK4" s="1" t="s">
+      <c r="Z7" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="2"/>
+      <c r="AB7" s="2"/>
+      <c r="AC7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="2"/>
+      <c r="AF7" s="2"/>
+      <c r="AG7" s="2"/>
+      <c r="AH7" s="2"/>
+      <c r="AI7" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="AJ7" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="AN4" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="AO4" s="1">
-        <v>1</v>
-      </c>
-      <c r="AP4" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="AW4" s="1">
+      <c r="AK7" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="AL7" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="AM7" s="2">
+        <v>1</v>
+      </c>
+      <c r="AN7" s="2"/>
+      <c r="AO7" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AP7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR7" s="2"/>
+      <c r="AS7" s="2"/>
+      <c r="AT7" s="2"/>
+      <c r="AU7" s="2"/>
+      <c r="AV7" s="2"/>
+      <c r="AW7" s="2"/>
+      <c r="AX7" s="2">
         <v>0.25</v>
       </c>
-      <c r="BB4" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="BC4" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="BD4" s="1" t="s">
+      <c r="AY7" s="2"/>
+      <c r="AZ7" s="2"/>
+      <c r="BA7" s="2"/>
+      <c r="BB7" s="2"/>
+      <c r="BC7" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="BE4" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="BF4" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="BG4" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="BH4" s="1">
+      <c r="BD7" s="2"/>
+      <c r="BE7" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="BF7" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="BG7" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="BH7" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="BI7" s="2">
         <v>6</v>
       </c>
-      <c r="BI4" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="BJ4" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="BK4" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="BM4" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="BN4" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="BP4" s="1" t="s">
+      <c r="BJ7" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="BK7" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="BL7" s="2"/>
+      <c r="BM7" s="2"/>
+      <c r="BN7" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="BQ4" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="BS4" s="1">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="BO7" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1</v>
-      </c>
-      <c r="I5" s="1">
-        <v>2</v>
-      </c>
-      <c r="J5" s="1">
-        <v>90</v>
-      </c>
-      <c r="K5" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M5" s="1">
-        <v>100</v>
-      </c>
-      <c r="O5" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>0</v>
-      </c>
-      <c r="S5" s="1">
-        <v>5</v>
-      </c>
-      <c r="U5" s="1">
-        <v>0</v>
-      </c>
-      <c r="V5" s="1">
-        <v>5</v>
-      </c>
-      <c r="Y5" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="Z5" s="1">
-        <v>1</v>
-      </c>
-      <c r="AC5" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH5" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="AI5" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="AJ5" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="AK5" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="AL5" s="1">
-        <v>1</v>
-      </c>
-      <c r="AN5" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="AO5" s="1">
-        <v>0</v>
-      </c>
-      <c r="AP5" s="1">
-        <v>0</v>
-      </c>
-      <c r="AW5" s="1">
-        <v>0.25</v>
-      </c>
-      <c r="BB5" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="BD5" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="BE5" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="BF5" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="BG5" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="BH5" s="1">
-        <v>6</v>
-      </c>
-      <c r="BI5" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="BJ5" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="BM5" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="BN5" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="BS5" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1</v>
-      </c>
-      <c r="I6" s="1">
-        <v>2</v>
-      </c>
-      <c r="J6" s="1">
-        <v>90</v>
-      </c>
-      <c r="K6" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M6" s="1">
-        <v>100</v>
-      </c>
-      <c r="O6" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>0</v>
-      </c>
-      <c r="S6" s="1">
-        <v>5</v>
-      </c>
-      <c r="U6" s="1">
-        <v>0</v>
-      </c>
-      <c r="V6" s="1">
-        <v>5</v>
-      </c>
-      <c r="Y6" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="Z6" s="1">
-        <v>1</v>
-      </c>
-      <c r="AC6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH6" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="AI6" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="AJ6" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="AK6" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="AL6" s="1">
-        <v>1</v>
-      </c>
-      <c r="AN6" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="AO6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AP6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AW6" s="1">
-        <v>0.25</v>
-      </c>
-      <c r="BB6" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="BD6" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="BE6" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="BF6" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="BG6" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="BH6" s="1">
-        <v>6</v>
-      </c>
-      <c r="BI6" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="BJ6" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="BM6" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="BN6" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="BS6" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1</v>
-      </c>
-      <c r="I7" s="1">
-        <v>2</v>
-      </c>
-      <c r="J7" s="1">
-        <v>90</v>
-      </c>
-      <c r="K7" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M7" s="1">
-        <v>100</v>
-      </c>
-      <c r="O7" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>0</v>
-      </c>
-      <c r="S7" s="1">
-        <v>5</v>
-      </c>
-      <c r="U7" s="1">
-        <v>0</v>
-      </c>
-      <c r="V7" s="1">
-        <v>5</v>
-      </c>
-      <c r="Y7" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="Z7" s="1">
-        <v>1</v>
-      </c>
-      <c r="AC7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH7" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="AI7" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="AJ7" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="AK7" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="AL7" s="1">
-        <v>1</v>
-      </c>
-      <c r="AN7" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="AO7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AP7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AW7" s="1">
-        <v>0.25</v>
-      </c>
-      <c r="BB7" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="BD7" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="BE7" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="BF7" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="BG7" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="BH7" s="1">
-        <v>6</v>
-      </c>
-      <c r="BI7" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="BJ7" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="BM7" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="BN7" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="BS7" s="1">
+      <c r="BP7" s="2"/>
+      <c r="BQ7" s="2"/>
+      <c r="BR7" s="2"/>
+      <c r="BS7" s="2"/>
+      <c r="BT7" s="2">
         <v>1</v>
       </c>
     </row>
@@ -3557,6 +3744,7 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -3566,762 +3754,762 @@
   <dimension ref="A1:DI645"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.08203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.58203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7.75" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.58203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="31.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7.33203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.83203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="7.33203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="15.75" style="1" customWidth="1"/>
-    <col min="11" max="13" width="8.33203125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="11.75" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13.08203125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="11.58203125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="21.5" style="1" customWidth="1"/>
-    <col min="18" max="18" width="19.83203125" style="1" customWidth="1"/>
-    <col min="19" max="19" width="16.58203125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="19.08203125" style="1" customWidth="1"/>
-    <col min="21" max="21" width="18.33203125" style="1" customWidth="1"/>
-    <col min="22" max="22" width="17.75" style="1" customWidth="1"/>
-    <col min="23" max="23" width="8.33203125" style="1" customWidth="1"/>
-    <col min="24" max="24" width="18.5" style="1" customWidth="1"/>
-    <col min="25" max="25" width="16.58203125" style="1" customWidth="1"/>
-    <col min="26" max="26" width="10.6640625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="8.33203125" style="1" customWidth="1"/>
-    <col min="28" max="28" width="15.1640625" style="1" customWidth="1"/>
-    <col min="29" max="30" width="8.58203125" style="1" customWidth="1"/>
-    <col min="31" max="31" width="13.4140625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="13.75" style="1" customWidth="1"/>
-    <col min="33" max="33" width="14.58203125" style="1" customWidth="1"/>
-    <col min="34" max="34" width="17.4140625" style="1" customWidth="1"/>
-    <col min="35" max="35" width="8.58203125" style="1" customWidth="1"/>
-    <col min="36" max="36" width="12.5" style="1" customWidth="1"/>
-    <col min="37" max="37" width="8.58203125" style="1" customWidth="1"/>
-    <col min="38" max="39" width="8.33203125" style="1" customWidth="1"/>
-    <col min="40" max="40" width="15" style="1" customWidth="1"/>
-    <col min="41" max="41" width="13.25" style="1" customWidth="1"/>
-    <col min="42" max="45" width="11.83203125" style="1" customWidth="1"/>
-    <col min="46" max="46" width="18.4140625" style="1" customWidth="1"/>
-    <col min="47" max="47" width="12.25" style="1" customWidth="1"/>
-    <col min="48" max="48" width="11.9140625" style="1" customWidth="1"/>
-    <col min="49" max="49" width="19.58203125" style="1" customWidth="1"/>
-    <col min="50" max="50" width="12.6640625" style="1" customWidth="1"/>
-    <col min="51" max="51" width="9" style="1" customWidth="1"/>
-    <col min="52" max="52" width="7" style="1" customWidth="1"/>
-    <col min="53" max="53" width="11.75" style="1" customWidth="1"/>
-    <col min="54" max="54" width="19.75" style="1" customWidth="1"/>
-    <col min="55" max="55" width="5.08203125" style="1" customWidth="1"/>
-    <col min="56" max="56" width="8.5" style="1" customWidth="1"/>
-    <col min="57" max="57" width="13.5" style="1" customWidth="1"/>
-    <col min="58" max="58" width="14.6640625" style="1" customWidth="1"/>
-    <col min="59" max="59" width="10.1640625" style="1" customWidth="1"/>
-    <col min="60" max="60" width="8.25" style="1" customWidth="1"/>
-    <col min="61" max="67" width="8.33203125" style="1" customWidth="1"/>
-    <col min="68" max="70" width="11.25" style="1" customWidth="1"/>
-    <col min="71" max="71" width="6.58203125" style="1" customWidth="1"/>
-    <col min="72" max="73" width="8" style="1" customWidth="1"/>
-    <col min="74" max="74" width="7.33203125" style="1" customWidth="1"/>
-    <col min="75" max="76" width="8.5" style="1" customWidth="1"/>
-    <col min="77" max="78" width="7.83203125" style="1" customWidth="1"/>
-    <col min="79" max="79" width="22.1640625" style="1" customWidth="1"/>
-    <col min="80" max="80" width="13.5" style="1" customWidth="1"/>
-    <col min="81" max="81" width="21.1640625" style="1" customWidth="1"/>
-    <col min="82" max="82" width="15.75" style="1" customWidth="1"/>
-    <col min="83" max="83" width="15.58203125" style="1" customWidth="1"/>
-    <col min="84" max="84" width="12.83203125" style="1" customWidth="1"/>
-    <col min="85" max="85" width="16.1640625" style="1" customWidth="1"/>
-    <col min="86" max="86" width="9" style="1" customWidth="1"/>
-    <col min="87" max="87" width="16" style="1" customWidth="1"/>
-    <col min="88" max="89" width="12.83203125" style="1" customWidth="1"/>
-    <col min="90" max="90" width="23.58203125" style="1" customWidth="1"/>
-    <col min="91" max="91" width="12.83203125" style="1" customWidth="1"/>
-    <col min="92" max="92" width="17.08203125" style="1" customWidth="1"/>
-    <col min="93" max="98" width="9" style="1" customWidth="1"/>
-    <col min="99" max="99" width="14" style="1" customWidth="1"/>
-    <col min="100" max="100" width="8" style="1" customWidth="1"/>
-    <col min="101" max="101" width="9" style="1" customWidth="1"/>
-    <col min="102" max="102" width="11.08203125" style="1" customWidth="1"/>
-    <col min="103" max="103" width="13.75" style="1" customWidth="1"/>
-    <col min="104" max="109" width="9" style="1" customWidth="1"/>
-    <col min="110" max="110" width="15.5" style="1" customWidth="1"/>
-    <col min="111" max="113" width="9" style="1" customWidth="1"/>
-    <col min="114" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="21.08203125" customWidth="1" style="1"/>
+    <col min="2" max="2" width="15.58203125" customWidth="1" style="1"/>
+    <col min="3" max="3" width="7.75" customWidth="1" style="1"/>
+    <col min="4" max="4" width="16.58203125" customWidth="1" style="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1" style="1"/>
+    <col min="6" max="6" width="31.33203125" customWidth="1" style="1"/>
+    <col min="7" max="7" width="7.33203125" customWidth="1" style="1"/>
+    <col min="8" max="8" width="17.83203125" customWidth="1" style="1"/>
+    <col min="9" max="9" width="7.33203125" customWidth="1" style="1"/>
+    <col min="10" max="10" width="15.75" customWidth="1" style="1"/>
+    <col min="11" max="13" width="8.33203125" customWidth="1" style="1"/>
+    <col min="14" max="14" width="11.75" customWidth="1" style="1"/>
+    <col min="15" max="15" width="13.08203125" customWidth="1" style="1"/>
+    <col min="16" max="16" width="11.58203125" customWidth="1" style="1"/>
+    <col min="17" max="17" width="21.5" customWidth="1" style="1"/>
+    <col min="18" max="18" width="19.83203125" customWidth="1" style="1"/>
+    <col min="19" max="19" width="16.58203125" customWidth="1" style="1"/>
+    <col min="20" max="20" width="19.08203125" customWidth="1" style="1"/>
+    <col min="21" max="21" width="18.33203125" customWidth="1" style="1"/>
+    <col min="22" max="22" width="17.75" customWidth="1" style="1"/>
+    <col min="23" max="23" width="8.33203125" customWidth="1" style="1"/>
+    <col min="24" max="24" width="18.5" customWidth="1" style="1"/>
+    <col min="25" max="25" width="16.58203125" customWidth="1" style="1"/>
+    <col min="26" max="26" width="10.6640625" customWidth="1" style="1"/>
+    <col min="27" max="27" width="8.33203125" customWidth="1" style="1"/>
+    <col min="28" max="28" width="15.1640625" customWidth="1" style="1"/>
+    <col min="29" max="30" width="8.58203125" customWidth="1" style="1"/>
+    <col min="31" max="31" width="13.4140625" customWidth="1" style="1"/>
+    <col min="32" max="32" width="13.75" customWidth="1" style="1"/>
+    <col min="33" max="33" width="14.58203125" customWidth="1" style="1"/>
+    <col min="34" max="34" width="17.4140625" customWidth="1" style="1"/>
+    <col min="35" max="35" width="8.58203125" customWidth="1" style="1"/>
+    <col min="36" max="36" width="12.5" customWidth="1" style="1"/>
+    <col min="37" max="37" width="8.58203125" customWidth="1" style="1"/>
+    <col min="38" max="39" width="8.33203125" customWidth="1" style="1"/>
+    <col min="40" max="40" width="15" customWidth="1" style="1"/>
+    <col min="41" max="41" width="13.25" customWidth="1" style="1"/>
+    <col min="42" max="45" width="11.83203125" customWidth="1" style="1"/>
+    <col min="46" max="46" width="18.4140625" customWidth="1" style="1"/>
+    <col min="47" max="47" width="12.25" customWidth="1" style="1"/>
+    <col min="48" max="48" width="11.9140625" customWidth="1" style="1"/>
+    <col min="49" max="49" width="19.58203125" customWidth="1" style="1"/>
+    <col min="50" max="50" width="12.6640625" customWidth="1" style="1"/>
+    <col min="51" max="51" width="9" customWidth="1" style="1"/>
+    <col min="52" max="52" width="7" customWidth="1" style="1"/>
+    <col min="53" max="53" width="11.75" customWidth="1" style="1"/>
+    <col min="54" max="54" width="19.75" customWidth="1" style="1"/>
+    <col min="55" max="55" width="5.08203125" customWidth="1" style="1"/>
+    <col min="56" max="56" width="8.5" customWidth="1" style="1"/>
+    <col min="57" max="57" width="13.5" customWidth="1" style="1"/>
+    <col min="58" max="58" width="14.6640625" customWidth="1" style="1"/>
+    <col min="59" max="59" width="10.1640625" customWidth="1" style="1"/>
+    <col min="60" max="60" width="8.25" customWidth="1" style="1"/>
+    <col min="61" max="67" width="8.33203125" customWidth="1" style="1"/>
+    <col min="68" max="70" width="11.25" customWidth="1" style="1"/>
+    <col min="71" max="71" width="6.58203125" customWidth="1" style="1"/>
+    <col min="72" max="73" width="8" customWidth="1" style="1"/>
+    <col min="74" max="74" width="7.33203125" customWidth="1" style="1"/>
+    <col min="75" max="76" width="8.5" customWidth="1" style="1"/>
+    <col min="77" max="78" width="7.83203125" customWidth="1" style="1"/>
+    <col min="79" max="79" width="22.1640625" customWidth="1" style="1"/>
+    <col min="80" max="80" width="13.5" customWidth="1" style="1"/>
+    <col min="81" max="81" width="21.1640625" customWidth="1" style="1"/>
+    <col min="82" max="82" width="15.75" customWidth="1" style="1"/>
+    <col min="83" max="83" width="15.58203125" customWidth="1" style="1"/>
+    <col min="84" max="84" width="12.83203125" customWidth="1" style="1"/>
+    <col min="85" max="85" width="16.1640625" customWidth="1" style="1"/>
+    <col min="86" max="86" width="9" customWidth="1" style="1"/>
+    <col min="87" max="87" width="16" customWidth="1" style="1"/>
+    <col min="88" max="89" width="12.83203125" customWidth="1" style="1"/>
+    <col min="90" max="90" width="23.58203125" customWidth="1" style="1"/>
+    <col min="91" max="91" width="12.83203125" customWidth="1" style="1"/>
+    <col min="92" max="92" width="17.08203125" customWidth="1" style="1"/>
+    <col min="93" max="98" width="9" customWidth="1" style="1"/>
+    <col min="99" max="99" width="14" customWidth="1" style="1"/>
+    <col min="100" max="100" width="8" customWidth="1" style="1"/>
+    <col min="101" max="101" width="9" customWidth="1" style="1"/>
+    <col min="102" max="102" width="11.08203125" customWidth="1" style="1"/>
+    <col min="103" max="103" width="13.75" customWidth="1" style="1"/>
+    <col min="104" max="109" width="9" customWidth="1" style="1"/>
+    <col min="110" max="110" width="15.5" customWidth="1" style="1"/>
+    <col min="111" max="113" width="9" customWidth="1" style="1"/>
+    <col min="114" max="16384" width="9" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="B1" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="BV1" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="BW1" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="BX1" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="BY1" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="BZ1" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="CA1" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="CB1" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="CC1" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="CD1" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="CE1" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="CF1" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="CG1" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="CH1" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="CI1" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="CJ1" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="CK1" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="CL1" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="CM1" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="CN1" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="CO1" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="CP1" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="CQ1" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="CR1" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="BW1" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="BX1" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="BY1" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="BZ1" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="CA1" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="CB1" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="CC1" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="CD1" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="CE1" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="CF1" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="CG1" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="CH1" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="CI1" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="CJ1" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="CK1" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="CL1" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="CM1" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="CN1" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="CO1" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="CP1" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="CQ1" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="CR1" s="1" t="s">
-        <v>227</v>
-      </c>
       <c r="CS1" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="2" spans="1:113" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AO2" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AP2" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AQ2" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AR2" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AS2" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AT2" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AU2" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AV2" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AW2" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AX2" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AY2" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AZ2" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="BA2" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="BB2" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="BC2" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="BD2" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="BE2" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="BF2" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="BG2" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="BH2" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="BI2" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="BJ2" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="BK2" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="BL2" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="BM2" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="BN2" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="BO2" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="BP2" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="BQ2" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="BR2" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="BS2" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="BT2" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="BU2" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="BV2" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="BW2" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="BX2" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="BY2" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="BZ2" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="CA2" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="CB2" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="CC2" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="CD2" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="CE2" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="CF2" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="CG2" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="CH2" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="CI2" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="CJ2" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="CK2" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="CL2" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="CM2" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="CN2" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="CO2" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="CP2" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="CQ2" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="CR2" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="CS2" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="CT2" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="CU2" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="CV2" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="CW2" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="CX2" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="CY2" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="CZ2" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="DA2" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="DB2" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="DC2" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="DD2" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="DE2" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="DF2" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="DG2" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="DH2" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="DI2" s="1" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="3" spans="1:113" x14ac:dyDescent="0.25">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -4338,112 +4526,112 @@
         <v>2</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="O3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="AC3" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="P3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="AB3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC3" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="AD3" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="AE3" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="AF3" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="AG3" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AH3" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="AI3" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="AJ3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="AK3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AL3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AM3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AN3" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="AO3" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AP3" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AQ3" s="1" t="s">
         <v>2</v>
@@ -4455,226 +4643,226 @@
         <v>2</v>
       </c>
       <c r="AT3" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AU3" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="AV3" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="AW3" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="AX3" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AY3" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="AZ3" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="BA3" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="BB3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="BC3" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="BD3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="BE3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="BF3" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="BG3" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="BH3" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="BI3" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="BJ3" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="BK3" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="BL3" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="BM3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="BN3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="BO3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="BP3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="BQ3" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="BR3" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="BS3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="BT3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU3" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="BP3" s="1" t="s">
+      <c r="BV3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="BW3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="BX3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="BY3" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="BZ3" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="BQ3" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="BR3" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="BS3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="BT3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="BU3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="BV3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="BW3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="BX3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="BY3" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="BZ3" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="CA3" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="CB3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="CC3" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="CD3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="CE3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="CF3" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="CG3" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="CH3" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="CI3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="CJ3" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="CK3" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="CL3" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="CM3" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="CN3" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="CO3" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="CP3" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="CQ3" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="CR3" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="CS3" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="CT3" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="CU3" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="CV3" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="CW3" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="CX3" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="CY3" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="CZ3" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="DA3" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="DB3" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="DC3" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="DD3" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="DE3" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="DF3" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="DG3" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="DH3" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="DI3" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="4" spans="1:113" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="1" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="6" spans="1:113" x14ac:dyDescent="0.25">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="1" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="8" spans="1:113" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AC8" s="1">
         <v>2</v>
@@ -4683,13 +4871,13 @@
         <v>1</v>
       </c>
       <c r="AO8" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AT8" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AX8" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AZ8" s="1">
         <v>1</v>
@@ -4698,63 +4886,63 @@
         <v>1</v>
       </c>
       <c r="CB8" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="CD8" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="CG8" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="CH8" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="CI8" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="CJ8" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="CY8" s="1" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="10" spans="1:113" x14ac:dyDescent="0.25">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="G10" s="1">
         <v>3</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AC10" s="1">
         <v>1</v>
       </c>
       <c r="AG10" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="BD10" s="1">
         <v>1</v>
       </c>
       <c r="BO10" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="BV10" s="1">
         <v>0</v>
@@ -4766,68 +4954,68 @@
         <v>1</v>
       </c>
       <c r="BY10" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="CU10" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="I11" s="1">
+        <v>1</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="AC11" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG11" s="1" t="s">
         <v>412</v>
       </c>
-    </row>
-    <row r="11" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="I11" s="1">
-        <v>1</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="AC11" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG11" s="1" t="s">
-        <v>410</v>
-      </c>
       <c r="BD11" s="1">
         <v>1</v>
       </c>
       <c r="CU11" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="DD11" s="1">
+        <v>1</v>
+      </c>
+      <c r="DF11" s="1">
+        <v>1</v>
+      </c>
+      <c r="DG11" s="1">
+        <v>1</v>
+      </c>
+      <c r="DH11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="DD11" s="1">
-        <v>1</v>
-      </c>
-      <c r="DF11" s="1">
-        <v>1</v>
-      </c>
-      <c r="DG11" s="1">
-        <v>1</v>
-      </c>
-      <c r="DH11" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="I12" s="1">
-        <v>1</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>414</v>
-      </c>
       <c r="L12" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AC12" s="1">
         <v>2</v>
@@ -4839,10 +5027,10 @@
         <v>99</v>
       </c>
       <c r="CG12" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="CN12" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="CO12" s="1">
         <v>-0.8</v>
@@ -4851,27 +5039,27 @@
         <v>10</v>
       </c>
       <c r="CX12" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="DH12" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I13" s="1">
         <v>1</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AC13" s="1">
         <v>2</v>
@@ -4883,10 +5071,10 @@
         <v>99</v>
       </c>
       <c r="CG13" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="CN13" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="CO13" s="1">
         <v>-0.8</v>
@@ -4895,51 +5083,51 @@
         <v>10</v>
       </c>
       <c r="CX13" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="DH13" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="G15" s="1">
         <v>3</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AC15" s="1">
         <v>1</v>
       </c>
       <c r="AG15" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="BD15" s="1">
         <v>1</v>
       </c>
       <c r="BO15" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="BP15" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="BT15" s="1">
         <v>20</v>
@@ -4954,10 +5142,10 @@
         <v>1</v>
       </c>
       <c r="BY15" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="CN15" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="CO15" s="1">
         <v>3</v>
@@ -4966,33 +5154,33 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="I16" s="1">
         <v>1</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AC16" s="1">
         <v>1</v>
       </c>
       <c r="AG16" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="BD16" s="1">
         <v>1</v>
       </c>
       <c r="CU16" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="DD16" s="1">
         <v>1</v>
@@ -5007,15 +5195,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AC17" s="1">
         <v>2</v>
@@ -5024,13 +5212,13 @@
         <v>1</v>
       </c>
       <c r="AO17" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AT17" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AX17" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AZ17" s="1">
         <v>1</v>
@@ -5039,7 +5227,7 @@
         <v>1</v>
       </c>
       <c r="BJ17" s="1">
-        <v>1.1000000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="BK17" s="1">
         <v>1</v>
@@ -5048,42 +5236,42 @@
         <v>1</v>
       </c>
       <c r="CB17" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="CG17" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="CH17" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="CI17" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="CJ17" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="CY17" s="1" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="18" spans="1:112" x14ac:dyDescent="0.25">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I18" s="1">
         <v>1</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AC18" s="1">
         <v>1</v>
       </c>
       <c r="AG18" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="BD18" s="1">
         <v>1</v>
@@ -5092,10 +5280,10 @@
         <v>0.5</v>
       </c>
       <c r="CB18" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="CG18" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="DD18" s="1">
         <v>1</v>
@@ -5110,27 +5298,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I19" s="1">
         <v>1</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AC19" s="1">
         <v>1</v>
       </c>
       <c r="AG19" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="BD19" s="1">
         <v>1</v>
@@ -5139,10 +5327,10 @@
         <v>0.5</v>
       </c>
       <c r="CB19" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="CG19" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="DD19" s="1">
         <v>1</v>
@@ -5157,33 +5345,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="I20" s="1">
+        <v>1</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="L20" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="I20" s="1">
-        <v>1</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>442</v>
-      </c>
       <c r="AC20" s="1">
         <v>1</v>
       </c>
       <c r="AG20" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="BD20" s="1">
         <v>1</v>
       </c>
       <c r="CU20" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="DD20" s="1">
         <v>1</v>
@@ -5198,21 +5386,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I21" s="1">
         <v>1</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AC21" s="1">
         <v>2</v>
@@ -5224,36 +5412,36 @@
         <v>99</v>
       </c>
       <c r="CG21" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="CN21" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="CR21" s="1">
         <v>5</v>
       </c>
       <c r="CX21" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="DH21" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="A22" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I22" s="1">
         <v>1</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AC22" s="1">
         <v>2</v>
@@ -5265,60 +5453,60 @@
         <v>99</v>
       </c>
       <c r="CG22" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="CN22" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="CR22" s="1">
         <v>5</v>
       </c>
       <c r="CX22" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="DH22" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="A24" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="G24" s="1">
         <v>3</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AC24" s="1">
         <v>1</v>
       </c>
       <c r="AG24" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="BD24" s="1">
         <v>1</v>
       </c>
       <c r="BO24" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="BP24" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="BT24" s="1">
         <v>40</v>
@@ -5336,16 +5524,16 @@
         <v>1</v>
       </c>
       <c r="BY24" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="CA24" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="CN24" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="CO24" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="CR24" s="1">
         <v>99999</v>
@@ -5354,33 +5542,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="A25" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="I25" s="1">
         <v>1</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AC25" s="1">
         <v>1</v>
       </c>
       <c r="AG25" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="BD25" s="1">
         <v>1</v>
       </c>
       <c r="CU25" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="DD25" s="1">
         <v>1</v>
@@ -5392,18 +5580,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="26">
       <c r="A26" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AC26" s="1">
         <v>2</v>
@@ -5412,57 +5600,57 @@
         <v>1</v>
       </c>
       <c r="AO26" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AT26" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="AX26" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="AZ26" s="1">
+        <v>1</v>
+      </c>
+      <c r="BD26" s="1">
+        <v>1</v>
+      </c>
+      <c r="CA26" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="CB26" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="CD26" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="CG26" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="CH26" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="CI26" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="CJ26" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="CY26" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="AX26" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="AZ26" s="1">
-        <v>1</v>
-      </c>
-      <c r="BD26" s="1">
-        <v>1</v>
-      </c>
-      <c r="CA26" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="CB26" s="1" t="s">
+      <c r="O27" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="CD26" s="1" t="s">
+      <c r="Q27" s="1" t="s">
         <v>464</v>
-      </c>
-      <c r="CG26" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="CH26" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="CI26" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="CJ26" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="CY26" s="1" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="27" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="O27" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="Q27" s="1" t="s">
-        <v>462</v>
       </c>
       <c r="AC27" s="1">
         <v>2</v>
@@ -5471,63 +5659,63 @@
         <v>1</v>
       </c>
       <c r="AO27" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AT27" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="AX27" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="AZ27" s="1">
+        <v>1</v>
+      </c>
+      <c r="BD27" s="1">
+        <v>1</v>
+      </c>
+      <c r="CA27" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="CB27" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="CD27" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="CG27" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="CH27" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="CI27" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="CJ27" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="CY27" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="AX27" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="AZ27" s="1">
-        <v>1</v>
-      </c>
-      <c r="BD27" s="1">
-        <v>1</v>
-      </c>
-      <c r="CA27" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="CB27" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="CD27" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="CG27" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="CH27" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="CI27" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="CJ27" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="CY27" s="1" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="28" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>392</v>
-      </c>
       <c r="I28" s="1">
         <v>1</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AC28" s="1">
         <v>1</v>
       </c>
       <c r="AG28" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="BD28" s="1">
         <v>1</v>
@@ -5536,10 +5724,10 @@
         <v>0.5</v>
       </c>
       <c r="CB28" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="CG28" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="DD28" s="1">
         <v>1</v>
@@ -5551,27 +5739,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="29">
       <c r="A29" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I29" s="1">
         <v>1</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AC29" s="1">
         <v>1</v>
       </c>
       <c r="AG29" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="BD29" s="1">
         <v>1</v>
@@ -5580,10 +5768,10 @@
         <v>0.5</v>
       </c>
       <c r="CB29" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="CG29" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="DD29" s="1">
         <v>1</v>
@@ -5595,33 +5783,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="30">
       <c r="A30" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="I30" s="1">
         <v>1</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AC30" s="1">
         <v>1</v>
       </c>
       <c r="AG30" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="BD30" s="1">
         <v>1</v>
       </c>
       <c r="CU30" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="DD30" s="1">
         <v>1</v>
@@ -5633,21 +5821,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="31">
       <c r="A31" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I31" s="1">
         <v>1</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="N31" s="1">
         <v>1</v>
@@ -5656,16 +5844,16 @@
         <v>1</v>
       </c>
       <c r="AG31" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="BD31" s="1">
         <v>1</v>
       </c>
       <c r="BO31" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="CN31" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="CR31" s="1">
         <v>99999</v>
@@ -5680,12 +5868,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="32">
       <c r="A32" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I32" s="1">
         <v>1</v>
@@ -5694,10 +5882,10 @@
         <v>1</v>
       </c>
       <c r="AG32" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AT32" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="BD32" s="1">
         <v>1</v>
@@ -5712,21 +5900,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="33">
       <c r="A33" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I33" s="1">
         <v>1</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AC33" s="1">
         <v>2</v>
@@ -5738,10 +5926,10 @@
         <v>99</v>
       </c>
       <c r="CG33" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="CN33" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="CO33" s="1">
         <v>-0.8</v>
@@ -5753,27 +5941,27 @@
         <v>7</v>
       </c>
       <c r="CX33" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="DH33" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="34">
       <c r="A34" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I34" s="1">
         <v>1</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AC34" s="1">
         <v>2</v>
@@ -5785,10 +5973,10 @@
         <v>99</v>
       </c>
       <c r="CG34" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="CN34" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="CO34" s="1">
         <v>-0.8</v>
@@ -5800,47 +5988,47 @@
         <v>7</v>
       </c>
       <c r="CX34" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="DH34" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="37">
       <c r="A37" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AC37" s="1">
         <v>2</v>
       </c>
       <c r="AT37" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="BD37" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="38">
       <c r="A38" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I38" s="1">
         <v>1</v>
@@ -5855,24 +6043,24 @@
         <v>1</v>
       </c>
       <c r="BP38" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="DH38" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="39">
       <c r="A39" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I39" s="1">
         <v>1</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AC39" s="1">
         <v>2</v>
@@ -5884,19 +6072,19 @@
         <v>99</v>
       </c>
       <c r="BP39" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="BS39" s="1">
         <v>0.5</v>
       </c>
       <c r="CB39" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="CG39" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="CN39" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="CO39" s="1">
         <v>-0.8</v>
@@ -5905,47 +6093,47 @@
         <v>10</v>
       </c>
       <c r="CX39" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="DH39" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="40">
       <c r="A40" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AC40" s="1">
         <v>2</v>
       </c>
       <c r="AT40" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="BD40" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="41">
       <c r="A41" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I41" s="1">
         <v>1</v>
@@ -5960,24 +6148,24 @@
         <v>1</v>
       </c>
       <c r="BP41" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="DH41" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="42">
       <c r="A42" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I42" s="1">
         <v>1</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AC42" s="1">
         <v>2</v>
@@ -5989,65 +6177,65 @@
         <v>99</v>
       </c>
       <c r="BP42" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="BS42" s="1">
         <v>0.5</v>
       </c>
       <c r="CB42" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="CG42" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="CN42" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="CR42" s="1">
         <v>5</v>
       </c>
       <c r="CX42" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="DH42" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="43">
       <c r="A43" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AC43" s="1">
         <v>2</v>
       </c>
       <c r="AT43" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="BD43" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="44">
       <c r="A44" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I44" s="1">
         <v>1</v>
@@ -6062,24 +6250,24 @@
         <v>1</v>
       </c>
       <c r="BP44" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="DH44" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="45">
       <c r="A45" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I45" s="1">
         <v>1</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AC45" s="1">
         <v>2</v>
@@ -6091,19 +6279,19 @@
         <v>99</v>
       </c>
       <c r="BP45" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="BS45" s="1">
         <v>0.5</v>
       </c>
       <c r="CB45" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="CG45" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="CN45" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="CO45" s="1">
         <v>-0.8</v>
@@ -6115,24 +6303,24 @@
         <v>7</v>
       </c>
       <c r="CX45" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="DH45" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="46">
       <c r="A46" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I46" s="1">
         <v>1</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AC46" s="1">
         <v>1</v>
@@ -6141,10 +6329,10 @@
         <v>1</v>
       </c>
       <c r="AG46" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AX46" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AZ46" s="1">
         <v>1</v>
@@ -6168,52 +6356,52 @@
         <v>1</v>
       </c>
     </row>
-    <row r="625" spans="90:90" x14ac:dyDescent="0.25">
+    <row r="625">
       <c r="CL625" s="1">
         <v>0.15</v>
       </c>
     </row>
-    <row r="627" spans="90:90" x14ac:dyDescent="0.25">
+    <row r="627">
       <c r="CL627" s="1">
         <v>0.2</v>
       </c>
     </row>
-    <row r="628" spans="90:90" x14ac:dyDescent="0.25">
+    <row r="628">
       <c r="CL628" s="1">
         <v>0.1</v>
       </c>
     </row>
-    <row r="630" spans="90:90" x14ac:dyDescent="0.25">
+    <row r="630">
       <c r="CL630" s="1">
         <v>0.2</v>
       </c>
     </row>
-    <row r="637" spans="90:90" x14ac:dyDescent="0.25">
+    <row r="637">
       <c r="CL637" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="639" spans="90:90" x14ac:dyDescent="0.25">
+    <row r="639">
       <c r="CL639" s="1">
         <v>0.4</v>
       </c>
     </row>
-    <row r="640" spans="90:90" x14ac:dyDescent="0.25">
+    <row r="640">
       <c r="CL640" s="1">
         <v>0.6</v>
       </c>
     </row>
-    <row r="643" spans="90:90" x14ac:dyDescent="0.25">
+    <row r="643">
       <c r="CL643" s="1">
         <v>0.5</v>
       </c>
     </row>
-    <row r="644" spans="90:90" x14ac:dyDescent="0.25">
+    <row r="644">
       <c r="CL644" s="1">
-        <v>0.66700000000000004</v>
-      </c>
-    </row>
-    <row r="645" spans="90:90" x14ac:dyDescent="0.25">
+        <v>0.667</v>
+      </c>
+    </row>
+    <row r="645">
       <c r="CL645" s="1">
         <v>0.2</v>
       </c>
@@ -6222,6 +6410,7 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -6231,111 +6420,111 @@
   <dimension ref="A1:Q10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13" style="1" customWidth="1"/>
-    <col min="2" max="2" width="31.25" style="1" customWidth="1"/>
-    <col min="3" max="6" width="9" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.75" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15" style="1" customWidth="1"/>
-    <col min="9" max="13" width="9" style="1" customWidth="1"/>
-    <col min="14" max="14" width="16.08203125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="9.5" style="1" customWidth="1"/>
-    <col min="16" max="16" width="9" style="1" customWidth="1"/>
-    <col min="17" max="17" width="12.83203125" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="13" customWidth="1" style="1"/>
+    <col min="2" max="2" width="31.25" customWidth="1" style="1"/>
+    <col min="3" max="6" width="9" customWidth="1" style="1"/>
+    <col min="7" max="7" width="18.75" customWidth="1" style="1"/>
+    <col min="8" max="8" width="15" customWidth="1" style="1"/>
+    <col min="9" max="13" width="9" customWidth="1" style="1"/>
+    <col min="14" max="14" width="16.08203125" customWidth="1" style="1"/>
+    <col min="15" max="15" width="9.5" customWidth="1" style="1"/>
+    <col min="16" max="16" width="9" customWidth="1" style="1"/>
+    <col min="17" max="17" width="12.83203125" customWidth="1" style="1"/>
+    <col min="18" max="16384" width="9" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -6346,150 +6535,151 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="H4" s="1">
         <v>1</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>513</v>
-      </c>
       <c r="H5" s="1">
         <v>1</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="H6" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="H7" s="1">
         <v>1</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="Q7" s="1" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>520</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="H8" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="H9" s="1">
-        <v>1</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>519</v>
-      </c>
       <c r="Q9" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="H10" s="1">
         <v>1</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -6498,36 +6688,36 @@
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.1640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="1" customWidth="1"/>
-    <col min="4" max="4" width="27.5" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="11.33203125" customWidth="1" style="1"/>
+    <col min="2" max="2" width="13.1640625" customWidth="1" style="1"/>
+    <col min="3" max="3" width="15" customWidth="1" style="1"/>
+    <col min="4" max="4" width="27.5" customWidth="1" style="1"/>
+    <col min="5" max="16384" width="9" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -6535,52 +6725,53 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -6589,52 +6780,52 @@
   <dimension ref="A1:J4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="1" customWidth="1"/>
-    <col min="5" max="10" width="9" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="15.25" customWidth="1" style="1"/>
+    <col min="2" max="2" width="9" customWidth="1" style="1"/>
+    <col min="3" max="3" width="27.25" customWidth="1" style="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1" style="1"/>
+    <col min="5" max="10" width="9" customWidth="1" style="1"/>
+    <col min="11" max="16384" width="9" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="I1" s="1" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -6648,33 +6839,33 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E4" s="1">
         <v>200</v>
@@ -6687,6 +6878,7 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -6695,89 +6887,89 @@
   <dimension ref="A1:L4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28" style="1" customWidth="1"/>
-    <col min="3" max="4" width="10.08203125" style="1" customWidth="1"/>
-    <col min="5" max="10" width="11.25" style="1" customWidth="1"/>
-    <col min="11" max="11" width="6.33203125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="15.25" customWidth="1" style="1"/>
+    <col min="2" max="2" width="28" customWidth="1" style="1"/>
+    <col min="3" max="4" width="10.08203125" customWidth="1" style="1"/>
+    <col min="5" max="10" width="11.25" customWidth="1" style="1"/>
+    <col min="11" max="11" width="6.33203125" customWidth="1" style="1"/>
+    <col min="12" max="12" width="9" customWidth="1" style="1"/>
+    <col min="13" max="16384" width="9" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -6785,42 +6977,42 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="I4" s="1">
         <v>1</v>
@@ -6836,6 +7028,7 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -6845,50 +7038,50 @@
   <dimension ref="A2:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.08203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.25" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="47.83203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" style="1" customWidth="1"/>
-    <col min="7" max="9" width="9" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.83203125" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="19.08203125" customWidth="1" style="1"/>
+    <col min="2" max="2" width="16.25" customWidth="1" style="1"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1" style="1"/>
+    <col min="4" max="4" width="47.83203125" customWidth="1" style="1"/>
+    <col min="5" max="5" width="10.25" customWidth="1" style="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1" style="1"/>
+    <col min="7" max="9" width="9" customWidth="1" style="1"/>
+    <col min="10" max="10" width="11.83203125" customWidth="1" style="1"/>
+    <col min="11" max="16384" width="9" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -6902,27 +7095,28 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>581</v>
+        <v>567</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -6931,84 +7125,84 @@
   <dimension ref="A1:I3"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.9140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14" style="1" customWidth="1"/>
-    <col min="6" max="7" width="15.1640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.9140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.75" style="1"/>
+    <col min="1" max="1" width="7.5" customWidth="1" style="1"/>
+    <col min="2" max="2" width="10.6640625" customWidth="1" style="1"/>
+    <col min="3" max="3" width="21.9140625" customWidth="1" style="1"/>
+    <col min="4" max="4" width="16.25" customWidth="1" style="1"/>
+    <col min="5" max="5" width="14" customWidth="1" style="1"/>
+    <col min="6" max="7" width="15.1640625" customWidth="1" style="1"/>
+    <col min="8" max="8" width="12.9140625" customWidth="1" style="1"/>
+    <col min="9" max="9" width="14" customWidth="1" style="1"/>
+    <col min="10" max="16384" width="8.75" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>2</v>
@@ -7032,6 +7226,7 @@
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 

--- a/Excel/一方通行/艾拉.xlsx
+++ b/Excel/一方通行/艾拉.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\一方通行\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C0E643B-98D0-493D-A44B-13F464B0812D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E80C6AE-7F2D-45D2-B928-F1539EE12BC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <sheet name="ContractData" sheetId="11" r:id="rId8"/>
     <sheet name="SpineData" sheetId="12" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -47,6 +47,30 @@
   </authors>
   <commentList>
     <comment ref="AK1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>PC:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+0:干员 1:敌人 2:仅技能条 3:技能+血条</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AM1" authorId="0" shapeId="0" xr:uid="{9BF3781C-EE4F-4519-81B7-7908C6A4F4D4}">
       <text>
         <r>
           <rPr>
@@ -299,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="590">
   <si>
     <t>Id</t>
   </si>
@@ -388,9 +412,6 @@
     <t>可选技能</t>
   </si>
   <si>
-    <t>血条类型</t>
-  </si>
-  <si>
     <t>高度</t>
   </si>
   <si>
@@ -2051,14 +2072,41 @@
   </si>
   <si>
     <t>BackSkelPath</t>
+  </si>
+  <si>
+    <t>血条</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>技力条</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpBarType</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>小型:蓝</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>小型:绿</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2070,6 +2118,34 @@
       <color theme="1"/>
       <name val="宋体"/>
       <family val="3"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2105,19 +2181,19 @@
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2422,11 +2498,11 @@
   <dimension ref="A2:B4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9" customWidth="1" style="1"/>
-    <col min="3" max="16384" width="9" customWidth="1" style="1"/>
+    <col min="1" max="3" width="9" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2434,7 +2510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -2442,7 +2518,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -2453,1290 +2529,1129 @@
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BT7"/>
+  <dimension ref="A1:BU7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.58203125" customWidth="1" style="2"/>
-    <col min="2" max="2" width="9" customWidth="1" style="2"/>
-    <col min="3" max="3" width="9" customWidth="1" style="2"/>
-    <col min="4" max="4" width="8.58203125" customWidth="1" style="2"/>
-    <col min="5" max="5" width="8.58203125" customWidth="1" style="2"/>
-    <col min="6" max="6" width="19.58203125" customWidth="1" style="2"/>
-    <col min="7" max="7" width="8.25" customWidth="1" style="2"/>
-    <col min="8" max="8" width="9" customWidth="1" style="2"/>
-    <col min="9" max="9" width="9" customWidth="1" style="2"/>
-    <col min="10" max="10" width="9" customWidth="1" style="2"/>
-    <col min="11" max="11" width="6" customWidth="1" style="2"/>
-    <col min="12" max="12" width="4.08203125" customWidth="1" style="2"/>
-    <col min="13" max="13" width="5.58203125" customWidth="1" style="2"/>
-    <col min="14" max="14" width="4" customWidth="1" style="2"/>
-    <col min="15" max="15" width="7.75" customWidth="1" style="2"/>
-    <col min="16" max="16" width="10.83203125" customWidth="1" style="2"/>
-    <col min="17" max="17" width="3.83203125" customWidth="1" style="2"/>
-    <col min="18" max="18" width="3.83203125" customWidth="1" style="2"/>
-    <col min="19" max="19" width="3.58203125" customWidth="1" style="2"/>
-    <col min="20" max="20" width="3.58203125" customWidth="1" style="2"/>
-    <col min="21" max="21" width="10.25" customWidth="1" style="2"/>
-    <col min="22" max="22" width="9.58203125" customWidth="1" style="2"/>
-    <col min="23" max="23" width="10.75" customWidth="1" style="2"/>
-    <col min="24" max="24" width="12.83203125" customWidth="1" style="2"/>
-    <col min="25" max="25" width="13.08203125" customWidth="1" style="2"/>
-    <col min="26" max="26" width="10.75" customWidth="1" style="2"/>
-    <col min="27" max="27" width="9" customWidth="1" style="2"/>
-    <col min="28" max="28" width="9" customWidth="1" style="2"/>
-    <col min="29" max="29" width="8" customWidth="1" style="2"/>
-    <col min="30" max="30" width="17.08203125" customWidth="1" style="2"/>
-    <col min="31" max="31" width="9" customWidth="1" style="2"/>
-    <col min="32" max="32" width="9" customWidth="1" style="2"/>
-    <col min="33" max="33" width="9.75" customWidth="1" style="2"/>
-    <col min="34" max="34" width="7.83203125" customWidth="1" style="2"/>
-    <col min="35" max="35" width="15.83203125" customWidth="1" style="2"/>
-    <col min="36" max="36" width="13.83203125" customWidth="1" style="2"/>
-    <col min="37" max="37" width="34.5" customWidth="1" style="2"/>
-    <col min="38" max="38" width="9.83203125" customWidth="1" style="2"/>
-    <col min="39" max="39" width="9.83203125" customWidth="1" style="2"/>
-    <col min="40" max="40" width="9" customWidth="1" style="2"/>
-    <col min="41" max="41" width="9" customWidth="1" style="2"/>
-    <col min="42" max="42" width="9" customWidth="1" style="2"/>
-    <col min="43" max="43" width="9" customWidth="1" style="2"/>
-    <col min="44" max="44" width="12.5" customWidth="1" style="2"/>
-    <col min="45" max="45" width="9" customWidth="1" style="2"/>
-    <col min="46" max="46" width="9" customWidth="1" style="2"/>
-    <col min="47" max="47" width="9" customWidth="1" style="2"/>
-    <col min="48" max="48" width="9" customWidth="1" style="2"/>
-    <col min="49" max="49" width="9" customWidth="1" style="2"/>
-    <col min="50" max="50" width="9" customWidth="1" style="2"/>
-    <col min="51" max="51" width="24.33203125" customWidth="1" style="2"/>
-    <col min="52" max="52" width="9" customWidth="1" style="2"/>
-    <col min="53" max="53" width="17.75" customWidth="1" style="2"/>
-    <col min="54" max="54" width="7.83203125" customWidth="1" style="2"/>
-    <col min="55" max="55" width="9" customWidth="1" style="2"/>
-    <col min="56" max="56" width="9" customWidth="1" style="2"/>
-    <col min="57" max="57" width="24.25" customWidth="1" style="2"/>
-    <col min="58" max="58" width="13.25" customWidth="1" style="2"/>
-    <col min="59" max="59" width="16.08203125" customWidth="1" style="2"/>
-    <col min="60" max="60" width="8" customWidth="1" style="2"/>
-    <col min="61" max="61" width="9" customWidth="1" style="2"/>
-    <col min="62" max="62" width="9" customWidth="1" style="2"/>
-    <col min="63" max="63" width="9" customWidth="1" style="2"/>
-    <col min="64" max="64" width="9" customWidth="1" style="2"/>
-    <col min="65" max="65" width="39.58203125" customWidth="1" style="2"/>
-    <col min="66" max="66" width="14" customWidth="1" style="2"/>
-    <col min="67" max="67" width="14.83203125" customWidth="1" style="2"/>
-    <col min="68" max="68" width="14" customWidth="1" style="2"/>
-    <col min="69" max="69" width="14" customWidth="1" style="2"/>
-    <col min="70" max="70" width="14" customWidth="1" style="2"/>
-    <col min="71" max="71" width="14" customWidth="1" style="2"/>
-    <col min="72" max="72" width="19.1640625" customWidth="1" style="2"/>
+    <col min="1" max="1" width="22.58203125" style="1" customWidth="1"/>
+    <col min="2" max="3" width="9" style="1" customWidth="1"/>
+    <col min="4" max="5" width="8.58203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.58203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.25" style="1" customWidth="1"/>
+    <col min="8" max="10" width="9" style="1" customWidth="1"/>
+    <col min="11" max="11" width="6" style="1" customWidth="1"/>
+    <col min="12" max="12" width="4.08203125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="5.58203125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="4" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.75" style="1" customWidth="1"/>
+    <col min="16" max="16" width="10.83203125" style="1" customWidth="1"/>
+    <col min="17" max="18" width="3.83203125" style="1" customWidth="1"/>
+    <col min="19" max="20" width="3.58203125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="10.25" style="1" customWidth="1"/>
+    <col min="22" max="22" width="9.58203125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="10.75" style="1" customWidth="1"/>
+    <col min="24" max="24" width="12.83203125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="13.08203125" style="1" customWidth="1"/>
+    <col min="26" max="26" width="10.75" style="1" customWidth="1"/>
+    <col min="27" max="28" width="9" style="1" customWidth="1"/>
+    <col min="29" max="29" width="8" style="1" customWidth="1"/>
+    <col min="30" max="30" width="17.08203125" style="1" customWidth="1"/>
+    <col min="31" max="32" width="9" style="1" customWidth="1"/>
+    <col min="33" max="33" width="9.75" style="1" customWidth="1"/>
+    <col min="34" max="34" width="7.83203125" style="1" customWidth="1"/>
+    <col min="35" max="35" width="15.83203125" style="1" customWidth="1"/>
+    <col min="36" max="36" width="13.83203125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="34.5" style="1" customWidth="1"/>
+    <col min="38" max="40" width="9.83203125" style="1" customWidth="1"/>
+    <col min="41" max="44" width="9" style="1" customWidth="1"/>
+    <col min="45" max="45" width="12.5" style="1" customWidth="1"/>
+    <col min="46" max="51" width="9" style="1" customWidth="1"/>
+    <col min="52" max="52" width="24.33203125" style="1" customWidth="1"/>
+    <col min="53" max="53" width="9" style="1" customWidth="1"/>
+    <col min="54" max="54" width="17.75" style="1" customWidth="1"/>
+    <col min="55" max="55" width="7.83203125" style="1" customWidth="1"/>
+    <col min="56" max="57" width="9" style="1" customWidth="1"/>
+    <col min="58" max="58" width="24.25" style="1" customWidth="1"/>
+    <col min="59" max="59" width="13.25" style="1" customWidth="1"/>
+    <col min="60" max="60" width="16.08203125" style="1" customWidth="1"/>
+    <col min="61" max="61" width="8" style="1" customWidth="1"/>
+    <col min="62" max="65" width="9" style="1" customWidth="1"/>
+    <col min="66" max="66" width="39.58203125" style="1" customWidth="1"/>
+    <col min="67" max="67" width="14" style="1" customWidth="1"/>
+    <col min="68" max="68" width="14.83203125" style="1" customWidth="1"/>
+    <col min="69" max="72" width="14" style="1" customWidth="1"/>
+    <col min="73" max="73" width="19.1640625" style="1" customWidth="1"/>
+    <col min="74" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2" t="s">
+    <row r="1" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="D1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AG1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AH1" s="2"/>
-      <c r="AI1" s="2"/>
-      <c r="AJ1" s="2" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AK1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AL1" s="1" t="s">
         <v>28</v>
       </c>
       <c r="AM1" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="AN1" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="AO1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AP1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AR1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AS1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AU1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AS1" s="2"/>
-      <c r="AT1" s="2" t="s">
+      <c r="AV1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AU1" s="2" t="s">
+      <c r="AW1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AV1" s="2" t="s">
+      <c r="AX1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AW1" s="2" t="s">
+      <c r="AY1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AX1" s="2" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AY1" s="2" t="s">
+      <c r="BA1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="BB1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="BC1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="BF1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="BC1" s="2"/>
-      <c r="BD1" s="2"/>
-      <c r="BE1" s="2" t="s">
+      <c r="BG1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="BF1" s="2" t="s">
+      <c r="BH1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="BG1" s="2" t="s">
+      <c r="BI1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="BH1" s="2" t="s">
+      <c r="BJ1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="BI1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="BJ1" s="2"/>
-      <c r="BK1" s="2"/>
-      <c r="BL1" s="2"/>
-      <c r="BM1" s="2"/>
-      <c r="BN1" s="2"/>
-      <c r="BO1" s="2"/>
-      <c r="BP1" s="2"/>
-      <c r="BQ1" s="2"/>
-      <c r="BR1" s="2"/>
-      <c r="BS1" s="2"/>
-      <c r="BT1" s="2"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="C2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN2" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="AO2" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AP2" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AQ2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AR2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AS2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AU2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AV2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AW2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="AX2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AY2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AZ2" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="BA2" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="BB2" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="BC2" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD2" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE2" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="BF2" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="BG2" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="BH2" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="BI2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="BJ2" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="BK2" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="BL2" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="BM2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="BN2" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="BO2" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="BP2" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="BQ2" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="BR2" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="BS2" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="BT2" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="BU2" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AE3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AG3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AH3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AI3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AJ3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AK3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="AL3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="AO3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="AQ3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AR3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="AS3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AU3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="AV3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AW3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AX3" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="AY3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="AZ3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="BB3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="BC3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="BD3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="BE3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BF3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BG3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BH3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BI3" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="BJ3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="BK3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BL3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="BM3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BN3" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="BO3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="BP3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="BQ3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="BR3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="BS3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="BT3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="BU3" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1">
+        <v>2</v>
+      </c>
+      <c r="J4" s="1">
+        <v>90</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1468</v>
+      </c>
+      <c r="M4" s="1">
+        <v>755</v>
+      </c>
+      <c r="O4" s="1">
+        <v>203</v>
+      </c>
+      <c r="Q4" s="1">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y2" s="2" t="s">
+      <c r="S4" s="1">
+        <v>12</v>
+      </c>
+      <c r="T4" s="1">
+        <v>-2</v>
+      </c>
+      <c r="U4" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="V4" s="1">
         <v>70</v>
       </c>
-      <c r="Z2" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AA2" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB2" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AC2" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AD2" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE2" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AF2" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AG2" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH2" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AI2" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AJ2" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AK2" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AL2" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AM2" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AN2" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO2" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AP2" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="AQ2" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="AR2" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="AS2" s="2" t="s">
+      <c r="Y4" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="Z4" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="AC4" s="1">
+        <v>1</v>
+      </c>
+      <c r="AI4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ4" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="AK4" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="AL4" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="AM4" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="AN4" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="AP4" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="AQ4" s="1">
+        <v>1</v>
+      </c>
+      <c r="AR4" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="AY4" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="BD4" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="BE4" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="BF4" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="BG4" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="BH4" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="BI4" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="BJ4" s="1">
+        <v>6</v>
+      </c>
+      <c r="BK4" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="BL4" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="BM4" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="BO4" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="BP4" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="BR4" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="BS4" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="BU4" s="1">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1">
+        <v>2</v>
+      </c>
+      <c r="J5" s="1">
         <v>90</v>
       </c>
-      <c r="AT2" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="AU2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AV2" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AW2" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AX2" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="AY2" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="AZ2" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="BA2" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="BB2" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="BC2" s="2" t="s">
+      <c r="K5" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M5" s="1">
         <v>100</v>
       </c>
-      <c r="BD2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="BE2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="BF2" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="BG2" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="BH2" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="BI2" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="BJ2" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="BK2" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="BL2" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="BM2" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="BN2" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="BO2" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="BP2" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="BQ2" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="BR2" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="BS2" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="BT2" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="O5" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>0</v>
+      </c>
+      <c r="S5" s="1">
+        <v>5</v>
+      </c>
+      <c r="U5" s="1">
+        <v>0</v>
+      </c>
+      <c r="V5" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="Z5" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="1">
+        <v>1</v>
+      </c>
+      <c r="AI5" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="AJ5" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="AK5" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="AL5" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM5" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="AN5" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="AP5" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="AQ5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY5" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="BD5" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="BF5" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="BG5" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="BH5" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="BI5" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="BJ5" s="1">
+        <v>6</v>
+      </c>
+      <c r="BK5" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="BL5" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="BO5" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="BP5" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="BU5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="J6" s="1">
+        <v>90</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M6" s="1">
+        <v>100</v>
+      </c>
+      <c r="O6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>0</v>
+      </c>
+      <c r="S6" s="1">
+        <v>5</v>
+      </c>
+      <c r="U6" s="1">
+        <v>0</v>
+      </c>
+      <c r="V6" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="1">
+        <v>1</v>
+      </c>
+      <c r="AI6" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="AJ6" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="AK6" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="AL6" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="AM6" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="AN6" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="AP6" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="AQ6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY6" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="BD6" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="BF6" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="BG6" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="BH6" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="BI6" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="BJ6" s="1">
+        <v>6</v>
+      </c>
+      <c r="BK6" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="BL6" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="BO6" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="BP6" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="BU6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AD3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AE3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AF3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AG3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AH3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AI3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AJ3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AK3" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="AL3" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="AM3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AN3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="AO3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AP3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AQ3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="AR3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AS3" s="2"/>
-      <c r="AT3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="AU3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AV3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AW3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AX3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="AY3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="AZ3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="BA3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="BB3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="BC3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BD3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BE3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BF3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BG3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BH3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="BI3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="BJ3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BK3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BL3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BM3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="BN3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BO3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BP3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BQ3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BR3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BS3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BT3" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="J7" s="1">
+        <v>90</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M7" s="1">
+        <v>100</v>
+      </c>
+      <c r="O7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>0</v>
+      </c>
+      <c r="S7" s="1">
+        <v>5</v>
+      </c>
+      <c r="U7" s="1">
+        <v>0</v>
+      </c>
+      <c r="V7" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="Z7" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>1</v>
+      </c>
+      <c r="AI7" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="AJ7" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="G4" s="2">
-        <v>1</v>
-      </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2">
-        <v>2</v>
-      </c>
-      <c r="J4" s="2">
-        <v>90</v>
-      </c>
-      <c r="K4" s="2">
-        <v>1468</v>
-      </c>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2">
-        <v>755</v>
-      </c>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2">
-        <v>203</v>
-      </c>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2">
+      <c r="AK7" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="AL7" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="AM7" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="AN7" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="AP7" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="AQ7" s="1">
         <v>0</v>
       </c>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2">
-        <v>12</v>
-      </c>
-      <c r="T4" s="2">
-        <v>-2</v>
-      </c>
-      <c r="U4" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="V4" s="2">
-        <v>70</v>
-      </c>
-      <c r="W4" s="2"/>
-      <c r="X4" s="2"/>
-      <c r="Y4" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="Z4" s="2">
-        <v>0.85</v>
-      </c>
-      <c r="AA4" s="2"/>
-      <c r="AB4" s="2"/>
-      <c r="AC4" s="2">
-        <v>1</v>
-      </c>
-      <c r="AD4" s="2"/>
-      <c r="AE4" s="2"/>
-      <c r="AF4" s="2"/>
-      <c r="AG4" s="2"/>
-      <c r="AH4" s="2"/>
-      <c r="AI4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ4" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="AK4" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="AL4" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="AM4" s="2"/>
-      <c r="AN4" s="2"/>
-      <c r="AO4" s="2" t="s">
+      <c r="AR7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY7" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="BD7" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="AP4" s="2">
-        <v>1</v>
-      </c>
-      <c r="AQ4" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="AR4" s="2"/>
-      <c r="AS4" s="2"/>
-      <c r="AT4" s="2"/>
-      <c r="AU4" s="2"/>
-      <c r="AV4" s="2"/>
-      <c r="AW4" s="2"/>
-      <c r="AX4" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="AY4" s="2"/>
-      <c r="AZ4" s="2"/>
-      <c r="BA4" s="2"/>
-      <c r="BB4" s="2"/>
-      <c r="BC4" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="BD4" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="BE4" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="BF4" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="BG4" s="2" t="s">
+      <c r="BF7" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="BG7" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="BH7" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="BI7" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="BH4" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="BI4" s="2">
+      <c r="BJ7" s="1">
         <v>6</v>
       </c>
-      <c r="BJ4" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="BK4" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="BL4" s="2" t="s">
+      <c r="BK7" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="BL7" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="BO7" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="BM4" s="2"/>
-      <c r="BN4" s="2" t="s">
+      <c r="BP7" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="BO4" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="BP4" s="2"/>
-      <c r="BQ4" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="BR4" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="BS4" s="2"/>
-      <c r="BT4" s="2">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="G5" s="2">
-        <v>1</v>
-      </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2">
-        <v>2</v>
-      </c>
-      <c r="J5" s="2">
-        <v>90</v>
-      </c>
-      <c r="K5" s="2">
-        <v>1000</v>
-      </c>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2">
-        <v>100</v>
-      </c>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2">
-        <v>0</v>
-      </c>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2">
-        <v>0</v>
-      </c>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2">
-        <v>5</v>
-      </c>
-      <c r="T5" s="2"/>
-      <c r="U5" s="2">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2">
-        <v>5</v>
-      </c>
-      <c r="W5" s="2"/>
-      <c r="X5" s="2"/>
-      <c r="Y5" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="Z5" s="2">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="2"/>
-      <c r="AB5" s="2"/>
-      <c r="AC5" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="2">
-        <v>1</v>
-      </c>
-      <c r="AE5" s="2"/>
-      <c r="AF5" s="2"/>
-      <c r="AG5" s="2"/>
-      <c r="AH5" s="2"/>
-      <c r="AI5" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="AJ5" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="AK5" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="AL5" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="AM5" s="2">
-        <v>1</v>
-      </c>
-      <c r="AN5" s="2"/>
-      <c r="AO5" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="AP5" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ5" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR5" s="2"/>
-      <c r="AS5" s="2"/>
-      <c r="AT5" s="2"/>
-      <c r="AU5" s="2"/>
-      <c r="AV5" s="2"/>
-      <c r="AW5" s="2"/>
-      <c r="AX5" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="AY5" s="2"/>
-      <c r="AZ5" s="2"/>
-      <c r="BA5" s="2"/>
-      <c r="BB5" s="2"/>
-      <c r="BC5" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="BD5" s="2"/>
-      <c r="BE5" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="BF5" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="BG5" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="BH5" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="BI5" s="2">
-        <v>6</v>
-      </c>
-      <c r="BJ5" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="BK5" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="BL5" s="2"/>
-      <c r="BM5" s="2"/>
-      <c r="BN5" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="BO5" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="BP5" s="2"/>
-      <c r="BQ5" s="2"/>
-      <c r="BR5" s="2"/>
-      <c r="BS5" s="2"/>
-      <c r="BT5" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="G6" s="2">
-        <v>1</v>
-      </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2">
-        <v>2</v>
-      </c>
-      <c r="J6" s="2">
-        <v>90</v>
-      </c>
-      <c r="K6" s="2">
-        <v>1000</v>
-      </c>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2">
-        <v>100</v>
-      </c>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2">
-        <v>0</v>
-      </c>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2">
-        <v>0</v>
-      </c>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2">
-        <v>5</v>
-      </c>
-      <c r="T6" s="2"/>
-      <c r="U6" s="2">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2">
-        <v>5</v>
-      </c>
-      <c r="W6" s="2"/>
-      <c r="X6" s="2"/>
-      <c r="Y6" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="Z6" s="2">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="2"/>
-      <c r="AB6" s="2"/>
-      <c r="AC6" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="2">
-        <v>1</v>
-      </c>
-      <c r="AE6" s="2"/>
-      <c r="AF6" s="2"/>
-      <c r="AG6" s="2"/>
-      <c r="AH6" s="2"/>
-      <c r="AI6" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="AJ6" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="AK6" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="AL6" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="AM6" s="2">
-        <v>1</v>
-      </c>
-      <c r="AN6" s="2"/>
-      <c r="AO6" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="AP6" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ6" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR6" s="2"/>
-      <c r="AS6" s="2"/>
-      <c r="AT6" s="2"/>
-      <c r="AU6" s="2"/>
-      <c r="AV6" s="2"/>
-      <c r="AW6" s="2"/>
-      <c r="AX6" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="AY6" s="2"/>
-      <c r="AZ6" s="2"/>
-      <c r="BA6" s="2"/>
-      <c r="BB6" s="2"/>
-      <c r="BC6" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="BD6" s="2"/>
-      <c r="BE6" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="BF6" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="BG6" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="BH6" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="BI6" s="2">
-        <v>6</v>
-      </c>
-      <c r="BJ6" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="BK6" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="BL6" s="2"/>
-      <c r="BM6" s="2"/>
-      <c r="BN6" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="BO6" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="BP6" s="2"/>
-      <c r="BQ6" s="2"/>
-      <c r="BR6" s="2"/>
-      <c r="BS6" s="2"/>
-      <c r="BT6" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="G7" s="2">
-        <v>1</v>
-      </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2">
-        <v>2</v>
-      </c>
-      <c r="J7" s="2">
-        <v>90</v>
-      </c>
-      <c r="K7" s="2">
-        <v>1000</v>
-      </c>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2">
-        <v>100</v>
-      </c>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2">
-        <v>0</v>
-      </c>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2">
-        <v>0</v>
-      </c>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2">
-        <v>5</v>
-      </c>
-      <c r="T7" s="2"/>
-      <c r="U7" s="2">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2">
-        <v>5</v>
-      </c>
-      <c r="W7" s="2"/>
-      <c r="X7" s="2"/>
-      <c r="Y7" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="Z7" s="2">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="2"/>
-      <c r="AB7" s="2"/>
-      <c r="AC7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="2">
-        <v>1</v>
-      </c>
-      <c r="AE7" s="2"/>
-      <c r="AF7" s="2"/>
-      <c r="AG7" s="2"/>
-      <c r="AH7" s="2"/>
-      <c r="AI7" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="AJ7" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="AK7" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="AL7" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="AM7" s="2">
-        <v>1</v>
-      </c>
-      <c r="AN7" s="2"/>
-      <c r="AO7" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="AP7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR7" s="2"/>
-      <c r="AS7" s="2"/>
-      <c r="AT7" s="2"/>
-      <c r="AU7" s="2"/>
-      <c r="AV7" s="2"/>
-      <c r="AW7" s="2"/>
-      <c r="AX7" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="AY7" s="2"/>
-      <c r="AZ7" s="2"/>
-      <c r="BA7" s="2"/>
-      <c r="BB7" s="2"/>
-      <c r="BC7" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="BD7" s="2"/>
-      <c r="BE7" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="BF7" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="BG7" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="BH7" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="BI7" s="2">
-        <v>6</v>
-      </c>
-      <c r="BJ7" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="BK7" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="BL7" s="2"/>
-      <c r="BM7" s="2"/>
-      <c r="BN7" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="BO7" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="BP7" s="2"/>
-      <c r="BQ7" s="2"/>
-      <c r="BR7" s="2"/>
-      <c r="BS7" s="2"/>
-      <c r="BT7" s="2">
+      <c r="BU7" s="1">
         <v>1</v>
       </c>
     </row>
@@ -3744,7 +3659,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -3754,762 +3668,762 @@
   <dimension ref="A1:DI645"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.08203125" customWidth="1" style="1"/>
-    <col min="2" max="2" width="15.58203125" customWidth="1" style="1"/>
-    <col min="3" max="3" width="7.75" customWidth="1" style="1"/>
-    <col min="4" max="4" width="16.58203125" customWidth="1" style="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1" style="1"/>
-    <col min="6" max="6" width="31.33203125" customWidth="1" style="1"/>
-    <col min="7" max="7" width="7.33203125" customWidth="1" style="1"/>
-    <col min="8" max="8" width="17.83203125" customWidth="1" style="1"/>
-    <col min="9" max="9" width="7.33203125" customWidth="1" style="1"/>
-    <col min="10" max="10" width="15.75" customWidth="1" style="1"/>
-    <col min="11" max="13" width="8.33203125" customWidth="1" style="1"/>
-    <col min="14" max="14" width="11.75" customWidth="1" style="1"/>
-    <col min="15" max="15" width="13.08203125" customWidth="1" style="1"/>
-    <col min="16" max="16" width="11.58203125" customWidth="1" style="1"/>
-    <col min="17" max="17" width="21.5" customWidth="1" style="1"/>
-    <col min="18" max="18" width="19.83203125" customWidth="1" style="1"/>
-    <col min="19" max="19" width="16.58203125" customWidth="1" style="1"/>
-    <col min="20" max="20" width="19.08203125" customWidth="1" style="1"/>
-    <col min="21" max="21" width="18.33203125" customWidth="1" style="1"/>
-    <col min="22" max="22" width="17.75" customWidth="1" style="1"/>
-    <col min="23" max="23" width="8.33203125" customWidth="1" style="1"/>
-    <col min="24" max="24" width="18.5" customWidth="1" style="1"/>
-    <col min="25" max="25" width="16.58203125" customWidth="1" style="1"/>
-    <col min="26" max="26" width="10.6640625" customWidth="1" style="1"/>
-    <col min="27" max="27" width="8.33203125" customWidth="1" style="1"/>
-    <col min="28" max="28" width="15.1640625" customWidth="1" style="1"/>
-    <col min="29" max="30" width="8.58203125" customWidth="1" style="1"/>
-    <col min="31" max="31" width="13.4140625" customWidth="1" style="1"/>
-    <col min="32" max="32" width="13.75" customWidth="1" style="1"/>
-    <col min="33" max="33" width="14.58203125" customWidth="1" style="1"/>
-    <col min="34" max="34" width="17.4140625" customWidth="1" style="1"/>
-    <col min="35" max="35" width="8.58203125" customWidth="1" style="1"/>
-    <col min="36" max="36" width="12.5" customWidth="1" style="1"/>
-    <col min="37" max="37" width="8.58203125" customWidth="1" style="1"/>
-    <col min="38" max="39" width="8.33203125" customWidth="1" style="1"/>
-    <col min="40" max="40" width="15" customWidth="1" style="1"/>
-    <col min="41" max="41" width="13.25" customWidth="1" style="1"/>
-    <col min="42" max="45" width="11.83203125" customWidth="1" style="1"/>
-    <col min="46" max="46" width="18.4140625" customWidth="1" style="1"/>
-    <col min="47" max="47" width="12.25" customWidth="1" style="1"/>
-    <col min="48" max="48" width="11.9140625" customWidth="1" style="1"/>
-    <col min="49" max="49" width="19.58203125" customWidth="1" style="1"/>
-    <col min="50" max="50" width="12.6640625" customWidth="1" style="1"/>
-    <col min="51" max="51" width="9" customWidth="1" style="1"/>
-    <col min="52" max="52" width="7" customWidth="1" style="1"/>
-    <col min="53" max="53" width="11.75" customWidth="1" style="1"/>
-    <col min="54" max="54" width="19.75" customWidth="1" style="1"/>
-    <col min="55" max="55" width="5.08203125" customWidth="1" style="1"/>
-    <col min="56" max="56" width="8.5" customWidth="1" style="1"/>
-    <col min="57" max="57" width="13.5" customWidth="1" style="1"/>
-    <col min="58" max="58" width="14.6640625" customWidth="1" style="1"/>
-    <col min="59" max="59" width="10.1640625" customWidth="1" style="1"/>
-    <col min="60" max="60" width="8.25" customWidth="1" style="1"/>
-    <col min="61" max="67" width="8.33203125" customWidth="1" style="1"/>
-    <col min="68" max="70" width="11.25" customWidth="1" style="1"/>
-    <col min="71" max="71" width="6.58203125" customWidth="1" style="1"/>
-    <col min="72" max="73" width="8" customWidth="1" style="1"/>
-    <col min="74" max="74" width="7.33203125" customWidth="1" style="1"/>
-    <col min="75" max="76" width="8.5" customWidth="1" style="1"/>
-    <col min="77" max="78" width="7.83203125" customWidth="1" style="1"/>
-    <col min="79" max="79" width="22.1640625" customWidth="1" style="1"/>
-    <col min="80" max="80" width="13.5" customWidth="1" style="1"/>
-    <col min="81" max="81" width="21.1640625" customWidth="1" style="1"/>
-    <col min="82" max="82" width="15.75" customWidth="1" style="1"/>
-    <col min="83" max="83" width="15.58203125" customWidth="1" style="1"/>
-    <col min="84" max="84" width="12.83203125" customWidth="1" style="1"/>
-    <col min="85" max="85" width="16.1640625" customWidth="1" style="1"/>
-    <col min="86" max="86" width="9" customWidth="1" style="1"/>
-    <col min="87" max="87" width="16" customWidth="1" style="1"/>
-    <col min="88" max="89" width="12.83203125" customWidth="1" style="1"/>
-    <col min="90" max="90" width="23.58203125" customWidth="1" style="1"/>
-    <col min="91" max="91" width="12.83203125" customWidth="1" style="1"/>
-    <col min="92" max="92" width="17.08203125" customWidth="1" style="1"/>
-    <col min="93" max="98" width="9" customWidth="1" style="1"/>
-    <col min="99" max="99" width="14" customWidth="1" style="1"/>
-    <col min="100" max="100" width="8" customWidth="1" style="1"/>
-    <col min="101" max="101" width="9" customWidth="1" style="1"/>
-    <col min="102" max="102" width="11.08203125" customWidth="1" style="1"/>
-    <col min="103" max="103" width="13.75" customWidth="1" style="1"/>
-    <col min="104" max="109" width="9" customWidth="1" style="1"/>
-    <col min="110" max="110" width="15.5" customWidth="1" style="1"/>
-    <col min="111" max="113" width="9" customWidth="1" style="1"/>
-    <col min="114" max="16384" width="9" customWidth="1" style="1"/>
+    <col min="1" max="1" width="21.08203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.58203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.75" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.58203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="31.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="7.33203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.83203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="7.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15.75" style="1" customWidth="1"/>
+    <col min="11" max="13" width="8.33203125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="11.75" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13.08203125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="11.58203125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="21.5" style="1" customWidth="1"/>
+    <col min="18" max="18" width="19.83203125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="16.58203125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="19.08203125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="18.33203125" style="1" customWidth="1"/>
+    <col min="22" max="22" width="17.75" style="1" customWidth="1"/>
+    <col min="23" max="23" width="8.33203125" style="1" customWidth="1"/>
+    <col min="24" max="24" width="18.5" style="1" customWidth="1"/>
+    <col min="25" max="25" width="16.58203125" style="1" customWidth="1"/>
+    <col min="26" max="26" width="10.6640625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="8.33203125" style="1" customWidth="1"/>
+    <col min="28" max="28" width="15.1640625" style="1" customWidth="1"/>
+    <col min="29" max="30" width="8.58203125" style="1" customWidth="1"/>
+    <col min="31" max="31" width="13.4140625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="13.75" style="1" customWidth="1"/>
+    <col min="33" max="33" width="14.58203125" style="1" customWidth="1"/>
+    <col min="34" max="34" width="17.4140625" style="1" customWidth="1"/>
+    <col min="35" max="35" width="8.58203125" style="1" customWidth="1"/>
+    <col min="36" max="36" width="12.5" style="1" customWidth="1"/>
+    <col min="37" max="37" width="8.58203125" style="1" customWidth="1"/>
+    <col min="38" max="39" width="8.33203125" style="1" customWidth="1"/>
+    <col min="40" max="40" width="15" style="1" customWidth="1"/>
+    <col min="41" max="41" width="13.25" style="1" customWidth="1"/>
+    <col min="42" max="45" width="11.83203125" style="1" customWidth="1"/>
+    <col min="46" max="46" width="18.4140625" style="1" customWidth="1"/>
+    <col min="47" max="47" width="12.25" style="1" customWidth="1"/>
+    <col min="48" max="48" width="11.9140625" style="1" customWidth="1"/>
+    <col min="49" max="49" width="19.58203125" style="1" customWidth="1"/>
+    <col min="50" max="50" width="12.6640625" style="1" customWidth="1"/>
+    <col min="51" max="51" width="9" style="1" customWidth="1"/>
+    <col min="52" max="52" width="7" style="1" customWidth="1"/>
+    <col min="53" max="53" width="11.75" style="1" customWidth="1"/>
+    <col min="54" max="54" width="19.75" style="1" customWidth="1"/>
+    <col min="55" max="55" width="5.08203125" style="1" customWidth="1"/>
+    <col min="56" max="56" width="8.5" style="1" customWidth="1"/>
+    <col min="57" max="57" width="13.5" style="1" customWidth="1"/>
+    <col min="58" max="58" width="14.6640625" style="1" customWidth="1"/>
+    <col min="59" max="59" width="10.1640625" style="1" customWidth="1"/>
+    <col min="60" max="60" width="8.25" style="1" customWidth="1"/>
+    <col min="61" max="67" width="8.33203125" style="1" customWidth="1"/>
+    <col min="68" max="70" width="11.25" style="1" customWidth="1"/>
+    <col min="71" max="71" width="6.58203125" style="1" customWidth="1"/>
+    <col min="72" max="73" width="8" style="1" customWidth="1"/>
+    <col min="74" max="74" width="7.33203125" style="1" customWidth="1"/>
+    <col min="75" max="76" width="8.5" style="1" customWidth="1"/>
+    <col min="77" max="78" width="7.83203125" style="1" customWidth="1"/>
+    <col min="79" max="79" width="22.1640625" style="1" customWidth="1"/>
+    <col min="80" max="80" width="13.5" style="1" customWidth="1"/>
+    <col min="81" max="81" width="21.1640625" style="1" customWidth="1"/>
+    <col min="82" max="82" width="15.75" style="1" customWidth="1"/>
+    <col min="83" max="83" width="15.58203125" style="1" customWidth="1"/>
+    <col min="84" max="84" width="12.83203125" style="1" customWidth="1"/>
+    <col min="85" max="85" width="16.1640625" style="1" customWidth="1"/>
+    <col min="86" max="86" width="9" style="1" customWidth="1"/>
+    <col min="87" max="87" width="16" style="1" customWidth="1"/>
+    <col min="88" max="89" width="12.83203125" style="1" customWidth="1"/>
+    <col min="90" max="90" width="23.58203125" style="1" customWidth="1"/>
+    <col min="91" max="91" width="12.83203125" style="1" customWidth="1"/>
+    <col min="92" max="92" width="17.08203125" style="1" customWidth="1"/>
+    <col min="93" max="98" width="9" style="1" customWidth="1"/>
+    <col min="99" max="99" width="14" style="1" customWidth="1"/>
+    <col min="100" max="100" width="8" style="1" customWidth="1"/>
+    <col min="101" max="101" width="9" style="1" customWidth="1"/>
+    <col min="102" max="102" width="11.08203125" style="1" customWidth="1"/>
+    <col min="103" max="103" width="13.75" style="1" customWidth="1"/>
+    <col min="104" max="109" width="9" style="1" customWidth="1"/>
+    <col min="110" max="110" width="15.5" style="1" customWidth="1"/>
+    <col min="111" max="114" width="9" style="1" customWidth="1"/>
+    <col min="115" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:113" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BE1" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BF1" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BG1" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BH1" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BJ1" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="BK1" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="BJ1" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BL1" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BM1" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BN1" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BO1" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BP1" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BQ1" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BR1" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BS1" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BT1" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BU1" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BV1" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BW1" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="BX1" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="BY1" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="BZ1" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+      <c r="CA1" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CB1" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CC1" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CD1" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="CD1" s="1" t="s">
+      <c r="CE1" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CF1" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="CF1" s="1" t="s">
+      <c r="CG1" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="CH1" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="CH1" s="1" t="s">
+      <c r="CI1" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="CI1" s="1" t="s">
+      <c r="CJ1" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="CJ1" s="1" t="s">
+      <c r="CK1" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="CK1" s="1" t="s">
+      <c r="CL1" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="CL1" s="1" t="s">
+      <c r="CM1" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="CM1" s="1" t="s">
+      <c r="CN1" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="CN1" s="1" t="s">
+      <c r="CO1" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="CO1" s="1" t="s">
+      <c r="CP1" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="CP1" s="1" t="s">
+      <c r="CQ1" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="CQ1" s="1" t="s">
+      <c r="CR1" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="CS1" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="CR1" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="CS1" s="1" t="s">
+      <c r="CT1" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="CT1" s="1" t="s">
+      <c r="CU1" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="CU1" s="1" t="s">
+      <c r="CV1" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="CV1" s="1" t="s">
+      <c r="CW1" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="CW1" s="1" t="s">
+      <c r="CX1" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="CX1" s="1" t="s">
+      <c r="CY1" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="CY1" s="1" t="s">
+      <c r="CZ1" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="DA1" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="CZ1" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="DA1" s="1" t="s">
+      <c r="DB1" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="DB1" s="1" t="s">
+      <c r="DC1" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="DC1" s="1" t="s">
+      <c r="DD1" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="DD1" s="1" t="s">
+      <c r="DE1" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="DE1" s="1" t="s">
+      <c r="DF1" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="DF1" s="1" t="s">
+      <c r="DG1" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="DG1" s="1" t="s">
+      <c r="DH1" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="DH1" s="1" t="s">
+      <c r="DI1" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="DI1" s="1" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="2">
+    </row>
+    <row r="2" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="Y2" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Z2" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="AA2" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="AB2" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="AC2" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AD2" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="AD2" s="1" t="s">
+      <c r="AE2" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AF2" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AG2" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="AG2" s="1" t="s">
+      <c r="AH2" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="AH2" s="1" t="s">
+      <c r="AI2" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="AI2" s="1" t="s">
+      <c r="AJ2" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="AJ2" s="1" t="s">
+      <c r="AK2" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="AK2" s="1" t="s">
+      <c r="AL2" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="AL2" s="1" t="s">
+      <c r="AM2" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="AM2" s="1" t="s">
+      <c r="AN2" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="AN2" s="1" t="s">
+      <c r="AO2" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AO2" s="1" t="s">
+      <c r="AP2" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="AP2" s="1" t="s">
+      <c r="AQ2" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="AQ2" s="1" t="s">
+      <c r="AR2" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="AR2" s="1" t="s">
+      <c r="AS2" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="AS2" s="1" t="s">
+      <c r="AT2" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="AT2" s="1" t="s">
+      <c r="AU2" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="AU2" s="1" t="s">
+      <c r="AV2" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="AV2" s="1" t="s">
+      <c r="AW2" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="AW2" s="1" t="s">
+      <c r="AX2" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="AX2" s="1" t="s">
+      <c r="AY2" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="AY2" s="1" t="s">
+      <c r="AZ2" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="AZ2" s="1" t="s">
+      <c r="BA2" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="BA2" s="1" t="s">
+      <c r="BB2" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="BB2" s="1" t="s">
+      <c r="BC2" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="BC2" s="1" t="s">
+      <c r="BD2" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="BD2" s="1" t="s">
+      <c r="BE2" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="BE2" s="1" t="s">
+      <c r="BF2" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="BF2" s="1" t="s">
+      <c r="BG2" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="BG2" s="1" t="s">
+      <c r="BH2" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="BH2" s="1" t="s">
+      <c r="BI2" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="BI2" s="1" t="s">
+      <c r="BJ2" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="BJ2" s="1" t="s">
+      <c r="BK2" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="BK2" s="1" t="s">
+      <c r="BL2" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="BL2" s="1" t="s">
+      <c r="BM2" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="BM2" s="1" t="s">
+      <c r="BN2" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="BN2" s="1" t="s">
+      <c r="BO2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="BP2" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="BO2" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="BP2" s="1" t="s">
+      <c r="BQ2" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="BQ2" s="1" t="s">
+      <c r="BR2" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="BR2" s="1" t="s">
+      <c r="BS2" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="BS2" s="1" t="s">
+      <c r="BT2" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="BT2" s="1" t="s">
+      <c r="BU2" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="BV2" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="BU2" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="BV2" s="1" t="s">
+      <c r="BW2" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="BW2" s="1" t="s">
+      <c r="BX2" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="BX2" s="1" t="s">
+      <c r="BY2" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="BY2" s="1" t="s">
+      <c r="BZ2" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="BZ2" s="1" t="s">
+      <c r="CA2" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="CA2" s="1" t="s">
+      <c r="CB2" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="CB2" s="1" t="s">
+      <c r="CC2" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="CC2" s="1" t="s">
+      <c r="CD2" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="CD2" s="1" t="s">
+      <c r="CE2" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="CE2" s="1" t="s">
+      <c r="CF2" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="CF2" s="1" t="s">
+      <c r="CG2" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="CG2" s="1" t="s">
+      <c r="CH2" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="CH2" s="1" t="s">
+      <c r="CI2" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="CI2" s="1" t="s">
+      <c r="CJ2" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="CJ2" s="1" t="s">
+      <c r="CK2" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="CK2" s="1" t="s">
+      <c r="CL2" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="CL2" s="1" t="s">
+      <c r="CM2" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="CM2" s="1" t="s">
+      <c r="CN2" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="CN2" s="1" t="s">
+      <c r="CO2" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="CO2" s="1" t="s">
+      <c r="CP2" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="CP2" s="1" t="s">
+      <c r="CQ2" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="CQ2" s="1" t="s">
+      <c r="CR2" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="CR2" s="1" t="s">
+      <c r="CS2" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="CS2" s="1" t="s">
+      <c r="CT2" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="CT2" s="1" t="s">
+      <c r="CU2" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="CU2" s="1" t="s">
+      <c r="CV2" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="CV2" s="1" t="s">
+      <c r="CW2" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="CW2" s="1" t="s">
+      <c r="CX2" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="CX2" s="1" t="s">
+      <c r="CY2" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="CY2" s="1" t="s">
+      <c r="CZ2" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="CZ2" s="1" t="s">
+      <c r="DA2" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="DA2" s="1" t="s">
+      <c r="DB2" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="DB2" s="1" t="s">
+      <c r="DC2" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="DC2" s="1" t="s">
+      <c r="DD2" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="DD2" s="1" t="s">
+      <c r="DE2" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="DE2" s="1" t="s">
+      <c r="DF2" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="DF2" s="1" t="s">
+      <c r="DG2" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="DG2" s="1" t="s">
+      <c r="DH2" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="DH2" s="1" t="s">
+      <c r="DI2" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="DI2" s="1" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="3">
+    </row>
+    <row r="3" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -4526,112 +4440,112 @@
         <v>2</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="T3" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="L3" s="1" t="s">
+      <c r="U3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AE3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AG3" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="AB3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="AC3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AD3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="AE3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="AF3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="AG3" s="1" t="s">
-        <v>378</v>
-      </c>
       <c r="AH3" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AI3" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AJ3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="AK3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AL3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AM3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AN3" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AO3" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="AP3" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="AP3" s="1" t="s">
-        <v>380</v>
       </c>
       <c r="AQ3" s="1" t="s">
         <v>2</v>
@@ -4643,226 +4557,226 @@
         <v>2</v>
       </c>
       <c r="AT3" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="AU3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AV3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="AW3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AX3" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="AU3" s="1" t="s">
+      <c r="AY3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AZ3" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="AV3" s="1" t="s">
+      <c r="BA3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="BB3" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="AW3" s="1" t="s">
+      <c r="BC3" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="AX3" s="1" t="s">
+      <c r="BD3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="BE3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="BF3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="BG3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="BH3" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="BI3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="BJ3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="BK3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="BL3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="BM3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="BN3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="BO3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="BP3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="BQ3" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="AY3" s="1" t="s">
+      <c r="BR3" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="BS3" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="AZ3" s="1" t="s">
+      <c r="BT3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="BU3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="BV3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="BW3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="BX3" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="BA3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="BB3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="BC3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="BD3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="BE3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="BF3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="BG3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="BH3" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="BI3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="BJ3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="BK3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="BL3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="BM3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="BN3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="BO3" s="1" t="s">
+      <c r="BY3" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="BZ3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="CA3" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="CB3" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="BP3" s="1" t="s">
+      <c r="CC3" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="CD3" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="BQ3" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="BR3" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="BS3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="BT3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="BU3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="BV3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="BW3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="BX3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="BY3" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="BZ3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="CA3" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="CB3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="CC3" s="1" t="s">
+      <c r="CE3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="CF3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="CG3" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="CD3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="CE3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="CF3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="CG3" s="1" t="s">
+      <c r="CH3" s="1" t="s">
         <v>387</v>
-      </c>
-      <c r="CH3" s="1" t="s">
-        <v>388</v>
       </c>
       <c r="CI3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="CJ3" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="CK3" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="CL3" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="CM3" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="CN3" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="CO3" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="CP3" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="CQ3" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="CR3" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="CS3" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="CT3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="CU3" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="CV3" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="CK3" s="1" t="s">
+      <c r="CW3" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="CX3" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="CY3" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="CL3" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="CM3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="CN3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="CO3" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="CP3" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="CQ3" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="CR3" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="CS3" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="CT3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="CU3" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="CV3" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="CW3" s="1" t="s">
+      <c r="CZ3" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="DA3" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="DB3" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="DC3" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="DD3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="DE3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="DF3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="DG3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="DH3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="DI3" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="CX3" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="CY3" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="CZ3" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="DA3" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="DB3" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="DC3" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="DD3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="DE3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="DF3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="DG3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="DH3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="DI3" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="s">
+    </row>
+    <row r="6" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="s">
+    <row r="8" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>393</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>394</v>
       </c>
       <c r="AC8" s="1">
         <v>2</v>
@@ -4871,78 +4785,78 @@
         <v>1</v>
       </c>
       <c r="AO8" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="AT8" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="AT8" s="1" t="s">
+      <c r="AX8" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="AX8" s="1" t="s">
+      <c r="AZ8" s="1">
+        <v>1</v>
+      </c>
+      <c r="BD8" s="1">
+        <v>1</v>
+      </c>
+      <c r="CB8" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="AZ8" s="1">
-        <v>1</v>
-      </c>
-      <c r="BD8" s="1">
-        <v>1</v>
-      </c>
-      <c r="CB8" s="1" t="s">
+      <c r="CD8" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="CD8" s="1" t="s">
+      <c r="CG8" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="CG8" s="1" t="s">
+      <c r="CH8" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="CH8" s="1" t="s">
+      <c r="CI8" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="CI8" s="1" t="s">
+      <c r="CJ8" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="CJ8" s="1" t="s">
+      <c r="CY8" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="CY8" s="1" t="s">
+    </row>
+    <row r="10" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>408</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>409</v>
       </c>
       <c r="G10" s="1">
         <v>3</v>
       </c>
       <c r="J10" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="AC10" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG10" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="AC10" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG10" s="1" t="s">
+      <c r="BD10" s="1">
+        <v>1</v>
+      </c>
+      <c r="BO10" s="1" t="s">
         <v>412</v>
-      </c>
-      <c r="BD10" s="1">
-        <v>1</v>
-      </c>
-      <c r="BO10" s="1" t="s">
-        <v>413</v>
       </c>
       <c r="BV10" s="1">
         <v>0</v>
@@ -4954,68 +4868,68 @@
         <v>1</v>
       </c>
       <c r="BY10" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="CU10" s="1" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="11" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="I11" s="1">
+        <v>1</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="AC11" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG11" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="CU10" s="1" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="BD11" s="1">
+        <v>1</v>
+      </c>
+      <c r="CU11" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="DD11" s="1">
+        <v>1</v>
+      </c>
+      <c r="DF11" s="1">
+        <v>1</v>
+      </c>
+      <c r="DG11" s="1">
+        <v>1</v>
+      </c>
+      <c r="DH11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="I11" s="1">
-        <v>1</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="AC11" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG11" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="BD11" s="1">
-        <v>1</v>
-      </c>
-      <c r="CU11" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="DD11" s="1">
-        <v>1</v>
-      </c>
-      <c r="DF11" s="1">
-        <v>1</v>
-      </c>
-      <c r="DG11" s="1">
-        <v>1</v>
-      </c>
-      <c r="DH11" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="L12" s="1" t="s">
         <v>419</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="I12" s="1">
-        <v>1</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>420</v>
       </c>
       <c r="AC12" s="1">
         <v>2</v>
@@ -5027,10 +4941,10 @@
         <v>99</v>
       </c>
       <c r="CG12" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="CN12" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="CO12" s="1">
         <v>-0.8</v>
@@ -5039,27 +4953,27 @@
         <v>10</v>
       </c>
       <c r="CX12" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="DH12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="DH12" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="s">
+      <c r="C13" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="I13" s="1">
+        <v>1</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="L13" s="1" t="s">
         <v>423</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="I13" s="1">
-        <v>1</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>424</v>
       </c>
       <c r="AC13" s="1">
         <v>2</v>
@@ -5071,10 +4985,10 @@
         <v>99</v>
       </c>
       <c r="CG13" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="CN13" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="CO13" s="1">
         <v>-0.8</v>
@@ -5083,51 +4997,51 @@
         <v>10</v>
       </c>
       <c r="CX13" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="DH13" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>427</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>428</v>
       </c>
       <c r="G15" s="1">
         <v>3</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="K15" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="AC15" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG15" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="BD15" s="1">
+        <v>1</v>
+      </c>
+      <c r="BO15" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="AC15" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG15" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="BD15" s="1">
-        <v>1</v>
-      </c>
-      <c r="BO15" s="1" t="s">
+      <c r="BP15" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="BP15" s="1" t="s">
-        <v>431</v>
       </c>
       <c r="BT15" s="1">
         <v>20</v>
@@ -5142,10 +5056,10 @@
         <v>1</v>
       </c>
       <c r="BY15" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="CN15" s="1" t="s">
         <v>432</v>
-      </c>
-      <c r="CN15" s="1" t="s">
-        <v>433</v>
       </c>
       <c r="CO15" s="1">
         <v>3</v>
@@ -5154,56 +5068,56 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="I16" s="1">
+        <v>1</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="AC16" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG16" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="BD16" s="1">
+        <v>1</v>
+      </c>
+      <c r="CU16" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="I16" s="1">
-        <v>1</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="AC16" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG16" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="BD16" s="1">
-        <v>1</v>
-      </c>
-      <c r="CU16" s="1" t="s">
+      <c r="DD16" s="1">
+        <v>1</v>
+      </c>
+      <c r="DF16" s="1">
+        <v>1</v>
+      </c>
+      <c r="DG16" s="1">
+        <v>1</v>
+      </c>
+      <c r="DH16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="DD16" s="1">
-        <v>1</v>
-      </c>
-      <c r="DF16" s="1">
-        <v>1</v>
-      </c>
-      <c r="DG16" s="1">
-        <v>1</v>
-      </c>
-      <c r="DH16" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="s">
+      <c r="C17" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="O17" s="1" t="s">
         <v>436</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="O17" s="1" t="s">
-        <v>437</v>
       </c>
       <c r="AC17" s="1">
         <v>2</v>
@@ -5212,66 +5126,66 @@
         <v>1</v>
       </c>
       <c r="AO17" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AT17" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="AX17" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="AZ17" s="1">
+        <v>1</v>
+      </c>
+      <c r="BD17" s="1">
+        <v>1</v>
+      </c>
+      <c r="BJ17" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="BK17" s="1">
+        <v>1</v>
+      </c>
+      <c r="BL17" s="1">
+        <v>1</v>
+      </c>
+      <c r="CB17" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="AX17" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="AZ17" s="1">
-        <v>1</v>
-      </c>
-      <c r="BD17" s="1">
-        <v>1</v>
-      </c>
-      <c r="BJ17" s="1">
-        <v>1.1</v>
-      </c>
-      <c r="BK17" s="1">
-        <v>1</v>
-      </c>
-      <c r="BL17" s="1">
-        <v>1</v>
-      </c>
-      <c r="CB17" s="1" t="s">
+      <c r="CG17" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="CH17" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="CI17" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="CJ17" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="CG17" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="CH17" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="CI17" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="CJ17" s="1" t="s">
+      <c r="CY17" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="CY17" s="1" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="18">
+    </row>
+    <row r="18" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I18" s="1">
         <v>1</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AC18" s="1">
         <v>1</v>
       </c>
       <c r="AG18" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="BD18" s="1">
         <v>1</v>
@@ -5280,45 +5194,45 @@
         <v>0.5</v>
       </c>
       <c r="CB18" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="CG18" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="DD18" s="1">
+        <v>1</v>
+      </c>
+      <c r="DF18" s="1">
+        <v>1</v>
+      </c>
+      <c r="DG18" s="1">
+        <v>1</v>
+      </c>
+      <c r="DH18" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="CG18" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="DD18" s="1">
-        <v>1</v>
-      </c>
-      <c r="DF18" s="1">
-        <v>1</v>
-      </c>
-      <c r="DG18" s="1">
-        <v>1</v>
-      </c>
-      <c r="DH18" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="s">
+      <c r="C19" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="I19" s="1">
+        <v>1</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="L19" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="I19" s="1">
-        <v>1</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="AC19" s="1">
         <v>1</v>
       </c>
       <c r="AG19" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="BD19" s="1">
         <v>1</v>
@@ -5327,80 +5241,80 @@
         <v>0.5</v>
       </c>
       <c r="CB19" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="CG19" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="DD19" s="1">
+        <v>1</v>
+      </c>
+      <c r="DF19" s="1">
+        <v>1</v>
+      </c>
+      <c r="DG19" s="1">
+        <v>1</v>
+      </c>
+      <c r="DH19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="CG19" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="DD19" s="1">
-        <v>1</v>
-      </c>
-      <c r="DF19" s="1">
-        <v>1</v>
-      </c>
-      <c r="DG19" s="1">
-        <v>1</v>
-      </c>
-      <c r="DH19" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="s">
+      <c r="C20" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="I20" s="1">
+        <v>1</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="AC20" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG20" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="BD20" s="1">
+        <v>1</v>
+      </c>
+      <c r="CU20" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="I20" s="1">
-        <v>1</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="AC20" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG20" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="BD20" s="1">
-        <v>1</v>
-      </c>
-      <c r="CU20" s="1" t="s">
+      <c r="DD20" s="1">
+        <v>1</v>
+      </c>
+      <c r="DF20" s="1">
+        <v>1</v>
+      </c>
+      <c r="DG20" s="1">
+        <v>1</v>
+      </c>
+      <c r="DH20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="DD20" s="1">
-        <v>1</v>
-      </c>
-      <c r="DF20" s="1">
-        <v>1</v>
-      </c>
-      <c r="DG20" s="1">
-        <v>1</v>
-      </c>
-      <c r="DH20" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="s">
-        <v>448</v>
-      </c>
       <c r="C21" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I21" s="1">
         <v>1</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AC21" s="1">
         <v>2</v>
@@ -5412,36 +5326,36 @@
         <v>99</v>
       </c>
       <c r="CG21" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="CN21" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="CR21" s="1">
         <v>5</v>
       </c>
       <c r="CX21" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="DH21" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I22" s="1">
         <v>1</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AC22" s="1">
         <v>2</v>
@@ -5453,60 +5367,60 @@
         <v>99</v>
       </c>
       <c r="CG22" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="CN22" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="CR22" s="1">
         <v>5</v>
       </c>
       <c r="CX22" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="DH22" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="D24" s="1" t="s">
+      <c r="E24" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="F24" s="1" t="s">
         <v>453</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>454</v>
       </c>
       <c r="G24" s="1">
         <v>3</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AC24" s="1">
         <v>1</v>
       </c>
       <c r="AG24" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="BD24" s="1">
         <v>1</v>
       </c>
       <c r="BO24" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="BP24" s="1" t="s">
         <v>455</v>
-      </c>
-      <c r="BP24" s="1" t="s">
-        <v>456</v>
       </c>
       <c r="BT24" s="1">
         <v>40</v>
@@ -5524,16 +5438,16 @@
         <v>1</v>
       </c>
       <c r="BY24" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="CA24" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="CN24" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="CN24" s="1" t="s">
+      <c r="CO24" s="1" t="s">
         <v>458</v>
-      </c>
-      <c r="CO24" s="1" t="s">
-        <v>459</v>
       </c>
       <c r="CR24" s="1">
         <v>99999</v>
@@ -5542,56 +5456,56 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="I25" s="1">
+        <v>1</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="AC25" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG25" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="BD25" s="1">
+        <v>1</v>
+      </c>
+      <c r="CU25" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="I25" s="1">
-        <v>1</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="AC25" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG25" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="BD25" s="1">
-        <v>1</v>
-      </c>
-      <c r="CU25" s="1" t="s">
+      <c r="DD25" s="1">
+        <v>1</v>
+      </c>
+      <c r="DG25" s="1">
+        <v>1</v>
+      </c>
+      <c r="DH25" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="DD25" s="1">
-        <v>1</v>
-      </c>
-      <c r="DG25" s="1">
-        <v>1</v>
-      </c>
-      <c r="DH25" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="s">
+      <c r="C26" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="O26" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="O26" s="1" t="s">
+      <c r="R26" s="1" t="s">
         <v>463</v>
-      </c>
-      <c r="R26" s="1" t="s">
-        <v>464</v>
       </c>
       <c r="AC26" s="1">
         <v>2</v>
@@ -5600,14 +5514,14 @@
         <v>1</v>
       </c>
       <c r="AO26" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="AT26" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="AT26" s="1" t="s">
+      <c r="AX26" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="AX26" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="AZ26" s="1">
         <v>1</v>
       </c>
@@ -5615,42 +5529,42 @@
         <v>1</v>
       </c>
       <c r="CA26" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="CB26" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="CD26" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="CD26" s="1" t="s">
+      <c r="CG26" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="CH26" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="CI26" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="CJ26" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="CG26" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="CH26" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="CI26" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="CJ26" s="1" t="s">
+      <c r="CY26" s="1" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="27" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="CY26" s="1" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="s">
-        <v>468</v>
-      </c>
       <c r="C27" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="O27" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="Q27" s="1" t="s">
         <v>463</v>
-      </c>
-      <c r="Q27" s="1" t="s">
-        <v>464</v>
       </c>
       <c r="AC27" s="1">
         <v>2</v>
@@ -5659,14 +5573,14 @@
         <v>1</v>
       </c>
       <c r="AO27" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="AT27" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="AT27" s="1" t="s">
+      <c r="AX27" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="AX27" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="AZ27" s="1">
         <v>1</v>
       </c>
@@ -5674,48 +5588,48 @@
         <v>1</v>
       </c>
       <c r="CA27" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="CB27" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="CD27" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="CD27" s="1" t="s">
-        <v>466</v>
-      </c>
       <c r="CG27" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="CH27" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="CH27" s="1" t="s">
+      <c r="CI27" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="CI27" s="1" t="s">
-        <v>402</v>
-      </c>
       <c r="CJ27" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="CY27" s="1" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="28" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I28" s="1">
         <v>1</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AC28" s="1">
         <v>1</v>
       </c>
       <c r="AG28" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="BD28" s="1">
         <v>1</v>
@@ -5724,42 +5638,42 @@
         <v>0.5</v>
       </c>
       <c r="CB28" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="CG28" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="DD28" s="1">
+        <v>1</v>
+      </c>
+      <c r="DG28" s="1">
+        <v>1</v>
+      </c>
+      <c r="DH28" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="CG28" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="DD28" s="1">
-        <v>1</v>
-      </c>
-      <c r="DG28" s="1">
-        <v>1</v>
-      </c>
-      <c r="DH28" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="s">
-        <v>471</v>
-      </c>
       <c r="C29" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I29" s="1">
         <v>1</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AC29" s="1">
         <v>1</v>
       </c>
       <c r="AG29" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="BD29" s="1">
         <v>1</v>
@@ -5768,92 +5682,92 @@
         <v>0.5</v>
       </c>
       <c r="CB29" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="CG29" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="DD29" s="1">
+        <v>1</v>
+      </c>
+      <c r="DG29" s="1">
+        <v>1</v>
+      </c>
+      <c r="DH29" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="CG29" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="DD29" s="1">
-        <v>1</v>
-      </c>
-      <c r="DG29" s="1">
-        <v>1</v>
-      </c>
-      <c r="DH29" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="s">
+      <c r="C30" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="I30" s="1">
+        <v>1</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="AC30" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG30" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="BD30" s="1">
+        <v>1</v>
+      </c>
+      <c r="CU30" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="I30" s="1">
-        <v>1</v>
-      </c>
-      <c r="K30" s="1" t="s">
+      <c r="DD30" s="1">
+        <v>1</v>
+      </c>
+      <c r="DG30" s="1">
+        <v>1</v>
+      </c>
+      <c r="DH30" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="I31" s="1">
+        <v>1</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="L31" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="L30" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="AC30" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG30" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="BD30" s="1">
-        <v>1</v>
-      </c>
-      <c r="CU30" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="DD30" s="1">
-        <v>1</v>
-      </c>
-      <c r="DG30" s="1">
-        <v>1</v>
-      </c>
-      <c r="DH30" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="s">
+      <c r="N31" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC31" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG31" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="BD31" s="1">
+        <v>1</v>
+      </c>
+      <c r="BO31" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="I31" s="1">
-        <v>1</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="L31" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="N31" s="1">
-        <v>1</v>
-      </c>
-      <c r="AC31" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG31" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="BD31" s="1">
-        <v>1</v>
-      </c>
-      <c r="BO31" s="1" t="s">
+      <c r="CN31" s="1" t="s">
         <v>476</v>
-      </c>
-      <c r="CN31" s="1" t="s">
-        <v>477</v>
       </c>
       <c r="CR31" s="1">
         <v>99999</v>
@@ -5868,12 +5782,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I32" s="1">
         <v>1</v>
@@ -5882,39 +5796,39 @@
         <v>1</v>
       </c>
       <c r="AG32" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AT32" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="BD32" s="1">
+        <v>1</v>
+      </c>
+      <c r="DD32" s="1">
+        <v>1</v>
+      </c>
+      <c r="DG32" s="1">
+        <v>1</v>
+      </c>
+      <c r="DH32" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:112" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="BD32" s="1">
-        <v>1</v>
-      </c>
-      <c r="DD32" s="1">
-        <v>1</v>
-      </c>
-      <c r="DG32" s="1">
-        <v>1</v>
-      </c>
-      <c r="DH32" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="s">
-        <v>479</v>
-      </c>
       <c r="C33" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I33" s="1">
         <v>1</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AC33" s="1">
         <v>2</v>
@@ -5926,10 +5840,10 @@
         <v>99</v>
       </c>
       <c r="CG33" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="CN33" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="CO33" s="1">
         <v>-0.8</v>
@@ -5941,27 +5855,27 @@
         <v>7</v>
       </c>
       <c r="CX33" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="DH33" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I34" s="1">
         <v>1</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AC34" s="1">
         <v>2</v>
@@ -5973,10 +5887,10 @@
         <v>99</v>
       </c>
       <c r="CG34" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="CN34" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="CO34" s="1">
         <v>-0.8</v>
@@ -5988,47 +5902,47 @@
         <v>7</v>
       </c>
       <c r="CX34" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="DH34" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AC37" s="1">
         <v>2</v>
       </c>
       <c r="AT37" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="BD37" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I38" s="1">
         <v>1</v>
@@ -6043,24 +5957,24 @@
         <v>1</v>
       </c>
       <c r="BP38" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="DH38" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I39" s="1">
         <v>1</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AC39" s="1">
         <v>2</v>
@@ -6072,19 +5986,19 @@
         <v>99</v>
       </c>
       <c r="BP39" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="BS39" s="1">
         <v>0.5</v>
       </c>
       <c r="CB39" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="CG39" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="CN39" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="CO39" s="1">
         <v>-0.8</v>
@@ -6093,47 +6007,47 @@
         <v>10</v>
       </c>
       <c r="CX39" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="DH39" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AC40" s="1">
         <v>2</v>
       </c>
       <c r="AT40" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="BD40" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I41" s="1">
         <v>1</v>
@@ -6148,24 +6062,24 @@
         <v>1</v>
       </c>
       <c r="BP41" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="DH41" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I42" s="1">
         <v>1</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AC42" s="1">
         <v>2</v>
@@ -6177,65 +6091,65 @@
         <v>99</v>
       </c>
       <c r="BP42" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="BS42" s="1">
         <v>0.5</v>
       </c>
       <c r="CB42" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="CG42" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="CN42" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="CR42" s="1">
         <v>5</v>
       </c>
       <c r="CX42" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="DH42" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AC43" s="1">
         <v>2</v>
       </c>
       <c r="AT43" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="BD43" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I44" s="1">
         <v>1</v>
@@ -6250,24 +6164,24 @@
         <v>1</v>
       </c>
       <c r="BP44" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="DH44" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I45" s="1">
         <v>1</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AC45" s="1">
         <v>2</v>
@@ -6279,19 +6193,19 @@
         <v>99</v>
       </c>
       <c r="BP45" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="BS45" s="1">
         <v>0.5</v>
       </c>
       <c r="CB45" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="CG45" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="CN45" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="CO45" s="1">
         <v>-0.8</v>
@@ -6303,24 +6217,24 @@
         <v>7</v>
       </c>
       <c r="CX45" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="DH45" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I46" s="1">
         <v>1</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AC46" s="1">
         <v>1</v>
@@ -6329,10 +6243,10 @@
         <v>1</v>
       </c>
       <c r="AG46" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AX46" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AZ46" s="1">
         <v>1</v>
@@ -6356,52 +6270,52 @@
         <v>1</v>
       </c>
     </row>
-    <row r="625">
+    <row r="625" spans="90:90" x14ac:dyDescent="0.25">
       <c r="CL625" s="1">
         <v>0.15</v>
       </c>
     </row>
-    <row r="627">
+    <row r="627" spans="90:90" x14ac:dyDescent="0.25">
       <c r="CL627" s="1">
         <v>0.2</v>
       </c>
     </row>
-    <row r="628">
+    <row r="628" spans="90:90" x14ac:dyDescent="0.25">
       <c r="CL628" s="1">
         <v>0.1</v>
       </c>
     </row>
-    <row r="630">
+    <row r="630" spans="90:90" x14ac:dyDescent="0.25">
       <c r="CL630" s="1">
         <v>0.2</v>
       </c>
     </row>
-    <row r="637">
+    <row r="637" spans="90:90" x14ac:dyDescent="0.25">
       <c r="CL637" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="639">
+    <row r="639" spans="90:90" x14ac:dyDescent="0.25">
       <c r="CL639" s="1">
         <v>0.4</v>
       </c>
     </row>
-    <row r="640">
+    <row r="640" spans="90:90" x14ac:dyDescent="0.25">
       <c r="CL640" s="1">
         <v>0.6</v>
       </c>
     </row>
-    <row r="643">
+    <row r="643" spans="90:90" x14ac:dyDescent="0.25">
       <c r="CL643" s="1">
         <v>0.5</v>
       </c>
     </row>
-    <row r="644">
+    <row r="644" spans="90:90" x14ac:dyDescent="0.25">
       <c r="CL644" s="1">
-        <v>0.667</v>
-      </c>
-    </row>
-    <row r="645">
+        <v>0.66700000000000004</v>
+      </c>
+    </row>
+    <row r="645" spans="90:90" x14ac:dyDescent="0.25">
       <c r="CL645" s="1">
         <v>0.2</v>
       </c>
@@ -6410,7 +6324,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -6420,20 +6333,21 @@
   <dimension ref="A1:Q10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1" style="1"/>
-    <col min="2" max="2" width="31.25" customWidth="1" style="1"/>
-    <col min="3" max="6" width="9" customWidth="1" style="1"/>
-    <col min="7" max="7" width="18.75" customWidth="1" style="1"/>
-    <col min="8" max="8" width="15" customWidth="1" style="1"/>
-    <col min="9" max="13" width="9" customWidth="1" style="1"/>
-    <col min="14" max="14" width="16.08203125" customWidth="1" style="1"/>
-    <col min="15" max="15" width="9.5" customWidth="1" style="1"/>
-    <col min="16" max="16" width="9" customWidth="1" style="1"/>
-    <col min="17" max="17" width="12.83203125" customWidth="1" style="1"/>
-    <col min="18" max="16384" width="9" customWidth="1" style="1"/>
+    <col min="1" max="1" width="13" style="1" customWidth="1"/>
+    <col min="2" max="2" width="31.25" style="1" customWidth="1"/>
+    <col min="3" max="6" width="9" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.75" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15" style="1" customWidth="1"/>
+    <col min="9" max="13" width="9" style="1" customWidth="1"/>
+    <col min="14" max="14" width="16.08203125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.5" style="1" customWidth="1"/>
+    <col min="16" max="16" width="9" style="1" customWidth="1"/>
+    <col min="17" max="17" width="12.83203125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6441,90 +6355,90 @@
         <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="2">
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>514</v>
-      </c>
       <c r="Q2" s="1" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -6535,151 +6449,150 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="L3" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="H4" s="1">
-        <v>1</v>
-      </c>
-      <c r="J4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>516</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="H5" s="1">
-        <v>1</v>
-      </c>
-      <c r="J5" s="1" t="s">
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>518</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="H6" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="H7" s="1">
-        <v>1</v>
-      </c>
-      <c r="J7" s="1" t="s">
+      <c r="Q7" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="Q7" s="1" t="s">
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>522</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
+      <c r="C8" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="H8" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="1" t="s">
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="Q9" s="1" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="H9" s="1">
-        <v>1</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="Q9" s="1" t="s">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>525</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="C10" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="1" t="s">
         <v>526</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="H10" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="1" t="s">
-        <v>527</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -6688,36 +6601,37 @@
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" customWidth="1" style="1"/>
-    <col min="2" max="2" width="13.1640625" customWidth="1" style="1"/>
-    <col min="3" max="3" width="15" customWidth="1" style="1"/>
-    <col min="4" max="4" width="27.5" customWidth="1" style="1"/>
-    <col min="5" max="16384" width="9" customWidth="1" style="1"/>
+    <col min="1" max="1" width="11.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="1" customWidth="1"/>
+    <col min="4" max="4" width="27.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -6725,53 +6639,52 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="D4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>531</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="D5" s="1" t="s">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>533</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>535</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>536</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -6780,52 +6693,52 @@
   <dimension ref="A1:J4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1" style="1"/>
-    <col min="2" max="2" width="9" customWidth="1" style="1"/>
-    <col min="3" max="3" width="27.25" customWidth="1" style="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1" style="1"/>
-    <col min="5" max="10" width="9" customWidth="1" style="1"/>
-    <col min="11" max="16384" width="9" customWidth="1" style="1"/>
+    <col min="1" max="1" width="15.25" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" style="1" customWidth="1"/>
+    <col min="5" max="11" width="9" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I1" s="1" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>540</v>
-      </c>
       <c r="I2" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -6839,33 +6752,33 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>120</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E4" s="1">
         <v>200</v>
@@ -6878,7 +6791,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -6887,89 +6799,89 @@
   <dimension ref="A1:L4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1" style="1"/>
-    <col min="2" max="2" width="28" customWidth="1" style="1"/>
-    <col min="3" max="4" width="10.08203125" customWidth="1" style="1"/>
-    <col min="5" max="10" width="11.25" customWidth="1" style="1"/>
-    <col min="11" max="11" width="6.33203125" customWidth="1" style="1"/>
-    <col min="12" max="12" width="9" customWidth="1" style="1"/>
-    <col min="13" max="16384" width="9" customWidth="1" style="1"/>
+    <col min="1" max="1" width="15.25" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28" style="1" customWidth="1"/>
+    <col min="3" max="4" width="10.08203125" style="1" customWidth="1"/>
+    <col min="5" max="10" width="11.25" style="1" customWidth="1"/>
+    <col min="11" max="11" width="6.33203125" style="1" customWidth="1"/>
+    <col min="12" max="13" width="9" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="2">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>560</v>
-      </c>
       <c r="K2" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -6977,42 +6889,42 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4">
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="I4" s="1">
         <v>1</v>
@@ -7028,7 +6940,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -7038,50 +6949,51 @@
   <dimension ref="A2:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.08203125" customWidth="1" style="1"/>
-    <col min="2" max="2" width="16.25" customWidth="1" style="1"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1" style="1"/>
-    <col min="4" max="4" width="47.83203125" customWidth="1" style="1"/>
-    <col min="5" max="5" width="10.25" customWidth="1" style="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1" style="1"/>
-    <col min="7" max="9" width="9" customWidth="1" style="1"/>
-    <col min="10" max="10" width="11.83203125" customWidth="1" style="1"/>
-    <col min="11" max="16384" width="9" customWidth="1" style="1"/>
+    <col min="1" max="1" width="19.08203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="47.83203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" style="1" customWidth="1"/>
+    <col min="7" max="9" width="9" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.83203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="9" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>566</v>
-      </c>
       <c r="J2" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -7095,28 +7007,27 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -7125,84 +7036,85 @@
   <dimension ref="A1:I3"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.5" customWidth="1" style="1"/>
-    <col min="2" max="2" width="10.6640625" customWidth="1" style="1"/>
-    <col min="3" max="3" width="21.9140625" customWidth="1" style="1"/>
-    <col min="4" max="4" width="16.25" customWidth="1" style="1"/>
-    <col min="5" max="5" width="14" customWidth="1" style="1"/>
-    <col min="6" max="7" width="15.1640625" customWidth="1" style="1"/>
-    <col min="8" max="8" width="12.9140625" customWidth="1" style="1"/>
-    <col min="9" max="9" width="14" customWidth="1" style="1"/>
-    <col min="10" max="16384" width="8.75" customWidth="1" style="1"/>
+    <col min="1" max="1" width="7.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.9140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14" style="1" customWidth="1"/>
+    <col min="6" max="7" width="15.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.9140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.75" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="2">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="3">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>2</v>
@@ -7226,7 +7138,6 @@
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 

--- a/Excel/一方通行/艾拉.xlsx
+++ b/Excel/一方通行/艾拉.xlsx
@@ -23,7 +23,7 @@
     <sheet name="ContractData" sheetId="11" r:id="rId8"/>
     <sheet name="SpineData" sheetId="12" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="590">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="590">
   <si>
     <t>Id</t>
   </si>
@@ -346,6 +346,9 @@
     <t>模型大小倍率</t>
   </si>
   <si>
+    <t>模型偏移</t>
+  </si>
+  <si>
     <t>精英化</t>
   </si>
   <si>
@@ -412,6 +415,12 @@
     <t>可选技能</t>
   </si>
   <si>
+    <t>血条</t>
+  </si>
+  <si>
+    <t>技力条</t>
+  </si>
+  <si>
     <t>高度</t>
   </si>
   <si>
@@ -481,6 +490,9 @@
     <t>ModelScale</t>
   </si>
   <si>
+    <t>ModelOffset</t>
+  </si>
+  <si>
     <t>engName</t>
   </si>
   <si>
@@ -577,6 +589,9 @@
     <t>HpBarType</t>
   </si>
   <si>
+    <t>SpBarType</t>
+  </si>
+  <si>
     <t>Height</t>
   </si>
   <si>
@@ -682,6 +697,9 @@
     <t>float</t>
   </si>
   <si>
+    <t>UnityEngine.Vector3</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -724,6 +742,12 @@
     <t>艾拉1,艾拉2,艾拉3</t>
   </si>
   <si>
+    <t>小型:蓝</t>
+  </si>
+  <si>
+    <t>小型:绿</t>
+  </si>
+  <si>
     <t>全地形</t>
   </si>
   <si>
@@ -781,6 +805,9 @@
     <t>艾拉地雷A技能描述</t>
   </si>
   <si>
+    <t>无</t>
+  </si>
+  <si>
     <t>头像_召唤物_触手</t>
   </si>
   <si>
@@ -1693,9 +1720,6 @@
     <t>艾拉3启动</t>
   </si>
   <si>
-    <t>无</t>
-  </si>
-  <si>
     <t>艾拉3加成,艾拉3动作</t>
   </si>
   <si>
@@ -2005,9 +2029,6 @@
     <t>ForwordDirection</t>
   </si>
   <si>
-    <t>UnityEngine.Vector3</t>
-  </si>
-  <si>
     <t>skgoat_skill_02_range</t>
   </si>
   <si>
@@ -2072,41 +2093,14 @@
   </si>
   <si>
     <t>BackSkelPath</t>
-  </si>
-  <si>
-    <t>血条</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>技力条</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpBarType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>小型:蓝</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>小型:绿</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>无</t>
-    <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2118,34 +2112,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <family val="3"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2181,19 +2147,19 @@
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2498,11 +2464,11 @@
   <dimension ref="A2:B4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="9" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="1"/>
+    <col min="1" max="3" width="9" customWidth="1" style="1"/>
+    <col min="4" max="16384" width="9" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2510,7 +2476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -2518,7 +2484,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -2529,1129 +2495,1328 @@
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BU7"/>
+  <dimension ref="A1:BV7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.58203125" style="1" customWidth="1"/>
-    <col min="2" max="3" width="9" style="1" customWidth="1"/>
-    <col min="4" max="5" width="8.58203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.58203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.25" style="1" customWidth="1"/>
-    <col min="8" max="10" width="9" style="1" customWidth="1"/>
-    <col min="11" max="11" width="6" style="1" customWidth="1"/>
-    <col min="12" max="12" width="4.08203125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="5.58203125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="4" style="1" customWidth="1"/>
-    <col min="15" max="15" width="7.75" style="1" customWidth="1"/>
-    <col min="16" max="16" width="10.83203125" style="1" customWidth="1"/>
-    <col min="17" max="18" width="3.83203125" style="1" customWidth="1"/>
-    <col min="19" max="20" width="3.58203125" style="1" customWidth="1"/>
-    <col min="21" max="21" width="10.25" style="1" customWidth="1"/>
-    <col min="22" max="22" width="9.58203125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="10.75" style="1" customWidth="1"/>
-    <col min="24" max="24" width="12.83203125" style="1" customWidth="1"/>
-    <col min="25" max="25" width="13.08203125" style="1" customWidth="1"/>
-    <col min="26" max="26" width="10.75" style="1" customWidth="1"/>
-    <col min="27" max="28" width="9" style="1" customWidth="1"/>
-    <col min="29" max="29" width="8" style="1" customWidth="1"/>
-    <col min="30" max="30" width="17.08203125" style="1" customWidth="1"/>
-    <col min="31" max="32" width="9" style="1" customWidth="1"/>
-    <col min="33" max="33" width="9.75" style="1" customWidth="1"/>
-    <col min="34" max="34" width="7.83203125" style="1" customWidth="1"/>
-    <col min="35" max="35" width="15.83203125" style="1" customWidth="1"/>
-    <col min="36" max="36" width="13.83203125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="34.5" style="1" customWidth="1"/>
-    <col min="38" max="40" width="9.83203125" style="1" customWidth="1"/>
-    <col min="41" max="44" width="9" style="1" customWidth="1"/>
-    <col min="45" max="45" width="12.5" style="1" customWidth="1"/>
-    <col min="46" max="51" width="9" style="1" customWidth="1"/>
-    <col min="52" max="52" width="24.33203125" style="1" customWidth="1"/>
-    <col min="53" max="53" width="9" style="1" customWidth="1"/>
-    <col min="54" max="54" width="17.75" style="1" customWidth="1"/>
-    <col min="55" max="55" width="7.83203125" style="1" customWidth="1"/>
-    <col min="56" max="57" width="9" style="1" customWidth="1"/>
-    <col min="58" max="58" width="24.25" style="1" customWidth="1"/>
-    <col min="59" max="59" width="13.25" style="1" customWidth="1"/>
-    <col min="60" max="60" width="16.08203125" style="1" customWidth="1"/>
-    <col min="61" max="61" width="8" style="1" customWidth="1"/>
-    <col min="62" max="65" width="9" style="1" customWidth="1"/>
-    <col min="66" max="66" width="39.58203125" style="1" customWidth="1"/>
-    <col min="67" max="67" width="14" style="1" customWidth="1"/>
-    <col min="68" max="68" width="14.83203125" style="1" customWidth="1"/>
-    <col min="69" max="72" width="14" style="1" customWidth="1"/>
-    <col min="73" max="73" width="19.1640625" style="1" customWidth="1"/>
-    <col min="74" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="22.58203125" customWidth="1" style="2"/>
+    <col min="2" max="2" width="9" customWidth="1" style="2"/>
+    <col min="3" max="3" width="9" customWidth="1" style="2"/>
+    <col min="4" max="4" width="8.58203125" customWidth="1" style="2"/>
+    <col min="5" max="5" width="8.58203125" customWidth="1" style="2"/>
+    <col min="6" max="6" width="19.58203125" customWidth="1" style="2"/>
+    <col min="7" max="7" width="8.25" customWidth="1" style="2"/>
+    <col min="8" max="8" width="9" customWidth="1" style="2"/>
+    <col min="9" max="9" width="9" customWidth="1" style="2"/>
+    <col min="10" max="10" width="9" customWidth="1" style="2"/>
+    <col min="11" max="11" width="9" customWidth="1" style="2"/>
+    <col min="12" max="12" width="6" customWidth="1" style="2"/>
+    <col min="13" max="13" width="4.08203125" customWidth="1" style="2"/>
+    <col min="14" max="14" width="5.58203125" customWidth="1" style="2"/>
+    <col min="15" max="15" width="4" customWidth="1" style="2"/>
+    <col min="16" max="16" width="7.75" customWidth="1" style="2"/>
+    <col min="17" max="17" width="10.83203125" customWidth="1" style="2"/>
+    <col min="18" max="18" width="3.83203125" customWidth="1" style="2"/>
+    <col min="19" max="19" width="3.83203125" customWidth="1" style="2"/>
+    <col min="20" max="20" width="3.58203125" customWidth="1" style="2"/>
+    <col min="21" max="21" width="3.58203125" customWidth="1" style="2"/>
+    <col min="22" max="22" width="10.25" customWidth="1" style="2"/>
+    <col min="23" max="23" width="9.58203125" customWidth="1" style="2"/>
+    <col min="24" max="24" width="10.75" customWidth="1" style="2"/>
+    <col min="25" max="25" width="12.83203125" customWidth="1" style="2"/>
+    <col min="26" max="26" width="13.08203125" customWidth="1" style="2"/>
+    <col min="27" max="27" width="10.75" customWidth="1" style="2"/>
+    <col min="28" max="28" width="9" customWidth="1" style="2"/>
+    <col min="29" max="29" width="9" customWidth="1" style="2"/>
+    <col min="30" max="30" width="8" customWidth="1" style="2"/>
+    <col min="31" max="31" width="17.08203125" customWidth="1" style="2"/>
+    <col min="32" max="32" width="9" customWidth="1" style="2"/>
+    <col min="33" max="33" width="9" customWidth="1" style="2"/>
+    <col min="34" max="34" width="9.75" customWidth="1" style="2"/>
+    <col min="35" max="35" width="7.83203125" customWidth="1" style="2"/>
+    <col min="36" max="36" width="15.83203125" customWidth="1" style="2"/>
+    <col min="37" max="37" width="13.83203125" customWidth="1" style="2"/>
+    <col min="38" max="38" width="34.5" customWidth="1" style="2"/>
+    <col min="39" max="39" width="9.83203125" customWidth="1" style="2"/>
+    <col min="40" max="40" width="9.83203125" customWidth="1" style="2"/>
+    <col min="41" max="41" width="9.83203125" customWidth="1" style="2"/>
+    <col min="42" max="42" width="9" customWidth="1" style="2"/>
+    <col min="43" max="43" width="9" customWidth="1" style="2"/>
+    <col min="44" max="44" width="9" customWidth="1" style="2"/>
+    <col min="45" max="45" width="9" customWidth="1" style="2"/>
+    <col min="46" max="46" width="12.5" customWidth="1" style="2"/>
+    <col min="47" max="47" width="9" customWidth="1" style="2"/>
+    <col min="48" max="48" width="9" customWidth="1" style="2"/>
+    <col min="49" max="49" width="9" customWidth="1" style="2"/>
+    <col min="50" max="50" width="9" customWidth="1" style="2"/>
+    <col min="51" max="51" width="9" customWidth="1" style="2"/>
+    <col min="52" max="52" width="9" customWidth="1" style="2"/>
+    <col min="53" max="53" width="24.33203125" customWidth="1" style="2"/>
+    <col min="54" max="54" width="9" customWidth="1" style="2"/>
+    <col min="55" max="55" width="17.75" customWidth="1" style="2"/>
+    <col min="56" max="56" width="7.83203125" customWidth="1" style="2"/>
+    <col min="57" max="57" width="9" customWidth="1" style="2"/>
+    <col min="58" max="58" width="9" customWidth="1" style="2"/>
+    <col min="59" max="59" width="24.25" customWidth="1" style="2"/>
+    <col min="60" max="60" width="13.25" customWidth="1" style="2"/>
+    <col min="61" max="61" width="16.08203125" customWidth="1" style="2"/>
+    <col min="62" max="62" width="8" customWidth="1" style="2"/>
+    <col min="63" max="63" width="9" customWidth="1" style="2"/>
+    <col min="64" max="64" width="9" customWidth="1" style="2"/>
+    <col min="65" max="65" width="9" customWidth="1" style="2"/>
+    <col min="66" max="66" width="9" customWidth="1" style="2"/>
+    <col min="67" max="67" width="39.58203125" customWidth="1" style="2"/>
+    <col min="68" max="68" width="14" customWidth="1" style="2"/>
+    <col min="69" max="69" width="14.83203125" customWidth="1" style="2"/>
+    <col min="70" max="70" width="14" customWidth="1" style="2"/>
+    <col min="71" max="71" width="14" customWidth="1" style="2"/>
+    <col min="72" max="72" width="14" customWidth="1" style="2"/>
+    <col min="73" max="73" width="14" customWidth="1" style="2"/>
+    <col min="74" max="74" width="19.1640625" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="D1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="F1" s="2"/>
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="I1" s="2"/>
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="M1" s="2"/>
+      <c r="N1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="O1" s="2"/>
+      <c r="P1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="S1" s="2"/>
+      <c r="T1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="U1" s="2"/>
+      <c r="V1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AG1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AH1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AI1" s="2"/>
+      <c r="AJ1" s="2"/>
+      <c r="AK1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AL1" s="2" t="s">
         <v>28</v>
       </c>
       <c r="AM1" s="2" t="s">
-        <v>583</v>
+        <v>29</v>
       </c>
       <c r="AN1" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AP1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AO1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AP1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AR1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AS1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AT1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AU1" s="2"/>
+      <c r="AV1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AW1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="AX1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="AY1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="AZ1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BA1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BB1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BC1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BD1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BE1" s="2"/>
+      <c r="BF1" s="2"/>
+      <c r="BG1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BH1" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="2" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="BI1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="BJ1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="BK1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="BL1" s="2"/>
+      <c r="BM1" s="2"/>
+      <c r="BN1" s="2"/>
+      <c r="BO1" s="2"/>
+      <c r="BP1" s="2"/>
+      <c r="BQ1" s="2"/>
+      <c r="BR1" s="2"/>
+      <c r="BS1" s="2"/>
+      <c r="BT1" s="2"/>
+      <c r="BU1" s="2"/>
+      <c r="BV1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="L2" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="M2" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="N2" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="O2" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="P2" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="Q2" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="R2" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="S2" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="T2" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="U2" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="V2" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="W2" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="X2" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="Y2" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="Z2" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="AD2" s="1" t="s">
+      <c r="AA2" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AB2" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AC2" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="AG2" s="1" t="s">
+      <c r="AD2" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="AH2" s="1" t="s">
+      <c r="AE2" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="AI2" s="1" t="s">
+      <c r="AF2" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="AJ2" s="1" t="s">
+      <c r="AG2" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="AK2" s="1" t="s">
+      <c r="AH2" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="AL2" s="1" t="s">
+      <c r="AI2" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="AM2" s="1" t="s">
+      <c r="AJ2" s="2" t="s">
         <v>83</v>
       </c>
+      <c r="AK2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AM2" s="2" t="s">
+        <v>86</v>
+      </c>
       <c r="AN2" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="AO2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AP2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AQ2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="AR2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="AS2" s="1" t="s">
+      <c r="AO2" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="AT2" s="1" t="s">
+      <c r="AP2" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="AU2" s="1" t="s">
+      <c r="AQ2" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="AV2" s="1" t="s">
+      <c r="AR2" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="AW2" s="1" t="s">
+      <c r="AS2" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="AX2" s="1" t="s">
+      <c r="AT2" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="AY2" s="1" t="s">
+      <c r="AU2" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="AZ2" s="1" t="s">
+      <c r="AV2" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="BA2" s="1" t="s">
+      <c r="AW2" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="BB2" s="1" t="s">
+      <c r="AX2" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="BC2" s="1" t="s">
+      <c r="AY2" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="BD2" s="1" t="s">
+      <c r="AZ2" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="BE2" s="1" t="s">
+      <c r="BA2" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="BF2" s="1" t="s">
+      <c r="BB2" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="BG2" s="1" t="s">
+      <c r="BC2" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="BH2" s="1" t="s">
+      <c r="BD2" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="BI2" s="1" t="s">
+      <c r="BE2" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="BJ2" s="1" t="s">
+      <c r="BF2" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="BK2" s="1" t="s">
+      <c r="BG2" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="BL2" s="1" t="s">
+      <c r="BH2" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="BM2" s="1" t="s">
+      <c r="BI2" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="BN2" s="1" t="s">
+      <c r="BJ2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="BO2" s="1" t="s">
+      <c r="BK2" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="BP2" s="1" t="s">
+      <c r="BL2" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="BQ2" s="1" t="s">
+      <c r="BM2" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="BR2" s="1" t="s">
+      <c r="BN2" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="BS2" s="1" t="s">
+      <c r="BO2" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="BT2" s="1" t="s">
+      <c r="BP2" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="BU2" s="1" t="s">
+      <c r="BQ2" s="2" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="3" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="BR2" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="BS2" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BT2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU2" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BV2" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F3" s="1" t="s">
+      <c r="C3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H3" s="1" t="s">
+      <c r="G3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="AB3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="AC3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="AD3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AE3" s="1" t="s">
+      <c r="J3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AF3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="AF3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="AG3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="AH3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="AI3" s="1" t="s">
+      <c r="AG3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="AJ3" s="1" t="s">
+      <c r="AK3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="AK3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL3" s="1" t="s">
-        <v>120</v>
+      <c r="AL3" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="AM3" s="2" t="s">
-        <v>586</v>
+        <v>126</v>
       </c>
       <c r="AN3" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="AO3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="AP3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="AQ3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="AR3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="AS3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AU3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="AV3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AW3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="AX3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AO3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AQ3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AR3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AS3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AT3" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="AY3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="AZ3" s="1" t="s">
+      <c r="AU3" s="2"/>
+      <c r="AV3" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="BA3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="BB3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="BC3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="BD3" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="BE3" s="1" t="s">
+      <c r="AW3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AX3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AY3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BB3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BC3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BD3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE3" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="BF3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="BF3" s="1" t="s">
+      <c r="BG3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="BG3" s="1" t="s">
+      <c r="BH3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="BH3" s="1" t="s">
+      <c r="BI3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="BI3" s="1" t="s">
+      <c r="BJ3" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="BK3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="BJ3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="BK3" s="1" t="s">
+      <c r="BL3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="BL3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="BM3" s="1" t="s">
+      <c r="BM3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BN3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="BN3" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="BO3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="BP3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="BQ3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="BR3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="BS3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="BT3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="BU3" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="4" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="BO3" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="BP3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BQ3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BR3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BS3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BT3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BU3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BV3" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1</v>
-      </c>
-      <c r="I4" s="1">
+      <c r="B4" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G4" s="2">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2">
         <v>2</v>
       </c>
-      <c r="J4" s="1">
+      <c r="K4" s="2">
         <v>90</v>
       </c>
-      <c r="K4" s="1">
+      <c r="L4" s="2">
         <v>1468</v>
       </c>
-      <c r="M4" s="1">
+      <c r="M4" s="2"/>
+      <c r="N4" s="2">
         <v>755</v>
       </c>
-      <c r="O4" s="1">
+      <c r="O4" s="2"/>
+      <c r="P4" s="2">
         <v>203</v>
       </c>
-      <c r="Q4" s="1">
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2">
         <v>0</v>
       </c>
-      <c r="S4" s="1">
+      <c r="S4" s="2"/>
+      <c r="T4" s="2">
         <v>12</v>
       </c>
-      <c r="T4" s="1">
+      <c r="U4" s="2">
         <v>-2</v>
       </c>
-      <c r="U4" s="1">
+      <c r="V4" s="2">
         <v>0.5</v>
       </c>
-      <c r="V4" s="1">
+      <c r="W4" s="2">
         <v>70</v>
       </c>
-      <c r="Y4" s="1">
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
+      <c r="Z4" s="2">
         <v>0.05</v>
       </c>
-      <c r="Z4" s="1">
+      <c r="AA4" s="2">
         <v>0.85</v>
       </c>
-      <c r="AC4" s="1">
-        <v>1</v>
-      </c>
-      <c r="AI4" s="1" t="s">
+      <c r="AB4" s="2"/>
+      <c r="AC4" s="2"/>
+      <c r="AD4" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="2"/>
+      <c r="AF4" s="2"/>
+      <c r="AG4" s="2"/>
+      <c r="AH4" s="2"/>
+      <c r="AI4" s="2"/>
+      <c r="AJ4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="AJ4" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="AK4" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="AL4" s="1" t="s">
-        <v>132</v>
+      <c r="AK4" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="AL4" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="AM4" s="2" t="s">
-        <v>587</v>
+        <v>138</v>
       </c>
       <c r="AN4" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="AP4" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="AO4" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="AP4" s="2"/>
+      <c r="AQ4" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AR4" s="2">
+        <v>1</v>
+      </c>
+      <c r="AS4" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="AT4" s="2"/>
+      <c r="AU4" s="2"/>
+      <c r="AV4" s="2"/>
+      <c r="AW4" s="2"/>
+      <c r="AX4" s="2"/>
+      <c r="AY4" s="2"/>
+      <c r="AZ4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="BA4" s="2"/>
+      <c r="BB4" s="2"/>
+      <c r="BC4" s="2"/>
+      <c r="BD4" s="2"/>
+      <c r="BE4" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="BF4" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="BG4" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="BH4" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="BI4" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="BJ4" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="BK4" s="2">
+        <v>6</v>
+      </c>
+      <c r="BL4" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="BM4" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="BN4" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="BO4" s="2"/>
+      <c r="BP4" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="BQ4" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="BR4" s="2"/>
+      <c r="BS4" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="BT4" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="BU4" s="2"/>
+      <c r="BV4" s="2">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="AQ4" s="1">
-        <v>1</v>
-      </c>
-      <c r="AR4" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="AY4" s="1">
+      <c r="C5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2">
+        <v>2</v>
+      </c>
+      <c r="K5" s="2">
+        <v>90</v>
+      </c>
+      <c r="L5" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2">
+        <v>100</v>
+      </c>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2">
+        <v>0</v>
+      </c>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2">
+        <v>5</v>
+      </c>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2">
+        <v>0</v>
+      </c>
+      <c r="W5" s="2">
+        <v>5</v>
+      </c>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2"/>
+      <c r="Z5" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="AA5" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="2"/>
+      <c r="AC5" s="2"/>
+      <c r="AD5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="2">
+        <v>1</v>
+      </c>
+      <c r="AF5" s="2"/>
+      <c r="AG5" s="2"/>
+      <c r="AH5" s="2"/>
+      <c r="AI5" s="2"/>
+      <c r="AJ5" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="AK5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="AL5" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="AM5" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="AN5" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="AO5" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="AP5" s="2"/>
+      <c r="AQ5" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AR5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT5" s="2"/>
+      <c r="AU5" s="2"/>
+      <c r="AV5" s="2"/>
+      <c r="AW5" s="2"/>
+      <c r="AX5" s="2"/>
+      <c r="AY5" s="2"/>
+      <c r="AZ5" s="2">
         <v>0.25</v>
       </c>
-      <c r="BD4" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="BE4" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="BF4" s="1" t="s">
+      <c r="BA5" s="2"/>
+      <c r="BB5" s="2"/>
+      <c r="BC5" s="2"/>
+      <c r="BD5" s="2"/>
+      <c r="BE5" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="BF5" s="2"/>
+      <c r="BG5" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="BH5" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="BI5" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="BJ5" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="BK5" s="2">
+        <v>6</v>
+      </c>
+      <c r="BL5" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="BM5" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="BN5" s="2"/>
+      <c r="BO5" s="2"/>
+      <c r="BP5" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="BQ5" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="BR5" s="2"/>
+      <c r="BS5" s="2"/>
+      <c r="BT5" s="2"/>
+      <c r="BU5" s="2"/>
+      <c r="BV5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2">
+        <v>2</v>
+      </c>
+      <c r="K6" s="2">
+        <v>90</v>
+      </c>
+      <c r="L6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2">
+        <v>100</v>
+      </c>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2">
+        <v>5</v>
+      </c>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2">
+        <v>5</v>
+      </c>
+      <c r="X6" s="2"/>
+      <c r="Y6" s="2"/>
+      <c r="Z6" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="AA6" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="2"/>
+      <c r="AC6" s="2"/>
+      <c r="AD6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="2">
+        <v>1</v>
+      </c>
+      <c r="AF6" s="2"/>
+      <c r="AG6" s="2"/>
+      <c r="AH6" s="2"/>
+      <c r="AI6" s="2"/>
+      <c r="AJ6" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="AK6" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="BG4" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="BH4" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="BI4" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="BJ4" s="1">
+      <c r="AL6" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="AM6" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="AN6" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="AO6" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="AP6" s="2"/>
+      <c r="AQ6" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AR6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT6" s="2"/>
+      <c r="AU6" s="2"/>
+      <c r="AV6" s="2"/>
+      <c r="AW6" s="2"/>
+      <c r="AX6" s="2"/>
+      <c r="AY6" s="2"/>
+      <c r="AZ6" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="BA6" s="2"/>
+      <c r="BB6" s="2"/>
+      <c r="BC6" s="2"/>
+      <c r="BD6" s="2"/>
+      <c r="BE6" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="BF6" s="2"/>
+      <c r="BG6" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="BH6" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="BI6" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="BJ6" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="BK6" s="2">
         <v>6</v>
       </c>
-      <c r="BK4" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="BL4" s="1" t="s">
+      <c r="BL6" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="BM6" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="BN6" s="2"/>
+      <c r="BO6" s="2"/>
+      <c r="BP6" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="BQ6" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="BR6" s="2"/>
+      <c r="BS6" s="2"/>
+      <c r="BT6" s="2"/>
+      <c r="BU6" s="2"/>
+      <c r="BV6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1</v>
+      </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2">
+        <v>2</v>
+      </c>
+      <c r="K7" s="2">
+        <v>90</v>
+      </c>
+      <c r="L7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2">
+        <v>100</v>
+      </c>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2">
+        <v>5</v>
+      </c>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2">
+        <v>0</v>
+      </c>
+      <c r="W7" s="2">
+        <v>5</v>
+      </c>
+      <c r="X7" s="2"/>
+      <c r="Y7" s="2"/>
+      <c r="Z7" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="AA7" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="2"/>
+      <c r="AC7" s="2"/>
+      <c r="AD7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="2">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="2"/>
+      <c r="AG7" s="2"/>
+      <c r="AH7" s="2"/>
+      <c r="AI7" s="2"/>
+      <c r="AJ7" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="AK7" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="AL7" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="AM7" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="AN7" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="AO7" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="AP7" s="2"/>
+      <c r="AQ7" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="BM4" s="1" t="s">
+      <c r="AR7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT7" s="2"/>
+      <c r="AU7" s="2"/>
+      <c r="AV7" s="2"/>
+      <c r="AW7" s="2"/>
+      <c r="AX7" s="2"/>
+      <c r="AY7" s="2"/>
+      <c r="AZ7" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="BA7" s="2"/>
+      <c r="BB7" s="2"/>
+      <c r="BC7" s="2"/>
+      <c r="BD7" s="2"/>
+      <c r="BE7" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="BO4" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="BP4" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="BR4" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="BS4" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="BU4" s="1">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="BF7" s="2"/>
+      <c r="BG7" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="BH7" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="BI7" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="BJ7" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1</v>
-      </c>
-      <c r="I5" s="1">
-        <v>2</v>
-      </c>
-      <c r="J5" s="1">
-        <v>90</v>
-      </c>
-      <c r="K5" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M5" s="1">
-        <v>100</v>
-      </c>
-      <c r="O5" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>0</v>
-      </c>
-      <c r="S5" s="1">
-        <v>5</v>
-      </c>
-      <c r="U5" s="1">
-        <v>0</v>
-      </c>
-      <c r="V5" s="1">
-        <v>5</v>
-      </c>
-      <c r="Y5" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="Z5" s="1">
-        <v>1</v>
-      </c>
-      <c r="AC5" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="1">
-        <v>1</v>
-      </c>
-      <c r="AI5" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="AJ5" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="AK5" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="AL5" s="1" t="s">
+      <c r="BK7" s="2">
+        <v>6</v>
+      </c>
+      <c r="BL7" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="BM7" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="BN7" s="2"/>
+      <c r="BO7" s="2"/>
+      <c r="BP7" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="AM5" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="AN5" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="AP5" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="AQ5" s="1">
-        <v>0</v>
-      </c>
-      <c r="AR5" s="1">
-        <v>0</v>
-      </c>
-      <c r="AY5" s="1">
-        <v>0.25</v>
-      </c>
-      <c r="BD5" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="BF5" s="1" t="s">
+      <c r="BQ7" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="BG5" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="BH5" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="BI5" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="BJ5" s="1">
-        <v>6</v>
-      </c>
-      <c r="BK5" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="BL5" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="BO5" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="BP5" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="BU5" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1</v>
-      </c>
-      <c r="I6" s="1">
-        <v>2</v>
-      </c>
-      <c r="J6" s="1">
-        <v>90</v>
-      </c>
-      <c r="K6" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M6" s="1">
-        <v>100</v>
-      </c>
-      <c r="O6" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>0</v>
-      </c>
-      <c r="S6" s="1">
-        <v>5</v>
-      </c>
-      <c r="U6" s="1">
-        <v>0</v>
-      </c>
-      <c r="V6" s="1">
-        <v>5</v>
-      </c>
-      <c r="Y6" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="Z6" s="1">
-        <v>1</v>
-      </c>
-      <c r="AC6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="1">
-        <v>1</v>
-      </c>
-      <c r="AI6" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="AJ6" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="AK6" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="AL6" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="AM6" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="AN6" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="AP6" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="AQ6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AR6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AY6" s="1">
-        <v>0.25</v>
-      </c>
-      <c r="BD6" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="BF6" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="BG6" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="BH6" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="BI6" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="BJ6" s="1">
-        <v>6</v>
-      </c>
-      <c r="BK6" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="BL6" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="BO6" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="BP6" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="BU6" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1</v>
-      </c>
-      <c r="I7" s="1">
-        <v>2</v>
-      </c>
-      <c r="J7" s="1">
-        <v>90</v>
-      </c>
-      <c r="K7" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M7" s="1">
-        <v>100</v>
-      </c>
-      <c r="O7" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>0</v>
-      </c>
-      <c r="S7" s="1">
-        <v>5</v>
-      </c>
-      <c r="U7" s="1">
-        <v>0</v>
-      </c>
-      <c r="V7" s="1">
-        <v>5</v>
-      </c>
-      <c r="Y7" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="Z7" s="1">
-        <v>1</v>
-      </c>
-      <c r="AC7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="1">
-        <v>1</v>
-      </c>
-      <c r="AI7" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="AJ7" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="AK7" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="AL7" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="AM7" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="AN7" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="AP7" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="AQ7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AR7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AY7" s="1">
-        <v>0.25</v>
-      </c>
-      <c r="BD7" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="BF7" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="BG7" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="BH7" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="BI7" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="BJ7" s="1">
-        <v>6</v>
-      </c>
-      <c r="BK7" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="BL7" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="BO7" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="BP7" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="BU7" s="1">
+      <c r="BR7" s="2"/>
+      <c r="BS7" s="2"/>
+      <c r="BT7" s="2"/>
+      <c r="BU7" s="2"/>
+      <c r="BV7" s="2">
         <v>1</v>
       </c>
     </row>
@@ -3659,6 +3824,7 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -3668,762 +3834,762 @@
   <dimension ref="A1:DI645"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.08203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.58203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7.75" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.58203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="31.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7.33203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.83203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="7.33203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="15.75" style="1" customWidth="1"/>
-    <col min="11" max="13" width="8.33203125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="11.75" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13.08203125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="11.58203125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="21.5" style="1" customWidth="1"/>
-    <col min="18" max="18" width="19.83203125" style="1" customWidth="1"/>
-    <col min="19" max="19" width="16.58203125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="19.08203125" style="1" customWidth="1"/>
-    <col min="21" max="21" width="18.33203125" style="1" customWidth="1"/>
-    <col min="22" max="22" width="17.75" style="1" customWidth="1"/>
-    <col min="23" max="23" width="8.33203125" style="1" customWidth="1"/>
-    <col min="24" max="24" width="18.5" style="1" customWidth="1"/>
-    <col min="25" max="25" width="16.58203125" style="1" customWidth="1"/>
-    <col min="26" max="26" width="10.6640625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="8.33203125" style="1" customWidth="1"/>
-    <col min="28" max="28" width="15.1640625" style="1" customWidth="1"/>
-    <col min="29" max="30" width="8.58203125" style="1" customWidth="1"/>
-    <col min="31" max="31" width="13.4140625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="13.75" style="1" customWidth="1"/>
-    <col min="33" max="33" width="14.58203125" style="1" customWidth="1"/>
-    <col min="34" max="34" width="17.4140625" style="1" customWidth="1"/>
-    <col min="35" max="35" width="8.58203125" style="1" customWidth="1"/>
-    <col min="36" max="36" width="12.5" style="1" customWidth="1"/>
-    <col min="37" max="37" width="8.58203125" style="1" customWidth="1"/>
-    <col min="38" max="39" width="8.33203125" style="1" customWidth="1"/>
-    <col min="40" max="40" width="15" style="1" customWidth="1"/>
-    <col min="41" max="41" width="13.25" style="1" customWidth="1"/>
-    <col min="42" max="45" width="11.83203125" style="1" customWidth="1"/>
-    <col min="46" max="46" width="18.4140625" style="1" customWidth="1"/>
-    <col min="47" max="47" width="12.25" style="1" customWidth="1"/>
-    <col min="48" max="48" width="11.9140625" style="1" customWidth="1"/>
-    <col min="49" max="49" width="19.58203125" style="1" customWidth="1"/>
-    <col min="50" max="50" width="12.6640625" style="1" customWidth="1"/>
-    <col min="51" max="51" width="9" style="1" customWidth="1"/>
-    <col min="52" max="52" width="7" style="1" customWidth="1"/>
-    <col min="53" max="53" width="11.75" style="1" customWidth="1"/>
-    <col min="54" max="54" width="19.75" style="1" customWidth="1"/>
-    <col min="55" max="55" width="5.08203125" style="1" customWidth="1"/>
-    <col min="56" max="56" width="8.5" style="1" customWidth="1"/>
-    <col min="57" max="57" width="13.5" style="1" customWidth="1"/>
-    <col min="58" max="58" width="14.6640625" style="1" customWidth="1"/>
-    <col min="59" max="59" width="10.1640625" style="1" customWidth="1"/>
-    <col min="60" max="60" width="8.25" style="1" customWidth="1"/>
-    <col min="61" max="67" width="8.33203125" style="1" customWidth="1"/>
-    <col min="68" max="70" width="11.25" style="1" customWidth="1"/>
-    <col min="71" max="71" width="6.58203125" style="1" customWidth="1"/>
-    <col min="72" max="73" width="8" style="1" customWidth="1"/>
-    <col min="74" max="74" width="7.33203125" style="1" customWidth="1"/>
-    <col min="75" max="76" width="8.5" style="1" customWidth="1"/>
-    <col min="77" max="78" width="7.83203125" style="1" customWidth="1"/>
-    <col min="79" max="79" width="22.1640625" style="1" customWidth="1"/>
-    <col min="80" max="80" width="13.5" style="1" customWidth="1"/>
-    <col min="81" max="81" width="21.1640625" style="1" customWidth="1"/>
-    <col min="82" max="82" width="15.75" style="1" customWidth="1"/>
-    <col min="83" max="83" width="15.58203125" style="1" customWidth="1"/>
-    <col min="84" max="84" width="12.83203125" style="1" customWidth="1"/>
-    <col min="85" max="85" width="16.1640625" style="1" customWidth="1"/>
-    <col min="86" max="86" width="9" style="1" customWidth="1"/>
-    <col min="87" max="87" width="16" style="1" customWidth="1"/>
-    <col min="88" max="89" width="12.83203125" style="1" customWidth="1"/>
-    <col min="90" max="90" width="23.58203125" style="1" customWidth="1"/>
-    <col min="91" max="91" width="12.83203125" style="1" customWidth="1"/>
-    <col min="92" max="92" width="17.08203125" style="1" customWidth="1"/>
-    <col min="93" max="98" width="9" style="1" customWidth="1"/>
-    <col min="99" max="99" width="14" style="1" customWidth="1"/>
-    <col min="100" max="100" width="8" style="1" customWidth="1"/>
-    <col min="101" max="101" width="9" style="1" customWidth="1"/>
-    <col min="102" max="102" width="11.08203125" style="1" customWidth="1"/>
-    <col min="103" max="103" width="13.75" style="1" customWidth="1"/>
-    <col min="104" max="109" width="9" style="1" customWidth="1"/>
-    <col min="110" max="110" width="15.5" style="1" customWidth="1"/>
-    <col min="111" max="114" width="9" style="1" customWidth="1"/>
-    <col min="115" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="21.08203125" customWidth="1" style="1"/>
+    <col min="2" max="2" width="15.58203125" customWidth="1" style="1"/>
+    <col min="3" max="3" width="7.75" customWidth="1" style="1"/>
+    <col min="4" max="4" width="16.58203125" customWidth="1" style="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1" style="1"/>
+    <col min="6" max="6" width="31.33203125" customWidth="1" style="1"/>
+    <col min="7" max="7" width="7.33203125" customWidth="1" style="1"/>
+    <col min="8" max="8" width="17.83203125" customWidth="1" style="1"/>
+    <col min="9" max="9" width="7.33203125" customWidth="1" style="1"/>
+    <col min="10" max="10" width="15.75" customWidth="1" style="1"/>
+    <col min="11" max="13" width="8.33203125" customWidth="1" style="1"/>
+    <col min="14" max="14" width="11.75" customWidth="1" style="1"/>
+    <col min="15" max="15" width="13.08203125" customWidth="1" style="1"/>
+    <col min="16" max="16" width="11.58203125" customWidth="1" style="1"/>
+    <col min="17" max="17" width="21.5" customWidth="1" style="1"/>
+    <col min="18" max="18" width="19.83203125" customWidth="1" style="1"/>
+    <col min="19" max="19" width="16.58203125" customWidth="1" style="1"/>
+    <col min="20" max="20" width="19.08203125" customWidth="1" style="1"/>
+    <col min="21" max="21" width="18.33203125" customWidth="1" style="1"/>
+    <col min="22" max="22" width="17.75" customWidth="1" style="1"/>
+    <col min="23" max="23" width="8.33203125" customWidth="1" style="1"/>
+    <col min="24" max="24" width="18.5" customWidth="1" style="1"/>
+    <col min="25" max="25" width="16.58203125" customWidth="1" style="1"/>
+    <col min="26" max="26" width="10.6640625" customWidth="1" style="1"/>
+    <col min="27" max="27" width="8.33203125" customWidth="1" style="1"/>
+    <col min="28" max="28" width="15.1640625" customWidth="1" style="1"/>
+    <col min="29" max="30" width="8.58203125" customWidth="1" style="1"/>
+    <col min="31" max="31" width="13.4140625" customWidth="1" style="1"/>
+    <col min="32" max="32" width="13.75" customWidth="1" style="1"/>
+    <col min="33" max="33" width="14.58203125" customWidth="1" style="1"/>
+    <col min="34" max="34" width="17.4140625" customWidth="1" style="1"/>
+    <col min="35" max="35" width="8.58203125" customWidth="1" style="1"/>
+    <col min="36" max="36" width="12.5" customWidth="1" style="1"/>
+    <col min="37" max="37" width="8.58203125" customWidth="1" style="1"/>
+    <col min="38" max="39" width="8.33203125" customWidth="1" style="1"/>
+    <col min="40" max="40" width="15" customWidth="1" style="1"/>
+    <col min="41" max="41" width="13.25" customWidth="1" style="1"/>
+    <col min="42" max="45" width="11.83203125" customWidth="1" style="1"/>
+    <col min="46" max="46" width="18.4140625" customWidth="1" style="1"/>
+    <col min="47" max="47" width="12.25" customWidth="1" style="1"/>
+    <col min="48" max="48" width="11.9140625" customWidth="1" style="1"/>
+    <col min="49" max="49" width="19.58203125" customWidth="1" style="1"/>
+    <col min="50" max="50" width="12.6640625" customWidth="1" style="1"/>
+    <col min="51" max="51" width="9" customWidth="1" style="1"/>
+    <col min="52" max="52" width="7" customWidth="1" style="1"/>
+    <col min="53" max="53" width="11.75" customWidth="1" style="1"/>
+    <col min="54" max="54" width="19.75" customWidth="1" style="1"/>
+    <col min="55" max="55" width="5.08203125" customWidth="1" style="1"/>
+    <col min="56" max="56" width="8.5" customWidth="1" style="1"/>
+    <col min="57" max="57" width="13.5" customWidth="1" style="1"/>
+    <col min="58" max="58" width="14.6640625" customWidth="1" style="1"/>
+    <col min="59" max="59" width="10.1640625" customWidth="1" style="1"/>
+    <col min="60" max="60" width="8.25" customWidth="1" style="1"/>
+    <col min="61" max="67" width="8.33203125" customWidth="1" style="1"/>
+    <col min="68" max="70" width="11.25" customWidth="1" style="1"/>
+    <col min="71" max="71" width="6.58203125" customWidth="1" style="1"/>
+    <col min="72" max="73" width="8" customWidth="1" style="1"/>
+    <col min="74" max="74" width="7.33203125" customWidth="1" style="1"/>
+    <col min="75" max="76" width="8.5" customWidth="1" style="1"/>
+    <col min="77" max="78" width="7.83203125" customWidth="1" style="1"/>
+    <col min="79" max="79" width="22.1640625" customWidth="1" style="1"/>
+    <col min="80" max="80" width="13.5" customWidth="1" style="1"/>
+    <col min="81" max="81" width="21.1640625" customWidth="1" style="1"/>
+    <col min="82" max="82" width="15.75" customWidth="1" style="1"/>
+    <col min="83" max="83" width="15.58203125" customWidth="1" style="1"/>
+    <col min="84" max="84" width="12.83203125" customWidth="1" style="1"/>
+    <col min="85" max="85" width="16.1640625" customWidth="1" style="1"/>
+    <col min="86" max="86" width="9" customWidth="1" style="1"/>
+    <col min="87" max="87" width="16" customWidth="1" style="1"/>
+    <col min="88" max="89" width="12.83203125" customWidth="1" style="1"/>
+    <col min="90" max="90" width="23.58203125" customWidth="1" style="1"/>
+    <col min="91" max="91" width="12.83203125" customWidth="1" style="1"/>
+    <col min="92" max="92" width="17.08203125" customWidth="1" style="1"/>
+    <col min="93" max="98" width="9" customWidth="1" style="1"/>
+    <col min="99" max="99" width="14" customWidth="1" style="1"/>
+    <col min="100" max="100" width="8" customWidth="1" style="1"/>
+    <col min="101" max="101" width="9" customWidth="1" style="1"/>
+    <col min="102" max="102" width="11.08203125" customWidth="1" style="1"/>
+    <col min="103" max="103" width="13.75" customWidth="1" style="1"/>
+    <col min="104" max="109" width="9" customWidth="1" style="1"/>
+    <col min="110" max="110" width="15.5" customWidth="1" style="1"/>
+    <col min="111" max="114" width="9" customWidth="1" style="1"/>
+    <col min="115" max="16384" width="9" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="B1" s="1" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="CC1" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="CD1" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="CE1" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="CF1" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="CG1" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="CH1" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="CI1" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="CJ1" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="CK1" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="CL1" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="CM1" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="CN1" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="CO1" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="CP1" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="CQ1" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="CR1" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="CD1" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="CE1" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="CF1" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="CG1" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="CH1" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="CI1" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="CJ1" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="CK1" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="CL1" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="CM1" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="CN1" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="CO1" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="CP1" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="CQ1" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="CR1" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="CS1" s="1" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="2" spans="1:113" x14ac:dyDescent="0.25">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="AO2" s="1" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="AP2" s="1" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="AQ2" s="1" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="AR2" s="1" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="AS2" s="1" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="AT2" s="1" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="AU2" s="1" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="AV2" s="1" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="AW2" s="1" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="AX2" s="1" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="AY2" s="1" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="AZ2" s="1" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="BA2" s="1" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="BB2" s="1" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="BC2" s="1" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="BD2" s="1" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="BE2" s="1" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="BF2" s="1" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="BG2" s="1" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="BH2" s="1" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="BI2" s="1" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="BJ2" s="1" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="BK2" s="1" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="BL2" s="1" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="BM2" s="1" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="BN2" s="1" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="BO2" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="BP2" s="1" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="BQ2" s="1" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="BR2" s="1" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="BS2" s="1" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="BT2" s="1" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="BU2" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="BV2" s="1" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="BW2" s="1" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="BX2" s="1" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="BY2" s="1" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="BZ2" s="1" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="CA2" s="1" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="CB2" s="1" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="CC2" s="1" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="CD2" s="1" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="CE2" s="1" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="CF2" s="1" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="CG2" s="1" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="CH2" s="1" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="CI2" s="1" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="CJ2" s="1" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="CK2" s="1" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="CL2" s="1" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="CM2" s="1" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="CN2" s="1" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="CO2" s="1" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="CP2" s="1" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="CQ2" s="1" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="CR2" s="1" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="CS2" s="1" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="CT2" s="1" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="CU2" s="1" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="CV2" s="1" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="CW2" s="1" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="CX2" s="1" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="CY2" s="1" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="CZ2" s="1" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="DA2" s="1" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="DB2" s="1" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="DC2" s="1" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="DD2" s="1" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="DE2" s="1" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="DF2" s="1" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="DG2" s="1" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="DH2" s="1" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="DI2" s="1" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="3" spans="1:113" x14ac:dyDescent="0.25">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -4440,112 +4606,112 @@
         <v>2</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="O3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="S3" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="T3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="W3" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="X3" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="Y3" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="S3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="Z3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="AC3" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="AD3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="AE3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="AF3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="AG3" s="1" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="AH3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="AI3" s="1" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="AJ3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="AK3" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="AL3" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="AM3" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="AN3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="AO3" s="1" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="AP3" s="1" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="AQ3" s="1" t="s">
         <v>2</v>
@@ -4557,226 +4723,226 @@
         <v>2</v>
       </c>
       <c r="AT3" s="1" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="AU3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="AV3" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="AW3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="AX3" s="1" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="AY3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="AZ3" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="BA3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="BB3" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="BC3" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="BD3" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="BE3" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="BF3" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="BG3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="BH3" s="1" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="BI3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="BJ3" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="BK3" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="BL3" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="BM3" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="BN3" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="BO3" s="1" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="BP3" s="1" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="BQ3" s="1" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="BR3" s="1" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="BS3" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="BT3" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="BU3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="BV3" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="BW3" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="BX3" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="BY3" s="1" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="BZ3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="CA3" s="1" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="CB3" s="1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="CC3" s="1" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="CD3" s="1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="CE3" s="1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="CF3" s="1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="CG3" s="1" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="CH3" s="1" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="CI3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="CJ3" s="1" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="CK3" s="1" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="CL3" s="1" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="CM3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO3" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="CP3" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="CQ3" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="CR3" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="CS3" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="CT3" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="CN3" s="1" t="s">
+      <c r="CU3" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="CV3" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="CW3" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="CX3" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="CY3" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="CZ3" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="DA3" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="DB3" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="DC3" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="DD3" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="CO3" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="CP3" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="CQ3" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="CR3" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="CS3" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="CT3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="CU3" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="CV3" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="CW3" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="CX3" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="CY3" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="CZ3" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="DA3" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="DB3" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="DC3" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="DD3" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="DE3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="DF3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="DG3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="DH3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="DI3" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="4" spans="1:113" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="1" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="6" spans="1:113" x14ac:dyDescent="0.25">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="8" spans="1:113" x14ac:dyDescent="0.25">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="1" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="AC8" s="1">
         <v>2</v>
@@ -4785,13 +4951,13 @@
         <v>1</v>
       </c>
       <c r="AO8" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="AT8" s="1" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="AX8" s="1" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="AZ8" s="1">
         <v>1</v>
@@ -4800,63 +4966,63 @@
         <v>1</v>
       </c>
       <c r="CB8" s="1" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="CD8" s="1" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="CG8" s="1" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="CH8" s="1" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="CI8" s="1" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="CJ8" s="1" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="CY8" s="1" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="10" spans="1:113" x14ac:dyDescent="0.25">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="1" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="G10" s="1">
         <v>3</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="AC10" s="1">
         <v>1</v>
       </c>
       <c r="AG10" s="1" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="BD10" s="1">
         <v>1</v>
       </c>
       <c r="BO10" s="1" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="BV10" s="1">
         <v>0</v>
@@ -4868,39 +5034,39 @@
         <v>1</v>
       </c>
       <c r="BY10" s="1" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="CU10" s="1" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="11" spans="1:113" x14ac:dyDescent="0.25">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>405</v>
-      </c>
       <c r="I11" s="1">
         <v>1</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="AC11" s="1">
         <v>1</v>
       </c>
       <c r="AG11" s="1" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="BD11" s="1">
         <v>1</v>
       </c>
       <c r="CU11" s="1" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="DD11" s="1">
         <v>1</v>
@@ -4915,21 +5081,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" s="1" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="I12" s="1">
         <v>1</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="AC12" s="1">
         <v>2</v>
@@ -4941,10 +5107,10 @@
         <v>99</v>
       </c>
       <c r="CG12" s="1" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="CN12" s="1" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="CO12" s="1">
         <v>-0.8</v>
@@ -4953,27 +5119,27 @@
         <v>10</v>
       </c>
       <c r="CX12" s="1" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="DH12" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" s="1" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="I13" s="1">
         <v>1</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="AC13" s="1">
         <v>2</v>
@@ -4985,10 +5151,10 @@
         <v>99</v>
       </c>
       <c r="CG13" s="1" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="CN13" s="1" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="CO13" s="1">
         <v>-0.8</v>
@@ -4997,51 +5163,51 @@
         <v>10</v>
       </c>
       <c r="CX13" s="1" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="DH13" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" s="1" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="G15" s="1">
         <v>3</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="AC15" s="1">
         <v>1</v>
       </c>
       <c r="AG15" s="1" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="BD15" s="1">
         <v>1</v>
       </c>
       <c r="BO15" s="1" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="BP15" s="1" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="BT15" s="1">
         <v>20</v>
@@ -5056,10 +5222,10 @@
         <v>1</v>
       </c>
       <c r="BY15" s="1" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="CN15" s="1" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="CO15" s="1">
         <v>3</v>
@@ -5068,33 +5234,33 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" s="1" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I16" s="1">
         <v>1</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="AC16" s="1">
         <v>1</v>
       </c>
       <c r="AG16" s="1" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="BD16" s="1">
         <v>1</v>
       </c>
       <c r="CU16" s="1" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="DD16" s="1">
         <v>1</v>
@@ -5109,15 +5275,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" s="1" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="AC17" s="1">
         <v>2</v>
@@ -5126,13 +5292,13 @@
         <v>1</v>
       </c>
       <c r="AO17" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="AT17" s="1" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="AX17" s="1" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="AZ17" s="1">
         <v>1</v>
@@ -5141,7 +5307,7 @@
         <v>1</v>
       </c>
       <c r="BJ17" s="1">
-        <v>1.1000000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="BK17" s="1">
         <v>1</v>
@@ -5150,42 +5316,42 @@
         <v>1</v>
       </c>
       <c r="CB17" s="1" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="CG17" s="1" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="CH17" s="1" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="CI17" s="1" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="CJ17" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="CY17" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="CY17" s="1" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="18" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>430</v>
-      </c>
       <c r="C18" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="I18" s="1">
         <v>1</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="AC18" s="1">
         <v>1</v>
       </c>
       <c r="AG18" s="1" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="BD18" s="1">
         <v>1</v>
@@ -5194,10 +5360,10 @@
         <v>0.5</v>
       </c>
       <c r="CB18" s="1" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="CG18" s="1" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="DD18" s="1">
         <v>1</v>
@@ -5212,27 +5378,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19" s="1" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="I19" s="1">
         <v>1</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="AC19" s="1">
         <v>1</v>
       </c>
       <c r="AG19" s="1" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="BD19" s="1">
         <v>1</v>
@@ -5241,10 +5407,10 @@
         <v>0.5</v>
       </c>
       <c r="CB19" s="1" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="CG19" s="1" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="DD19" s="1">
         <v>1</v>
@@ -5259,33 +5425,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20" s="1" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I20" s="1">
         <v>1</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="AC20" s="1">
         <v>1</v>
       </c>
       <c r="AG20" s="1" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="BD20" s="1">
         <v>1</v>
       </c>
       <c r="CU20" s="1" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="DD20" s="1">
         <v>1</v>
@@ -5300,21 +5466,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21" s="1" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="I21" s="1">
         <v>1</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="AC21" s="1">
         <v>2</v>
@@ -5326,36 +5492,36 @@
         <v>99</v>
       </c>
       <c r="CG21" s="1" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="CN21" s="1" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="CR21" s="1">
         <v>5</v>
       </c>
       <c r="CX21" s="1" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="DH21" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="A22" s="1" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="I22" s="1">
         <v>1</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="AC22" s="1">
         <v>2</v>
@@ -5367,60 +5533,60 @@
         <v>99</v>
       </c>
       <c r="CG22" s="1" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="CN22" s="1" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="CR22" s="1">
         <v>5</v>
       </c>
       <c r="CX22" s="1" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="DH22" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="A24" s="1" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="G24" s="1">
         <v>3</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="AC24" s="1">
         <v>1</v>
       </c>
       <c r="AG24" s="1" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="BD24" s="1">
         <v>1</v>
       </c>
       <c r="BO24" s="1" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="BP24" s="1" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="BT24" s="1">
         <v>40</v>
@@ -5438,16 +5604,16 @@
         <v>1</v>
       </c>
       <c r="BY24" s="1" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="CA24" s="1" t="s">
-        <v>456</v>
+        <v>160</v>
       </c>
       <c r="CN24" s="1" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="CO24" s="1" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="CR24" s="1">
         <v>99999</v>
@@ -5456,33 +5622,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="A25" s="1" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I25" s="1">
         <v>1</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="AC25" s="1">
         <v>1</v>
       </c>
       <c r="AG25" s="1" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="BD25" s="1">
         <v>1</v>
       </c>
       <c r="CU25" s="1" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="DD25" s="1">
         <v>1</v>
@@ -5494,18 +5660,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="26">
       <c r="A26" s="1" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="AC26" s="1">
         <v>2</v>
@@ -5514,13 +5680,13 @@
         <v>1</v>
       </c>
       <c r="AO26" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="AT26" s="1" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="AX26" s="1" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="AZ26" s="1">
         <v>1</v>
@@ -5529,42 +5695,42 @@
         <v>1</v>
       </c>
       <c r="CA26" s="1" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="CB26" s="1" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="CD26" s="1" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="CG26" s="1" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="CH26" s="1" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="CI26" s="1" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="CJ26" s="1" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="CY26" s="1" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="27" spans="1:112" x14ac:dyDescent="0.25">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27" s="1" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="AC27" s="1">
         <v>2</v>
@@ -5573,13 +5739,13 @@
         <v>1</v>
       </c>
       <c r="AO27" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="AT27" s="1" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="AX27" s="1" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="AZ27" s="1">
         <v>1</v>
@@ -5588,48 +5754,48 @@
         <v>1</v>
       </c>
       <c r="CA27" s="1" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="CB27" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="CD27" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="CG27" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="CH27" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="CI27" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="CJ27" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="CY27" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="CD27" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="CG27" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="CH27" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="CI27" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="CJ27" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="CY27" s="1" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="28" spans="1:112" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>455</v>
-      </c>
       <c r="C28" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="I28" s="1">
         <v>1</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="AC28" s="1">
         <v>1</v>
       </c>
       <c r="AG28" s="1" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="BD28" s="1">
         <v>1</v>
@@ -5638,10 +5804,10 @@
         <v>0.5</v>
       </c>
       <c r="CB28" s="1" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="CG28" s="1" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="DD28" s="1">
         <v>1</v>
@@ -5653,27 +5819,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="29">
       <c r="A29" s="1" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="I29" s="1">
         <v>1</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="AC29" s="1">
         <v>1</v>
       </c>
       <c r="AG29" s="1" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="BD29" s="1">
         <v>1</v>
@@ -5682,10 +5848,10 @@
         <v>0.5</v>
       </c>
       <c r="CB29" s="1" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="CG29" s="1" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="DD29" s="1">
         <v>1</v>
@@ -5697,33 +5863,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="30">
       <c r="A30" s="1" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="I30" s="1">
         <v>1</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="AC30" s="1">
         <v>1</v>
       </c>
       <c r="AG30" s="1" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="BD30" s="1">
         <v>1</v>
       </c>
       <c r="CU30" s="1" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="DD30" s="1">
         <v>1</v>
@@ -5735,21 +5901,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="31">
       <c r="A31" s="1" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="I31" s="1">
         <v>1</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="N31" s="1">
         <v>1</v>
@@ -5758,16 +5924,16 @@
         <v>1</v>
       </c>
       <c r="AG31" s="1" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="BD31" s="1">
         <v>1</v>
       </c>
       <c r="BO31" s="1" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="CN31" s="1" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="CR31" s="1">
         <v>99999</v>
@@ -5782,12 +5948,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="32">
       <c r="A32" s="1" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="I32" s="1">
         <v>1</v>
@@ -5796,10 +5962,10 @@
         <v>1</v>
       </c>
       <c r="AG32" s="1" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="AT32" s="1" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="BD32" s="1">
         <v>1</v>
@@ -5814,21 +5980,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="33">
       <c r="A33" s="1" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="I33" s="1">
         <v>1</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="AC33" s="1">
         <v>2</v>
@@ -5840,10 +6006,10 @@
         <v>99</v>
       </c>
       <c r="CG33" s="1" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="CN33" s="1" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="CO33" s="1">
         <v>-0.8</v>
@@ -5855,27 +6021,27 @@
         <v>7</v>
       </c>
       <c r="CX33" s="1" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="DH33" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="34">
       <c r="A34" s="1" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="I34" s="1">
         <v>1</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="AC34" s="1">
         <v>2</v>
@@ -5887,10 +6053,10 @@
         <v>99</v>
       </c>
       <c r="CG34" s="1" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="CN34" s="1" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="CO34" s="1">
         <v>-0.8</v>
@@ -5902,47 +6068,47 @@
         <v>7</v>
       </c>
       <c r="CX34" s="1" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="DH34" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="37">
       <c r="A37" s="1" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="AC37" s="1">
         <v>2</v>
       </c>
       <c r="AT37" s="1" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="BD37" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="38">
       <c r="A38" s="1" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="I38" s="1">
         <v>1</v>
@@ -5957,24 +6123,24 @@
         <v>1</v>
       </c>
       <c r="BP38" s="1" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="DH38" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="39">
       <c r="A39" s="1" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="I39" s="1">
         <v>1</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="AC39" s="1">
         <v>2</v>
@@ -5986,19 +6152,19 @@
         <v>99</v>
       </c>
       <c r="BP39" s="1" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="BS39" s="1">
         <v>0.5</v>
       </c>
       <c r="CB39" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="CG39" s="1" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="CN39" s="1" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="CO39" s="1">
         <v>-0.8</v>
@@ -6007,47 +6173,47 @@
         <v>10</v>
       </c>
       <c r="CX39" s="1" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="DH39" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="40">
       <c r="A40" s="1" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="AC40" s="1">
         <v>2</v>
       </c>
       <c r="AT40" s="1" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="BD40" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="41">
       <c r="A41" s="1" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="I41" s="1">
         <v>1</v>
@@ -6062,24 +6228,24 @@
         <v>1</v>
       </c>
       <c r="BP41" s="1" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="DH41" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="42">
       <c r="A42" s="1" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="I42" s="1">
         <v>1</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="AC42" s="1">
         <v>2</v>
@@ -6091,65 +6257,65 @@
         <v>99</v>
       </c>
       <c r="BP42" s="1" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="BS42" s="1">
         <v>0.5</v>
       </c>
       <c r="CB42" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="CG42" s="1" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="CN42" s="1" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="CR42" s="1">
         <v>5</v>
       </c>
       <c r="CX42" s="1" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="DH42" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="43">
       <c r="A43" s="1" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="AC43" s="1">
         <v>2</v>
       </c>
       <c r="AT43" s="1" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="BD43" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="44">
       <c r="A44" s="1" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="I44" s="1">
         <v>1</v>
@@ -6164,24 +6330,24 @@
         <v>1</v>
       </c>
       <c r="BP44" s="1" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="DH44" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="45">
       <c r="A45" s="1" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="I45" s="1">
         <v>1</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="AC45" s="1">
         <v>2</v>
@@ -6193,19 +6359,19 @@
         <v>99</v>
       </c>
       <c r="BP45" s="1" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="BS45" s="1">
         <v>0.5</v>
       </c>
       <c r="CB45" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="CG45" s="1" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="CN45" s="1" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="CO45" s="1">
         <v>-0.8</v>
@@ -6217,24 +6383,24 @@
         <v>7</v>
       </c>
       <c r="CX45" s="1" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="DH45" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:112" x14ac:dyDescent="0.25">
+    <row r="46">
       <c r="A46" s="1" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="I46" s="1">
         <v>1</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="AC46" s="1">
         <v>1</v>
@@ -6243,10 +6409,10 @@
         <v>1</v>
       </c>
       <c r="AG46" s="1" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="AX46" s="1" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="AZ46" s="1">
         <v>1</v>
@@ -6270,52 +6436,52 @@
         <v>1</v>
       </c>
     </row>
-    <row r="625" spans="90:90" x14ac:dyDescent="0.25">
+    <row r="625">
       <c r="CL625" s="1">
         <v>0.15</v>
       </c>
     </row>
-    <row r="627" spans="90:90" x14ac:dyDescent="0.25">
+    <row r="627">
       <c r="CL627" s="1">
         <v>0.2</v>
       </c>
     </row>
-    <row r="628" spans="90:90" x14ac:dyDescent="0.25">
+    <row r="628">
       <c r="CL628" s="1">
         <v>0.1</v>
       </c>
     </row>
-    <row r="630" spans="90:90" x14ac:dyDescent="0.25">
+    <row r="630">
       <c r="CL630" s="1">
         <v>0.2</v>
       </c>
     </row>
-    <row r="637" spans="90:90" x14ac:dyDescent="0.25">
+    <row r="637">
       <c r="CL637" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="639" spans="90:90" x14ac:dyDescent="0.25">
+    <row r="639">
       <c r="CL639" s="1">
         <v>0.4</v>
       </c>
     </row>
-    <row r="640" spans="90:90" x14ac:dyDescent="0.25">
+    <row r="640">
       <c r="CL640" s="1">
         <v>0.6</v>
       </c>
     </row>
-    <row r="643" spans="90:90" x14ac:dyDescent="0.25">
+    <row r="643">
       <c r="CL643" s="1">
         <v>0.5</v>
       </c>
     </row>
-    <row r="644" spans="90:90" x14ac:dyDescent="0.25">
+    <row r="644">
       <c r="CL644" s="1">
-        <v>0.66700000000000004</v>
-      </c>
-    </row>
-    <row r="645" spans="90:90" x14ac:dyDescent="0.25">
+        <v>0.667</v>
+      </c>
+    </row>
+    <row r="645">
       <c r="CL645" s="1">
         <v>0.2</v>
       </c>
@@ -6324,6 +6490,7 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -6333,21 +6500,21 @@
   <dimension ref="A1:Q10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13" style="1" customWidth="1"/>
-    <col min="2" max="2" width="31.25" style="1" customWidth="1"/>
-    <col min="3" max="6" width="9" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.75" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15" style="1" customWidth="1"/>
-    <col min="9" max="13" width="9" style="1" customWidth="1"/>
-    <col min="14" max="14" width="16.08203125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="9.5" style="1" customWidth="1"/>
-    <col min="16" max="16" width="9" style="1" customWidth="1"/>
-    <col min="17" max="17" width="12.83203125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="13" customWidth="1" style="1"/>
+    <col min="2" max="2" width="31.25" customWidth="1" style="1"/>
+    <col min="3" max="6" width="9" customWidth="1" style="1"/>
+    <col min="7" max="7" width="18.75" customWidth="1" style="1"/>
+    <col min="8" max="8" width="15" customWidth="1" style="1"/>
+    <col min="9" max="13" width="9" customWidth="1" style="1"/>
+    <col min="14" max="14" width="16.08203125" customWidth="1" style="1"/>
+    <col min="15" max="15" width="9.5" customWidth="1" style="1"/>
+    <col min="16" max="16" width="9" customWidth="1" style="1"/>
+    <col min="17" max="17" width="12.83203125" customWidth="1" style="1"/>
+    <col min="18" max="18" width="9" customWidth="1" style="1"/>
+    <col min="19" max="16384" width="9" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6355,90 +6522,90 @@
         <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -6449,150 +6616,151 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="1" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="H4" s="1">
         <v>1</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="1" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="H5" s="1">
         <v>1</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="1" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="H6" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" s="1" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="H7" s="1">
         <v>1</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="1" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H8" s="1">
         <v>1</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" s="1" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="H9" s="1">
         <v>1</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="1" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H10" s="1">
         <v>1</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -6601,37 +6769,37 @@
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.1640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="1" customWidth="1"/>
-    <col min="4" max="4" width="27.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="11.33203125" customWidth="1" style="1"/>
+    <col min="2" max="2" width="13.1640625" customWidth="1" style="1"/>
+    <col min="3" max="3" width="15" customWidth="1" style="1"/>
+    <col min="4" max="4" width="27.5" customWidth="1" style="1"/>
+    <col min="5" max="5" width="9" customWidth="1" style="1"/>
+    <col min="6" max="16384" width="9" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -6639,52 +6807,53 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="1" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="1" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="1" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -6693,52 +6862,52 @@
   <dimension ref="A1:J4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="1" customWidth="1"/>
-    <col min="5" max="11" width="9" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="15.25" customWidth="1" style="1"/>
+    <col min="2" max="2" width="9" customWidth="1" style="1"/>
+    <col min="3" max="3" width="27.25" customWidth="1" style="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1" style="1"/>
+    <col min="5" max="11" width="9" customWidth="1" style="1"/>
+    <col min="12" max="16384" width="9" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="I1" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -6752,33 +6921,33 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="1" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="E4" s="1">
         <v>200</v>
@@ -6791,6 +6960,7 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -6799,89 +6969,89 @@
   <dimension ref="A1:L4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28" style="1" customWidth="1"/>
-    <col min="3" max="4" width="10.08203125" style="1" customWidth="1"/>
-    <col min="5" max="10" width="11.25" style="1" customWidth="1"/>
-    <col min="11" max="11" width="6.33203125" style="1" customWidth="1"/>
-    <col min="12" max="13" width="9" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="15.25" customWidth="1" style="1"/>
+    <col min="2" max="2" width="28" customWidth="1" style="1"/>
+    <col min="3" max="4" width="10.08203125" customWidth="1" style="1"/>
+    <col min="5" max="10" width="11.25" customWidth="1" style="1"/>
+    <col min="11" max="11" width="6.33203125" customWidth="1" style="1"/>
+    <col min="12" max="13" width="9" customWidth="1" style="1"/>
+    <col min="14" max="16384" width="9" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -6889,42 +7059,42 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>560</v>
+        <v>124</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="1" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="I4" s="1">
         <v>1</v>
@@ -6940,6 +7110,7 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -6949,51 +7120,51 @@
   <dimension ref="A2:J3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.08203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.25" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="47.83203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" style="1" customWidth="1"/>
-    <col min="7" max="9" width="9" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.83203125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="9" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="19.08203125" customWidth="1" style="1"/>
+    <col min="2" max="2" width="16.25" customWidth="1" style="1"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1" style="1"/>
+    <col min="4" max="4" width="47.83203125" customWidth="1" style="1"/>
+    <col min="5" max="5" width="10.25" customWidth="1" style="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1" style="1"/>
+    <col min="7" max="9" width="9" customWidth="1" style="1"/>
+    <col min="10" max="10" width="11.83203125" customWidth="1" style="1"/>
+    <col min="11" max="11" width="9" customWidth="1" style="1"/>
+    <col min="12" max="16384" width="9" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -7007,27 +7178,28 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -7036,85 +7208,85 @@
   <dimension ref="A1:I3"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.9140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14" style="1" customWidth="1"/>
-    <col min="6" max="7" width="15.1640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.9140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.75" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.75" style="1"/>
+    <col min="1" max="1" width="7.5" customWidth="1" style="1"/>
+    <col min="2" max="2" width="10.6640625" customWidth="1" style="1"/>
+    <col min="3" max="3" width="21.9140625" customWidth="1" style="1"/>
+    <col min="4" max="4" width="16.25" customWidth="1" style="1"/>
+    <col min="5" max="5" width="14" customWidth="1" style="1"/>
+    <col min="6" max="7" width="15.1640625" customWidth="1" style="1"/>
+    <col min="8" max="8" width="12.9140625" customWidth="1" style="1"/>
+    <col min="9" max="9" width="14" customWidth="1" style="1"/>
+    <col min="10" max="10" width="8.75" customWidth="1" style="1"/>
+    <col min="11" max="16384" width="8.75" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>2</v>
@@ -7138,6 +7310,7 @@
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 

--- a/Excel/一方通行/艾拉.xlsx
+++ b/Excel/一方通行/艾拉.xlsx
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="590">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="592">
   <si>
     <t>Id</t>
   </si>
@@ -670,6 +670,9 @@
     <t>Ablititys</t>
   </si>
   <si>
+    <t>StartAnimation</t>
+  </si>
+  <si>
     <t>DefaultAnimation</t>
   </si>
   <si>
@@ -686,6 +689,9 @@
   </si>
   <si>
     <t>ForwardAnimation</t>
+  </si>
+  <si>
+    <t>DieAnimation</t>
   </si>
   <si>
     <t>MaxAnimationScale</t>
@@ -2501,7 +2507,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BV7"/>
+  <dimension ref="A1:BX7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1" style="2"/>
@@ -2571,13 +2577,15 @@
     <col min="65" max="65" width="9" customWidth="1" style="2"/>
     <col min="66" max="66" width="9" customWidth="1" style="2"/>
     <col min="67" max="67" width="39.58203125" customWidth="1" style="2"/>
-    <col min="68" max="68" width="14" customWidth="1" style="2"/>
-    <col min="69" max="69" width="14.83203125" customWidth="1" style="2"/>
-    <col min="70" max="70" width="14" customWidth="1" style="2"/>
+    <col min="68" max="68" width="9" customWidth="1" style="2"/>
+    <col min="69" max="69" width="14" customWidth="1" style="2"/>
+    <col min="70" max="70" width="14.83203125" customWidth="1" style="2"/>
     <col min="71" max="71" width="14" customWidth="1" style="2"/>
     <col min="72" max="72" width="14" customWidth="1" style="2"/>
     <col min="73" max="73" width="14" customWidth="1" style="2"/>
-    <col min="74" max="74" width="19.1640625" customWidth="1" style="2"/>
+    <col min="74" max="74" width="14" customWidth="1" style="2"/>
+    <col min="75" max="75" width="9" customWidth="1" style="2"/>
+    <col min="76" max="76" width="19.1640625" customWidth="1" style="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2749,6 +2757,8 @@
       <c r="BT1" s="2"/>
       <c r="BU1" s="2"/>
       <c r="BV1" s="2"/>
+      <c r="BW1" s="2"/>
+      <c r="BX1" s="2"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
@@ -2969,6 +2979,12 @@
       <c r="BV2" s="2" t="s">
         <v>121</v>
       </c>
+      <c r="BW2" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BX2" s="2" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
@@ -2978,7 +2994,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -2986,91 +3002,91 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="J3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="V3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="W3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Y3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="Z3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="AA3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="AB3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AC3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="O3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="AD3" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AF3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="AG3" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AH3" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AI3" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AJ3" s="2" t="s">
         <v>2</v>
@@ -3079,10 +3095,10 @@
         <v>2</v>
       </c>
       <c r="AL3" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AM3" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AN3" s="2" t="s">
         <v>2</v>
@@ -3091,50 +3107,50 @@
         <v>2</v>
       </c>
       <c r="AP3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AQ3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AR3" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="AR3" s="2" t="s">
+      <c r="AS3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="AS3" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="AT3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AU3" s="2"/>
       <c r="AV3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AW3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AX3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AY3" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="AY3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="AZ3" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="BA3" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="BB3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="BC3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="BD3" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="BE3" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="BF3" s="2" t="s">
         <v>2</v>
@@ -3149,43 +3165,49 @@
         <v>2</v>
       </c>
       <c r="BJ3" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="BK3" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="BL3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="BM3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BN3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="BO3" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="BP3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BQ3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BR3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BS3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BT3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BU3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BV3" s="2" t="s">
-        <v>123</v>
+        <v>129</v>
+      </c>
+      <c r="BW3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BX3" s="2" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="4">
@@ -3193,17 +3215,17 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G4" s="2">
         <v>1</v>
@@ -3266,23 +3288,23 @@
         <v>4</v>
       </c>
       <c r="AK4" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AL4" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AM4" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AN4" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AO4" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AP4" s="2"/>
       <c r="AQ4" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AR4" s="2">
         <v>1</v>
@@ -3304,70 +3326,72 @@
       <c r="BC4" s="2"/>
       <c r="BD4" s="2"/>
       <c r="BE4" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="BF4" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="BG4" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BH4" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BI4" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BJ4" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BK4" s="2">
         <v>6</v>
       </c>
       <c r="BL4" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="BM4" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="BN4" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="BO4" s="2"/>
-      <c r="BP4" s="2" t="s">
-        <v>151</v>
-      </c>
+      <c r="BP4" s="2"/>
       <c r="BQ4" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="BR4" s="2"/>
-      <c r="BS4" s="2" t="s">
         <v>153</v>
       </c>
+      <c r="BR4" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="BS4" s="2"/>
       <c r="BT4" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="BU4" s="2"/>
-      <c r="BV4" s="2">
+        <v>155</v>
+      </c>
+      <c r="BU4" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="BV4" s="2"/>
+      <c r="BW4" s="2"/>
+      <c r="BX4" s="2">
         <v>1.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G5" s="2">
         <v>1</v>
@@ -3427,26 +3451,26 @@
       <c r="AH5" s="2"/>
       <c r="AI5" s="2"/>
       <c r="AJ5" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AK5" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AL5" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AM5" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AN5" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AO5" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AP5" s="2"/>
       <c r="AQ5" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AR5" s="2">
         <v>0</v>
@@ -3468,62 +3492,64 @@
       <c r="BC5" s="2"/>
       <c r="BD5" s="2"/>
       <c r="BE5" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="BF5" s="2"/>
       <c r="BG5" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BH5" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BI5" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="BJ5" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BK5" s="2">
         <v>6</v>
       </c>
       <c r="BL5" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="BM5" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="BN5" s="2"/>
       <c r="BO5" s="2"/>
-      <c r="BP5" s="2" t="s">
-        <v>151</v>
-      </c>
+      <c r="BP5" s="2"/>
       <c r="BQ5" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="BR5" s="2"/>
+        <v>153</v>
+      </c>
+      <c r="BR5" s="2" t="s">
+        <v>154</v>
+      </c>
       <c r="BS5" s="2"/>
       <c r="BT5" s="2"/>
       <c r="BU5" s="2"/>
-      <c r="BV5" s="2">
+      <c r="BV5" s="2"/>
+      <c r="BW5" s="2"/>
+      <c r="BX5" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -3583,26 +3609,26 @@
       <c r="AH6" s="2"/>
       <c r="AI6" s="2"/>
       <c r="AJ6" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AK6" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AL6" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AM6" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AN6" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AO6" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AP6" s="2"/>
       <c r="AQ6" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AR6" s="2">
         <v>0</v>
@@ -3624,62 +3650,64 @@
       <c r="BC6" s="2"/>
       <c r="BD6" s="2"/>
       <c r="BE6" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="BF6" s="2"/>
       <c r="BG6" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BH6" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BI6" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="BJ6" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BK6" s="2">
         <v>6</v>
       </c>
       <c r="BL6" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="BM6" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="BN6" s="2"/>
       <c r="BO6" s="2"/>
-      <c r="BP6" s="2" t="s">
-        <v>151</v>
-      </c>
+      <c r="BP6" s="2"/>
       <c r="BQ6" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="BR6" s="2"/>
+        <v>153</v>
+      </c>
+      <c r="BR6" s="2" t="s">
+        <v>154</v>
+      </c>
       <c r="BS6" s="2"/>
       <c r="BT6" s="2"/>
       <c r="BU6" s="2"/>
-      <c r="BV6" s="2">
+      <c r="BV6" s="2"/>
+      <c r="BW6" s="2"/>
+      <c r="BX6" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -3739,26 +3767,26 @@
       <c r="AH7" s="2"/>
       <c r="AI7" s="2"/>
       <c r="AJ7" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AK7" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AL7" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AM7" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AN7" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AO7" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AP7" s="2"/>
       <c r="AQ7" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AR7" s="2">
         <v>0</v>
@@ -3780,43 +3808,45 @@
       <c r="BC7" s="2"/>
       <c r="BD7" s="2"/>
       <c r="BE7" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="BF7" s="2"/>
       <c r="BG7" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BH7" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BI7" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="BJ7" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BK7" s="2">
         <v>6</v>
       </c>
       <c r="BL7" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="BM7" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="BN7" s="2"/>
       <c r="BO7" s="2"/>
-      <c r="BP7" s="2" t="s">
-        <v>151</v>
-      </c>
+      <c r="BP7" s="2"/>
       <c r="BQ7" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="BR7" s="2"/>
+        <v>153</v>
+      </c>
+      <c r="BR7" s="2" t="s">
+        <v>154</v>
+      </c>
       <c r="BS7" s="2"/>
       <c r="BT7" s="2"/>
       <c r="BU7" s="2"/>
-      <c r="BV7" s="2">
+      <c r="BV7" s="2"/>
+      <c r="BW7" s="2"/>
+      <c r="BX7" s="2">
         <v>1</v>
       </c>
     </row>
@@ -3921,334 +3951,334 @@
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="BV1" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="BW1" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="BX1" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="BY1" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="BZ1" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="CA1" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="CB1" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="CC1" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="CD1" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="CE1" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="CF1" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="CG1" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="CH1" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="CI1" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="CJ1" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="CK1" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="CL1" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="CM1" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="CN1" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="CO1" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="CP1" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="CQ1" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="CR1" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="BW1" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="BX1" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="BY1" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="BZ1" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="CA1" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="CB1" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="CC1" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="CD1" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="CE1" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="CF1" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="CG1" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="CH1" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="CI1" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="CJ1" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="CK1" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="CL1" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="CM1" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="CN1" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="CO1" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="CP1" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="CQ1" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="CR1" s="1" t="s">
-        <v>237</v>
-      </c>
       <c r="CS1" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2">
@@ -4262,331 +4292,331 @@
         <v>83</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>57</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AO2" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AP2" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AQ2" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AR2" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AS2" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AT2" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AU2" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AV2" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AW2" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AX2" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AY2" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AZ2" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="BA2" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="BB2" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="BC2" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="BD2" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="BE2" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="BF2" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="BG2" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="BH2" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="BI2" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="BJ2" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="BK2" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="BL2" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="BM2" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="BN2" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="BO2" s="1" t="s">
         <v>85</v>
       </c>
       <c r="BP2" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="BQ2" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="BR2" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="BS2" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="BT2" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="BU2" s="1" t="s">
         <v>101</v>
       </c>
       <c r="BV2" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="BW2" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="BX2" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="BY2" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="BZ2" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="CA2" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="CB2" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="CC2" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="CD2" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="CE2" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="CF2" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="CG2" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="CH2" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="CI2" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="CJ2" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="CK2" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="CL2" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="CM2" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="CN2" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="CO2" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="CP2" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="CQ2" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="CR2" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="CS2" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="CT2" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="CU2" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="CV2" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="CW2" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="CX2" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="CY2" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="CZ2" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="DA2" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="DB2" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="DC2" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="DD2" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="DE2" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="DF2" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="DG2" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="DH2" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="DI2" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="3">
@@ -4606,112 +4636,112 @@
         <v>2</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="T3" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="U3" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="O3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="V3" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AC3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AD3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AE3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AF3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AG3" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AH3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AI3" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AJ3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="AK3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AL3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AM3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AN3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AO3" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AP3" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AQ3" s="1" t="s">
         <v>2</v>
@@ -4723,226 +4753,226 @@
         <v>2</v>
       </c>
       <c r="AT3" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AU3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AV3" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AW3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AX3" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AY3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AZ3" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="BA3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="BB3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="BC3" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="BC3" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="BD3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="BE3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="BF3" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="BE3" s="1" t="s">
+      <c r="BG3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="BH3" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="BI3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="BJ3" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="BF3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="BG3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="BH3" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="BI3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="BJ3" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="BK3" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="BL3" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="BM3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="BN3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="BO3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="BP3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="BQ3" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="BR3" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="BS3" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="BN3" s="1" t="s">
+      <c r="BT3" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="BO3" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="BP3" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="BQ3" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="BR3" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="BS3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="BT3" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="BU3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="BV3" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="BW3" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="BX3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="BY3" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="BZ3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="CA3" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="CB3" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="CC3" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="CD3" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="CE3" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="CF3" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="CG3" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="CH3" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="CI3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="CJ3" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="CK3" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="CL3" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="CM3" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="CN3" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="CO3" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="CP3" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="CQ3" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="CR3" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="CS3" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="CT3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="CU3" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="CV3" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="CW3" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="CX3" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="CY3" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="CZ3" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="DA3" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="DB3" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="DC3" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="DD3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="DE3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="DF3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="DG3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="DH3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="DI3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AC8" s="1">
         <v>2</v>
@@ -4951,13 +4981,13 @@
         <v>1</v>
       </c>
       <c r="AO8" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AT8" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AX8" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AZ8" s="1">
         <v>1</v>
@@ -4966,63 +4996,63 @@
         <v>1</v>
       </c>
       <c r="CB8" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="CD8" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="CG8" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="CH8" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="CI8" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="CJ8" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="CY8" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="G10" s="1">
         <v>3</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AC10" s="1">
         <v>1</v>
       </c>
       <c r="AG10" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="BD10" s="1">
         <v>1</v>
       </c>
       <c r="BO10" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="BV10" s="1">
         <v>0</v>
@@ -5034,39 +5064,39 @@
         <v>1</v>
       </c>
       <c r="BY10" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="CU10" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="I11" s="1">
         <v>1</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AC11" s="1">
         <v>1</v>
       </c>
       <c r="AG11" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="BD11" s="1">
         <v>1</v>
       </c>
       <c r="CU11" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="DD11" s="1">
         <v>1</v>
@@ -5083,19 +5113,19 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I12" s="1">
         <v>1</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AC12" s="1">
         <v>2</v>
@@ -5107,10 +5137,10 @@
         <v>99</v>
       </c>
       <c r="CG12" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="CN12" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="CO12" s="1">
         <v>-0.8</v>
@@ -5119,7 +5149,7 @@
         <v>10</v>
       </c>
       <c r="CX12" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="DH12" s="1">
         <v>1</v>
@@ -5127,19 +5157,19 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I13" s="1">
         <v>1</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AC13" s="1">
         <v>2</v>
@@ -5151,10 +5181,10 @@
         <v>99</v>
       </c>
       <c r="CG13" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="CN13" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="CO13" s="1">
         <v>-0.8</v>
@@ -5163,7 +5193,7 @@
         <v>10</v>
       </c>
       <c r="CX13" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="DH13" s="1">
         <v>1</v>
@@ -5171,43 +5201,43 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="G15" s="1">
         <v>3</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AC15" s="1">
         <v>1</v>
       </c>
       <c r="AG15" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="BD15" s="1">
         <v>1</v>
       </c>
       <c r="BO15" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="BP15" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="BT15" s="1">
         <v>20</v>
@@ -5222,10 +5252,10 @@
         <v>1</v>
       </c>
       <c r="BY15" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="CN15" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="CO15" s="1">
         <v>3</v>
@@ -5236,31 +5266,31 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="I16" s="1">
         <v>1</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AC16" s="1">
         <v>1</v>
       </c>
       <c r="AG16" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="BD16" s="1">
         <v>1</v>
       </c>
       <c r="CU16" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="DD16" s="1">
         <v>1</v>
@@ -5277,13 +5307,13 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AC17" s="1">
         <v>2</v>
@@ -5292,13 +5322,13 @@
         <v>1</v>
       </c>
       <c r="AO17" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AT17" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AX17" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AZ17" s="1">
         <v>1</v>
@@ -5316,42 +5346,42 @@
         <v>1</v>
       </c>
       <c r="CB17" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="CG17" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="CH17" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="CI17" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="CJ17" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="CY17" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I18" s="1">
         <v>1</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AC18" s="1">
         <v>1</v>
       </c>
       <c r="AG18" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="BD18" s="1">
         <v>1</v>
@@ -5360,10 +5390,10 @@
         <v>0.5</v>
       </c>
       <c r="CB18" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="CG18" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="DD18" s="1">
         <v>1</v>
@@ -5380,25 +5410,25 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I19" s="1">
         <v>1</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AC19" s="1">
         <v>1</v>
       </c>
       <c r="AG19" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="BD19" s="1">
         <v>1</v>
@@ -5407,10 +5437,10 @@
         <v>0.5</v>
       </c>
       <c r="CB19" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="CG19" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="DD19" s="1">
         <v>1</v>
@@ -5427,31 +5457,31 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="I20" s="1">
+        <v>1</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="L20" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="I20" s="1">
-        <v>1</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>452</v>
-      </c>
       <c r="AC20" s="1">
         <v>1</v>
       </c>
       <c r="AG20" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="BD20" s="1">
         <v>1</v>
       </c>
       <c r="CU20" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="DD20" s="1">
         <v>1</v>
@@ -5468,19 +5498,19 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I21" s="1">
         <v>1</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AC21" s="1">
         <v>2</v>
@@ -5492,16 +5522,16 @@
         <v>99</v>
       </c>
       <c r="CG21" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="CN21" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="CR21" s="1">
         <v>5</v>
       </c>
       <c r="CX21" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="DH21" s="1">
         <v>1</v>
@@ -5509,19 +5539,19 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I22" s="1">
         <v>1</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AC22" s="1">
         <v>2</v>
@@ -5533,16 +5563,16 @@
         <v>99</v>
       </c>
       <c r="CG22" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="CN22" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="CR22" s="1">
         <v>5</v>
       </c>
       <c r="CX22" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="DH22" s="1">
         <v>1</v>
@@ -5550,43 +5580,43 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="G24" s="1">
         <v>3</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AC24" s="1">
         <v>1</v>
       </c>
       <c r="AG24" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="BD24" s="1">
         <v>1</v>
       </c>
       <c r="BO24" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="BP24" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="BT24" s="1">
         <v>40</v>
@@ -5604,16 +5634,16 @@
         <v>1</v>
       </c>
       <c r="BY24" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="CA24" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="CN24" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="CO24" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="CR24" s="1">
         <v>99999</v>
@@ -5624,31 +5654,31 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="I25" s="1">
         <v>1</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AC25" s="1">
         <v>1</v>
       </c>
       <c r="AG25" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="BD25" s="1">
         <v>1</v>
       </c>
       <c r="CU25" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="DD25" s="1">
         <v>1</v>
@@ -5662,16 +5692,16 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AC26" s="1">
         <v>2</v>
@@ -5680,13 +5710,13 @@
         <v>1</v>
       </c>
       <c r="AO26" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AT26" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AX26" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AZ26" s="1">
         <v>1</v>
@@ -5695,42 +5725,42 @@
         <v>1</v>
       </c>
       <c r="CA26" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="CB26" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="CD26" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="CG26" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="CH26" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="CI26" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="CJ26" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="CY26" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AC27" s="1">
         <v>2</v>
@@ -5739,13 +5769,13 @@
         <v>1</v>
       </c>
       <c r="AO27" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AT27" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AX27" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AZ27" s="1">
         <v>1</v>
@@ -5754,48 +5784,48 @@
         <v>1</v>
       </c>
       <c r="CA27" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="CB27" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="CD27" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="CG27" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="CH27" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="CI27" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="CJ27" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="CY27" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I28" s="1">
         <v>1</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AC28" s="1">
         <v>1</v>
       </c>
       <c r="AG28" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="BD28" s="1">
         <v>1</v>
@@ -5804,10 +5834,10 @@
         <v>0.5</v>
       </c>
       <c r="CB28" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="CG28" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="DD28" s="1">
         <v>1</v>
@@ -5821,25 +5851,25 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I29" s="1">
         <v>1</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AC29" s="1">
         <v>1</v>
       </c>
       <c r="AG29" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="BD29" s="1">
         <v>1</v>
@@ -5848,10 +5878,10 @@
         <v>0.5</v>
       </c>
       <c r="CB29" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="CG29" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="DD29" s="1">
         <v>1</v>
@@ -5865,31 +5895,31 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="I30" s="1">
         <v>1</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AC30" s="1">
         <v>1</v>
       </c>
       <c r="AG30" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="BD30" s="1">
         <v>1</v>
       </c>
       <c r="CU30" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="DD30" s="1">
         <v>1</v>
@@ -5903,19 +5933,19 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I31" s="1">
         <v>1</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="N31" s="1">
         <v>1</v>
@@ -5924,16 +5954,16 @@
         <v>1</v>
       </c>
       <c r="AG31" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="BD31" s="1">
         <v>1</v>
       </c>
       <c r="BO31" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="CN31" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="CR31" s="1">
         <v>99999</v>
@@ -5950,10 +5980,10 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I32" s="1">
         <v>1</v>
@@ -5962,10 +5992,10 @@
         <v>1</v>
       </c>
       <c r="AG32" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AT32" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="BD32" s="1">
         <v>1</v>
@@ -5982,19 +6012,19 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I33" s="1">
         <v>1</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AC33" s="1">
         <v>2</v>
@@ -6006,10 +6036,10 @@
         <v>99</v>
       </c>
       <c r="CG33" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="CN33" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="CO33" s="1">
         <v>-0.8</v>
@@ -6021,7 +6051,7 @@
         <v>7</v>
       </c>
       <c r="CX33" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="DH33" s="1">
         <v>1</v>
@@ -6029,19 +6059,19 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I34" s="1">
         <v>1</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AC34" s="1">
         <v>2</v>
@@ -6053,10 +6083,10 @@
         <v>99</v>
       </c>
       <c r="CG34" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="CN34" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="CO34" s="1">
         <v>-0.8</v>
@@ -6068,7 +6098,7 @@
         <v>7</v>
       </c>
       <c r="CX34" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="DH34" s="1">
         <v>1</v>
@@ -6076,28 +6106,28 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AC37" s="1">
         <v>2</v>
       </c>
       <c r="AT37" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="BD37" s="1">
         <v>1</v>
@@ -6105,10 +6135,10 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I38" s="1">
         <v>1</v>
@@ -6123,7 +6153,7 @@
         <v>1</v>
       </c>
       <c r="BP38" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="DH38" s="1">
         <v>1</v>
@@ -6131,16 +6161,16 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I39" s="1">
         <v>1</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AC39" s="1">
         <v>2</v>
@@ -6152,7 +6182,7 @@
         <v>99</v>
       </c>
       <c r="BP39" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="BS39" s="1">
         <v>0.5</v>
@@ -6161,10 +6191,10 @@
         <v>61</v>
       </c>
       <c r="CG39" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="CN39" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="CO39" s="1">
         <v>-0.8</v>
@@ -6173,7 +6203,7 @@
         <v>10</v>
       </c>
       <c r="CX39" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="DH39" s="1">
         <v>1</v>
@@ -6181,28 +6211,28 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AC40" s="1">
         <v>2</v>
       </c>
       <c r="AT40" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="BD40" s="1">
         <v>1</v>
@@ -6210,10 +6240,10 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I41" s="1">
         <v>1</v>
@@ -6228,7 +6258,7 @@
         <v>1</v>
       </c>
       <c r="BP41" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="DH41" s="1">
         <v>1</v>
@@ -6236,16 +6266,16 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I42" s="1">
         <v>1</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AC42" s="1">
         <v>2</v>
@@ -6257,7 +6287,7 @@
         <v>99</v>
       </c>
       <c r="BP42" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="BS42" s="1">
         <v>0.5</v>
@@ -6266,16 +6296,16 @@
         <v>61</v>
       </c>
       <c r="CG42" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="CN42" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="CR42" s="1">
         <v>5</v>
       </c>
       <c r="CX42" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="DH42" s="1">
         <v>1</v>
@@ -6283,28 +6313,28 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AC43" s="1">
         <v>2</v>
       </c>
       <c r="AT43" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="BD43" s="1">
         <v>1</v>
@@ -6312,10 +6342,10 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I44" s="1">
         <v>1</v>
@@ -6330,7 +6360,7 @@
         <v>1</v>
       </c>
       <c r="BP44" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="DH44" s="1">
         <v>1</v>
@@ -6338,16 +6368,16 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I45" s="1">
         <v>1</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AC45" s="1">
         <v>2</v>
@@ -6359,7 +6389,7 @@
         <v>99</v>
       </c>
       <c r="BP45" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="BS45" s="1">
         <v>0.5</v>
@@ -6368,10 +6398,10 @@
         <v>61</v>
       </c>
       <c r="CG45" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="CN45" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="CO45" s="1">
         <v>-0.8</v>
@@ -6383,7 +6413,7 @@
         <v>7</v>
       </c>
       <c r="CX45" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="DH45" s="1">
         <v>1</v>
@@ -6391,16 +6421,16 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I46" s="1">
         <v>1</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AC46" s="1">
         <v>1</v>
@@ -6409,10 +6439,10 @@
         <v>1</v>
       </c>
       <c r="AG46" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AX46" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AZ46" s="1">
         <v>1</v>
@@ -6522,37 +6552,37 @@
         <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="2">
@@ -6566,43 +6596,43 @@
         <v>83</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>57</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="3">
@@ -6616,79 +6646,79 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="L3" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="H4" s="1">
         <v>1</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>522</v>
-      </c>
       <c r="H5" s="1">
         <v>1</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="H6" s="1">
         <v>1</v>
@@ -6696,64 +6726,64 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="H7" s="1">
         <v>1</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H8" s="1">
         <v>1</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="H9" s="1">
         <v>1</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H10" s="1">
         <v>1</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
   </sheetData>
@@ -6782,7 +6812,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="2">
@@ -6793,10 +6823,10 @@
         <v>51</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="3">
@@ -6807,46 +6837,46 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
   </sheetData>
@@ -6872,7 +6902,7 @@
   <sheetData>
     <row r="1">
       <c r="I1" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="2">
@@ -6886,25 +6916,25 @@
         <v>53</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="3">
@@ -6921,33 +6951,33 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E4" s="1">
         <v>200</v>
@@ -6983,34 +7013,34 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="2">
@@ -7018,34 +7048,34 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>103</v>
@@ -7059,42 +7089,42 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="I4" s="1">
         <v>1</v>
@@ -7137,28 +7167,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>85</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>58</v>
@@ -7178,22 +7208,22 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -7225,28 +7255,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="2">
@@ -7254,28 +7284,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="3">
@@ -7283,10 +7313,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>2</v>
